--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="180">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,306 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Costa Rican Primera Division</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Honduras Liga Nacional</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Scottish Premiership</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:45:00</t>
+  </si>
+  <si>
+    <t>Inter San Carlos</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>Toluca</t>
+  </si>
+  <si>
+    <t>CD Olimpia</t>
+  </si>
+  <si>
+    <t>FC Bukovyna</t>
+  </si>
+  <si>
+    <t>FK Auda</t>
+  </si>
+  <si>
+    <t>Shakhtar</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>Zalaegerszeg</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
+    <t>Halmstads</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>Cracovia Krakow</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Chrobry Glogow</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Zeleznicar Pancevo</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
+    <t>Sarmiento de Junin</t>
+  </si>
+  <si>
+    <t>Cs Herediano</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Necaxa</t>
+  </si>
+  <si>
+    <t>Lobos UPNFM</t>
+  </si>
+  <si>
+    <t>LNZ-Lebedyn</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>FK Kudrivka</t>
+  </si>
+  <si>
+    <t>Botosani</t>
+  </si>
+  <si>
+    <t>FK Banga Gargzdu</t>
+  </si>
+  <si>
+    <t>HJK Helsinki</t>
+  </si>
+  <si>
+    <t>Paks</t>
+  </si>
+  <si>
+    <t>FC Dziugas</t>
+  </si>
+  <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Macva Sabac</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Pogon Szczecin</t>
+  </si>
+  <si>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Varnamo</t>
+  </si>
+  <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
+    <t>Farul Constanta</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Mladost Lucani</t>
+  </si>
+  <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>2026-08-01 00:30:37</t>
   </si>
 </sst>
 </file>
@@ -585,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1128,7024 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>5.3</v>
+      </c>
+      <c r="H2">
+        <v>1.86</v>
+      </c>
+      <c r="I2">
+        <v>2.1</v>
+      </c>
+      <c r="J2">
+        <v>2.98</v>
+      </c>
+      <c r="K2">
+        <v>4.8</v>
+      </c>
+      <c r="L2">
+        <v>1.35</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>3.15</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.72</v>
+      </c>
+      <c r="Q2">
+        <v>2.06</v>
+      </c>
+      <c r="R2">
+        <v>1.25</v>
+      </c>
+      <c r="S2">
+        <v>3.6</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.9</v>
+      </c>
+      <c r="W2">
+        <v>1.23</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3">
+        <v>2.12</v>
+      </c>
+      <c r="G3">
+        <v>2.26</v>
+      </c>
+      <c r="H3">
+        <v>4.2</v>
+      </c>
+      <c r="I3">
+        <v>4.8</v>
+      </c>
+      <c r="J3">
+        <v>3.05</v>
+      </c>
+      <c r="K3">
+        <v>3.15</v>
+      </c>
+      <c r="L3">
+        <v>1.52</v>
+      </c>
+      <c r="M3">
+        <v>1.13</v>
+      </c>
+      <c r="N3">
+        <v>2.4</v>
+      </c>
+      <c r="O3">
+        <v>1.64</v>
+      </c>
+      <c r="P3">
+        <v>1.46</v>
+      </c>
+      <c r="Q3">
+        <v>2.88</v>
+      </c>
+      <c r="R3">
+        <v>1.15</v>
+      </c>
+      <c r="S3">
+        <v>6.2</v>
+      </c>
+      <c r="T3">
+        <v>2.32</v>
+      </c>
+      <c r="U3">
+        <v>1.64</v>
+      </c>
+      <c r="V3">
+        <v>1.26</v>
+      </c>
+      <c r="W3">
+        <v>1.79</v>
+      </c>
+      <c r="X3">
+        <v>8</v>
+      </c>
+      <c r="Y3">
+        <v>12.5</v>
+      </c>
+      <c r="Z3">
+        <v>38</v>
+      </c>
+      <c r="AA3">
+        <v>160</v>
+      </c>
+      <c r="AB3">
+        <v>6.8</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>24</v>
+      </c>
+      <c r="AE3">
+        <v>110</v>
+      </c>
+      <c r="AF3">
+        <v>14.5</v>
+      </c>
+      <c r="AG3">
+        <v>13.5</v>
+      </c>
+      <c r="AH3">
+        <v>36</v>
+      </c>
+      <c r="AI3">
+        <v>150</v>
+      </c>
+      <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
+        <v>42</v>
+      </c>
+      <c r="AL3">
+        <v>90</v>
+      </c>
+      <c r="AM3">
+        <v>340</v>
+      </c>
+      <c r="AN3">
+        <v>44</v>
+      </c>
+      <c r="AO3">
+        <v>200</v>
+      </c>
+      <c r="AP3">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3">
+        <v>5.1</v>
+      </c>
+      <c r="AS3">
+        <v>5.7</v>
+      </c>
+      <c r="AT3">
+        <v>5.5</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>4.7</v>
+      </c>
+      <c r="AW3">
+        <v>5.6</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>5.1</v>
+      </c>
+      <c r="BA3">
+        <v>5.7</v>
+      </c>
+      <c r="BB3">
+        <v>5.1</v>
+      </c>
+      <c r="BC3">
+        <v>5.2</v>
+      </c>
+      <c r="BD3">
+        <v>5.6</v>
+      </c>
+      <c r="BE3">
+        <v>5.8</v>
+      </c>
+      <c r="BF3">
+        <v>5.2</v>
+      </c>
+      <c r="BG3">
+        <v>5.8</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4">
+        <v>2.16</v>
+      </c>
+      <c r="G4">
+        <v>2.36</v>
+      </c>
+      <c r="H4">
+        <v>3.5</v>
+      </c>
+      <c r="I4">
+        <v>4.2</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
+        <v>3.65</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.65</v>
+      </c>
+      <c r="O4">
+        <v>1.36</v>
+      </c>
+      <c r="P4">
+        <v>1.65</v>
+      </c>
+      <c r="Q4">
+        <v>1.92</v>
+      </c>
+      <c r="R4">
+        <v>1.24</v>
+      </c>
+      <c r="S4">
+        <v>3.2</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.31</v>
+      </c>
+      <c r="W4">
+        <v>1.73</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>9.6</v>
+      </c>
+      <c r="AQ4">
+        <v>9.4</v>
+      </c>
+      <c r="AR4">
+        <v>17.5</v>
+      </c>
+      <c r="AS4">
+        <v>40</v>
+      </c>
+      <c r="AT4">
+        <v>7</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>11</v>
+      </c>
+      <c r="AW4">
+        <v>28</v>
+      </c>
+      <c r="AX4">
+        <v>9.6</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>38</v>
+      </c>
+      <c r="BB4">
+        <v>20</v>
+      </c>
+      <c r="BC4">
+        <v>18.5</v>
+      </c>
+      <c r="BD4">
+        <v>30</v>
+      </c>
+      <c r="BE4">
+        <v>40</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5">
+        <v>1.56</v>
+      </c>
+      <c r="G5">
+        <v>1.63</v>
+      </c>
+      <c r="H5">
+        <v>5.8</v>
+      </c>
+      <c r="I5">
+        <v>6.4</v>
+      </c>
+      <c r="J5">
+        <v>4.7</v>
+      </c>
+      <c r="K5">
+        <v>5.1</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>6</v>
+      </c>
+      <c r="O5">
+        <v>1.17</v>
+      </c>
+      <c r="P5">
+        <v>2.72</v>
+      </c>
+      <c r="Q5">
+        <v>1.51</v>
+      </c>
+      <c r="R5">
+        <v>1.7</v>
+      </c>
+      <c r="S5">
+        <v>2.24</v>
+      </c>
+      <c r="T5">
+        <v>1.63</v>
+      </c>
+      <c r="U5">
+        <v>2.4</v>
+      </c>
+      <c r="V5">
+        <v>1.18</v>
+      </c>
+      <c r="W5">
+        <v>2.58</v>
+      </c>
+      <c r="X5">
+        <v>29</v>
+      </c>
+      <c r="Y5">
+        <v>38</v>
+      </c>
+      <c r="Z5">
+        <v>65</v>
+      </c>
+      <c r="AA5">
+        <v>170</v>
+      </c>
+      <c r="AB5">
+        <v>13</v>
+      </c>
+      <c r="AC5">
+        <v>12</v>
+      </c>
+      <c r="AD5">
+        <v>25</v>
+      </c>
+      <c r="AE5">
+        <v>85</v>
+      </c>
+      <c r="AF5">
+        <v>13</v>
+      </c>
+      <c r="AG5">
+        <v>13</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
+        <v>70</v>
+      </c>
+      <c r="AJ5">
+        <v>17</v>
+      </c>
+      <c r="AK5">
+        <v>15.5</v>
+      </c>
+      <c r="AL5">
+        <v>26</v>
+      </c>
+      <c r="AM5">
+        <v>70</v>
+      </c>
+      <c r="AN5">
+        <v>7</v>
+      </c>
+      <c r="AO5">
+        <v>65</v>
+      </c>
+      <c r="AP5">
+        <v>5.9</v>
+      </c>
+      <c r="AQ5">
+        <v>20</v>
+      </c>
+      <c r="AR5">
+        <v>6.6</v>
+      </c>
+      <c r="AS5">
+        <v>7.2</v>
+      </c>
+      <c r="AT5">
+        <v>11.5</v>
+      </c>
+      <c r="AU5">
+        <v>10</v>
+      </c>
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5">
+        <v>6.6</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>15.5</v>
+      </c>
+      <c r="BA5">
+        <v>6.8</v>
+      </c>
+      <c r="BB5">
+        <v>14</v>
+      </c>
+      <c r="BC5">
+        <v>5</v>
+      </c>
+      <c r="BD5">
+        <v>5.8</v>
+      </c>
+      <c r="BE5">
+        <v>6.8</v>
+      </c>
+      <c r="BF5">
+        <v>5.2</v>
+      </c>
+      <c r="BG5">
+        <v>6.6</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.04</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.04</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.04</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.04</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.04</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.04</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.04</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.04</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.04</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.04</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6">
+        <v>1.04</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.04</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.24</v>
+      </c>
+      <c r="O6">
+        <v>1.16</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.16</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>1.16</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.02</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>600</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>870</v>
+      </c>
+      <c r="J7">
+        <v>1.02</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8">
+        <v>1.04</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1.01</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F9">
+        <v>1.04</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.04</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.01</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10">
+        <v>1.85</v>
+      </c>
+      <c r="G10">
+        <v>2.04</v>
+      </c>
+      <c r="H10">
+        <v>3.95</v>
+      </c>
+      <c r="I10">
+        <v>5.5</v>
+      </c>
+      <c r="J10">
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <v>4.8</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>3.1</v>
+      </c>
+      <c r="O10">
+        <v>1.35</v>
+      </c>
+      <c r="P10">
+        <v>1.75</v>
+      </c>
+      <c r="Q10">
+        <v>2.04</v>
+      </c>
+      <c r="R10">
+        <v>1.27</v>
+      </c>
+      <c r="S10">
+        <v>3.5</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.28</v>
+      </c>
+      <c r="W10">
+        <v>1.96</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11">
+        <v>3.45</v>
+      </c>
+      <c r="G11">
+        <v>4.7</v>
+      </c>
+      <c r="H11">
+        <v>1.98</v>
+      </c>
+      <c r="I11">
+        <v>2.22</v>
+      </c>
+      <c r="J11">
+        <v>3.55</v>
+      </c>
+      <c r="K11">
+        <v>3.85</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.84</v>
+      </c>
+      <c r="Q11">
+        <v>1.84</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12">
+        <v>3.45</v>
+      </c>
+      <c r="G12">
+        <v>3.8</v>
+      </c>
+      <c r="H12">
+        <v>1.99</v>
+      </c>
+      <c r="I12">
+        <v>2.12</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>4.5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.34</v>
+      </c>
+      <c r="Q12">
+        <v>1.44</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13">
+        <v>3.15</v>
+      </c>
+      <c r="G13">
+        <v>3.9</v>
+      </c>
+      <c r="H13">
+        <v>2.1</v>
+      </c>
+      <c r="I13">
+        <v>2.38</v>
+      </c>
+      <c r="J13">
+        <v>3.05</v>
+      </c>
+      <c r="K13">
+        <v>4.9</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.38</v>
+      </c>
+      <c r="Q13">
+        <v>1.54</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14">
+        <v>3.2</v>
+      </c>
+      <c r="G14">
+        <v>4.6</v>
+      </c>
+      <c r="H14">
+        <v>2.08</v>
+      </c>
+      <c r="I14">
+        <v>2.84</v>
+      </c>
+      <c r="J14">
+        <v>2.32</v>
+      </c>
+      <c r="K14">
+        <v>4.9</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.64</v>
+      </c>
+      <c r="Q14">
+        <v>1.89</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15">
+        <v>1.04</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>1.04</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
+        <v>1.01</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16">
+        <v>7.2</v>
+      </c>
+      <c r="G16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H16">
+        <v>1.42</v>
+      </c>
+      <c r="I16">
+        <v>1.47</v>
+      </c>
+      <c r="J16">
+        <v>5.3</v>
+      </c>
+      <c r="K16">
+        <v>5.8</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.84</v>
+      </c>
+      <c r="Q16">
+        <v>1.47</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17">
+        <v>1.5</v>
+      </c>
+      <c r="G17">
+        <v>1.56</v>
+      </c>
+      <c r="H17">
+        <v>5.9</v>
+      </c>
+      <c r="I17">
+        <v>6.8</v>
+      </c>
+      <c r="J17">
+        <v>5.1</v>
+      </c>
+      <c r="K17">
+        <v>5.5</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.78</v>
+      </c>
+      <c r="Q17">
+        <v>1.48</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18">
+        <v>1.04</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
+        <v>1.04</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>1.01</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.07</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19">
+        <v>2.98</v>
+      </c>
+      <c r="G19">
+        <v>3.65</v>
+      </c>
+      <c r="H19">
+        <v>2.08</v>
+      </c>
+      <c r="I19">
+        <v>2.34</v>
+      </c>
+      <c r="J19">
+        <v>3.3</v>
+      </c>
+      <c r="K19">
+        <v>5.5</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.24</v>
+      </c>
+      <c r="Q19">
+        <v>1.01</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F20">
+        <v>2.28</v>
+      </c>
+      <c r="G20">
+        <v>2.44</v>
+      </c>
+      <c r="H20">
+        <v>3.5</v>
+      </c>
+      <c r="I20">
+        <v>3.9</v>
+      </c>
+      <c r="J20">
+        <v>3.1</v>
+      </c>
+      <c r="K20">
+        <v>3.4</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.56</v>
+      </c>
+      <c r="Q20">
+        <v>2.06</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21">
+        <v>2.22</v>
+      </c>
+      <c r="G21">
+        <v>2.3</v>
+      </c>
+      <c r="H21">
+        <v>3.25</v>
+      </c>
+      <c r="I21">
+        <v>3.5</v>
+      </c>
+      <c r="J21">
+        <v>3.7</v>
+      </c>
+      <c r="K21">
+        <v>3.85</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.26</v>
+      </c>
+      <c r="Q21">
+        <v>1.64</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" t="s">
+        <v>170</v>
+      </c>
+      <c r="F22">
+        <v>2.02</v>
+      </c>
+      <c r="G22">
+        <v>2.72</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>4.5</v>
+      </c>
+      <c r="J22">
+        <v>3.1</v>
+      </c>
+      <c r="K22">
+        <v>5.9</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.61</v>
+      </c>
+      <c r="Q22">
+        <v>1.98</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23">
+        <v>2.02</v>
+      </c>
+      <c r="G23">
+        <v>2.66</v>
+      </c>
+      <c r="H23">
+        <v>3.1</v>
+      </c>
+      <c r="I23">
+        <v>4.5</v>
+      </c>
+      <c r="J23">
+        <v>3.1</v>
+      </c>
+      <c r="K23">
+        <v>5.5</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.87</v>
+      </c>
+      <c r="Q23">
+        <v>1.66</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24">
+        <v>1.04</v>
+      </c>
+      <c r="G24">
+        <v>1000</v>
+      </c>
+      <c r="H24">
+        <v>1.04</v>
+      </c>
+      <c r="I24">
+        <v>1000</v>
+      </c>
+      <c r="J24">
+        <v>1.01</v>
+      </c>
+      <c r="K24">
+        <v>1000</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.24</v>
+      </c>
+      <c r="Q24">
+        <v>1.01</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25">
+        <v>3.05</v>
+      </c>
+      <c r="G25">
+        <v>3.5</v>
+      </c>
+      <c r="H25">
+        <v>2.34</v>
+      </c>
+      <c r="I25">
+        <v>2.62</v>
+      </c>
+      <c r="J25">
+        <v>3.25</v>
+      </c>
+      <c r="K25">
+        <v>3.7</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.82</v>
+      </c>
+      <c r="Q25">
+        <v>1.95</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26">
+        <v>1.69</v>
+      </c>
+      <c r="G26">
+        <v>2.12</v>
+      </c>
+      <c r="H26">
+        <v>1.92</v>
+      </c>
+      <c r="I26">
+        <v>7.4</v>
+      </c>
+      <c r="J26">
+        <v>3.7</v>
+      </c>
+      <c r="K26">
+        <v>950</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.86</v>
+      </c>
+      <c r="Q26">
+        <v>1.69</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" t="s">
+        <v>175</v>
+      </c>
+      <c r="F27">
+        <v>1.2</v>
+      </c>
+      <c r="G27">
+        <v>1.21</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
+      </c>
+      <c r="I27">
+        <v>17.5</v>
+      </c>
+      <c r="J27">
+        <v>8.6</v>
+      </c>
+      <c r="K27">
+        <v>9</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
+        <v>7.6</v>
+      </c>
+      <c r="O27">
+        <v>1.12</v>
+      </c>
+      <c r="P27">
+        <v>3.3</v>
+      </c>
+      <c r="Q27">
+        <v>1.37</v>
+      </c>
+      <c r="R27">
+        <v>1.93</v>
+      </c>
+      <c r="S27">
+        <v>1.92</v>
+      </c>
+      <c r="T27">
+        <v>1.89</v>
+      </c>
+      <c r="U27">
+        <v>1.97</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>55</v>
+      </c>
+      <c r="Y27">
+        <v>85</v>
+      </c>
+      <c r="Z27">
+        <v>190</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>15.5</v>
+      </c>
+      <c r="AC27">
+        <v>26</v>
+      </c>
+      <c r="AD27">
+        <v>65</v>
+      </c>
+      <c r="AE27">
+        <v>260</v>
+      </c>
+      <c r="AF27">
+        <v>12</v>
+      </c>
+      <c r="AG27">
+        <v>12</v>
+      </c>
+      <c r="AH27">
+        <v>44</v>
+      </c>
+      <c r="AI27">
+        <v>180</v>
+      </c>
+      <c r="AJ27">
+        <v>13</v>
+      </c>
+      <c r="AK27">
+        <v>15.5</v>
+      </c>
+      <c r="AL27">
+        <v>30</v>
+      </c>
+      <c r="AM27">
+        <v>180</v>
+      </c>
+      <c r="AN27">
+        <v>3.2</v>
+      </c>
+      <c r="AO27">
+        <v>250</v>
+      </c>
+      <c r="AP27">
+        <v>6.6</v>
+      </c>
+      <c r="AQ27">
+        <v>6</v>
+      </c>
+      <c r="AR27">
+        <v>6.4</v>
+      </c>
+      <c r="AS27">
+        <v>6.6</v>
+      </c>
+      <c r="AT27">
+        <v>11.5</v>
+      </c>
+      <c r="AU27">
+        <v>19</v>
+      </c>
+      <c r="AV27">
+        <v>6.6</v>
+      </c>
+      <c r="AW27">
+        <v>6.4</v>
+      </c>
+      <c r="AX27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>6.4</v>
+      </c>
+      <c r="BA27">
+        <v>6.4</v>
+      </c>
+      <c r="BB27">
+        <v>9.4</v>
+      </c>
+      <c r="BC27">
+        <v>11.5</v>
+      </c>
+      <c r="BD27">
+        <v>6</v>
+      </c>
+      <c r="BE27">
+        <v>6.4</v>
+      </c>
+      <c r="BF27">
+        <v>2.92</v>
+      </c>
+      <c r="BG27">
+        <v>6.4</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28">
+        <v>1.75</v>
+      </c>
+      <c r="G28">
+        <v>1.99</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>1000</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>1000</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.73</v>
+      </c>
+      <c r="Q28">
+        <v>2.02</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1.24</v>
+      </c>
+      <c r="Q29">
+        <v>1.01</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30">
+        <v>3.45</v>
+      </c>
+      <c r="G30">
+        <v>3.65</v>
+      </c>
+      <c r="H30">
+        <v>2.36</v>
+      </c>
+      <c r="I30">
+        <v>2.52</v>
+      </c>
+      <c r="J30">
+        <v>3.15</v>
+      </c>
+      <c r="K30">
+        <v>3.3</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.56</v>
+      </c>
+      <c r="Q30">
+        <v>2.5</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -553,7 +553,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 00:30:37</t>
+    <t>2026-08-01 02:51:55</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1153,7 @@
         <v>5.3</v>
       </c>
       <c r="H2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I2">
         <v>2.1</v>
@@ -1162,7 +1162,7 @@
         <v>2.98</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1398,7 +1398,7 @@
         <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3">
         <v>3.05</v>
@@ -1437,7 +1437,7 @@
         <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
         <v>1.79</v>
@@ -1470,13 +1470,13 @@
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH3">
         <v>36</v>
       </c>
       <c r="AI3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ3">
         <v>38</v>
@@ -1488,13 +1488,13 @@
         <v>90</v>
       </c>
       <c r="AM3">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP3">
         <v>6.8</v>
@@ -1503,10 +1503,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT3">
         <v>5.5</v>
@@ -1515,10 +1515,10 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1527,28 +1527,28 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA3">
+        <v>5.9</v>
+      </c>
+      <c r="BB3">
+        <v>5.3</v>
+      </c>
+      <c r="BC3">
+        <v>5.3</v>
+      </c>
+      <c r="BD3">
         <v>5.7</v>
       </c>
-      <c r="BB3">
-        <v>5.1</v>
-      </c>
-      <c r="BC3">
-        <v>5.2</v>
-      </c>
-      <c r="BD3">
-        <v>5.6</v>
-      </c>
       <c r="BE3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1873,7 +1873,7 @@
         <v>153</v>
       </c>
       <c r="F5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G5">
         <v>1.63</v>
@@ -1915,7 +1915,7 @@
         <v>2.24</v>
       </c>
       <c r="T5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
         <v>2.4</v>
@@ -1930,13 +1930,13 @@
         <v>29</v>
       </c>
       <c r="Y5">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -1975,25 +1975,25 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO5">
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD5">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.16</v>
@@ -3116,7 +3116,7 @@
         <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
         <v>1.27</v>
@@ -3570,7 +3570,7 @@
         <v>3.45</v>
       </c>
       <c r="G12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H12">
         <v>1.99</v>
@@ -4535,10 +4535,10 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="G16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H16">
         <v>1.42</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4783,13 +4783,13 @@
         <v>1.56</v>
       </c>
       <c r="H17">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I17">
         <v>6.8</v>
       </c>
       <c r="J17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>5.5</v>
@@ -4810,7 +4810,7 @@
         <v>2.78</v>
       </c>
       <c r="Q17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>2.98</v>
       </c>
       <c r="G19">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
         <v>2.08</v>
@@ -5273,7 +5273,7 @@
         <v>2.34</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
         <v>5.5</v>
@@ -5503,7 +5503,7 @@
         <v>168</v>
       </c>
       <c r="F20">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G20">
         <v>2.44</v>
@@ -5515,7 +5515,7 @@
         <v>3.9</v>
       </c>
       <c r="J20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K20">
         <v>3.4</v>
@@ -5536,7 +5536,7 @@
         <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>3.5</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
         <v>3.85</v>
@@ -5987,10 +5987,10 @@
         <v>170</v>
       </c>
       <c r="F22">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G22">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H22">
         <v>3</v>
@@ -6002,7 +6002,7 @@
         <v>3.1</v>
       </c>
       <c r="K22">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q22">
         <v>1.98</v>
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q23">
         <v>1.66</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q25">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6955,16 +6955,16 @@
         <v>174</v>
       </c>
       <c r="F26">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I26">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>3.7</v>
@@ -6988,7 +6988,7 @@
         <v>1.86</v>
       </c>
       <c r="Q26">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>1.21</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I27">
         <v>17.5</v>
@@ -7212,7 +7212,7 @@
         <v>8.6</v>
       </c>
       <c r="K27">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7224,25 +7224,25 @@
         <v>7.6</v>
       </c>
       <c r="O27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q27">
         <v>1.37</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
+        <v>1.96</v>
+      </c>
+      <c r="T27">
         <v>1.92</v>
       </c>
-      <c r="T27">
-        <v>1.89</v>
-      </c>
       <c r="U27">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7263,10 +7263,10 @@
         <v>1000</v>
       </c>
       <c r="AB27">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD27">
         <v>65</v>
@@ -7293,13 +7293,13 @@
         <v>15.5</v>
       </c>
       <c r="AL27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM27">
         <v>180</v>
       </c>
       <c r="AN27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AO27">
         <v>250</v>
@@ -7308,31 +7308,31 @@
         <v>6.6</v>
       </c>
       <c r="AQ27">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR27">
         <v>6.4</v>
       </c>
       <c r="AS27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU27">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AV27">
         <v>6.6</v>
       </c>
       <c r="AW27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27">
         <v>6.4</v>
@@ -7341,22 +7341,22 @@
         <v>6.4</v>
       </c>
       <c r="BB27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC27">
         <v>11.5</v>
       </c>
       <c r="BD27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE27">
         <v>6.4</v>
       </c>
       <c r="BF27">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BG27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7926,16 +7926,16 @@
         <v>3.45</v>
       </c>
       <c r="G30">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H30">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="I30">
         <v>2.52</v>
       </c>
       <c r="J30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
         <v>3.3</v>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q30">
         <v>2.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -553,7 +553,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 02:51:55</t>
+    <t>2026-08-01 03:57:15</t>
   </si>
 </sst>
 </file>
@@ -1255,52 +1255,52 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
@@ -1419,13 +1419,13 @@
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.2</v>
@@ -1739,52 +1739,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -2118,19 +2118,19 @@
         <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6">
         <v>1.04</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6">
         <v>1.04</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
         <v>1.16</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2614,7 +2614,7 @@
         <v>1.01</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>1.01</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>2.04</v>
       </c>
       <c r="H10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>5.5</v>
@@ -3110,7 +3110,7 @@
         <v>3.1</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
         <v>1.75</v>
@@ -3573,7 +3573,7 @@
         <v>3.75</v>
       </c>
       <c r="H12">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>2.12</v>
@@ -3815,16 +3815,16 @@
         <v>3.9</v>
       </c>
       <c r="H13">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I13">
         <v>2.38</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>2.84</v>
       </c>
       <c r="J14">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="K14">
         <v>4.9</v>
@@ -4308,7 +4308,7 @@
         <v>1.01</v>
       </c>
       <c r="K15">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>7.6</v>
       </c>
       <c r="G16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H16">
         <v>1.42</v>
@@ -5031,10 +5031,10 @@
         <v>1000</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>2.98</v>
       </c>
       <c r="G19">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="H19">
         <v>2.08</v>
@@ -5273,7 +5273,7 @@
         <v>2.34</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>5.5</v>
@@ -6002,7 +6002,7 @@
         <v>3.1</v>
       </c>
       <c r="K22">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         <v>1.01</v>
       </c>
       <c r="K24">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6713,19 +6713,19 @@
         <v>173</v>
       </c>
       <c r="F25">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I25">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
         <v>3.7</v>
@@ -6746,7 +6746,7 @@
         <v>1.81</v>
       </c>
       <c r="Q25">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7305,10 +7305,10 @@
         <v>250</v>
       </c>
       <c r="AP27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR27">
         <v>6.4</v>
@@ -7323,13 +7323,13 @@
         <v>18.5</v>
       </c>
       <c r="AV27">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="AW27">
         <v>6.6</v>
       </c>
       <c r="AX27">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY27">
         <v>9.800000000000001</v>
@@ -7445,16 +7445,16 @@
         <v>1.99</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="K28">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="L28">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -553,7 +553,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 03:57:15</t>
+    <t>2026-08-01 06:17:45</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1419,7 @@
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1437,7 +1437,7 @@
         <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
         <v>1.79</v>
@@ -1885,7 +1885,7 @@
         <v>6.4</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
         <v>5.1</v>
@@ -1975,7 +1975,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1987,10 +1987,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
         <v>1.16</v>
@@ -2844,16 +2844,16 @@
         <v>1.04</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>1.28</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
         <v>610</v>
@@ -3083,13 +3083,13 @@
         <v>158</v>
       </c>
       <c r="F10">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
         <v>2.04</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
         <v>5.5</v>
@@ -3098,7 +3098,7 @@
         <v>3.5</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3110,7 +3110,7 @@
         <v>3.1</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
         <v>1.75</v>
@@ -3567,19 +3567,19 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G12">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I12">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K12">
         <v>4.5</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q16">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
         <v>1.49</v>
@@ -5264,7 +5264,7 @@
         <v>2.98</v>
       </c>
       <c r="G19">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
         <v>2.08</v>
@@ -5503,7 +5503,7 @@
         <v>168</v>
       </c>
       <c r="F20">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G20">
         <v>2.44</v>
@@ -5512,7 +5512,7 @@
         <v>3.5</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J20">
         <v>3.05</v>
@@ -6229,22 +6229,22 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G23">
         <v>2.66</v>
       </c>
       <c r="H23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I23">
         <v>4.5</v>
       </c>
       <c r="J23">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="K23">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6474,7 +6474,7 @@
         <v>1.04</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="H24">
         <v>1.04</v>
@@ -6719,16 +6719,16 @@
         <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="I25">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>1.21</v>
       </c>
       <c r="H27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="I27">
         <v>17.5</v>
@@ -7212,7 +7212,7 @@
         <v>8.6</v>
       </c>
       <c r="K27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>1.02</v>
       </c>
       <c r="N27">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O27">
         <v>1.13</v>
@@ -7236,10 +7236,10 @@
         <v>1.92</v>
       </c>
       <c r="S27">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="T27">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U27">
         <v>1.96</v>
@@ -7299,22 +7299,22 @@
         <v>180</v>
       </c>
       <c r="AN27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO27">
         <v>250</v>
       </c>
       <c r="AP27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT27">
         <v>11</v>
@@ -7326,7 +7326,7 @@
         <v>40</v>
       </c>
       <c r="AW27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX27">
         <v>7.2</v>
@@ -7335,10 +7335,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB27">
         <v>9.199999999999999</v>
@@ -7347,16 +7347,16 @@
         <v>11.5</v>
       </c>
       <c r="BD27">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BE27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF27">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BG27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -553,7 +553,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 06:17:45</t>
+    <t>2026-08-01 08:38:50</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +1147,7 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G2">
         <v>5.3</v>
@@ -1162,7 +1162,7 @@
         <v>2.98</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1467,7 +1467,7 @@
         <v>110</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1506,7 +1506,7 @@
         <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>5.5</v>
@@ -1518,7 +1518,7 @@
         <v>4.9</v>
       </c>
       <c r="AW3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1527,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA3">
         <v>5.9</v>
@@ -1536,19 +1536,19 @@
         <v>5.3</v>
       </c>
       <c r="BC3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE3">
         <v>6</v>
       </c>
       <c r="BF3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1631,7 +1631,7 @@
         <v>152</v>
       </c>
       <c r="F4">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
         <v>2.36</v>
@@ -1646,7 +1646,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1876,7 +1876,7 @@
         <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>5.8</v>
@@ -1885,7 +1885,7 @@
         <v>6.4</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
         <v>5.1</v>
@@ -1924,7 +1924,7 @@
         <v>1.18</v>
       </c>
       <c r="W5">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -1975,7 +1975,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1987,10 +1987,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD5">
+        <v>5.9</v>
+      </c>
+      <c r="BE5">
         <v>6.8</v>
-      </c>
-      <c r="BE5">
-        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q6">
         <v>1.16</v>
@@ -2841,7 +2841,7 @@
         <v>157</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
         <v>1.28</v>
@@ -3098,7 +3098,7 @@
         <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3573,16 +3573,16 @@
         <v>4.3</v>
       </c>
       <c r="H12">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="I12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J12">
         <v>3.9</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>161</v>
       </c>
       <c r="F13">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="G13">
         <v>3.9</v>
@@ -3824,7 +3824,7 @@
         <v>3.65</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>7.6</v>
       </c>
       <c r="G16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H16">
         <v>1.42</v>
@@ -4547,7 +4547,7 @@
         <v>1.47</v>
       </c>
       <c r="J16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K16">
         <v>5.8</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>1.53</v>
@@ -5019,22 +5019,22 @@
         <v>166</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>1.19</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="J18">
         <v>8</v>
       </c>
       <c r="K18">
-        <v>510</v>
+        <v>13</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1.07</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5512,10 +5512,10 @@
         <v>3.5</v>
       </c>
       <c r="I20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J20">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K20">
         <v>3.4</v>
@@ -5745,13 +5745,13 @@
         <v>169</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G21">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I21">
         <v>3.5</v>
@@ -5778,7 +5778,7 @@
         <v>2.26</v>
       </c>
       <c r="Q21">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>2.62</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6474,7 +6474,7 @@
         <v>1.04</v>
       </c>
       <c r="G24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H24">
         <v>1.04</v>
@@ -6719,7 +6719,7 @@
         <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I25">
         <v>2.64</v>
@@ -7203,13 +7203,13 @@
         <v>1.21</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I27">
         <v>17.5</v>
       </c>
       <c r="J27">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K27">
         <v>9.199999999999999</v>
@@ -7221,16 +7221,16 @@
         <v>1.02</v>
       </c>
       <c r="N27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O27">
         <v>1.13</v>
       </c>
       <c r="P27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R27">
         <v>1.92</v>
@@ -7239,10 +7239,10 @@
         <v>1.94</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7272,7 +7272,7 @@
         <v>65</v>
       </c>
       <c r="AE27">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AF27">
         <v>12</v>
@@ -7287,7 +7287,7 @@
         <v>180</v>
       </c>
       <c r="AJ27">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK27">
         <v>15.5</v>
@@ -7302,19 +7302,19 @@
         <v>3.25</v>
       </c>
       <c r="AO27">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27">
         <v>7</v>
       </c>
       <c r="AR27">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS27">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT27">
         <v>11</v>
@@ -7323,22 +7323,22 @@
         <v>18.5</v>
       </c>
       <c r="AV27">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="AW27">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX27">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY27">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BA27">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB27">
         <v>9.199999999999999</v>
@@ -7350,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="BE27">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF27">
         <v>2.96</v>
       </c>
       <c r="BG27">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH27">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -553,7 +553,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 08:38:50</t>
+    <t>2026-08-01 10:59:44</t>
   </si>
 </sst>
 </file>
@@ -1147,10 +1147,10 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H2">
         <v>1.87</v>
@@ -1159,10 +1159,10 @@
         <v>2.1</v>
       </c>
       <c r="J2">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1183,7 +1183,7 @@
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>3.6</v>
@@ -1198,7 +1198,7 @@
         <v>1.9</v>
       </c>
       <c r="W2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1389,28 +1389,28 @@
         <v>151</v>
       </c>
       <c r="F3">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
         <v>2.4</v>
@@ -1422,52 +1422,52 @@
         <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
         <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
+        <v>11</v>
+      </c>
+      <c r="Z3">
+        <v>30</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>6.6</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
+        <v>23</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
         <v>12.5</v>
-      </c>
-      <c r="Z3">
-        <v>38</v>
-      </c>
-      <c r="AA3">
-        <v>160</v>
-      </c>
-      <c r="AB3">
-        <v>6.8</v>
-      </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
-      <c r="AD3">
-        <v>24</v>
-      </c>
-      <c r="AE3">
-        <v>110</v>
-      </c>
-      <c r="AF3">
-        <v>14</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1476,79 +1476,79 @@
         <v>36</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>330</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AO3">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR3">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BD3">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BE3">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1631,13 +1631,13 @@
         <v>152</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I4">
         <v>4.2</v>
@@ -1646,7 +1646,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1682,7 +1682,7 @@
         <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1876,10 +1876,10 @@
         <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -1894,37 +1894,37 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O5">
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T5">
         <v>1.64</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -1975,7 +1975,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1987,10 +1987,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2014,85 +2014,85 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
+        <v>7</v>
+      </c>
+      <c r="BH5">
+        <v>4.8</v>
+      </c>
+      <c r="BI5">
+        <v>3.7</v>
+      </c>
+      <c r="BJ5">
+        <v>9.4</v>
+      </c>
+      <c r="BK5">
+        <v>7</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>13</v>
+      </c>
+      <c r="BN5">
+        <v>4.6</v>
+      </c>
+      <c r="BO5">
+        <v>3.55</v>
+      </c>
+      <c r="BP5">
+        <v>9.4</v>
+      </c>
+      <c r="BQ5">
+        <v>5.9</v>
+      </c>
+      <c r="BR5">
+        <v>19</v>
+      </c>
+      <c r="BS5">
+        <v>8.6</v>
+      </c>
+      <c r="BT5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU5">
+        <v>6</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>11.5</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>11</v>
+      </c>
+      <c r="BZ5">
+        <v>12</v>
+      </c>
+      <c r="CA5">
         <v>6.8</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.04</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.04</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.04</v>
-      </c>
-      <c r="BZ5">
-        <v>1000</v>
-      </c>
-      <c r="CA5">
-        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>179</v>
@@ -2369,214 +2369,214 @@
         <v>870</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
         <v>950</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>179</v>
@@ -3089,7 +3089,7 @@
         <v>2.04</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
         <v>5.5</v>
@@ -3098,7 +3098,7 @@
         <v>3.5</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3325,22 +3325,22 @@
         <v>159</v>
       </c>
       <c r="F11">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H11">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="I11">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3573,16 +3573,16 @@
         <v>4.3</v>
       </c>
       <c r="H12">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="I12">
         <v>2.1</v>
       </c>
       <c r="J12">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>161</v>
       </c>
       <c r="F13">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G13">
         <v>3.9</v>
@@ -3824,7 +3824,7 @@
         <v>3.65</v>
       </c>
       <c r="K13">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4051,22 +4051,22 @@
         <v>162</v>
       </c>
       <c r="F14">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G14">
         <v>4.6</v>
       </c>
       <c r="H14">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I14">
         <v>2.84</v>
       </c>
       <c r="J14">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K14">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4544,7 +4544,7 @@
         <v>1.42</v>
       </c>
       <c r="I16">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="J16">
         <v>5.2</v>
@@ -4777,7 +4777,7 @@
         <v>165</v>
       </c>
       <c r="F17">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G17">
         <v>1.56</v>
@@ -4789,7 +4789,7 @@
         <v>6.8</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K17">
         <v>5.5</v>
@@ -4810,7 +4810,7 @@
         <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5019,19 +5019,19 @@
         <v>166</v>
       </c>
       <c r="F18">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G18">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="H18">
-        <v>1.08</v>
+        <v>19</v>
       </c>
       <c r="I18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="K18">
         <v>13</v>
@@ -5503,7 +5503,7 @@
         <v>168</v>
       </c>
       <c r="F20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G20">
         <v>2.44</v>
@@ -5512,7 +5512,7 @@
         <v>3.5</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J20">
         <v>3.1</v>
@@ -5748,10 +5748,10 @@
         <v>2.24</v>
       </c>
       <c r="G21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
         <v>3.5</v>
@@ -5987,22 +5987,22 @@
         <v>170</v>
       </c>
       <c r="F22">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="G22">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I22">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J22">
         <v>3.1</v>
       </c>
       <c r="K22">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6229,22 +6229,22 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G23">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="H23">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I23">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J23">
-        <v>2.62</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6728,7 +6728,7 @@
         <v>3.25</v>
       </c>
       <c r="K25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6955,19 +6955,19 @@
         <v>174</v>
       </c>
       <c r="F26">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G26">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -7203,10 +7203,10 @@
         <v>1.21</v>
       </c>
       <c r="H27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I27">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <v>8.800000000000001</v>
@@ -7230,7 +7230,7 @@
         <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R27">
         <v>1.92</v>
@@ -7239,10 +7239,10 @@
         <v>1.94</v>
       </c>
       <c r="T27">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>1000</v>
       </c>
       <c r="AB27">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC27">
         <v>27</v>
@@ -7275,10 +7275,10 @@
         <v>270</v>
       </c>
       <c r="AF27">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH27">
         <v>44</v>
@@ -7287,10 +7287,10 @@
         <v>180</v>
       </c>
       <c r="AJ27">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK27">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL27">
         <v>32</v>
@@ -7299,22 +7299,22 @@
         <v>180</v>
       </c>
       <c r="AN27">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AO27">
         <v>260</v>
       </c>
       <c r="AP27">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR27">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS27">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT27">
         <v>11</v>
@@ -7323,10 +7323,10 @@
         <v>18.5</v>
       </c>
       <c r="AV27">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW27">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27">
         <v>8.6</v>
@@ -7338,7 +7338,7 @@
         <v>28</v>
       </c>
       <c r="BA27">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB27">
         <v>9.199999999999999</v>
@@ -7350,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF27">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BG27">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7923,19 +7923,19 @@
         <v>178</v>
       </c>
       <c r="F30">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G30">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="H30">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="I30">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K30">
         <v>3.3</v>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q30">
         <v>2.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="195">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>Latvian Virsliga</t>
   </si>
   <si>
@@ -283,33 +286,36 @@
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
-    <t>Swedish Allsvenskan</t>
-  </si>
-  <si>
-    <t>Serbian Super League</t>
-  </si>
-  <si>
-    <t>Norwegian 1st Division</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -343,6 +349,9 @@
     <t>12:30:00</t>
   </si>
   <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -397,51 +406,69 @@
     <t>FC Bukovyna</t>
   </si>
   <si>
+    <t>IF Vestri</t>
+  </si>
+  <si>
+    <t>Shakhtar</t>
+  </si>
+  <si>
     <t>FK Auda</t>
   </si>
   <si>
-    <t>Shakhtar</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Fk Siauliai</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
     <t>SJK</t>
   </si>
   <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
     <t>Zalaegerszeg</t>
   </si>
   <si>
-    <t>Panevezys</t>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>Cracovia Krakow</t>
+  </si>
+  <si>
+    <t>Chrobry Glogow</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Halmstads</t>
   </si>
   <si>
     <t>Vasalunds IF</t>
   </si>
   <si>
-    <t>Halmstads</t>
-  </si>
-  <si>
-    <t>Djurgardens</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Ranheim IL</t>
-  </si>
-  <si>
-    <t>Cracovia Krakow</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
-    <t>Chrobry Glogow</t>
-  </si>
-  <si>
     <t>Orebro</t>
   </si>
   <si>
@@ -457,12 +484,12 @@
     <t>Celtic</t>
   </si>
   <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
     <t>Zeleznicar Pancevo</t>
   </si>
   <si>
-    <t>Sportivo Trinidense</t>
-  </si>
-  <si>
     <t>Sarmiento de Junin</t>
   </si>
   <si>
@@ -484,51 +511,69 @@
     <t>LNZ-Lebedyn</t>
   </si>
   <si>
+    <t>Grotta</t>
+  </si>
+  <si>
+    <t>FK Kudrivka</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>FK Kudrivka</t>
-  </si>
-  <si>
     <t>Botosani</t>
   </si>
   <si>
     <t>FK Banga Gargzdu</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>HJK Helsinki</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>FC Dziugas</t>
+  </si>
+  <si>
     <t>Paks</t>
   </si>
   <si>
-    <t>FC Dziugas</t>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Pogon Szczecin</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Macva Sabac</t>
+  </si>
+  <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Sirius</t>
   </si>
   <si>
     <t>Sollentuna FF</t>
   </si>
   <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Vasteras SK</t>
-  </si>
-  <si>
-    <t>Macva Sabac</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Pogon Szczecin</t>
-  </si>
-  <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
     <t>Varnamo</t>
   </si>
   <si>
@@ -544,16 +589,16 @@
     <t>Dundee</t>
   </si>
   <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
     <t>Mladost Lucani</t>
   </si>
   <si>
-    <t>Sportivo San Lorenzo</t>
-  </si>
-  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 10:59:44</t>
+    <t>2026-08-01 13:18:12</t>
   </si>
 </sst>
 </file>
@@ -885,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1135,22 +1180,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="H2">
         <v>1.87</v>
@@ -1159,10 +1204,10 @@
         <v>2.1</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1198,7 +1243,7 @@
         <v>1.9</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1369,7 +1414,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1377,28 +1422,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F3">
         <v>2.18</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H3">
         <v>4.1</v>
       </c>
       <c r="I3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
         <v>3.05</v>
@@ -1416,7 +1461,7 @@
         <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.46</v>
@@ -1437,16 +1482,16 @@
         <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X3">
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>30</v>
@@ -1479,7 +1524,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AK3">
         <v>40</v>
@@ -1509,7 +1554,7 @@
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
@@ -1611,7 +1656,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1619,19 +1664,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
         <v>2.32</v>
@@ -1652,34 +1697,34 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>1.65</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
         <v>1.75</v>
@@ -1688,46 +1733,46 @@
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1739,58 +1784,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1853,7 +1898,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1861,25 +1906,25 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F5">
         <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -1888,13 +1933,13 @@
         <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
         <v>6.2</v>
@@ -1903,28 +1948,28 @@
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
         <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
         <v>2.42</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -1987,13 +2032,13 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2002,7 +2047,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2014,25 +2059,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>4.8</v>
@@ -2044,7 +2089,7 @@
         <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2095,7 +2140,7 @@
         <v>6.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2103,16 +2148,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -2139,22 +2184,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2337,7 +2382,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2345,16 +2390,16 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -2369,7 +2414,7 @@
         <v>870</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2390,13 +2435,13 @@
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2405,10 +2450,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2579,7 +2624,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2587,241 +2632,241 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
-        <v>370</v>
+        <v>6.6</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2829,16 +2874,16 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F9">
         <v>1.1</v>
@@ -2859,16 +2904,16 @@
         <v>610</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
         <v>1.24</v>
@@ -2877,193 +2922,193 @@
         <v>1.01</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3071,34 +3116,34 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F10">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>370</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3107,22 +3152,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>1.12</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
+        <v>1.12</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3131,10 +3176,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3305,7 +3350,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3313,241 +3358,241 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="G11">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J11">
         <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3555,232 +3600,232 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F12">
+        <v>3.3</v>
+      </c>
+      <c r="G12">
+        <v>4.1</v>
+      </c>
+      <c r="H12">
+        <v>2.06</v>
+      </c>
+      <c r="I12">
+        <v>2.3</v>
+      </c>
+      <c r="J12">
         <v>3.5</v>
       </c>
-      <c r="G12">
-        <v>4.3</v>
-      </c>
-      <c r="H12">
-        <v>1.96</v>
-      </c>
-      <c r="I12">
-        <v>2.1</v>
-      </c>
-      <c r="J12">
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>3.35</v>
+      </c>
+      <c r="O12">
+        <v>1.29</v>
+      </c>
+      <c r="P12">
+        <v>1.84</v>
+      </c>
+      <c r="Q12">
+        <v>1.84</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>1.92</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.76</v>
+      </c>
+      <c r="W12">
+        <v>1.32</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
         <v>4</v>
       </c>
-      <c r="K12">
-        <v>4.9</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>2.34</v>
-      </c>
-      <c r="Q12">
-        <v>1.44</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>0</v>
-      </c>
-      <c r="BD12">
-        <v>0</v>
-      </c>
-      <c r="BE12">
-        <v>0</v>
-      </c>
-      <c r="BF12">
-        <v>0</v>
-      </c>
-      <c r="BG12">
-        <v>0</v>
-      </c>
-      <c r="BH12">
-        <v>0</v>
-      </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3789,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3797,34 +3842,34 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3839,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4031,42 +4076,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F14">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="G14">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H14">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="I14">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="J14">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4081,10 +4126,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4273,42 +4318,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4515,42 +4560,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F16">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4565,10 +4610,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4757,42 +4802,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F17">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4807,10 +4852,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q17">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4999,42 +5044,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F18">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5049,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q18">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5241,42 +5286,42 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F19">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G19">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="H19">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I19">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="K19">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5291,10 +5336,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5483,42 +5528,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F20">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="G20">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="H20">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="I20">
-        <v>3.95</v>
+        <v>2.38</v>
       </c>
       <c r="J20">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5533,10 +5578,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q20">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5725,24 +5770,24 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F21">
         <v>2.24</v>
@@ -5751,7 +5796,7 @@
         <v>2.26</v>
       </c>
       <c r="H21">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I21">
         <v>3.5</v>
@@ -5760,7 +5805,7 @@
         <v>3.75</v>
       </c>
       <c r="K21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5778,7 +5823,7 @@
         <v>2.26</v>
       </c>
       <c r="Q21">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5967,42 +6012,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F22">
-        <v>2.2</v>
+        <v>2.98</v>
       </c>
       <c r="G22">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="H22">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="I22">
-        <v>3.95</v>
+        <v>2.34</v>
       </c>
       <c r="J22">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6017,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6209,42 +6254,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F23">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="G23">
         <v>2.44</v>
       </c>
       <c r="H23">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I23">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J23">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6259,10 +6304,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q23">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6451,42 +6496,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G24">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J24">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K24">
-        <v>350</v>
+        <v>3.65</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6501,10 +6546,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6693,42 +6738,42 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
         <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="G25">
-        <v>3.45</v>
+        <v>1.16</v>
       </c>
       <c r="H25">
-        <v>2.34</v>
+        <v>19</v>
       </c>
       <c r="I25">
-        <v>2.64</v>
+        <v>29</v>
       </c>
       <c r="J25">
-        <v>3.25</v>
+        <v>9.6</v>
       </c>
       <c r="K25">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6743,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6935,42 +6980,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="F26">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="G26">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="H26">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="I26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J26">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="K26">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6985,10 +7030,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7177,72 +7222,72 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F27">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="G27">
-        <v>1.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>1.42</v>
       </c>
       <c r="I27">
-        <v>18</v>
+        <v>1.43</v>
       </c>
       <c r="J27">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="K27">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="Q27">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="R27">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7251,166 +7296,166 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BG27">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7419,42 +7464,42 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F28">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G28">
-        <v>1.99</v>
+        <v>1000</v>
       </c>
       <c r="H28">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="I28">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J28">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K28">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7469,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q28">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7661,42 +7706,42 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7711,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7903,249 +7948,1701 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30">
+        <v>1.04</v>
+      </c>
+      <c r="G30">
+        <v>1.57</v>
+      </c>
+      <c r="H30">
+        <v>1.04</v>
+      </c>
+      <c r="I30">
+        <v>1000</v>
+      </c>
+      <c r="J30">
+        <v>1.01</v>
+      </c>
+      <c r="K30">
+        <v>350</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.24</v>
+      </c>
+      <c r="Q30">
+        <v>1.01</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>3.45</v>
+      </c>
+      <c r="H31">
+        <v>2.34</v>
+      </c>
+      <c r="I31">
+        <v>2.64</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>3.75</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>1.86</v>
+      </c>
+      <c r="Q31">
+        <v>1.92</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31">
+        <v>0</v>
+      </c>
+      <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
+        <v>0</v>
+      </c>
+      <c r="BU31">
+        <v>0</v>
+      </c>
+      <c r="BV31">
+        <v>0</v>
+      </c>
+      <c r="BW31">
+        <v>0</v>
+      </c>
+      <c r="BX31">
+        <v>0</v>
+      </c>
+      <c r="BY31">
+        <v>0</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32">
+        <v>1.75</v>
+      </c>
+      <c r="G32">
+        <v>2.12</v>
+      </c>
+      <c r="H32">
+        <v>1.92</v>
+      </c>
+      <c r="I32">
+        <v>6.2</v>
+      </c>
+      <c r="J32">
+        <v>3.75</v>
+      </c>
+      <c r="K32">
+        <v>950</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>1.86</v>
+      </c>
+      <c r="Q32">
+        <v>1.7</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33">
+        <v>1.19</v>
+      </c>
+      <c r="G33">
+        <v>1.2</v>
+      </c>
+      <c r="H33">
+        <v>17</v>
+      </c>
+      <c r="I33">
+        <v>18.5</v>
+      </c>
+      <c r="J33">
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <v>9.4</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>1.02</v>
+      </c>
+      <c r="N33">
+        <v>7.6</v>
+      </c>
+      <c r="O33">
+        <v>1.13</v>
+      </c>
+      <c r="P33">
+        <v>3.3</v>
+      </c>
+      <c r="Q33">
+        <v>1.38</v>
+      </c>
+      <c r="R33">
+        <v>1.92</v>
+      </c>
+      <c r="S33">
+        <v>1.94</v>
+      </c>
+      <c r="T33">
+        <v>1.9</v>
+      </c>
+      <c r="U33">
+        <v>1.93</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>55</v>
+      </c>
+      <c r="Y33">
+        <v>85</v>
+      </c>
+      <c r="Z33">
+        <v>190</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>12.5</v>
+      </c>
+      <c r="AC33">
+        <v>26</v>
+      </c>
+      <c r="AD33">
+        <v>65</v>
+      </c>
+      <c r="AE33">
+        <v>270</v>
+      </c>
+      <c r="AF33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG33">
+        <v>11.5</v>
+      </c>
+      <c r="AH33">
+        <v>44</v>
+      </c>
+      <c r="AI33">
+        <v>180</v>
+      </c>
+      <c r="AJ33">
+        <v>10</v>
+      </c>
+      <c r="AK33">
+        <v>13</v>
+      </c>
+      <c r="AL33">
+        <v>32</v>
+      </c>
+      <c r="AM33">
+        <v>180</v>
+      </c>
+      <c r="AN33">
+        <v>3.1</v>
+      </c>
+      <c r="AO33">
+        <v>260</v>
+      </c>
+      <c r="AP33">
+        <v>36</v>
+      </c>
+      <c r="AQ33">
+        <v>46</v>
+      </c>
+      <c r="AR33">
+        <v>12</v>
+      </c>
+      <c r="AS33">
+        <v>12.5</v>
+      </c>
+      <c r="AT33">
+        <v>11</v>
+      </c>
+      <c r="AU33">
+        <v>19</v>
+      </c>
+      <c r="AV33">
+        <v>42</v>
+      </c>
+      <c r="AW33">
+        <v>12</v>
+      </c>
+      <c r="AX33">
+        <v>8.4</v>
+      </c>
+      <c r="AY33">
+        <v>11</v>
+      </c>
+      <c r="AZ33">
+        <v>30</v>
+      </c>
+      <c r="BA33">
+        <v>11.5</v>
+      </c>
+      <c r="BB33">
+        <v>9</v>
+      </c>
+      <c r="BC33">
+        <v>11</v>
+      </c>
+      <c r="BD33">
+        <v>26</v>
+      </c>
+      <c r="BE33">
+        <v>11.5</v>
+      </c>
+      <c r="BF33">
+        <v>2.94</v>
+      </c>
+      <c r="BG33">
+        <v>12</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>0</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" t="s">
+        <v>191</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1.24</v>
+      </c>
+      <c r="Q34">
+        <v>1.01</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35">
+        <v>1.75</v>
+      </c>
+      <c r="G35">
+        <v>1.99</v>
+      </c>
+      <c r="H35">
+        <v>2.04</v>
+      </c>
+      <c r="I35">
+        <v>7.6</v>
+      </c>
+      <c r="J35">
+        <v>3.4</v>
+      </c>
+      <c r="K35">
+        <v>240</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1.73</v>
+      </c>
+      <c r="Q35">
+        <v>2.02</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
+        <v>0</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>0</v>
+      </c>
+      <c r="BY35">
+        <v>0</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="B30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>178</v>
-      </c>
-      <c r="F30">
-        <v>3.55</v>
-      </c>
-      <c r="G30">
-        <v>3.9</v>
-      </c>
-      <c r="H30">
-        <v>2.36</v>
-      </c>
-      <c r="I30">
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+      <c r="F36">
+        <v>3.5</v>
+      </c>
+      <c r="G36">
+        <v>3.8</v>
+      </c>
+      <c r="H36">
         <v>2.4</v>
       </c>
-      <c r="J30">
-        <v>3.15</v>
-      </c>
-      <c r="K30">
+      <c r="I36">
+        <v>2.48</v>
+      </c>
+      <c r="J36">
+        <v>3.1</v>
+      </c>
+      <c r="K36">
         <v>3.3</v>
       </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>1.58</v>
-      </c>
-      <c r="Q30">
-        <v>2.5</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>0</v>
-      </c>
-      <c r="AO30">
-        <v>0</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
-      <c r="AX30">
-        <v>0</v>
-      </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>0</v>
-      </c>
-      <c r="BC30">
-        <v>0</v>
-      </c>
-      <c r="BD30">
-        <v>0</v>
-      </c>
-      <c r="BE30">
-        <v>0</v>
-      </c>
-      <c r="BF30">
-        <v>0</v>
-      </c>
-      <c r="BG30">
-        <v>0</v>
-      </c>
-      <c r="BH30">
-        <v>0</v>
-      </c>
-      <c r="BI30">
-        <v>0</v>
-      </c>
-      <c r="BJ30">
-        <v>0</v>
-      </c>
-      <c r="BK30">
-        <v>0</v>
-      </c>
-      <c r="BL30">
-        <v>0</v>
-      </c>
-      <c r="BM30">
-        <v>0</v>
-      </c>
-      <c r="BN30">
-        <v>0</v>
-      </c>
-      <c r="BO30">
-        <v>0</v>
-      </c>
-      <c r="BP30">
-        <v>0</v>
-      </c>
-      <c r="BQ30">
-        <v>0</v>
-      </c>
-      <c r="BR30">
-        <v>0</v>
-      </c>
-      <c r="BS30">
-        <v>0</v>
-      </c>
-      <c r="BT30">
-        <v>0</v>
-      </c>
-      <c r="BU30">
-        <v>0</v>
-      </c>
-      <c r="BV30">
-        <v>0</v>
-      </c>
-      <c r="BW30">
-        <v>0</v>
-      </c>
-      <c r="BX30">
-        <v>0</v>
-      </c>
-      <c r="BY30">
-        <v>0</v>
-      </c>
-      <c r="BZ30">
-        <v>0</v>
-      </c>
-      <c r="CA30">
-        <v>0</v>
-      </c>
-      <c r="CB30" t="s">
-        <v>179</v>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1.57</v>
+      </c>
+      <c r="Q36">
+        <v>2.52</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>0</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+      <c r="BQ36">
+        <v>0</v>
+      </c>
+      <c r="BR36">
+        <v>0</v>
+      </c>
+      <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
+        <v>0</v>
+      </c>
+      <c r="BU36">
+        <v>0</v>
+      </c>
+      <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36">
+        <v>0</v>
+      </c>
+      <c r="BX36">
+        <v>0</v>
+      </c>
+      <c r="BY36">
+        <v>0</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="198">
   <si>
     <t>League</t>
   </si>
@@ -322,6 +322,9 @@
     <t>Bulgarian A League</t>
   </si>
   <si>
+    <t>Argentinian Torneo A</t>
+  </si>
+  <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
@@ -478,6 +481,9 @@
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>Defensores de Puerto Vi</t>
+  </si>
+  <si>
     <t>FCSB</t>
   </si>
   <si>
@@ -583,6 +589,9 @@
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Sarmiento de Resistenci</t>
+  </si>
+  <si>
     <t>Farul Constanta</t>
   </si>
   <si>
@@ -598,7 +607,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 13:18:12</t>
+    <t>2026-08-01 15:34:58</t>
   </si>
 </sst>
 </file>
@@ -930,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1180,19 +1189,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G2">
         <v>5.2</v>
@@ -1201,10 +1210,10 @@
         <v>1.87</v>
       </c>
       <c r="I2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
         <v>3.85</v>
@@ -1216,7 +1225,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.35</v>
@@ -1240,7 +1249,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W2">
         <v>1.24</v>
@@ -1414,7 +1423,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1422,28 +1431,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F3">
         <v>2.18</v>
       </c>
       <c r="G3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
         <v>3.05</v>
@@ -1485,7 +1494,7 @@
         <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
         <v>7.8</v>
@@ -1506,7 +1515,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1518,7 +1527,7 @@
         <v>13</v>
       </c>
       <c r="AH3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI3">
         <v>1000</v>
@@ -1527,7 +1536,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1656,7 +1665,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1664,22 +1673,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H4">
         <v>3.6</v>
@@ -1691,13 +1700,13 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.35</v>
@@ -1706,136 +1715,136 @@
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD4">
+        <v>18.5</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>16</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
         <v>22</v>
       </c>
-      <c r="AE4">
+      <c r="AI4">
         <v>70</v>
       </c>
-      <c r="AF4">
-        <v>19</v>
-      </c>
-      <c r="AG4">
+      <c r="AJ4">
+        <v>34</v>
+      </c>
+      <c r="AK4">
+        <v>30</v>
+      </c>
+      <c r="AL4">
+        <v>48</v>
+      </c>
+      <c r="AM4">
+        <v>130</v>
+      </c>
+      <c r="AN4">
+        <v>24</v>
+      </c>
+      <c r="AO4">
+        <v>65</v>
+      </c>
+      <c r="AP4">
+        <v>9.6</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>20</v>
+      </c>
+      <c r="AS4">
+        <v>4.8</v>
+      </c>
+      <c r="AT4">
+        <v>7.6</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>4.6</v>
+      </c>
+      <c r="AX4">
+        <v>11</v>
+      </c>
+      <c r="AY4">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4">
         <v>15.5</v>
       </c>
-      <c r="AH4">
-        <v>26</v>
-      </c>
-      <c r="AI4">
-        <v>85</v>
-      </c>
-      <c r="AJ4">
-        <v>40</v>
-      </c>
-      <c r="AK4">
-        <v>36</v>
-      </c>
-      <c r="AL4">
-        <v>60</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>2.28</v>
-      </c>
-      <c r="AQ4">
-        <v>9.4</v>
-      </c>
-      <c r="AR4">
-        <v>18</v>
-      </c>
-      <c r="AS4">
-        <v>2.24</v>
-      </c>
-      <c r="AT4">
-        <v>1.93</v>
-      </c>
-      <c r="AU4">
-        <v>1.88</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>2.2</v>
-      </c>
-      <c r="AX4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>1.99</v>
-      </c>
-      <c r="AZ4">
-        <v>2.1</v>
-      </c>
       <c r="BA4">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="BB4">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="BC4">
-        <v>2.14</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE4">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="BF4">
-        <v>2.28</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1898,7 +1907,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1906,16 +1915,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F5">
         <v>1.57</v>
@@ -1924,7 +1933,7 @@
         <v>1.61</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -1936,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="M5">
         <v>1.03</v>
@@ -1951,7 +1960,7 @@
         <v>2.76</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R5">
         <v>1.71</v>
@@ -1963,7 +1972,7 @@
         <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.18</v>
@@ -2020,7 +2029,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -2032,10 +2041,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2047,7 +2056,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2059,7 +2068,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
         <v>14</v>
@@ -2068,16 +2077,16 @@
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH5">
         <v>4.8</v>
@@ -2140,7 +2149,7 @@
         <v>6.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2148,34 +2157,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>1.04</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H6">
         <v>1.04</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J6">
         <v>1.04</v>
       </c>
       <c r="K6">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2184,13 +2193,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q6">
         <v>1.15</v>
@@ -2202,10 +2211,10 @@
         <v>1.15</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
         <v>1.02</v>
@@ -2382,7 +2391,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2390,31 +2399,31 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F7">
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H7">
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2444,10 +2453,10 @@
         <v>1.41</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.02</v>
@@ -2567,64 +2576,64 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2632,16 +2641,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>1.98</v>
@@ -2866,7 +2875,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2874,31 +2883,31 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F9">
         <v>1.1</v>
       </c>
       <c r="G9">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>610</v>
@@ -2925,19 +2934,19 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3108,7 +3117,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3116,31 +3125,31 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>1.04</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>1.04</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K10">
         <v>370</v>
@@ -3176,10 +3185,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3350,7 +3359,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3358,19 +3367,19 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G11">
         <v>2.04</v>
@@ -3385,7 +3394,7 @@
         <v>3.5</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3400,7 +3409,7 @@
         <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q11">
         <v>2.02</v>
@@ -3409,19 +3418,19 @@
         <v>1.27</v>
       </c>
       <c r="S11">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.22</v>
       </c>
       <c r="W11">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3535,64 +3544,64 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3600,19 +3609,19 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G12">
         <v>4.1</v>
@@ -3627,37 +3636,37 @@
         <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
         <v>3.35</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
         <v>1.84</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V12">
         <v>1.76</v>
@@ -3666,118 +3675,118 @@
         <v>1.32</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
         <v>4</v>
       </c>
       <c r="BI12">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12">
         <v>13.5</v>
@@ -3834,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3842,232 +3851,232 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4076,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4084,46 +4093,46 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F14">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G14">
         <v>3.6</v>
       </c>
       <c r="H14">
+        <v>2.06</v>
+      </c>
+      <c r="I14">
         <v>2.08</v>
       </c>
-      <c r="I14">
-        <v>2.1</v>
-      </c>
       <c r="J14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
         <v>2.6</v>
@@ -4132,193 +4141,193 @@
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4326,232 +4335,232 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4560,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4568,232 +4577,232 @@
         <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4802,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4810,232 +4819,232 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5044,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5052,232 +5061,232 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5286,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5294,16 +5303,16 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F19">
         <v>3.05</v>
@@ -5324,211 +5333,211 @@
         <v>4.6</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
         <v>1.94</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="CB19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5536,16 +5545,16 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F20">
         <v>3.15</v>
@@ -5560,22 +5569,22 @@
         <v>2.38</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
         <v>2.38</v>
@@ -5584,193 +5593,193 @@
         <v>1.54</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5778,16 +5787,16 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F21">
         <v>2.24</v>
@@ -5808,16 +5817,16 @@
         <v>3.8</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P21">
         <v>2.26</v>
@@ -5826,193 +5835,193 @@
         <v>1.66</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CB21" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6020,16 +6029,16 @@
         <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F22">
         <v>2.98</v>
@@ -6044,217 +6053,217 @@
         <v>2.34</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K22">
         <v>5.5</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6262,232 +6271,232 @@
         <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F23">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G23">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H23">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I23">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K23">
         <v>3.4</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q23">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6496,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6504,16 +6513,16 @@
         <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F24">
         <v>2.2</v>
@@ -6528,22 +6537,22 @@
         <v>3.95</v>
       </c>
       <c r="J24">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K24">
         <v>3.65</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P24">
         <v>1.7</v>
@@ -6552,184 +6561,184 @@
         <v>2.12</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6738,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6746,19 +6755,19 @@
         <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G25">
         <v>1.16</v>
@@ -6776,16 +6785,16 @@
         <v>13</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P25">
         <v>3.35</v>
@@ -6794,193 +6803,193 @@
         <v>1.28</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="CB25" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6988,241 +6997,241 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F26">
         <v>1.51</v>
       </c>
       <c r="G26">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K26">
         <v>5.5</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7230,16 +7239,16 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F27">
         <v>8.4</v>
@@ -7248,10 +7257,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H27">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="I27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="J27">
         <v>5.5</v>
@@ -7260,211 +7269,211 @@
         <v>5.7</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7472,241 +7481,241 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F28">
         <v>1.04</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H28">
         <v>1.04</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J28">
         <v>1.01</v>
       </c>
       <c r="K28">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P28">
+        <v>1.25</v>
+      </c>
+      <c r="Q28">
+        <v>1.16</v>
+      </c>
+      <c r="R28">
         <v>1.24</v>
       </c>
-      <c r="Q28">
-        <v>1.01</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7714,16 +7723,16 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F29">
         <v>2.16</v>
@@ -7738,217 +7747,217 @@
         <v>3.7</v>
       </c>
       <c r="J29">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K29">
         <v>4</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7956,22 +7965,22 @@
         <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F30">
         <v>1.04</v>
       </c>
       <c r="G30">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H30">
         <v>1.04</v>
@@ -7980,217 +7989,217 @@
         <v>1000</v>
       </c>
       <c r="J30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K30">
         <v>350</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P30">
+        <v>1.25</v>
+      </c>
+      <c r="Q30">
+        <v>1.14</v>
+      </c>
+      <c r="R30">
         <v>1.24</v>
       </c>
-      <c r="Q30">
-        <v>1.01</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8198,46 +8207,46 @@
         <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H31">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I31">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J31">
         <v>3.25</v>
       </c>
       <c r="K31">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P31">
         <v>1.86</v>
@@ -8246,500 +8255,500 @@
         <v>1.92</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F32">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G32">
-        <v>2.12</v>
+        <v>110</v>
       </c>
       <c r="H32">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="I32">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K32">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P32">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q32">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F33">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
       <c r="G33">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="H33">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="I33">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="K33">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q33">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="R33">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -8748,166 +8757,166 @@
         <v>0</v>
       </c>
       <c r="X33">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AL33">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN33">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AP33">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AQ33">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AR33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS33">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT33">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU33">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AV33">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AW33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AX33">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY33">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ33">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BA33">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BB33">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BC33">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BD33">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE33">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BF33">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BG33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ33">
         <v>0</v>
@@ -8916,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8924,232 +8933,232 @@
         <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P34">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BG34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9158,42 +9167,42 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F35">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9208,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9400,249 +9409,491 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
         <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F36">
+        <v>1.75</v>
+      </c>
+      <c r="G36">
+        <v>1.99</v>
+      </c>
+      <c r="H36">
+        <v>2.04</v>
+      </c>
+      <c r="I36">
+        <v>7.6</v>
+      </c>
+      <c r="J36">
+        <v>3.4</v>
+      </c>
+      <c r="K36">
+        <v>240</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1.73</v>
+      </c>
+      <c r="Q36">
+        <v>2.02</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>0</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+      <c r="BQ36">
+        <v>0</v>
+      </c>
+      <c r="BR36">
+        <v>0</v>
+      </c>
+      <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
+        <v>0</v>
+      </c>
+      <c r="BU36">
+        <v>0</v>
+      </c>
+      <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36">
+        <v>0</v>
+      </c>
+      <c r="BX36">
+        <v>0</v>
+      </c>
+      <c r="BY36">
+        <v>0</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37">
         <v>3.5</v>
       </c>
-      <c r="G36">
-        <v>3.8</v>
-      </c>
-      <c r="H36">
-        <v>2.4</v>
-      </c>
-      <c r="I36">
+      <c r="G37">
+        <v>3.9</v>
+      </c>
+      <c r="H37">
+        <v>2.42</v>
+      </c>
+      <c r="I37">
         <v>2.48</v>
       </c>
-      <c r="J36">
-        <v>3.1</v>
-      </c>
-      <c r="K36">
+      <c r="J37">
+        <v>3</v>
+      </c>
+      <c r="K37">
         <v>3.3</v>
       </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>1.57</v>
-      </c>
-      <c r="Q36">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>1.55</v>
+      </c>
+      <c r="Q37">
         <v>2.52</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <v>0</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
-      <c r="AK36">
-        <v>0</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
-        <v>0</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>0</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>0</v>
-      </c>
-      <c r="BC36">
-        <v>0</v>
-      </c>
-      <c r="BD36">
-        <v>0</v>
-      </c>
-      <c r="BE36">
-        <v>0</v>
-      </c>
-      <c r="BF36">
-        <v>0</v>
-      </c>
-      <c r="BG36">
-        <v>0</v>
-      </c>
-      <c r="BH36">
-        <v>0</v>
-      </c>
-      <c r="BI36">
-        <v>0</v>
-      </c>
-      <c r="BJ36">
-        <v>0</v>
-      </c>
-      <c r="BK36">
-        <v>0</v>
-      </c>
-      <c r="BL36">
-        <v>0</v>
-      </c>
-      <c r="BM36">
-        <v>0</v>
-      </c>
-      <c r="BN36">
-        <v>0</v>
-      </c>
-      <c r="BO36">
-        <v>0</v>
-      </c>
-      <c r="BP36">
-        <v>0</v>
-      </c>
-      <c r="BQ36">
-        <v>0</v>
-      </c>
-      <c r="BR36">
-        <v>0</v>
-      </c>
-      <c r="BS36">
-        <v>0</v>
-      </c>
-      <c r="BT36">
-        <v>0</v>
-      </c>
-      <c r="BU36">
-        <v>0</v>
-      </c>
-      <c r="BV36">
-        <v>0</v>
-      </c>
-      <c r="BW36">
-        <v>0</v>
-      </c>
-      <c r="BX36">
-        <v>0</v>
-      </c>
-      <c r="BY36">
-        <v>0</v>
-      </c>
-      <c r="BZ36">
-        <v>0</v>
-      </c>
-      <c r="CA36">
-        <v>0</v>
-      </c>
-      <c r="CB36" t="s">
-        <v>194</v>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37">
+        <v>0</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+      <c r="BQ37">
+        <v>0</v>
+      </c>
+      <c r="BR37">
+        <v>0</v>
+      </c>
+      <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
+        <v>0</v>
+      </c>
+      <c r="BU37">
+        <v>0</v>
+      </c>
+      <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
+        <v>0</v>
+      </c>
+      <c r="BX37">
+        <v>0</v>
+      </c>
+      <c r="BY37">
+        <v>0</v>
+      </c>
+      <c r="BZ37">
+        <v>0</v>
+      </c>
+      <c r="CA37">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="202">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,9 @@
     <t>Latvian Virsliga</t>
   </si>
   <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -292,9 +295,6 @@
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
-    <t>Hungarian NB I</t>
-  </si>
-  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
@@ -331,6 +331,9 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
     <t>2026-08-03</t>
   </si>
   <si>
@@ -388,6 +391,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>19:45:00</t>
   </si>
   <si>
@@ -418,36 +424,36 @@
     <t>FK Auda</t>
   </si>
   <si>
+    <t>Zalaegerszeg</t>
+  </si>
+  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Fk Siauliai</t>
   </si>
   <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>SJK</t>
-  </si>
-  <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Longford</t>
-  </si>
-  <si>
     <t>Panevezys</t>
   </si>
   <si>
-    <t>Zalaegerszeg</t>
-  </si>
-  <si>
     <t>OB</t>
   </si>
   <si>
@@ -496,6 +502,9 @@
     <t>Zeleznicar Pancevo</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>Sarmiento de Junin</t>
   </si>
   <si>
@@ -526,36 +535,36 @@
     <t>Ogre United</t>
   </si>
   <si>
+    <t>Paks</t>
+  </si>
+  <si>
     <t>Botosani</t>
   </si>
   <si>
     <t>FK Banga Gargzdu</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>HJK Helsinki</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>HJK Helsinki</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>FC Dziugas</t>
   </si>
   <si>
-    <t>Paks</t>
-  </si>
-  <si>
     <t>SonderjyskE</t>
   </si>
   <si>
@@ -604,10 +613,13 @@
     <t>Mladost Lucani</t>
   </si>
   <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 15:34:58</t>
+    <t>2026-08-01 17:51:07</t>
   </si>
 </sst>
 </file>
@@ -939,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB37"/>
+  <dimension ref="A1:CB38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1189,16 +1201,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F2">
         <v>4.1</v>
@@ -1231,7 +1243,7 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1243,10 +1255,10 @@
         <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
         <v>1.94</v>
@@ -1423,7 +1435,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1431,16 +1443,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F3">
         <v>2.18</v>
@@ -1467,7 +1479,7 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
         <v>1.66</v>
@@ -1485,7 +1497,7 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
         <v>1.64</v>
@@ -1500,7 +1512,7 @@
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
         <v>30</v>
@@ -1515,7 +1527,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1569,7 +1581,7 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AW3">
         <v>36</v>
@@ -1581,7 +1593,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>42</v>
@@ -1665,7 +1677,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1673,22 +1685,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
         <v>3.6</v>
@@ -1700,7 +1712,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1715,10 +1727,10 @@
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
         <v>1.29</v>
@@ -1736,7 +1748,7 @@
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X4">
         <v>14.5</v>
@@ -1802,13 +1814,13 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT4">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV4">
         <v>12</v>
@@ -1817,13 +1829,13 @@
         <v>4.6</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>4.7</v>
@@ -1832,19 +1844,19 @@
         <v>4.4</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF4">
         <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1907,7 +1919,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1915,16 +1927,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>1.57</v>
@@ -2149,7 +2161,7 @@
         <v>6.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2157,25 +2169,25 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6">
         <v>990</v>
@@ -2193,13 +2205,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q6">
         <v>1.15</v>
@@ -2208,7 +2220,7 @@
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2391,7 +2403,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2399,31 +2411,31 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2435,13 +2447,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q7">
         <v>1.05</v>
@@ -2450,7 +2462,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2519,52 +2531,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2633,7 +2645,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2641,16 +2653,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F8">
         <v>1.98</v>
@@ -2677,13 +2689,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="O8">
         <v>1.07</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
         <v>1.07</v>
@@ -2695,10 +2707,10 @@
         <v>1.75</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.33</v>
@@ -2761,52 +2773,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2875,7 +2887,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2883,31 +2895,31 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F9">
         <v>1.1</v>
       </c>
       <c r="G9">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="H9">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
         <v>610</v>
@@ -2919,22 +2931,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2946,7 +2958,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3003,52 +3015,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3117,7 +3129,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3125,34 +3137,34 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F10">
         <v>1.04</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H10">
         <v>1.04</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J10">
         <v>1.04</v>
       </c>
       <c r="K10">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3161,28 +3173,28 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
         <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.02</v>
@@ -3245,52 +3257,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3359,7 +3371,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3367,82 +3379,82 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F11">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="I11">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="O11">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="Q11">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T11">
         <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="W11">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB11">
         <v>1000</v>
@@ -3457,22 +3469,22 @@
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
         <v>1000</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL11">
         <v>1000</v>
@@ -3487,52 +3499,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3544,64 +3556,64 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="CB11" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3609,31 +3621,31 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F12">
-        <v>3.25</v>
+        <v>1.84</v>
       </c>
       <c r="G12">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="H12">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3645,205 +3657,205 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="R12">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T12">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="X12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3851,232 +3863,232 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F13">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="G13">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="H13">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>2.34</v>
       </c>
       <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13">
+        <v>1.29</v>
+      </c>
+      <c r="P13">
+        <v>1.25</v>
+      </c>
+      <c r="Q13">
+        <v>1.94</v>
+      </c>
+      <c r="R13">
+        <v>1.28</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>1.75</v>
+      </c>
+      <c r="U13">
+        <v>1.9</v>
+      </c>
+      <c r="V13">
+        <v>1.74</v>
+      </c>
+      <c r="W13">
+        <v>1.32</v>
+      </c>
+      <c r="X13">
+        <v>17</v>
+      </c>
+      <c r="Y13">
+        <v>11.5</v>
+      </c>
+      <c r="Z13">
+        <v>17</v>
+      </c>
+      <c r="AA13">
+        <v>34</v>
+      </c>
+      <c r="AB13">
+        <v>17</v>
+      </c>
+      <c r="AC13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>13.5</v>
+      </c>
+      <c r="AE13">
+        <v>29</v>
+      </c>
+      <c r="AF13">
+        <v>34</v>
+      </c>
+      <c r="AG13">
+        <v>19</v>
+      </c>
+      <c r="AH13">
+        <v>22</v>
+      </c>
+      <c r="AI13">
+        <v>48</v>
+      </c>
+      <c r="AJ13">
+        <v>90</v>
+      </c>
+      <c r="AK13">
+        <v>60</v>
+      </c>
+      <c r="AL13">
+        <v>70</v>
+      </c>
+      <c r="AM13">
+        <v>120</v>
+      </c>
+      <c r="AN13">
+        <v>60</v>
+      </c>
+      <c r="AO13">
+        <v>22</v>
+      </c>
+      <c r="AP13">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13">
+        <v>1.03</v>
+      </c>
+      <c r="AR13">
+        <v>1.03</v>
+      </c>
+      <c r="AS13">
+        <v>1.03</v>
+      </c>
+      <c r="AT13">
+        <v>1.03</v>
+      </c>
+      <c r="AU13">
+        <v>1.03</v>
+      </c>
+      <c r="AV13">
+        <v>1.03</v>
+      </c>
+      <c r="AW13">
+        <v>1.03</v>
+      </c>
+      <c r="AX13">
+        <v>1.03</v>
+      </c>
+      <c r="AY13">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13">
+        <v>1.03</v>
+      </c>
+      <c r="BA13">
+        <v>1.03</v>
+      </c>
+      <c r="BB13">
+        <v>1.03</v>
+      </c>
+      <c r="BC13">
+        <v>1.03</v>
+      </c>
+      <c r="BD13">
+        <v>1.03</v>
+      </c>
+      <c r="BE13">
+        <v>1.03</v>
+      </c>
+      <c r="BF13">
+        <v>10</v>
+      </c>
+      <c r="BG13">
+        <v>12.5</v>
+      </c>
+      <c r="BH13">
+        <v>4</v>
+      </c>
+      <c r="BI13">
+        <v>2.64</v>
+      </c>
+      <c r="BJ13">
+        <v>13.5</v>
+      </c>
+      <c r="BK13">
+        <v>6.2</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN13">
+        <v>10</v>
+      </c>
+      <c r="BO13">
+        <v>4.5</v>
+      </c>
+      <c r="BP13">
+        <v>46</v>
+      </c>
+      <c r="BQ13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT13">
+        <v>6.8</v>
+      </c>
+      <c r="BU13">
         <v>3.3</v>
       </c>
-      <c r="K13">
-        <v>500</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>4.2</v>
-      </c>
-      <c r="O13">
-        <v>1.23</v>
-      </c>
-      <c r="P13">
-        <v>2.16</v>
-      </c>
-      <c r="Q13">
-        <v>1.65</v>
-      </c>
-      <c r="R13">
-        <v>1.46</v>
-      </c>
-      <c r="S13">
-        <v>2.58</v>
-      </c>
-      <c r="T13">
-        <v>1.01</v>
-      </c>
-      <c r="U13">
-        <v>1.01</v>
-      </c>
-      <c r="V13">
-        <v>1.16</v>
-      </c>
-      <c r="W13">
-        <v>2.24</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>1.01</v>
-      </c>
-      <c r="AR13">
-        <v>1.01</v>
-      </c>
-      <c r="AS13">
-        <v>1.01</v>
-      </c>
-      <c r="AT13">
-        <v>1.01</v>
-      </c>
-      <c r="AU13">
-        <v>1.01</v>
-      </c>
-      <c r="AV13">
-        <v>1.01</v>
-      </c>
-      <c r="AW13">
-        <v>1.01</v>
-      </c>
-      <c r="AX13">
-        <v>1.01</v>
-      </c>
-      <c r="AY13">
-        <v>1.01</v>
-      </c>
-      <c r="AZ13">
-        <v>1.01</v>
-      </c>
-      <c r="BA13">
-        <v>1.01</v>
-      </c>
-      <c r="BB13">
-        <v>1.01</v>
-      </c>
-      <c r="BC13">
-        <v>1.01</v>
-      </c>
-      <c r="BD13">
-        <v>1.01</v>
-      </c>
-      <c r="BE13">
-        <v>1.01</v>
-      </c>
-      <c r="BF13">
-        <v>1.01</v>
-      </c>
-      <c r="BG13">
-        <v>1.01</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.01</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.01</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.01</v>
-      </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4085,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4093,91 +4105,91 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F14">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="G14">
-        <v>3.6</v>
+        <v>1.86</v>
       </c>
       <c r="H14">
-        <v>2.06</v>
+        <v>4.8</v>
       </c>
       <c r="I14">
-        <v>2.08</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>5.7</v>
+        <v>2.94</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="S14">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
         <v>1.11</v>
       </c>
       <c r="U14">
-        <v>2.44</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="W14">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="X14">
         <v>1000</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
         <v>1000</v>
       </c>
       <c r="AA14">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
         <v>1000</v>
       </c>
       <c r="AC14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
         <v>1000</v>
@@ -4189,7 +4201,7 @@
         <v>1000</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
         <v>1000</v>
@@ -4204,7 +4216,7 @@
         <v>1000</v>
       </c>
       <c r="AM14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
         <v>1000</v>
@@ -4213,64 +4225,64 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4321,192 +4333,192 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F15">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="G15">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H15">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="I15">
+        <v>2.08</v>
+      </c>
+      <c r="J15">
+        <v>4.1</v>
+      </c>
+      <c r="K15">
+        <v>4.3</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>5.8</v>
+      </c>
+      <c r="O15">
+        <v>1.18</v>
+      </c>
+      <c r="P15">
+        <v>2.6</v>
+      </c>
+      <c r="Q15">
+        <v>1.54</v>
+      </c>
+      <c r="R15">
+        <v>1.65</v>
+      </c>
+      <c r="S15">
+        <v>2.34</v>
+      </c>
+      <c r="T15">
+        <v>1.53</v>
+      </c>
+      <c r="U15">
         <v>2.62</v>
       </c>
-      <c r="J15">
-        <v>3.55</v>
-      </c>
-      <c r="K15">
-        <v>4.8</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>4</v>
-      </c>
-      <c r="O15">
-        <v>1.23</v>
-      </c>
-      <c r="P15">
-        <v>2.04</v>
-      </c>
-      <c r="Q15">
-        <v>1.73</v>
-      </c>
-      <c r="R15">
-        <v>1.4</v>
-      </c>
-      <c r="S15">
-        <v>2.74</v>
-      </c>
-      <c r="T15">
-        <v>1.11</v>
-      </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="W15">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4563,48 +4575,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F16">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="G16">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="H16">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4613,34 +4625,34 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="Q16">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4697,52 +4709,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -4751,10 +4763,10 @@
         <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
@@ -4811,66 +4823,66 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F17">
-        <v>1.36</v>
+        <v>2.46</v>
       </c>
       <c r="G17">
-        <v>1.53</v>
+        <v>2.86</v>
       </c>
       <c r="H17">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="J17">
+        <v>3.25</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
         <v>3.55</v>
       </c>
-      <c r="K17">
-        <v>7.8</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>3.85</v>
-      </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q17">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="R17">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S17">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -4879,10 +4891,10 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
-        <v>2.88</v>
+        <v>1.54</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4939,52 +4951,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4993,10 +5005,10 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
@@ -5053,42 +5065,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F18">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="G18">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="H18">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>990</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5097,34 +5109,34 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.81</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P18">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S18">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5181,52 +5193,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5235,10 +5247,10 @@
         <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
@@ -5295,42 +5307,42 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
         <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F19">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="G19">
-        <v>4.6</v>
+        <v>1.81</v>
       </c>
       <c r="H19">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>2.84</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>500</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5339,22 +5351,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P19">
+        <v>2.16</v>
+      </c>
+      <c r="Q19">
         <v>1.65</v>
       </c>
-      <c r="Q19">
-        <v>1.94</v>
-      </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5363,10 +5375,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="W19">
-        <v>1.27</v>
+        <v>2.24</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5423,52 +5435,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5477,309 +5489,309 @@
         <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F20">
         <v>3.15</v>
       </c>
       <c r="G20">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="H20">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>4.8</v>
+        <v>2.96</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="P20">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="Q20">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="R20">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="T20">
         <v>1.11</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="W20">
+        <v>1.28</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>4</v>
+      </c>
+      <c r="BI20">
+        <v>2.58</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
         <v>1.34</v>
       </c>
-      <c r="X20">
-        <v>1000</v>
-      </c>
-      <c r="Y20">
-        <v>1000</v>
-      </c>
-      <c r="Z20">
-        <v>1000</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>1000</v>
-      </c>
-      <c r="AC20">
-        <v>1000</v>
-      </c>
-      <c r="AD20">
-        <v>1000</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
-      <c r="AG20">
-        <v>1000</v>
-      </c>
-      <c r="AH20">
-        <v>1000</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>1000</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20">
-        <v>1.01</v>
-      </c>
-      <c r="AR20">
-        <v>1.01</v>
-      </c>
-      <c r="AS20">
-        <v>1.01</v>
-      </c>
-      <c r="AT20">
-        <v>1.01</v>
-      </c>
-      <c r="AU20">
-        <v>1.01</v>
-      </c>
-      <c r="AV20">
-        <v>1.01</v>
-      </c>
-      <c r="AW20">
-        <v>1.01</v>
-      </c>
-      <c r="AX20">
-        <v>1.01</v>
-      </c>
-      <c r="AY20">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20">
-        <v>1.01</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>1.01</v>
-      </c>
-      <c r="BC20">
-        <v>1.01</v>
-      </c>
-      <c r="BD20">
-        <v>1.01</v>
-      </c>
-      <c r="BE20">
-        <v>1.01</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>1.01</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>12.5</v>
-      </c>
-      <c r="BK20">
-        <v>5.4</v>
-      </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BN20">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>1.34</v>
       </c>
       <c r="BP20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BR20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BT20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.6</v>
+        <v>1.34</v>
       </c>
       <c r="BV20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BX20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BZ20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="CB20" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5787,28 +5799,28 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F21">
+        <v>2.22</v>
+      </c>
+      <c r="G21">
         <v>2.24</v>
       </c>
-      <c r="G21">
-        <v>2.26</v>
-      </c>
       <c r="H21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I21">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J21">
         <v>3.75</v>
@@ -5838,7 +5850,7 @@
         <v>1.51</v>
       </c>
       <c r="S21">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T21">
         <v>1.59</v>
@@ -5847,16 +5859,16 @@
         <v>2.24</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X21">
         <v>24</v>
       </c>
       <c r="Y21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z21">
         <v>32</v>
@@ -5871,13 +5883,13 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE21">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF21">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG21">
         <v>13</v>
@@ -5886,7 +5898,7 @@
         <v>18</v>
       </c>
       <c r="AI21">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ21">
         <v>32</v>
@@ -5895,7 +5907,7 @@
         <v>25</v>
       </c>
       <c r="AL21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM21">
         <v>75</v>
@@ -5916,7 +5928,7 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5928,7 +5940,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX21">
         <v>12</v>
@@ -5940,7 +5952,7 @@
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB21">
         <v>20</v>
@@ -5949,10 +5961,10 @@
         <v>16</v>
       </c>
       <c r="BD21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE21">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF21">
         <v>9.4</v>
@@ -5982,28 +5994,28 @@
         <v>7.4</v>
       </c>
       <c r="BO21">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR21">
         <v>34</v>
       </c>
       <c r="BS21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT21">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW21">
         <v>15</v>
@@ -6021,7 +6033,7 @@
         <v>11.5</v>
       </c>
       <c r="CB21" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6029,16 +6041,16 @@
         <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F22">
         <v>2.98</v>
@@ -6065,13 +6077,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
         <v>1.05</v>
       </c>
       <c r="P22">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>1.05</v>
@@ -6080,13 +6092,13 @@
         <v>2.16</v>
       </c>
       <c r="S22">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
         <v>1.74</v>
@@ -6263,7 +6275,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6271,25 +6283,25 @@
         <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G23">
         <v>2.4</v>
       </c>
       <c r="H23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I23">
         <v>4.1</v>
@@ -6298,7 +6310,7 @@
         <v>3.05</v>
       </c>
       <c r="K23">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6328,13 +6340,13 @@
         <v>1.88</v>
       </c>
       <c r="U23">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V23">
         <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X23">
         <v>13</v>
@@ -6364,7 +6376,7 @@
         <v>14.5</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH23">
         <v>20</v>
@@ -6373,7 +6385,7 @@
         <v>85</v>
       </c>
       <c r="AJ23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK23">
         <v>29</v>
@@ -6388,10 +6400,10 @@
         <v>25</v>
       </c>
       <c r="AO23">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ23">
         <v>9.4</v>
@@ -6400,7 +6412,7 @@
         <v>20</v>
       </c>
       <c r="AS23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT23">
         <v>6.2</v>
@@ -6412,7 +6424,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AX23">
         <v>10</v>
@@ -6424,25 +6436,25 @@
         <v>16</v>
       </c>
       <c r="BA23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC23">
         <v>19.5</v>
       </c>
       <c r="BD23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF23">
         <v>17.5</v>
       </c>
       <c r="BG23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6505,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6513,22 +6525,22 @@
         <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F24">
         <v>2.2</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H24">
         <v>3.35</v>
@@ -6561,7 +6573,7 @@
         <v>2.12</v>
       </c>
       <c r="R24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
         <v>3.4</v>
@@ -6576,7 +6588,7 @@
         <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6747,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6755,16 +6767,16 @@
         <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F25">
         <v>1.13</v>
@@ -6776,10 +6788,10 @@
         <v>19</v>
       </c>
       <c r="I25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J25">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K25">
         <v>13</v>
@@ -6800,13 +6812,13 @@
         <v>3.35</v>
       </c>
       <c r="Q25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T25">
         <v>2.04</v>
@@ -6824,10 +6836,10 @@
         <v>60</v>
       </c>
       <c r="Y25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z25">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AA25">
         <v>1000</v>
@@ -6842,7 +6854,7 @@
         <v>100</v>
       </c>
       <c r="AE25">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AF25">
         <v>11.5</v>
@@ -6854,7 +6866,7 @@
         <v>50</v>
       </c>
       <c r="AI25">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AJ25">
         <v>10</v>
@@ -6872,7 +6884,7 @@
         <v>2.72</v>
       </c>
       <c r="AO25">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AP25">
         <v>9.199999999999999</v>
@@ -6989,7 +7001,7 @@
         <v>3.95</v>
       </c>
       <c r="CB25" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6997,22 +7009,22 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F26">
         <v>1.51</v>
       </c>
       <c r="G26">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H26">
         <v>6.2</v>
@@ -7027,7 +7039,7 @@
         <v>5.5</v>
       </c>
       <c r="L26">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M26">
         <v>1.02</v>
@@ -7045,16 +7057,16 @@
         <v>1.5</v>
       </c>
       <c r="R26">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S26">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T26">
         <v>1.68</v>
       </c>
       <c r="U26">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V26">
         <v>1.17</v>
@@ -7078,7 +7090,7 @@
         <v>16</v>
       </c>
       <c r="AC26">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD26">
         <v>30</v>
@@ -7099,10 +7111,10 @@
         <v>70</v>
       </c>
       <c r="AJ26">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AK26">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL26">
         <v>32</v>
@@ -7117,16 +7129,16 @@
         <v>70</v>
       </c>
       <c r="AP26">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ26">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AR26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS26">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT26">
         <v>11.5</v>
@@ -7135,10 +7147,10 @@
         <v>11</v>
       </c>
       <c r="AV26">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AW26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -7147,37 +7159,37 @@
         <v>9.4</v>
       </c>
       <c r="AZ26">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB26">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC26">
         <v>13</v>
       </c>
       <c r="BD26">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE26">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF26">
         <v>4.8</v>
       </c>
       <c r="BG26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI26">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BJ26">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK26">
         <v>5.9</v>
@@ -7186,52 +7198,52 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BN26">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO26">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BP26">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BQ26">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR26">
         <v>28</v>
       </c>
       <c r="BS26">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT26">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BU26">
         <v>6.4</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW26">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY26">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BZ26">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CA26">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB26" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7239,16 +7251,16 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F27">
         <v>8.4</v>
@@ -7269,7 +7281,7 @@
         <v>5.7</v>
       </c>
       <c r="L27">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
         <v>1.03</v>
@@ -7281,13 +7293,13 @@
         <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q27">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S27">
         <v>2.22</v>
@@ -7314,16 +7326,16 @@
         <v>11</v>
       </c>
       <c r="AA27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC27">
         <v>13</v>
       </c>
       <c r="AD27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE27">
         <v>14.5</v>
@@ -7332,10 +7344,10 @@
         <v>80</v>
       </c>
       <c r="AG27">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27">
         <v>29</v>
@@ -7359,7 +7371,7 @@
         <v>4.7</v>
       </c>
       <c r="AP27">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ27">
         <v>11</v>
@@ -7371,7 +7383,7 @@
         <v>11</v>
       </c>
       <c r="AT27">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AU27">
         <v>11.5</v>
@@ -7383,31 +7395,31 @@
         <v>12.5</v>
       </c>
       <c r="AX27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY27">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA27">
         <v>21</v>
       </c>
       <c r="BB27">
+        <v>12</v>
+      </c>
+      <c r="BC27">
         <v>11</v>
       </c>
-      <c r="BC27">
+      <c r="BD27">
         <v>10.5</v>
       </c>
-      <c r="BD27">
-        <v>10</v>
-      </c>
       <c r="BE27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG27">
         <v>4.3</v>
@@ -7473,7 +7485,7 @@
         <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7481,31 +7493,31 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F28">
         <v>1.04</v>
       </c>
       <c r="G28">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H28">
         <v>1.04</v>
       </c>
       <c r="I28">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K28">
         <v>500</v>
@@ -7517,7 +7529,7 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O28">
         <v>1.16</v>
@@ -7535,10 +7547,10 @@
         <v>1.16</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28">
         <v>1.01</v>
@@ -7715,7 +7727,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7723,16 +7735,16 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F29">
         <v>2.16</v>
@@ -7957,7 +7969,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7965,16 +7977,16 @@
         <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F30">
         <v>1.04</v>
@@ -7983,16 +7995,16 @@
         <v>1.56</v>
       </c>
       <c r="H30">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I30">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J30">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="K30">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8001,34 +8013,34 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O30">
         <v>1.14</v>
       </c>
       <c r="P30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q30">
         <v>1.14</v>
       </c>
       <c r="R30">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
         <v>1.14</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V30">
         <v>1.01</v>
       </c>
       <c r="W30">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8199,7 +8211,7 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8207,43 +8219,43 @@
         <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H31">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I31">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J31">
         <v>3.25</v>
       </c>
       <c r="K31">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L31">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
         <v>1.33</v>
@@ -8252,7 +8264,7 @@
         <v>1.86</v>
       </c>
       <c r="Q31">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R31">
         <v>1.28</v>
@@ -8261,10 +8273,10 @@
         <v>3.25</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
         <v>1.64</v>
@@ -8276,7 +8288,7 @@
         <v>1000</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z31">
         <v>1000</v>
@@ -8327,79 +8339,79 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AQ31">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="AR31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AS31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AU31">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AV31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AW31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AX31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AY31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AZ31">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BA31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BC31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BD31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BE31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BF31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG31">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ31">
         <v>13.5</v>
       </c>
       <c r="BK31">
-        <v>5.9</v>
+        <v>1.59</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BN31">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO31">
         <v>4.1</v>
@@ -8408,40 +8420,40 @@
         <v>36</v>
       </c>
       <c r="BQ31">
-        <v>14.5</v>
+        <v>1.72</v>
       </c>
       <c r="BR31">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BT31">
         <v>7.6</v>
       </c>
       <c r="BU31">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV31">
         <v>28</v>
       </c>
       <c r="BW31">
-        <v>11.5</v>
+        <v>1.69</v>
       </c>
       <c r="BX31">
         <v>46</v>
       </c>
       <c r="BY31">
-        <v>18.5</v>
+        <v>1.74</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="CB31" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8449,34 +8461,34 @@
         <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F32">
         <v>1.04</v>
       </c>
       <c r="G32">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H32">
         <v>1.04</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J32">
         <v>1.02</v>
       </c>
       <c r="K32">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8485,28 +8497,28 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O32">
         <v>1.01</v>
       </c>
       <c r="P32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R32">
         <v>1.12</v>
       </c>
       <c r="S32">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32">
         <v>1.01</v>
@@ -8683,249 +8695,249 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F33">
         <v>1.77</v>
       </c>
       <c r="G33">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="H33">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="J33">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K33">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P33">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="Q33">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BD33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BE33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BF33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BH33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8933,16 +8945,16 @@
         <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F34">
         <v>1.19</v>
@@ -8951,19 +8963,19 @@
         <v>1.2</v>
       </c>
       <c r="H34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M34">
         <v>1.02</v>
@@ -8972,25 +8984,25 @@
         <v>7.8</v>
       </c>
       <c r="O34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P34">
         <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R34">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S34">
+        <v>1.93</v>
+      </c>
+      <c r="T34">
+        <v>1.93</v>
+      </c>
+      <c r="U34">
         <v>1.94</v>
-      </c>
-      <c r="T34">
-        <v>1.92</v>
-      </c>
-      <c r="U34">
-        <v>1.93</v>
       </c>
       <c r="V34">
         <v>1.05</v>
@@ -9002,7 +9014,7 @@
         <v>55</v>
       </c>
       <c r="Y34">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Z34">
         <v>190</v>
@@ -9020,7 +9032,7 @@
         <v>65</v>
       </c>
       <c r="AE34">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF34">
         <v>9.199999999999999</v>
@@ -9038,7 +9050,7 @@
         <v>10</v>
       </c>
       <c r="AK34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL34">
         <v>32</v>
@@ -9050,19 +9062,19 @@
         <v>3.1</v>
       </c>
       <c r="AO34">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ34">
         <v>46</v>
       </c>
       <c r="AR34">
+        <v>12.5</v>
+      </c>
+      <c r="AS34">
         <v>13.5</v>
-      </c>
-      <c r="AS34">
-        <v>14.5</v>
       </c>
       <c r="AT34">
         <v>11</v>
@@ -9074,19 +9086,19 @@
         <v>44</v>
       </c>
       <c r="AW34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX34">
         <v>8.6</v>
       </c>
       <c r="AY34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34">
         <v>30</v>
       </c>
       <c r="BA34">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB34">
         <v>9</v>
@@ -9101,10 +9113,10 @@
         <v>13.5</v>
       </c>
       <c r="BF34">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BG34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9167,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9175,16 +9187,16 @@
         <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -9205,202 +9217,202 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q35">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9409,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9417,276 +9429,276 @@
         <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F36">
         <v>1.75</v>
       </c>
       <c r="G36">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="H36">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="I36">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J36">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K36">
-        <v>240</v>
+        <v>4.6</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P36">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
         <v>2.02</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ36">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN36">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP36">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR36">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT36">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F37">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9701,10 +9713,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q37">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9893,7 +9905,249 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>197</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38">
+        <v>3.7</v>
+      </c>
+      <c r="G38">
+        <v>3.8</v>
+      </c>
+      <c r="H38">
+        <v>2.4</v>
+      </c>
+      <c r="I38">
+        <v>2.44</v>
+      </c>
+      <c r="J38">
+        <v>3.1</v>
+      </c>
+      <c r="K38">
+        <v>3.2</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.11</v>
+      </c>
+      <c r="N38">
+        <v>2.76</v>
+      </c>
+      <c r="O38">
+        <v>1.51</v>
+      </c>
+      <c r="P38">
+        <v>1.58</v>
+      </c>
+      <c r="Q38">
+        <v>2.52</v>
+      </c>
+      <c r="R38">
+        <v>1.21</v>
+      </c>
+      <c r="S38">
+        <v>5.2</v>
+      </c>
+      <c r="T38">
+        <v>1.94</v>
+      </c>
+      <c r="U38">
+        <v>1.69</v>
+      </c>
+      <c r="V38">
+        <v>1.69</v>
+      </c>
+      <c r="W38">
+        <v>1.36</v>
+      </c>
+      <c r="X38">
+        <v>9.4</v>
+      </c>
+      <c r="Y38">
+        <v>8.6</v>
+      </c>
+      <c r="Z38">
+        <v>14</v>
+      </c>
+      <c r="AA38">
+        <v>38</v>
+      </c>
+      <c r="AB38">
+        <v>12</v>
+      </c>
+      <c r="AC38">
+        <v>7.4</v>
+      </c>
+      <c r="AD38">
+        <v>12</v>
+      </c>
+      <c r="AE38">
+        <v>38</v>
+      </c>
+      <c r="AF38">
+        <v>25</v>
+      </c>
+      <c r="AG38">
+        <v>16.5</v>
+      </c>
+      <c r="AH38">
+        <v>24</v>
+      </c>
+      <c r="AI38">
+        <v>70</v>
+      </c>
+      <c r="AJ38">
+        <v>90</v>
+      </c>
+      <c r="AK38">
+        <v>70</v>
+      </c>
+      <c r="AL38">
+        <v>90</v>
+      </c>
+      <c r="AM38">
+        <v>210</v>
+      </c>
+      <c r="AN38">
+        <v>95</v>
+      </c>
+      <c r="AO38">
+        <v>40</v>
+      </c>
+      <c r="AP38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ38">
+        <v>6.6</v>
+      </c>
+      <c r="AR38">
+        <v>12</v>
+      </c>
+      <c r="AS38">
+        <v>7</v>
+      </c>
+      <c r="AT38">
+        <v>9</v>
+      </c>
+      <c r="AU38">
+        <v>6.6</v>
+      </c>
+      <c r="AV38">
+        <v>10.5</v>
+      </c>
+      <c r="AW38">
+        <v>7</v>
+      </c>
+      <c r="AX38">
+        <v>21</v>
+      </c>
+      <c r="AY38">
+        <v>14</v>
+      </c>
+      <c r="AZ38">
+        <v>20</v>
+      </c>
+      <c r="BA38">
+        <v>7.8</v>
+      </c>
+      <c r="BB38">
+        <v>8</v>
+      </c>
+      <c r="BC38">
+        <v>7.8</v>
+      </c>
+      <c r="BD38">
+        <v>8</v>
+      </c>
+      <c r="BE38">
+        <v>8.4</v>
+      </c>
+      <c r="BF38">
+        <v>8</v>
+      </c>
+      <c r="BG38">
+        <v>7</v>
+      </c>
+      <c r="BH38">
+        <v>1000</v>
+      </c>
+      <c r="BI38">
+        <v>2.24</v>
+      </c>
+      <c r="BJ38">
+        <v>15.5</v>
+      </c>
+      <c r="BK38">
+        <v>7.2</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>21</v>
+      </c>
+      <c r="BN38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO38">
+        <v>4.5</v>
+      </c>
+      <c r="BP38">
+        <v>50</v>
+      </c>
+      <c r="BQ38">
+        <v>21</v>
+      </c>
+      <c r="BR38">
+        <v>1000</v>
+      </c>
+      <c r="BS38">
+        <v>21</v>
+      </c>
+      <c r="BT38">
+        <v>6.6</v>
+      </c>
+      <c r="BU38">
+        <v>3.45</v>
+      </c>
+      <c r="BV38">
+        <v>29</v>
+      </c>
+      <c r="BW38">
+        <v>13</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>21</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
+        <v>21</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -619,7 +619,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 17:51:07</t>
+    <t>2026-08-01 20:06:49</t>
   </si>
 </sst>
 </file>
@@ -1213,10 +1213,10 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H2">
         <v>1.87</v>
@@ -1225,7 +1225,7 @@
         <v>2.08</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.85</v>
@@ -1243,7 +1243,7 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1461,7 +1461,7 @@
         <v>2.26</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
         <v>4.5</v>
@@ -1470,7 +1470,7 @@
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1581,7 +1581,7 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AW3">
         <v>36</v>
@@ -1593,7 +1593,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA3">
         <v>42</v>
@@ -1602,7 +1602,7 @@
         <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD3">
         <v>36</v>
@@ -1620,61 +1620,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>201</v>
@@ -1712,7 +1712,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1727,10 +1727,10 @@
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.29</v>
@@ -1739,10 +1739,10 @@
         <v>3.7</v>
       </c>
       <c r="T4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.32</v>
@@ -1972,7 +1972,7 @@
         <v>2.76</v>
       </c>
       <c r="Q5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
         <v>1.71</v>
@@ -2041,7 +2041,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -2053,10 +2053,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2068,7 +2068,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2080,25 +2080,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5">
         <v>4.8</v>
@@ -2140,7 +2140,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2158,7 +2158,7 @@
         <v>12</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>201</v>
@@ -2181,22 +2181,22 @@
         <v>168</v>
       </c>
       <c r="F6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="K6">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2423,19 +2423,19 @@
         <v>169</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2447,16 +2447,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2665,22 +2665,22 @@
         <v>170</v>
       </c>
       <c r="F8">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H8">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2689,13 +2689,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="O8">
         <v>1.07</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="Q8">
         <v>1.07</v>
@@ -2713,10 +2713,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2919,10 +2919,10 @@
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K9">
-        <v>610</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2931,7 +2931,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
         <v>1.06</v>
@@ -3161,10 +3161,10 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K10">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3173,7 +3173,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="O10">
         <v>1.12</v>
@@ -3185,10 +3185,10 @@
         <v>1.11</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3394,7 +3394,7 @@
         <v>3.1</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H11">
         <v>2.08</v>
@@ -3409,7 +3409,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3430,10 +3430,10 @@
         <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U11">
         <v>2.18</v>
@@ -3556,7 +3556,7 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BJ11">
         <v>12.5</v>
@@ -3580,13 +3580,13 @@
         <v>34</v>
       </c>
       <c r="BQ11">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BR11">
         <v>44</v>
       </c>
       <c r="BS11">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BT11">
         <v>7.8</v>
@@ -3598,19 +3598,19 @@
         <v>21</v>
       </c>
       <c r="BW11">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="BX11">
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BZ11">
         <v>23</v>
       </c>
       <c r="CA11">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CB11" t="s">
         <v>201</v>
@@ -3896,19 +3896,19 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O13">
         <v>1.29</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
         <v>1.28</v>
@@ -3917,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="T13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U13">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
         <v>1.74</v>
@@ -3962,7 +3962,7 @@
         <v>22</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ13">
         <v>90</v>
@@ -3980,7 +3980,7 @@
         <v>60</v>
       </c>
       <c r="AO13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP13">
         <v>1.03</v>
@@ -4117,10 +4117,10 @@
         <v>176</v>
       </c>
       <c r="F14">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H14">
         <v>4.8</v>
@@ -4288,49 +4288,49 @@
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>5.8</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
         <v>2.6</v>
@@ -4434,7 +4434,7 @@
         <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AF15">
         <v>29</v>
@@ -4464,7 +4464,7 @@
         <v>22</v>
       </c>
       <c r="AO15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP15">
         <v>20</v>
@@ -4503,16 +4503,16 @@
         <v>20</v>
       </c>
       <c r="BB15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15">
         <v>16.5</v>
@@ -4524,61 +4524,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>201</v>
@@ -4766,55 +4766,55 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4849,7 +4849,7 @@
         <v>2.86</v>
       </c>
       <c r="H17">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I17">
         <v>3.3</v>
@@ -4858,7 +4858,7 @@
         <v>3.25</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4876,10 +4876,10 @@
         <v>1.87</v>
       </c>
       <c r="Q17">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
         <v>3.15</v>
@@ -5014,49 +5014,49 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5115,7 +5115,7 @@
         <v>1.23</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q18">
         <v>1.58</v>
@@ -5250,55 +5250,55 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5330,19 +5330,19 @@
         <v>1.63</v>
       </c>
       <c r="G19">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H19">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>500</v>
+        <v>5.8</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5375,10 +5375,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5677,52 +5677,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5856,7 +5856,7 @@
         <v>1.59</v>
       </c>
       <c r="U21">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
         <v>1.39</v>
@@ -5976,19 +5976,19 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ21">
         <v>12</v>
       </c>
       <c r="BK21">
-        <v>5.8</v>
+        <v>1.72</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="BN21">
         <v>7.4</v>
@@ -5997,16 +5997,16 @@
         <v>3.7</v>
       </c>
       <c r="BP21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ21">
-        <v>9.6</v>
+        <v>1.82</v>
       </c>
       <c r="BR21">
         <v>34</v>
       </c>
       <c r="BS21">
-        <v>15.5</v>
+        <v>1.89</v>
       </c>
       <c r="BT21">
         <v>9.199999999999999</v>
@@ -6018,19 +6018,19 @@
         <v>32</v>
       </c>
       <c r="BW21">
-        <v>15</v>
+        <v>1.89</v>
       </c>
       <c r="BX21">
         <v>44</v>
       </c>
       <c r="BY21">
-        <v>19</v>
+        <v>1.92</v>
       </c>
       <c r="BZ21">
         <v>25</v>
       </c>
       <c r="CA21">
-        <v>11.5</v>
+        <v>1.86</v>
       </c>
       <c r="CB21" t="s">
         <v>201</v>
@@ -6062,13 +6062,13 @@
         <v>2.08</v>
       </c>
       <c r="I22">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K22">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6089,10 +6089,10 @@
         <v>1.05</v>
       </c>
       <c r="R22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -6101,7 +6101,7 @@
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W22">
         <v>1.44</v>
@@ -6161,52 +6161,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6346,7 +6346,7 @@
         <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X23">
         <v>13</v>
@@ -6367,7 +6367,7 @@
         <v>7.6</v>
       </c>
       <c r="AD23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23">
         <v>60</v>
@@ -6412,7 +6412,7 @@
         <v>20</v>
       </c>
       <c r="AS23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT23">
         <v>6.2</v>
@@ -6439,22 +6439,22 @@
         <v>6.6</v>
       </c>
       <c r="BB23">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC23">
         <v>19.5</v>
       </c>
       <c r="BD23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF23">
         <v>17.5</v>
       </c>
       <c r="BG23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6573,7 +6573,7 @@
         <v>2.12</v>
       </c>
       <c r="R24">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S24">
         <v>3.4</v>
@@ -6594,43 +6594,43 @@
         <v>1000</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI24">
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL24">
         <v>1000</v>
@@ -6645,52 +6645,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6788,13 +6788,13 @@
         <v>19</v>
       </c>
       <c r="I25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J25">
         <v>9.800000000000001</v>
       </c>
       <c r="K25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6803,28 +6803,28 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O25">
         <v>1.09</v>
       </c>
       <c r="P25">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q25">
         <v>1.3</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="T25">
         <v>2.04</v>
       </c>
       <c r="U25">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V25">
         <v>1.03</v>
@@ -6833,7 +6833,7 @@
         <v>7.2</v>
       </c>
       <c r="X25">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -6854,7 +6854,7 @@
         <v>100</v>
       </c>
       <c r="AE25">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AF25">
         <v>11.5</v>
@@ -6866,7 +6866,7 @@
         <v>50</v>
       </c>
       <c r="AI25">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ25">
         <v>10</v>
@@ -6878,61 +6878,61 @@
         <v>46</v>
       </c>
       <c r="AM25">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN25">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AO25">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AP25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
         <v>2.18</v>
@@ -6950,13 +6950,13 @@
         <v>20</v>
       </c>
       <c r="BK25">
-        <v>8.800000000000001</v>
+        <v>2.74</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BN25">
         <v>5.4</v>
@@ -6968,37 +6968,37 @@
         <v>7.8</v>
       </c>
       <c r="BQ25">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="BR25">
         <v>28</v>
       </c>
       <c r="BS25">
-        <v>8.800000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="BT25">
         <v>30</v>
       </c>
       <c r="BU25">
-        <v>8.800000000000001</v>
+        <v>2.86</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BZ25">
         <v>7.8</v>
       </c>
       <c r="CA25">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="CB25" t="s">
         <v>201</v>
@@ -7024,10 +7024,10 @@
         <v>1.51</v>
       </c>
       <c r="G26">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I26">
         <v>6.6</v>
@@ -7039,7 +7039,7 @@
         <v>5.5</v>
       </c>
       <c r="L26">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M26">
         <v>1.02</v>
@@ -7048,16 +7048,16 @@
         <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P26">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q26">
         <v>1.5</v>
       </c>
       <c r="R26">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S26">
         <v>2.24</v>
@@ -7066,7 +7066,7 @@
         <v>1.68</v>
       </c>
       <c r="U26">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V26">
         <v>1.17</v>
@@ -7087,10 +7087,10 @@
         <v>180</v>
       </c>
       <c r="AB26">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AC26">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD26">
         <v>30</v>
@@ -7111,10 +7111,10 @@
         <v>70</v>
       </c>
       <c r="AJ26">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AK26">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AL26">
         <v>32</v>
@@ -7129,16 +7129,16 @@
         <v>70</v>
       </c>
       <c r="AP26">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ26">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR26">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AS26">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT26">
         <v>11.5</v>
@@ -7147,10 +7147,10 @@
         <v>11</v>
       </c>
       <c r="AV26">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW26">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -7159,28 +7159,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ26">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA26">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BB26">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BC26">
         <v>13</v>
       </c>
       <c r="BD26">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BE26">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BF26">
         <v>4.8</v>
       </c>
       <c r="BG26">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BH26">
         <v>4.9</v>
@@ -7296,7 +7296,7 @@
         <v>2.82</v>
       </c>
       <c r="Q27">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R27">
         <v>1.73</v>
@@ -7359,10 +7359,10 @@
         <v>130</v>
       </c>
       <c r="AL27">
+        <v>80</v>
+      </c>
+      <c r="AM27">
         <v>85</v>
-      </c>
-      <c r="AM27">
-        <v>90</v>
       </c>
       <c r="AN27">
         <v>110</v>
@@ -7395,7 +7395,7 @@
         <v>12.5</v>
       </c>
       <c r="AX27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY27">
         <v>8.800000000000001</v>
@@ -7410,10 +7410,10 @@
         <v>12</v>
       </c>
       <c r="BC27">
+        <v>11.5</v>
+      </c>
+      <c r="BD27">
         <v>11</v>
-      </c>
-      <c r="BD27">
-        <v>10.5</v>
       </c>
       <c r="BE27">
         <v>11</v>
@@ -7428,37 +7428,37 @@
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BJ27">
         <v>15</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BN27">
         <v>17</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BT27">
         <v>6</v>
@@ -7476,13 +7476,13 @@
         <v>28</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BZ27">
         <v>14.5</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB27" t="s">
         <v>201</v>
@@ -7517,7 +7517,7 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K28">
         <v>500</v>
@@ -7553,10 +7553,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7613,52 +7613,52 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
         <v>1.01</v>
@@ -7750,7 +7750,7 @@
         <v>2.16</v>
       </c>
       <c r="G29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H29">
         <v>3.2</v>
@@ -7798,37 +7798,37 @@
         <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X29">
         <v>1000</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA29">
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC29">
         <v>11.5</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE29">
         <v>1000</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH29">
         <v>23</v>
@@ -7837,10 +7837,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL29">
         <v>1000</v>
@@ -7855,118 +7855,118 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>1.16</v>
+        <v>16</v>
       </c>
       <c r="AS29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="AT29">
-        <v>1.16</v>
+        <v>7.4</v>
       </c>
       <c r="AU29">
-        <v>1.05</v>
+        <v>1.71</v>
       </c>
       <c r="AV29">
-        <v>1.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="AX29">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AY29">
-        <v>1.16</v>
+        <v>7.2</v>
       </c>
       <c r="AZ29">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="BA29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="BB29">
-        <v>1.16</v>
+        <v>18.5</v>
       </c>
       <c r="BC29">
-        <v>1.16</v>
+        <v>14.5</v>
       </c>
       <c r="BD29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="BE29">
-        <v>1.15</v>
+        <v>1.97</v>
       </c>
       <c r="BF29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="BG29">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>201</v>
@@ -8037,7 +8037,7 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30">
         <v>2.78</v>
@@ -8097,52 +8097,52 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
         <v>1.01</v>
@@ -8291,28 +8291,28 @@
         <v>14.5</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC31">
         <v>11.5</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH31">
         <v>25</v>
@@ -8339,58 +8339,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="AQ31">
         <v>6.8</v>
       </c>
       <c r="AR31">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AS31">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="AT31">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="AU31">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="AV31">
-        <v>1.24</v>
+        <v>7.6</v>
       </c>
       <c r="AW31">
-        <v>1.24</v>
+        <v>17</v>
       </c>
       <c r="AX31">
-        <v>1.24</v>
+        <v>13.5</v>
       </c>
       <c r="AY31">
-        <v>1.24</v>
+        <v>8.6</v>
       </c>
       <c r="AZ31">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="BA31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BB31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BC31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BD31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BE31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BF31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BG31">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8485,7 +8485,7 @@
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K32">
         <v>500</v>
@@ -8500,7 +8500,7 @@
         <v>1.25</v>
       </c>
       <c r="O32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P32">
         <v>1.25</v>
@@ -8521,10 +8521,10 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8581,52 +8581,52 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32">
         <v>1.01</v>
@@ -8715,10 +8715,10 @@
         <v>195</v>
       </c>
       <c r="F33">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G33">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H33">
         <v>4.5</v>
@@ -8736,205 +8736,205 @@
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N33">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P33">
         <v>2.08</v>
       </c>
       <c r="Q33">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R33">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S33">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="T33">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U33">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V33">
         <v>1.23</v>
       </c>
       <c r="W33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP33">
-        <v>1.12</v>
+        <v>13</v>
       </c>
       <c r="AQ33">
-        <v>1.12</v>
+        <v>16</v>
       </c>
       <c r="AR33">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="AS33">
-        <v>1.12</v>
+        <v>7.4</v>
       </c>
       <c r="AT33">
-        <v>1.12</v>
+        <v>8.6</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV33">
-        <v>1.12</v>
+        <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="AX33">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="AY33">
-        <v>1.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ33">
-        <v>1.08</v>
+        <v>16</v>
       </c>
       <c r="BA33">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="BB33">
-        <v>1.12</v>
+        <v>17</v>
       </c>
       <c r="BC33">
-        <v>1.12</v>
+        <v>5.6</v>
       </c>
       <c r="BD33">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="BE33">
-        <v>1.12</v>
+        <v>7.4</v>
       </c>
       <c r="BF33">
-        <v>1.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG33">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>201</v>
@@ -8957,61 +8957,61 @@
         <v>196</v>
       </c>
       <c r="F34">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G34">
+        <v>1.22</v>
+      </c>
+      <c r="H34">
+        <v>16</v>
+      </c>
+      <c r="I34">
+        <v>17.5</v>
+      </c>
+      <c r="J34">
+        <v>8.6</v>
+      </c>
+      <c r="K34">
+        <v>9</v>
+      </c>
+      <c r="L34">
         <v>1.2</v>
-      </c>
-      <c r="H34">
-        <v>16.5</v>
-      </c>
-      <c r="I34">
-        <v>19</v>
-      </c>
-      <c r="J34">
-        <v>9</v>
-      </c>
-      <c r="K34">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L34">
-        <v>1.19</v>
       </c>
       <c r="M34">
         <v>1.02</v>
       </c>
       <c r="N34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P34">
         <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="R34">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S34">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T34">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U34">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="X34">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y34">
         <v>80</v>
@@ -9026,7 +9026,7 @@
         <v>12.5</v>
       </c>
       <c r="AC34">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AD34">
         <v>65</v>
@@ -9038,7 +9038,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH34">
         <v>44</v>
@@ -9047,7 +9047,7 @@
         <v>180</v>
       </c>
       <c r="AJ34">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK34">
         <v>12.5</v>
@@ -9071,22 +9071,22 @@
         <v>46</v>
       </c>
       <c r="AR34">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT34">
         <v>11</v>
       </c>
       <c r="AU34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AV34">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX34">
         <v>8.6</v>
@@ -9098,25 +9098,25 @@
         <v>30</v>
       </c>
       <c r="BA34">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB34">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC34">
         <v>11</v>
       </c>
       <c r="BD34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE34">
         <v>13.5</v>
       </c>
       <c r="BF34">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BG34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9307,52 +9307,52 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AR35">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS35">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT35">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU35">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV35">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW35">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX35">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY35">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA35">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB35">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BC35">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD35">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BE35">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF35">
         <v>1.01</v>
@@ -9364,55 +9364,55 @@
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN35">
         <v>1000</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9483,10 +9483,10 @@
         <v>3</v>
       </c>
       <c r="T36">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U36">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V36">
         <v>1.17</v>
@@ -9498,7 +9498,7 @@
         <v>1000</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z36">
         <v>1000</v>
@@ -9507,10 +9507,10 @@
         <v>1000</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD36">
         <v>1000</v>
@@ -9549,52 +9549,52 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36">
         <v>1.01</v>
@@ -9612,55 +9612,55 @@
         <v>15.5</v>
       </c>
       <c r="BK36">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BN36">
         <v>6</v>
       </c>
       <c r="BO36">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BP36">
         <v>18.5</v>
       </c>
       <c r="BQ36">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BR36">
         <v>46</v>
       </c>
       <c r="BS36">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BT36">
         <v>12.5</v>
       </c>
       <c r="BU36">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BZ36">
         <v>40</v>
       </c>
       <c r="CA36">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="CB36" t="s">
         <v>201</v>
@@ -9683,226 +9683,226 @@
         <v>199</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P37">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="s">
         <v>201</v>
@@ -9967,10 +9967,10 @@
         <v>5.2</v>
       </c>
       <c r="T38">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="U38">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="V38">
         <v>1.69</v>
@@ -9982,13 +9982,13 @@
         <v>9.4</v>
       </c>
       <c r="Y38">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA38">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB38">
         <v>12</v>
@@ -10003,7 +10003,7 @@
         <v>38</v>
       </c>
       <c r="AF38">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG38">
         <v>16.5</v>
@@ -10015,7 +10015,7 @@
         <v>70</v>
       </c>
       <c r="AJ38">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AK38">
         <v>70</v>
@@ -10030,7 +10030,7 @@
         <v>95</v>
       </c>
       <c r="AO38">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP38">
         <v>8.199999999999999</v>
@@ -10042,7 +10042,7 @@
         <v>12</v>
       </c>
       <c r="AS38">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT38">
         <v>9</v>
@@ -10054,7 +10054,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX38">
         <v>21</v>
@@ -10066,25 +10066,25 @@
         <v>20</v>
       </c>
       <c r="BA38">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC38">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE38">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG38">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10096,13 +10096,13 @@
         <v>15.5</v>
       </c>
       <c r="BK38">
-        <v>7.2</v>
+        <v>1.57</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BN38">
         <v>9.199999999999999</v>
@@ -10114,13 +10114,13 @@
         <v>50</v>
       </c>
       <c r="BQ38">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>21</v>
+        <v>1.7</v>
       </c>
       <c r="BT38">
         <v>6.6</v>
@@ -10132,19 +10132,19 @@
         <v>29</v>
       </c>
       <c r="BW38">
-        <v>13</v>
+        <v>1.64</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>21</v>
+        <v>1.69</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>21</v>
+        <v>1.7</v>
       </c>
       <c r="CB38" t="s">
         <v>201</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -619,7 +619,7 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>2026-08-01 20:06:49</t>
+    <t>2026-08-01 22:23:33</t>
   </si>
 </sst>
 </file>
@@ -1216,16 +1216,16 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.85</v>
@@ -1240,10 +1240,10 @@
         <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1252,7 +1252,7 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -1261,7 +1261,7 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W2">
         <v>1.24</v>
@@ -1455,28 +1455,28 @@
         <v>165</v>
       </c>
       <c r="F3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
         <v>2.26</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
         <v>2.38</v>
@@ -1488,19 +1488,19 @@
         <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T3">
         <v>2.46</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
         <v>1.28</v>
@@ -1509,7 +1509,7 @@
         <v>1.79</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
@@ -1524,7 +1524,7 @@
         <v>6.6</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
         <v>21</v>
@@ -1533,7 +1533,7 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AK3">
         <v>65</v>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS3">
         <v>38</v>
@@ -1578,28 +1578,28 @@
         <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC3">
         <v>24</v>
@@ -1614,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1700,7 +1700,7 @@
         <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H4">
         <v>3.6</v>
@@ -1736,7 +1736,7 @@
         <v>1.29</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
         <v>1.81</v>
@@ -1793,7 +1793,7 @@
         <v>30</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>130</v>
@@ -1841,13 +1841,13 @@
         <v>4.7</v>
       </c>
       <c r="BB4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BE4">
         <v>4.8</v>
@@ -1939,7 +1939,7 @@
         <v>167</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G5">
         <v>1.61</v>
@@ -1954,7 +1954,7 @@
         <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.21</v>
@@ -2041,10 +2041,10 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP5">
         <v>19</v>
@@ -2053,10 +2053,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2068,7 +2068,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2080,25 +2080,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>4.8</v>
@@ -2122,7 +2122,7 @@
         <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>9.4</v>
@@ -2140,7 +2140,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2181,19 +2181,19 @@
         <v>168</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2220,7 +2220,7 @@
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2346,61 +2346,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>201</v>
@@ -2423,19 +2423,19 @@
         <v>169</v>
       </c>
       <c r="F7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2447,13 +2447,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
         <v>1.02</v>
@@ -2462,7 +2462,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2689,7 +2689,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="O8">
         <v>1.07</v>
@@ -2931,7 +2931,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
         <v>1.06</v>
@@ -2946,7 +2946,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -3072,61 +3072,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>201</v>
@@ -3149,19 +3149,19 @@
         <v>172</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G10">
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3173,13 +3173,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
         <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q10">
         <v>1.11</v>
@@ -3188,7 +3188,7 @@
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3197,7 +3197,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
         <v>1.02</v>
@@ -3391,7 +3391,7 @@
         <v>173</v>
       </c>
       <c r="F11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
         <v>3.9</v>
@@ -3400,13 +3400,13 @@
         <v>2.08</v>
       </c>
       <c r="I11">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
         <v>1.21</v>
@@ -3439,7 +3439,7 @@
         <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W11">
         <v>1.34</v>
@@ -3448,7 +3448,7 @@
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
         <v>22</v>
@@ -3523,7 +3523,7 @@
         <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY11">
         <v>10</v>
@@ -3532,7 +3532,7 @@
         <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>1.03</v>
@@ -3556,7 +3556,7 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BJ11">
         <v>12.5</v>
@@ -3571,7 +3571,7 @@
         <v>1.93</v>
       </c>
       <c r="BN11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO11">
         <v>4.7</v>
@@ -3580,7 +3580,7 @@
         <v>34</v>
       </c>
       <c r="BQ11">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BR11">
         <v>44</v>
@@ -3604,13 +3604,13 @@
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BZ11">
         <v>23</v>
       </c>
       <c r="CA11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CB11" t="s">
         <v>201</v>
@@ -3657,7 +3657,7 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
         <v>1.35</v>
@@ -3875,7 +3875,7 @@
         <v>175</v>
       </c>
       <c r="F13">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G13">
         <v>4.1</v>
@@ -3896,25 +3896,25 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T13">
         <v>1.76</v>
@@ -3923,13 +3923,13 @@
         <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W13">
         <v>1.32</v>
       </c>
       <c r="X13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y13">
         <v>11.5</v>
@@ -3983,58 +3983,58 @@
         <v>21</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF13">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="BG13">
-        <v>12.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH13">
         <v>4</v>
@@ -4046,49 +4046,49 @@
         <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>2.68</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="BN13">
         <v>10</v>
       </c>
       <c r="BO13">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="BP13">
         <v>46</v>
       </c>
       <c r="BQ13">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BT13">
         <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="BV13">
         <v>23</v>
       </c>
       <c r="BW13">
-        <v>8.800000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="BX13">
         <v>44</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4601,217 +4601,217 @@
         <v>178</v>
       </c>
       <c r="F16">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H16">
         <v>2.26</v>
       </c>
       <c r="I16">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J16">
         <v>3.55</v>
       </c>
       <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>1.29</v>
+      </c>
+      <c r="M16">
+        <v>1.05</v>
+      </c>
+      <c r="N16">
+        <v>4.2</v>
+      </c>
+      <c r="O16">
+        <v>1.26</v>
+      </c>
+      <c r="P16">
+        <v>2.08</v>
+      </c>
+      <c r="Q16">
+        <v>1.75</v>
+      </c>
+      <c r="R16">
+        <v>1.42</v>
+      </c>
+      <c r="S16">
+        <v>2.88</v>
+      </c>
+      <c r="T16">
+        <v>1.63</v>
+      </c>
+      <c r="U16">
+        <v>2.28</v>
+      </c>
+      <c r="V16">
+        <v>1.63</v>
+      </c>
+      <c r="W16">
+        <v>1.42</v>
+      </c>
+      <c r="X16">
+        <v>22</v>
+      </c>
+      <c r="Y16">
+        <v>15</v>
+      </c>
+      <c r="Z16">
+        <v>21</v>
+      </c>
+      <c r="AA16">
+        <v>40</v>
+      </c>
+      <c r="AB16">
+        <v>17.5</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16">
+        <v>30</v>
+      </c>
+      <c r="AF16">
+        <v>28</v>
+      </c>
+      <c r="AG16">
+        <v>16.5</v>
+      </c>
+      <c r="AH16">
+        <v>19.5</v>
+      </c>
+      <c r="AI16">
+        <v>42</v>
+      </c>
+      <c r="AJ16">
+        <v>65</v>
+      </c>
+      <c r="AK16">
+        <v>40</v>
+      </c>
+      <c r="AL16">
+        <v>48</v>
+      </c>
+      <c r="AM16">
+        <v>90</v>
+      </c>
+      <c r="AN16">
+        <v>32</v>
+      </c>
+      <c r="AO16">
+        <v>21</v>
+      </c>
+      <c r="AP16">
+        <v>13</v>
+      </c>
+      <c r="AQ16">
+        <v>9</v>
+      </c>
+      <c r="AR16">
+        <v>12</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>10.5</v>
+      </c>
+      <c r="AU16">
+        <v>6.4</v>
+      </c>
+      <c r="AV16">
+        <v>8.6</v>
+      </c>
+      <c r="AW16">
+        <v>17.5</v>
+      </c>
+      <c r="AX16">
+        <v>16.5</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>11.5</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>19</v>
+      </c>
+      <c r="BG16">
+        <v>12</v>
+      </c>
+      <c r="BH16">
+        <v>3.9</v>
+      </c>
+      <c r="BI16">
+        <v>2.98</v>
+      </c>
+      <c r="BJ16">
+        <v>9.4</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>6.8</v>
+      </c>
+      <c r="BO16">
         <v>4.8</v>
       </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>4</v>
-      </c>
-      <c r="O16">
-        <v>1.23</v>
-      </c>
-      <c r="P16">
-        <v>2.04</v>
-      </c>
-      <c r="Q16">
-        <v>1.73</v>
-      </c>
-      <c r="R16">
-        <v>1.4</v>
-      </c>
-      <c r="S16">
-        <v>2.74</v>
-      </c>
-      <c r="T16">
-        <v>1.11</v>
-      </c>
-      <c r="U16">
-        <v>1.11</v>
-      </c>
-      <c r="V16">
-        <v>1.62</v>
-      </c>
-      <c r="W16">
-        <v>1.41</v>
-      </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.03</v>
-      </c>
-      <c r="AQ16">
-        <v>1.03</v>
-      </c>
-      <c r="AR16">
-        <v>1.03</v>
-      </c>
-      <c r="AS16">
-        <v>1.03</v>
-      </c>
-      <c r="AT16">
-        <v>1.03</v>
-      </c>
-      <c r="AU16">
-        <v>1.03</v>
-      </c>
-      <c r="AV16">
-        <v>1.03</v>
-      </c>
-      <c r="AW16">
-        <v>1.03</v>
-      </c>
-      <c r="AX16">
-        <v>1.03</v>
-      </c>
-      <c r="AY16">
-        <v>1.03</v>
-      </c>
-      <c r="AZ16">
-        <v>1.03</v>
-      </c>
-      <c r="BA16">
-        <v>1.03</v>
-      </c>
-      <c r="BB16">
-        <v>1.03</v>
-      </c>
-      <c r="BC16">
-        <v>1.03</v>
-      </c>
-      <c r="BD16">
-        <v>1.03</v>
-      </c>
-      <c r="BE16">
-        <v>1.03</v>
-      </c>
-      <c r="BF16">
-        <v>1.01</v>
-      </c>
-      <c r="BG16">
-        <v>1.01</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ16">
         <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS16">
         <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW16">
         <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY16">
         <v>1.04</v>
@@ -4846,7 +4846,7 @@
         <v>2.46</v>
       </c>
       <c r="G17">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H17">
         <v>2.78</v>
@@ -5336,10 +5336,10 @@
         <v>4.7</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
         <v>5.8</v>
@@ -5572,7 +5572,7 @@
         <v>3.15</v>
       </c>
       <c r="G20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H20">
         <v>2.22</v>
@@ -5829,13 +5829,13 @@
         <v>3.8</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O21">
         <v>1.22</v>
@@ -5868,7 +5868,7 @@
         <v>24</v>
       </c>
       <c r="Y21">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z21">
         <v>32</v>
@@ -5895,13 +5895,13 @@
         <v>13</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI21">
         <v>42</v>
       </c>
       <c r="AJ21">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK21">
         <v>25</v>
@@ -5916,7 +5916,7 @@
         <v>14</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP21">
         <v>16</v>
@@ -5928,7 +5928,7 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5940,7 +5940,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX21">
         <v>12</v>
@@ -5952,7 +5952,7 @@
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB21">
         <v>20</v>
@@ -5961,10 +5961,10 @@
         <v>16</v>
       </c>
       <c r="BD21">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE21">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF21">
         <v>9.4</v>
@@ -5973,64 +5973,64 @@
         <v>19.5</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI21">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK21">
-        <v>1.72</v>
+        <v>4.7</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN21">
+        <v>5.6</v>
+      </c>
+      <c r="BO21">
+        <v>4.6</v>
+      </c>
+      <c r="BP21">
+        <v>15.5</v>
+      </c>
+      <c r="BQ21">
+        <v>6</v>
+      </c>
+      <c r="BR21">
+        <v>25</v>
+      </c>
+      <c r="BS21">
+        <v>7</v>
+      </c>
+      <c r="BT21">
+        <v>7.2</v>
+      </c>
+      <c r="BU21">
+        <v>5.4</v>
+      </c>
+      <c r="BV21">
+        <v>25</v>
+      </c>
+      <c r="BW21">
+        <v>7</v>
+      </c>
+      <c r="BX21">
+        <v>32</v>
+      </c>
+      <c r="BY21">
         <v>7.4</v>
       </c>
-      <c r="BO21">
-        <v>3.7</v>
-      </c>
-      <c r="BP21">
-        <v>20</v>
-      </c>
-      <c r="BQ21">
-        <v>1.82</v>
-      </c>
-      <c r="BR21">
-        <v>34</v>
-      </c>
-      <c r="BS21">
-        <v>1.89</v>
-      </c>
-      <c r="BT21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU21">
-        <v>4.5</v>
-      </c>
-      <c r="BV21">
-        <v>32</v>
-      </c>
-      <c r="BW21">
-        <v>1.89</v>
-      </c>
-      <c r="BX21">
-        <v>44</v>
-      </c>
-      <c r="BY21">
-        <v>1.92</v>
-      </c>
       <c r="BZ21">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="CA21">
-        <v>1.86</v>
+        <v>6.4</v>
       </c>
       <c r="CB21" t="s">
         <v>201</v>
@@ -6095,10 +6095,10 @@
         <v>1.67</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="V22">
         <v>1.8</v>
@@ -6110,22 +6110,22 @@
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE22">
         <v>1000</v>
@@ -6134,10 +6134,10 @@
         <v>1000</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI22">
         <v>1000</v>
@@ -6146,10 +6146,10 @@
         <v>1000</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22">
         <v>1000</v>
@@ -6176,7 +6176,7 @@
         <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV22">
         <v>1.03</v>
@@ -6200,10 +6200,10 @@
         <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BE22">
         <v>1.03</v>
@@ -6307,7 +6307,7 @@
         <v>4.1</v>
       </c>
       <c r="J23">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
         <v>3.2</v>
@@ -6406,10 +6406,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR23">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="AS23">
         <v>6.8</v>
@@ -6460,19 +6460,19 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BJ23">
         <v>15</v>
       </c>
       <c r="BK23">
-        <v>6.4</v>
+        <v>1.57</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BN23">
         <v>7</v>
@@ -6484,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="BQ23">
-        <v>11</v>
+        <v>1.64</v>
       </c>
       <c r="BR23">
         <v>50</v>
       </c>
       <c r="BS23">
-        <v>21</v>
+        <v>1.69</v>
       </c>
       <c r="BT23">
         <v>9.6</v>
@@ -6499,16 +6499,16 @@
         <v>4.4</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW23">
-        <v>19</v>
+        <v>1.69</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>21</v>
+        <v>1.71</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>2.2</v>
       </c>
       <c r="G24">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
         <v>3.35</v>
@@ -6549,19 +6549,19 @@
         <v>3.95</v>
       </c>
       <c r="J24">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
         <v>3.65</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N24">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="O24">
         <v>1.38</v>
@@ -6570,187 +6570,187 @@
         <v>1.7</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R24">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S24">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T24">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="U24">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
         <v>1.66</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y24">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z24">
+        <v>29</v>
+      </c>
+      <c r="AA24">
+        <v>85</v>
+      </c>
+      <c r="AB24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24">
+        <v>8.6</v>
+      </c>
+      <c r="AD24">
+        <v>16</v>
+      </c>
+      <c r="AE24">
+        <v>60</v>
+      </c>
+      <c r="AF24">
+        <v>16.5</v>
+      </c>
+      <c r="AG24">
+        <v>13.5</v>
+      </c>
+      <c r="AH24">
+        <v>20</v>
+      </c>
+      <c r="AI24">
+        <v>70</v>
+      </c>
+      <c r="AJ24">
+        <v>38</v>
+      </c>
+      <c r="AK24">
         <v>34</v>
       </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>12.5</v>
-      </c>
-      <c r="AC24">
-        <v>10</v>
-      </c>
-      <c r="AD24">
+      <c r="AL24">
+        <v>55</v>
+      </c>
+      <c r="AM24">
+        <v>140</v>
+      </c>
+      <c r="AN24">
+        <v>29</v>
+      </c>
+      <c r="AO24">
+        <v>65</v>
+      </c>
+      <c r="AP24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR24">
+        <v>19</v>
+      </c>
+      <c r="AS24">
+        <v>1.03</v>
+      </c>
+      <c r="AT24">
+        <v>6.8</v>
+      </c>
+      <c r="AU24">
+        <v>5.9</v>
+      </c>
+      <c r="AV24">
+        <v>13</v>
+      </c>
+      <c r="AW24">
+        <v>1.03</v>
+      </c>
+      <c r="AX24">
+        <v>11</v>
+      </c>
+      <c r="AY24">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24">
+        <v>16</v>
+      </c>
+      <c r="BA24">
+        <v>1.03</v>
+      </c>
+      <c r="BB24">
+        <v>1.03</v>
+      </c>
+      <c r="BC24">
         <v>21</v>
       </c>
-      <c r="AE24">
-        <v>1000</v>
-      </c>
-      <c r="AF24">
-        <v>20</v>
-      </c>
-      <c r="AG24">
-        <v>16</v>
-      </c>
-      <c r="AH24">
-        <v>28</v>
-      </c>
-      <c r="AI24">
-        <v>1000</v>
-      </c>
-      <c r="AJ24">
-        <v>46</v>
-      </c>
-      <c r="AK24">
-        <v>40</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>1000</v>
-      </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24">
+      <c r="BD24">
+        <v>1.03</v>
+      </c>
+      <c r="BE24">
+        <v>1.03</v>
+      </c>
+      <c r="BF24">
+        <v>18.5</v>
+      </c>
+      <c r="BG24">
+        <v>42</v>
+      </c>
+      <c r="BH24">
+        <v>3.2</v>
+      </c>
+      <c r="BI24">
+        <v>2.74</v>
+      </c>
+      <c r="BJ24">
+        <v>10.5</v>
+      </c>
+      <c r="BK24">
+        <v>8</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN24">
+        <v>5.3</v>
+      </c>
+      <c r="BO24">
+        <v>4</v>
+      </c>
+      <c r="BP24">
+        <v>19</v>
+      </c>
+      <c r="BQ24">
+        <v>6.8</v>
+      </c>
+      <c r="BR24">
+        <v>36</v>
+      </c>
+      <c r="BS24">
+        <v>8</v>
+      </c>
+      <c r="BT24">
+        <v>7</v>
+      </c>
+      <c r="BU24">
+        <v>5.2</v>
+      </c>
+      <c r="BV24">
+        <v>32</v>
+      </c>
+      <c r="BW24">
         <v>7.8</v>
       </c>
-      <c r="AR24">
-        <v>15.5</v>
-      </c>
-      <c r="AS24">
-        <v>1.03</v>
-      </c>
-      <c r="AT24">
-        <v>5.8</v>
-      </c>
-      <c r="AU24">
-        <v>5</v>
-      </c>
-      <c r="AV24">
-        <v>9.6</v>
-      </c>
-      <c r="AW24">
-        <v>1.03</v>
-      </c>
-      <c r="AX24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY24">
-        <v>7.4</v>
-      </c>
-      <c r="AZ24">
-        <v>12</v>
-      </c>
-      <c r="BA24">
-        <v>1.03</v>
-      </c>
-      <c r="BB24">
-        <v>1.03</v>
-      </c>
-      <c r="BC24">
-        <v>17.5</v>
-      </c>
-      <c r="BD24">
-        <v>1.03</v>
-      </c>
-      <c r="BE24">
-        <v>1.03</v>
-      </c>
-      <c r="BF24">
-        <v>1.01</v>
-      </c>
-      <c r="BG24">
-        <v>1.01</v>
-      </c>
-      <c r="BH24">
-        <v>3.75</v>
-      </c>
-      <c r="BI24">
-        <v>2.52</v>
-      </c>
-      <c r="BJ24">
-        <v>13.5</v>
-      </c>
-      <c r="BK24">
-        <v>2.84</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>3.6</v>
-      </c>
-      <c r="BN24">
-        <v>6.6</v>
-      </c>
-      <c r="BO24">
-        <v>3.45</v>
-      </c>
-      <c r="BP24">
-        <v>25</v>
-      </c>
-      <c r="BQ24">
-        <v>3.15</v>
-      </c>
-      <c r="BR24">
+      <c r="BX24">
         <v>48</v>
       </c>
-      <c r="BS24">
-        <v>3.35</v>
-      </c>
-      <c r="BT24">
-        <v>9</v>
-      </c>
-      <c r="BU24">
-        <v>4.5</v>
-      </c>
-      <c r="BV24">
-        <v>44</v>
-      </c>
-      <c r="BW24">
-        <v>3.3</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
       <c r="BY24">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>13.5</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M25">
         <v>1.01</v>
@@ -6815,7 +6815,7 @@
         <v>1.3</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.67</v>
@@ -6824,7 +6824,7 @@
         <v>2.04</v>
       </c>
       <c r="U25">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V25">
         <v>1.03</v>
@@ -6941,64 +6941,64 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH25">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BI25">
         <v>4.2</v>
       </c>
       <c r="BJ25">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BK25">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BN25">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO25">
         <v>2.88</v>
       </c>
       <c r="BP25">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BQ25">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="BR25">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BS25">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="BT25">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BU25">
-        <v>2.86</v>
+        <v>5.7</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BZ25">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="CA25">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="CB25" t="s">
         <v>201</v>
@@ -7048,7 +7048,7 @@
         <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
         <v>2.8</v>
@@ -7204,7 +7204,7 @@
         <v>4.5</v>
       </c>
       <c r="BO26">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BP26">
         <v>9</v>
@@ -7222,7 +7222,7 @@
         <v>10.5</v>
       </c>
       <c r="BU26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV26">
         <v>65</v>
@@ -7266,10 +7266,10 @@
         <v>8.4</v>
       </c>
       <c r="G27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="I27">
         <v>1.44</v>
@@ -7302,7 +7302,7 @@
         <v>1.73</v>
       </c>
       <c r="S27">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T27">
         <v>1.75</v>
@@ -7314,7 +7314,7 @@
         <v>3.3</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>38</v>
@@ -7398,7 +7398,7 @@
         <v>11</v>
       </c>
       <c r="AY27">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AZ27">
         <v>19</v>
@@ -7517,10 +7517,10 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K28">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7529,19 +7529,19 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O28">
         <v>1.16</v>
       </c>
       <c r="P28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q28">
         <v>1.16</v>
       </c>
       <c r="R28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S28">
         <v>1.16</v>
@@ -7768,13 +7768,13 @@
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="O29">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P29">
         <v>2.06</v>
@@ -7783,130 +7783,130 @@
         <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="T29">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="U29">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V29">
         <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y29">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Z29">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB29">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AC29">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF29">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG29">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ29">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK29">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM29">
         <v>100</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AQ29">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AS29">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="AT29">
+        <v>9.6</v>
+      </c>
+      <c r="AU29">
+        <v>7.2</v>
+      </c>
+      <c r="AV29">
+        <v>12</v>
+      </c>
+      <c r="AW29">
+        <v>7.2</v>
+      </c>
+      <c r="AX29">
+        <v>13</v>
+      </c>
+      <c r="AY29">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29">
+        <v>14</v>
+      </c>
+      <c r="BA29">
         <v>7.4</v>
       </c>
-      <c r="AU29">
-        <v>1.71</v>
-      </c>
-      <c r="AV29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW29">
-        <v>2</v>
-      </c>
-      <c r="AX29">
-        <v>10</v>
-      </c>
-      <c r="AY29">
-        <v>7.2</v>
-      </c>
-      <c r="AZ29">
-        <v>1.84</v>
-      </c>
-      <c r="BA29">
-        <v>2</v>
-      </c>
       <c r="BB29">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC29">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BE29">
-        <v>1.97</v>
+        <v>8</v>
       </c>
       <c r="BF29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="BG29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7989,7 +7989,7 @@
         <v>192</v>
       </c>
       <c r="F30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G30">
         <v>1.56</v>
@@ -8004,7 +8004,7 @@
         <v>4.4</v>
       </c>
       <c r="K30">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8037,7 +8037,7 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W30">
         <v>2.78</v>
@@ -8234,7 +8234,7 @@
         <v>3</v>
       </c>
       <c r="G31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H31">
         <v>2.34</v>
@@ -8252,7 +8252,7 @@
         <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
         <v>3.5</v>
@@ -8267,10 +8267,10 @@
         <v>1.94</v>
       </c>
       <c r="R31">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T31">
         <v>1.74</v>
@@ -8285,112 +8285,112 @@
         <v>1.42</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y31">
+        <v>11</v>
+      </c>
+      <c r="Z31">
+        <v>17</v>
+      </c>
+      <c r="AA31">
+        <v>38</v>
+      </c>
+      <c r="AB31">
+        <v>13</v>
+      </c>
+      <c r="AC31">
+        <v>8.4</v>
+      </c>
+      <c r="AD31">
+        <v>12.5</v>
+      </c>
+      <c r="AE31">
+        <v>29</v>
+      </c>
+      <c r="AF31">
+        <v>23</v>
+      </c>
+      <c r="AG31">
         <v>14.5</v>
       </c>
-      <c r="Z31">
-        <v>23</v>
-      </c>
-      <c r="AA31">
+      <c r="AH31">
+        <v>18</v>
+      </c>
+      <c r="AI31">
+        <v>42</v>
+      </c>
+      <c r="AJ31">
+        <v>60</v>
+      </c>
+      <c r="AK31">
+        <v>40</v>
+      </c>
+      <c r="AL31">
         <v>50</v>
       </c>
-      <c r="AB31">
-        <v>17.5</v>
-      </c>
-      <c r="AC31">
+      <c r="AM31">
+        <v>120</v>
+      </c>
+      <c r="AN31">
+        <v>38</v>
+      </c>
+      <c r="AO31">
+        <v>27</v>
+      </c>
+      <c r="AP31">
+        <v>10</v>
+      </c>
+      <c r="AQ31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR31">
+        <v>13.5</v>
+      </c>
+      <c r="AS31">
+        <v>6.4</v>
+      </c>
+      <c r="AT31">
+        <v>10.5</v>
+      </c>
+      <c r="AU31">
+        <v>6.8</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>6</v>
+      </c>
+      <c r="AX31">
+        <v>18.5</v>
+      </c>
+      <c r="AY31">
         <v>11.5</v>
       </c>
-      <c r="AD31">
-        <v>17</v>
-      </c>
-      <c r="AE31">
-        <v>40</v>
-      </c>
-      <c r="AF31">
-        <v>30</v>
-      </c>
-      <c r="AG31">
-        <v>19.5</v>
-      </c>
-      <c r="AH31">
-        <v>25</v>
-      </c>
-      <c r="AI31">
-        <v>1000</v>
-      </c>
-      <c r="AJ31">
-        <v>1000</v>
-      </c>
-      <c r="AK31">
-        <v>1000</v>
-      </c>
-      <c r="AL31">
-        <v>1000</v>
-      </c>
-      <c r="AM31">
-        <v>1000</v>
-      </c>
-      <c r="AN31">
-        <v>1000</v>
-      </c>
-      <c r="AO31">
-        <v>1000</v>
-      </c>
-      <c r="AP31">
-        <v>1.94</v>
-      </c>
-      <c r="AQ31">
+      <c r="AZ31">
+        <v>14.5</v>
+      </c>
+      <c r="BA31">
+        <v>6.4</v>
+      </c>
+      <c r="BB31">
         <v>6.8</v>
       </c>
-      <c r="AR31">
-        <v>10.5</v>
-      </c>
-      <c r="AS31">
-        <v>21</v>
-      </c>
-      <c r="AT31">
-        <v>7.8</v>
-      </c>
-      <c r="AU31">
-        <v>1.66</v>
-      </c>
-      <c r="AV31">
-        <v>7.6</v>
-      </c>
-      <c r="AW31">
-        <v>17</v>
-      </c>
-      <c r="AX31">
-        <v>13.5</v>
-      </c>
-      <c r="AY31">
-        <v>8.6</v>
-      </c>
-      <c r="AZ31">
-        <v>1.8</v>
-      </c>
-      <c r="BA31">
-        <v>1.94</v>
-      </c>
-      <c r="BB31">
-        <v>1.94</v>
-      </c>
       <c r="BC31">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="BD31">
-        <v>1.94</v>
+        <v>6.6</v>
       </c>
       <c r="BE31">
-        <v>1.94</v>
+        <v>7.2</v>
       </c>
       <c r="BF31">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="BG31">
-        <v>1.94</v>
+        <v>16</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8414,7 +8414,7 @@
         <v>9</v>
       </c>
       <c r="BO31">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP31">
         <v>36</v>
@@ -8485,10 +8485,10 @@
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K32">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8506,13 +8506,13 @@
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R32">
         <v>1.12</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
         <v>1.11</v>
@@ -8757,7 +8757,7 @@
         <v>2.98</v>
       </c>
       <c r="T33">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U33">
         <v>2.12</v>
@@ -8769,7 +8769,7 @@
         <v>2.12</v>
       </c>
       <c r="X33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y33">
         <v>19</v>
@@ -8832,10 +8832,10 @@
         <v>6.8</v>
       </c>
       <c r="AS33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT33">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU33">
         <v>8.199999999999999</v>
@@ -8865,10 +8865,10 @@
         <v>5.6</v>
       </c>
       <c r="BD33">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF33">
         <v>9.199999999999999</v>
@@ -9038,7 +9038,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH34">
         <v>44</v>
@@ -9053,7 +9053,7 @@
         <v>12.5</v>
       </c>
       <c r="AL34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM34">
         <v>180</v>
@@ -9071,10 +9071,10 @@
         <v>46</v>
       </c>
       <c r="AR34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT34">
         <v>11</v>
@@ -9083,22 +9083,22 @@
         <v>18.5</v>
       </c>
       <c r="AV34">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW34">
         <v>14</v>
       </c>
       <c r="AX34">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY34">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34">
         <v>30</v>
       </c>
       <c r="BA34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB34">
         <v>9.199999999999999</v>
@@ -9110,7 +9110,7 @@
         <v>25</v>
       </c>
       <c r="BE34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF34">
         <v>3</v>
@@ -9122,55 +9122,55 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9307,52 +9307,52 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
         <v>3.45</v>
       </c>
       <c r="K36">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
         <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="R37">
         <v>2.06</v>
@@ -9928,13 +9928,13 @@
         <v>3.7</v>
       </c>
       <c r="G38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H38">
         <v>2.4</v>
       </c>
       <c r="I38">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J38">
         <v>3.1</v>
@@ -9949,22 +9949,22 @@
         <v>1.11</v>
       </c>
       <c r="N38">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="O38">
         <v>1.51</v>
       </c>
       <c r="P38">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q38">
         <v>2.52</v>
       </c>
       <c r="R38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T38">
         <v>2.08</v>
@@ -9973,10 +9973,10 @@
         <v>1.8</v>
       </c>
       <c r="V38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W38">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X38">
         <v>9.4</v>
@@ -10096,7 +10096,7 @@
         <v>15.5</v>
       </c>
       <c r="BK38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BL38">
         <v>1000</v>
@@ -10126,7 +10126,7 @@
         <v>6.6</v>
       </c>
       <c r="BU38">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV38">
         <v>29</v>
@@ -10144,7 +10144,7 @@
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CB38" t="s">
         <v>201</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="215">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
     <t>Costa Rican Primera Division</t>
   </si>
   <si>
-    <t>Argentinian Primera Division</t>
-  </si>
-  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -343,9 +343,6 @@
     <t>2026-08-03</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>00:30:00</t>
   </si>
   <si>
@@ -409,12 +406,12 @@
     <t>22:00:00</t>
   </si>
   <si>
+    <t>Lanus</t>
+  </si>
+  <si>
     <t>Inter San Carlos</t>
   </si>
   <si>
-    <t>Lanus</t>
-  </si>
-  <si>
     <t>Santa Fe</t>
   </si>
   <si>
@@ -535,12 +532,12 @@
     <t>Paysandu FC</t>
   </si>
   <si>
+    <t>Instituto</t>
+  </si>
+  <si>
     <t>Cs Herediano</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
     <t>Once Caldas</t>
   </si>
   <si>
@@ -661,7 +658,7 @@
     <t>Club Oriental de La Paz</t>
   </si>
   <si>
-    <t>2026-08-02 00:38:45</t>
+    <t>2026-08-02 02:52:46</t>
   </si>
 </sst>
 </file>
@@ -1249,235 +1246,235 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>5.3</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
+        <v>10.5</v>
+      </c>
+      <c r="Z2">
+        <v>30</v>
+      </c>
+      <c r="AA2">
+        <v>130</v>
+      </c>
+      <c r="AB2">
+        <v>6.6</v>
+      </c>
+      <c r="AC2">
+        <v>7.4</v>
+      </c>
+      <c r="AD2">
+        <v>21</v>
+      </c>
+      <c r="AE2">
+        <v>95</v>
+      </c>
+      <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>32</v>
+      </c>
+      <c r="AK2">
+        <v>36</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>330</v>
+      </c>
+      <c r="AN2">
+        <v>38</v>
+      </c>
+      <c r="AO2">
+        <v>160</v>
+      </c>
+      <c r="AP2">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2">
+        <v>9</v>
+      </c>
+      <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>38</v>
+      </c>
+      <c r="AT2">
+        <v>5.9</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>17.5</v>
+      </c>
+      <c r="AW2">
+        <v>65</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
+        <v>24</v>
+      </c>
+      <c r="BA2">
+        <v>42</v>
+      </c>
+      <c r="BB2">
+        <v>19.5</v>
+      </c>
+      <c r="BC2">
+        <v>28</v>
+      </c>
+      <c r="BD2">
+        <v>36</v>
+      </c>
+      <c r="BE2">
+        <v>70</v>
+      </c>
+      <c r="BF2">
+        <v>29</v>
+      </c>
+      <c r="BG2">
+        <v>42</v>
+      </c>
+      <c r="BH2">
+        <v>2.6</v>
+      </c>
+      <c r="BI2">
+        <v>2.1</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2">
+        <v>6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>10.5</v>
+      </c>
+      <c r="BN2">
+        <v>4.9</v>
+      </c>
+      <c r="BO2">
+        <v>3.6</v>
+      </c>
+      <c r="BP2">
+        <v>21</v>
+      </c>
+      <c r="BQ2">
+        <v>7.2</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z2">
-        <v>13.5</v>
-      </c>
-      <c r="AA2">
-        <v>27</v>
-      </c>
-      <c r="AB2">
-        <v>16.5</v>
-      </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>12.5</v>
-      </c>
-      <c r="AE2">
-        <v>27</v>
-      </c>
-      <c r="AF2">
-        <v>40</v>
-      </c>
-      <c r="AG2">
-        <v>22</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>50</v>
-      </c>
-      <c r="AJ2">
-        <v>130</v>
-      </c>
-      <c r="AK2">
-        <v>80</v>
-      </c>
-      <c r="AL2">
-        <v>90</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>100</v>
-      </c>
-      <c r="AO2">
-        <v>20</v>
-      </c>
-      <c r="AP2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>6.2</v>
-      </c>
-      <c r="AR2">
-        <v>9</v>
-      </c>
-      <c r="AS2">
-        <v>18</v>
-      </c>
-      <c r="AT2">
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <v>6.2</v>
-      </c>
-      <c r="AV2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>17.5</v>
-      </c>
-      <c r="AX2">
-        <v>1.03</v>
-      </c>
-      <c r="AY2">
-        <v>14</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
-      <c r="BA2">
-        <v>1.03</v>
-      </c>
-      <c r="BB2">
-        <v>1.03</v>
-      </c>
-      <c r="BC2">
-        <v>1.03</v>
-      </c>
-      <c r="BD2">
-        <v>1.03</v>
-      </c>
-      <c r="BE2">
-        <v>1.03</v>
-      </c>
-      <c r="BF2">
-        <v>60</v>
-      </c>
-      <c r="BG2">
-        <v>13</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.04</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.04</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.04</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.04</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.04</v>
-      </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1488,238 +1485,238 @@
         <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="I3">
+        <v>2.06</v>
+      </c>
+      <c r="J3">
+        <v>3.4</v>
+      </c>
+      <c r="K3">
+        <v>3.7</v>
+      </c>
+      <c r="L3">
+        <v>1.46</v>
+      </c>
+      <c r="M3">
+        <v>1.08</v>
+      </c>
+      <c r="N3">
+        <v>3.3</v>
+      </c>
+      <c r="O3">
+        <v>1.38</v>
+      </c>
+      <c r="P3">
+        <v>1.77</v>
+      </c>
+      <c r="Q3">
+        <v>2.16</v>
+      </c>
+      <c r="R3">
+        <v>1.29</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>1.9</v>
+      </c>
+      <c r="U3">
+        <v>1.9</v>
+      </c>
+      <c r="V3">
+        <v>1.94</v>
+      </c>
+      <c r="W3">
+        <v>1.28</v>
+      </c>
+      <c r="X3">
+        <v>14</v>
+      </c>
+      <c r="Y3">
+        <v>9.4</v>
+      </c>
+      <c r="Z3">
+        <v>14</v>
+      </c>
+      <c r="AA3">
+        <v>29</v>
+      </c>
+      <c r="AB3">
+        <v>16</v>
+      </c>
+      <c r="AC3">
+        <v>9</v>
+      </c>
+      <c r="AD3">
+        <v>12.5</v>
+      </c>
+      <c r="AE3">
+        <v>28</v>
+      </c>
+      <c r="AF3">
+        <v>38</v>
+      </c>
+      <c r="AG3">
+        <v>21</v>
+      </c>
+      <c r="AH3">
+        <v>24</v>
+      </c>
+      <c r="AI3">
+        <v>50</v>
+      </c>
+      <c r="AJ3">
+        <v>120</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
+        <v>85</v>
+      </c>
+      <c r="AM3">
+        <v>150</v>
+      </c>
+      <c r="AN3">
+        <v>90</v>
+      </c>
+      <c r="AO3">
+        <v>22</v>
+      </c>
+      <c r="AP3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>6.2</v>
+      </c>
+      <c r="AR3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3">
+        <v>19</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW3">
+        <v>18</v>
+      </c>
+      <c r="AX3">
         <v>4.5</v>
       </c>
-      <c r="J3">
-        <v>3.05</v>
-      </c>
-      <c r="K3">
-        <v>3.15</v>
-      </c>
-      <c r="L3">
-        <v>1.52</v>
-      </c>
-      <c r="M3">
-        <v>1.15</v>
-      </c>
-      <c r="N3">
-        <v>2.38</v>
-      </c>
-      <c r="O3">
-        <v>1.67</v>
-      </c>
-      <c r="P3">
-        <v>1.46</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3">
-        <v>1.16</v>
-      </c>
-      <c r="S3">
-        <v>6.8</v>
-      </c>
-      <c r="T3">
-        <v>2.46</v>
-      </c>
-      <c r="U3">
-        <v>1.65</v>
-      </c>
-      <c r="V3">
-        <v>1.29</v>
-      </c>
-      <c r="W3">
-        <v>1.79</v>
-      </c>
-      <c r="X3">
-        <v>7.4</v>
-      </c>
-      <c r="Y3">
-        <v>10.5</v>
-      </c>
-      <c r="Z3">
-        <v>30</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>6.6</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>21</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>12</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
-      </c>
-      <c r="AH3">
+      <c r="AY3">
+        <v>13.5</v>
+      </c>
+      <c r="AZ3">
+        <v>15.5</v>
+      </c>
+      <c r="BA3">
+        <v>4.6</v>
+      </c>
+      <c r="BB3">
+        <v>4.9</v>
+      </c>
+      <c r="BC3">
+        <v>4.8</v>
+      </c>
+      <c r="BD3">
+        <v>4.8</v>
+      </c>
+      <c r="BE3">
+        <v>4.9</v>
+      </c>
+      <c r="BF3">
+        <v>4.8</v>
+      </c>
+      <c r="BG3">
+        <v>14</v>
+      </c>
+      <c r="BH3">
+        <v>3.25</v>
+      </c>
+      <c r="BI3">
+        <v>2.6</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>5.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>10</v>
+      </c>
+      <c r="BN3">
+        <v>7.8</v>
+      </c>
+      <c r="BO3">
+        <v>4.5</v>
+      </c>
+      <c r="BP3">
+        <v>42</v>
+      </c>
+      <c r="BQ3">
+        <v>8.4</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT3">
+        <v>4.8</v>
+      </c>
+      <c r="BU3">
+        <v>3.7</v>
+      </c>
+      <c r="BV3">
+        <v>16</v>
+      </c>
+      <c r="BW3">
+        <v>6.4</v>
+      </c>
+      <c r="BX3">
+        <v>34</v>
+      </c>
+      <c r="BY3">
+        <v>8</v>
+      </c>
+      <c r="BZ3">
         <v>32</v>
       </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>34</v>
-      </c>
-      <c r="AK3">
-        <v>65</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>330</v>
-      </c>
-      <c r="AN3">
-        <v>70</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>6.8</v>
-      </c>
-      <c r="AQ3">
-        <v>9</v>
-      </c>
-      <c r="AR3">
-        <v>18</v>
-      </c>
-      <c r="AS3">
-        <v>38</v>
-      </c>
-      <c r="AT3">
-        <v>5.8</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>17.5</v>
-      </c>
-      <c r="AW3">
-        <v>34</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>19.5</v>
-      </c>
-      <c r="BA3">
-        <v>42</v>
-      </c>
-      <c r="BB3">
-        <v>19.5</v>
-      </c>
-      <c r="BC3">
-        <v>24</v>
-      </c>
-      <c r="BD3">
-        <v>36</v>
-      </c>
-      <c r="BE3">
-        <v>55</v>
-      </c>
-      <c r="BF3">
-        <v>29</v>
-      </c>
-      <c r="BG3">
-        <v>42</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.04</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>1.04</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>1.04</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1730,55 +1727,55 @@
         <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H4">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
         <v>1.81</v>
@@ -1787,10 +1784,10 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X4">
         <v>14.5</v>
@@ -1907,16 +1904,16 @@
         <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>5.1</v>
@@ -1928,13 +1925,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
@@ -1946,22 +1943,22 @@
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1972,13 +1969,13 @@
         <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>1.58</v>
@@ -1987,7 +1984,7 @@
         <v>1.61</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -1999,7 +1996,7 @@
         <v>4.9</v>
       </c>
       <c r="L5">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M5">
         <v>1.03</v>
@@ -2008,19 +2005,19 @@
         <v>6.2</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R5">
         <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T5">
         <v>1.65</v>
@@ -2029,7 +2026,7 @@
         <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
         <v>2.62</v>
@@ -2038,7 +2035,7 @@
         <v>29</v>
       </c>
       <c r="Y5">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z5">
         <v>55</v>
@@ -2053,7 +2050,7 @@
         <v>14</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE5">
         <v>85</v>
@@ -2089,16 +2086,16 @@
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5">
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2122,7 +2119,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB5">
         <v>14</v>
@@ -2134,13 +2131,13 @@
         <v>6</v>
       </c>
       <c r="BE5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -2203,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="CB5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2214,28 +2211,28 @@
         <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2331,52 +2328,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2445,7 +2442,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2456,28 +2453,28 @@
         <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2489,13 +2486,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
         <v>1.02</v>
@@ -2504,7 +2501,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2573,52 +2570,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2687,7 +2684,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2698,13 +2695,13 @@
         <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F8">
         <v>2.02</v>
@@ -2815,16 +2812,16 @@
         <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8">
         <v>21</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT8">
         <v>17.5</v>
@@ -2851,7 +2848,7 @@
         <v>19</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2860,13 +2857,13 @@
         <v>16</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF8">
         <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2929,7 +2926,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2940,28 +2937,28 @@
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2997,10 +2994,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3057,52 +3054,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3171,7 +3168,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3182,13 +3179,13 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3299,52 +3296,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3413,7 +3410,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3424,25 +3421,25 @@
         <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F11">
         <v>3.15</v>
       </c>
       <c r="G11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J11">
         <v>3.85</v>
@@ -3478,10 +3475,10 @@
         <v>1.55</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W11">
         <v>1.39</v>
@@ -3535,7 +3532,7 @@
         <v>70</v>
       </c>
       <c r="AN11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>13.5</v>
@@ -3550,7 +3547,7 @@
         <v>12</v>
       </c>
       <c r="AS11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT11">
         <v>13</v>
@@ -3562,13 +3559,13 @@
         <v>8.4</v>
       </c>
       <c r="AW11">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AX11">
         <v>18</v>
       </c>
       <c r="AY11">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
         <v>13</v>
@@ -3577,22 +3574,22 @@
         <v>20</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF11">
         <v>16</v>
       </c>
       <c r="BG11">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH11">
         <v>4.4</v>
@@ -3610,25 +3607,25 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO11">
         <v>5.2</v>
       </c>
       <c r="BP11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11">
         <v>44</v>
       </c>
       <c r="BS11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT11">
         <v>5.5</v>
@@ -3640,22 +3637,22 @@
         <v>14.5</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX11">
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
         <v>16.5</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3666,13 +3663,13 @@
         <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F12">
         <v>1.86</v>
@@ -3696,145 +3693,145 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P12">
         <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
         <v>1.98</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y12">
+        <v>17.5</v>
+      </c>
+      <c r="Z12">
+        <v>42</v>
+      </c>
+      <c r="AA12">
+        <v>140</v>
+      </c>
+      <c r="AB12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC12">
+        <v>9.4</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>80</v>
+      </c>
+      <c r="AF12">
+        <v>13</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>24</v>
+      </c>
+      <c r="AI12">
+        <v>90</v>
+      </c>
+      <c r="AJ12">
+        <v>26</v>
+      </c>
+      <c r="AK12">
+        <v>26</v>
+      </c>
+      <c r="AL12">
+        <v>48</v>
+      </c>
+      <c r="AM12">
+        <v>150</v>
+      </c>
+      <c r="AN12">
         <v>18.5</v>
       </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>9.6</v>
-      </c>
-      <c r="AC12">
-        <v>9.6</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>27</v>
-      </c>
-      <c r="AK12">
-        <v>27</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>1.39</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS12">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT12">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU12">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX12">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="AZ12">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="BB12">
-        <v>1.42</v>
+        <v>4.4</v>
       </c>
       <c r="BC12">
-        <v>1.42</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE12">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF12">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="BG12">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3897,7 +3894,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3908,13 +3905,13 @@
         <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F13">
         <v>3.3</v>
@@ -3941,7 +3938,7 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O13">
         <v>1.32</v>
@@ -3950,7 +3947,7 @@
         <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
         <v>1.33</v>
@@ -3962,13 +3959,13 @@
         <v>1.76</v>
       </c>
       <c r="U13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
         <v>1.76</v>
       </c>
       <c r="W13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -4082,7 +4079,7 @@
         <v>3.5</v>
       </c>
       <c r="BI13">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ13">
         <v>10</v>
@@ -4139,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4150,22 +4147,22 @@
         <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F14">
         <v>3.55</v>
       </c>
       <c r="G14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I14">
         <v>2.08</v>
@@ -4189,22 +4186,22 @@
         <v>1.19</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q14">
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U14">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V14">
         <v>1.92</v>
@@ -4213,7 +4210,7 @@
         <v>1.38</v>
       </c>
       <c r="X14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y14">
         <v>15</v>
@@ -4237,10 +4234,10 @@
         <v>970</v>
       </c>
       <c r="AF14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AG14">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
@@ -4249,10 +4246,10 @@
         <v>27</v>
       </c>
       <c r="AJ14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL14">
         <v>36</v>
@@ -4261,10 +4258,10 @@
         <v>55</v>
       </c>
       <c r="AN14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP14">
         <v>20</v>
@@ -4273,13 +4270,13 @@
         <v>13</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS14">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
         <v>9</v>
@@ -4288,37 +4285,37 @@
         <v>10</v>
       </c>
       <c r="AW14">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX14">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
         <v>20</v>
       </c>
       <c r="BB14">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BC14">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD14">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE14">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14">
         <v>16.5</v>
       </c>
       <c r="BG14">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4381,7 +4378,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4392,13 +4389,13 @@
         <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F15">
         <v>2.9</v>
@@ -4407,7 +4404,7 @@
         <v>3.4</v>
       </c>
       <c r="H15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I15">
         <v>2.58</v>
@@ -4431,22 +4428,22 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R15">
         <v>1.42</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
         <v>1.63</v>
@@ -4497,7 +4494,7 @@
         <v>40</v>
       </c>
       <c r="AL15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM15">
         <v>90</v>
@@ -4509,7 +4506,7 @@
         <v>21</v>
       </c>
       <c r="AP15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15">
         <v>9</v>
@@ -4518,7 +4515,7 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AT15">
         <v>10.5</v>
@@ -4542,19 +4539,19 @@
         <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF15">
         <v>19</v>
@@ -4623,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4634,31 +4631,31 @@
         <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F16">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H16">
         <v>2.78</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
         <v>3.25</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4670,16 +4667,16 @@
         <v>3.55</v>
       </c>
       <c r="O16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P16">
         <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
         <v>3.15</v>
@@ -4691,10 +4688,10 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W16">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4751,52 +4748,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -4865,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4876,13 +4873,13 @@
         <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F17">
         <v>1.36</v>
@@ -4993,52 +4990,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -5107,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5118,13 +5115,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F18">
         <v>1.66</v>
@@ -5163,7 +5160,7 @@
         <v>1.96</v>
       </c>
       <c r="R18">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
         <v>3.3</v>
@@ -5235,52 +5232,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5349,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5360,22 +5357,22 @@
         <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F19">
         <v>1.65</v>
       </c>
       <c r="G19">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H19">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -5393,25 +5390,25 @@
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
         <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U19">
         <v>2.14</v>
@@ -5483,13 +5480,13 @@
         <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
         <v>7.4</v>
@@ -5498,10 +5495,10 @@
         <v>15</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX19">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY19">
         <v>7.6</v>
@@ -5510,10 +5507,10 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC19">
         <v>12</v>
@@ -5522,13 +5519,13 @@
         <v>21</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF19">
         <v>6.4</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH19">
         <v>4.1</v>
@@ -5540,16 +5537,16 @@
         <v>10</v>
       </c>
       <c r="BK19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO19">
         <v>3.5</v>
@@ -5558,31 +5555,31 @@
         <v>11.5</v>
       </c>
       <c r="BQ19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR19">
         <v>24</v>
       </c>
       <c r="BS19">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT19">
         <v>9.199999999999999</v>
       </c>
       <c r="BU19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5591,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5602,13 +5599,13 @@
         <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F20">
         <v>3.15</v>
@@ -5620,7 +5617,7 @@
         <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J20">
         <v>2.84</v>
@@ -5659,7 +5656,7 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
         <v>1.28</v>
@@ -5719,52 +5716,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5833,7 +5830,7 @@
         <v>1.34</v>
       </c>
       <c r="CB20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5844,19 +5841,19 @@
         <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F21">
         <v>1.04</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H21">
         <v>1.04</v>
@@ -5865,7 +5862,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5877,13 +5874,13 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
         <v>1.16</v>
@@ -5961,52 +5958,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -6075,7 +6072,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6086,13 +6083,13 @@
         <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F22">
         <v>8.4</v>
@@ -6113,19 +6110,19 @@
         <v>5.7</v>
       </c>
       <c r="L22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q22">
         <v>1.5</v>
@@ -6134,13 +6131,13 @@
         <v>1.73</v>
       </c>
       <c r="S22">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T22">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
         <v>3.3</v>
@@ -6176,7 +6173,7 @@
         <v>80</v>
       </c>
       <c r="AG22">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AH22">
         <v>22</v>
@@ -6191,10 +6188,10 @@
         <v>130</v>
       </c>
       <c r="AL22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM22">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AN22">
         <v>110</v>
@@ -6203,7 +6200,7 @@
         <v>4.7</v>
       </c>
       <c r="AP22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ22">
         <v>11</v>
@@ -6215,7 +6212,7 @@
         <v>11</v>
       </c>
       <c r="AT22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
         <v>11.5</v>
@@ -6227,7 +6224,7 @@
         <v>12.5</v>
       </c>
       <c r="AX22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY22">
         <v>22</v>
@@ -6239,13 +6236,13 @@
         <v>21</v>
       </c>
       <c r="BB22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE22">
         <v>11</v>
@@ -6260,13 +6257,13 @@
         <v>4.9</v>
       </c>
       <c r="BI22">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ22">
         <v>10.5</v>
       </c>
       <c r="BK22">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6278,28 +6275,28 @@
         <v>12</v>
       </c>
       <c r="BO22">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BP22">
         <v>60</v>
       </c>
       <c r="BQ22">
+        <v>12</v>
+      </c>
+      <c r="BR22">
+        <v>55</v>
+      </c>
+      <c r="BS22">
         <v>11.5</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>11</v>
       </c>
       <c r="BT22">
         <v>4.3</v>
       </c>
       <c r="BU22">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BV22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW22">
         <v>6</v>
@@ -6314,10 +6311,10 @@
         <v>10.5</v>
       </c>
       <c r="CA22">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="CB22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6328,19 +6325,19 @@
         <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F23">
         <v>1.51</v>
       </c>
       <c r="G23">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H23">
         <v>6.4</v>
@@ -6349,22 +6346,22 @@
         <v>6.6</v>
       </c>
       <c r="J23">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K23">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
         <v>1.22</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
         <v>6.2</v>
       </c>
       <c r="O23">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P23">
         <v>2.8</v>
@@ -6376,7 +6373,7 @@
         <v>1.72</v>
       </c>
       <c r="S23">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T23">
         <v>1.68</v>
@@ -6388,7 +6385,7 @@
         <v>1.17</v>
       </c>
       <c r="W23">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X23">
         <v>38</v>
@@ -6403,7 +6400,7 @@
         <v>180</v>
       </c>
       <c r="AB23">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AC23">
         <v>15</v>
@@ -6445,16 +6442,16 @@
         <v>70</v>
       </c>
       <c r="AP23">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ23">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AR23">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS23">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT23">
         <v>11.5</v>
@@ -6466,7 +6463,7 @@
         <v>20</v>
       </c>
       <c r="AW23">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX23">
         <v>10.5</v>
@@ -6478,10 +6475,10 @@
         <v>16</v>
       </c>
       <c r="BA23">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB23">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BC23">
         <v>13</v>
@@ -6490,13 +6487,13 @@
         <v>19</v>
       </c>
       <c r="BE23">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF23">
         <v>4.8</v>
       </c>
       <c r="BG23">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH23">
         <v>4.9</v>
@@ -6541,13 +6538,13 @@
         <v>7.8</v>
       </c>
       <c r="BV23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
         <v>11.5</v>
       </c>
       <c r="BX23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
         <v>11.5</v>
@@ -6559,7 +6556,7 @@
         <v>8</v>
       </c>
       <c r="CB23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6570,13 +6567,13 @@
         <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F24">
         <v>1.13</v>
@@ -6588,7 +6585,7 @@
         <v>19</v>
       </c>
       <c r="I24">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J24">
         <v>9.800000000000001</v>
@@ -6636,7 +6633,7 @@
         <v>70</v>
       </c>
       <c r="Y24">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z24">
         <v>290</v>
@@ -6651,7 +6648,7 @@
         <v>28</v>
       </c>
       <c r="AD24">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE24">
         <v>410</v>
@@ -6687,58 +6684,58 @@
         <v>430</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24">
         <v>2.18</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH24">
         <v>7</v>
@@ -6801,7 +6798,7 @@
         <v>3.95</v>
       </c>
       <c r="CB24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6812,28 +6809,28 @@
         <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F25">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H25">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I25">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K25">
         <v>5.2</v>
@@ -6854,7 +6851,7 @@
         <v>3.6</v>
       </c>
       <c r="Q25">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="R25">
         <v>2.14</v>
@@ -6863,13 +6860,13 @@
         <v>1.67</v>
       </c>
       <c r="T25">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U25">
         <v>3.4</v>
       </c>
       <c r="V25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W25">
         <v>1.44</v>
@@ -6878,7 +6875,7 @@
         <v>1000</v>
       </c>
       <c r="Y25">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Z25">
         <v>34</v>
@@ -6887,10 +6884,10 @@
         <v>42</v>
       </c>
       <c r="AB25">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AC25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD25">
         <v>17.5</v>
@@ -6902,10 +6899,10 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI25">
         <v>1000</v>
@@ -6926,10 +6923,10 @@
         <v>1000</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AQ25">
         <v>18</v>
@@ -6938,49 +6935,49 @@
         <v>17</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AU25">
         <v>10</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BC25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD25">
-        <v>17</v>
+        <v>1.89</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7043,7 +7040,7 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7054,22 +7051,22 @@
         <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F26">
         <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I26">
         <v>4.1</v>
@@ -7114,7 +7111,7 @@
         <v>1.32</v>
       </c>
       <c r="W26">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X26">
         <v>13</v>
@@ -7183,7 +7180,7 @@
         <v>6.8</v>
       </c>
       <c r="AT26">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU26">
         <v>6.2</v>
@@ -7246,7 +7243,7 @@
         <v>5.2</v>
       </c>
       <c r="BO26">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP26">
         <v>19</v>
@@ -7264,7 +7261,7 @@
         <v>7</v>
       </c>
       <c r="BU26">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV26">
         <v>1000</v>
@@ -7285,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7296,19 +7293,19 @@
         <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27">
         <v>2.2</v>
       </c>
       <c r="G27">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H27">
         <v>3.35</v>
@@ -7317,13 +7314,13 @@
         <v>3.95</v>
       </c>
       <c r="J27">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7338,25 +7335,25 @@
         <v>1.7</v>
       </c>
       <c r="Q27">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
         <v>1.26</v>
       </c>
       <c r="S27">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X27">
         <v>13.5</v>
@@ -7371,7 +7368,7 @@
         <v>85</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>8.6</v>
@@ -7383,7 +7380,7 @@
         <v>60</v>
       </c>
       <c r="AF27">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG27">
         <v>13.5</v>
@@ -7419,10 +7416,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT27">
         <v>6.8</v>
@@ -7434,7 +7431,7 @@
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX27">
         <v>11</v>
@@ -7446,25 +7443,25 @@
         <v>16</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF27">
         <v>18.5</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH27">
         <v>3.2</v>
@@ -7527,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7538,13 +7535,13 @@
         <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F28">
         <v>2.22</v>
@@ -7616,7 +7613,7 @@
         <v>15</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD28">
         <v>15.5</v>
@@ -7631,7 +7628,7 @@
         <v>13</v>
       </c>
       <c r="AH28">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI28">
         <v>42</v>
@@ -7664,7 +7661,7 @@
         <v>20</v>
       </c>
       <c r="AS28">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT28">
         <v>10</v>
@@ -7676,7 +7673,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7688,7 +7685,7 @@
         <v>13</v>
       </c>
       <c r="BA28">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB28">
         <v>20</v>
@@ -7697,10 +7694,10 @@
         <v>16</v>
       </c>
       <c r="BD28">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE28">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
@@ -7709,7 +7706,7 @@
         <v>19.5</v>
       </c>
       <c r="BH28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI28">
         <v>3.3</v>
@@ -7718,31 +7715,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK28">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28">
         <v>5.6</v>
       </c>
       <c r="BO28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP28">
         <v>15.5</v>
       </c>
       <c r="BQ28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR28">
         <v>25</v>
       </c>
       <c r="BS28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT28">
         <v>7.2</v>
@@ -7754,22 +7751,22 @@
         <v>25</v>
       </c>
       <c r="BW28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX28">
         <v>32</v>
       </c>
       <c r="BY28">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ28">
         <v>19</v>
       </c>
       <c r="CA28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7780,19 +7777,19 @@
         <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F29">
         <v>2.16</v>
       </c>
       <c r="G29">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H29">
         <v>3.2</v>
@@ -7804,13 +7801,13 @@
         <v>3.55</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
         <v>4.1</v>
@@ -7825,10 +7822,10 @@
         <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="T29">
         <v>1.66</v>
@@ -7837,7 +7834,7 @@
         <v>2.26</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
         <v>1.73</v>
@@ -8011,7 +8008,7 @@
         <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8022,28 +8019,28 @@
         <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F30">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G30">
-        <v>990</v>
+        <v>1.6</v>
       </c>
       <c r="H30">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="I30">
         <v>990</v>
       </c>
       <c r="J30">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="K30">
         <v>950</v>
@@ -8079,10 +8076,10 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8139,52 +8136,52 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
         <v>1.01</v>
@@ -8253,7 +8250,7 @@
         <v>1.04</v>
       </c>
       <c r="CB30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8264,13 +8261,13 @@
         <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -8288,10 +8285,10 @@
         <v>3.25</v>
       </c>
       <c r="K31">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -8435,67 +8432,67 @@
         <v>16</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI31">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="BJ31">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK31">
-        <v>1.59</v>
+        <v>5.9</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.8</v>
+        <v>9.6</v>
       </c>
       <c r="BN31">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BO31">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP31">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BQ31">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS31">
-        <v>1.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT31">
+        <v>5.6</v>
+      </c>
+      <c r="BU31">
+        <v>4.6</v>
+      </c>
+      <c r="BV31">
+        <v>19.5</v>
+      </c>
+      <c r="BW31">
+        <v>6.8</v>
+      </c>
+      <c r="BX31">
+        <v>34</v>
+      </c>
+      <c r="BY31">
+        <v>8</v>
+      </c>
+      <c r="BZ31">
+        <v>29</v>
+      </c>
+      <c r="CA31">
         <v>7.6</v>
       </c>
-      <c r="BU31">
-        <v>3.65</v>
-      </c>
-      <c r="BV31">
-        <v>28</v>
-      </c>
-      <c r="BW31">
-        <v>1.69</v>
-      </c>
-      <c r="BX31">
-        <v>46</v>
-      </c>
-      <c r="BY31">
-        <v>1.74</v>
-      </c>
-      <c r="BZ31">
-        <v>40</v>
-      </c>
-      <c r="CA31">
-        <v>1.73</v>
-      </c>
       <c r="CB31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8506,13 +8503,13 @@
         <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F32">
         <v>1.78</v>
@@ -8542,7 +8539,7 @@
         <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P32">
         <v>2.08</v>
@@ -8638,7 +8635,7 @@
         <v>7.2</v>
       </c>
       <c r="AU32">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV32">
         <v>16.5</v>
@@ -8665,10 +8662,10 @@
         <v>5.6</v>
       </c>
       <c r="BD32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF32">
         <v>9.199999999999999</v>
@@ -8737,7 +8734,7 @@
         <v>1.04</v>
       </c>
       <c r="CB32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8748,13 +8745,13 @@
         <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F33">
         <v>1.21</v>
@@ -8766,13 +8763,13 @@
         <v>15.5</v>
       </c>
       <c r="I33">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J33">
         <v>8.6</v>
       </c>
       <c r="K33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>1.2</v>
@@ -8787,7 +8784,7 @@
         <v>1.13</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q33">
         <v>1.37</v>
@@ -8829,7 +8826,7 @@
         <v>24</v>
       </c>
       <c r="AD33">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AE33">
         <v>260</v>
@@ -8868,13 +8865,13 @@
         <v>38</v>
       </c>
       <c r="AQ33">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AR33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS33">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT33">
         <v>11</v>
@@ -8886,19 +8883,19 @@
         <v>46</v>
       </c>
       <c r="AW33">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX33">
         <v>8.800000000000001</v>
       </c>
       <c r="AY33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ33">
         <v>30</v>
       </c>
       <c r="BA33">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB33">
         <v>9.199999999999999</v>
@@ -8907,16 +8904,16 @@
         <v>11</v>
       </c>
       <c r="BD33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE33">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF33">
         <v>3</v>
       </c>
       <c r="BG33">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8979,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8990,28 +8987,28 @@
         <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G34">
         <v>990</v>
       </c>
       <c r="H34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I34">
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9023,10 +9020,10 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O34">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="P34">
         <v>1.25</v>
@@ -9107,52 +9104,52 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34">
         <v>1.01</v>
@@ -9221,7 +9218,7 @@
         <v>1.04</v>
       </c>
       <c r="CB34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9232,13 +9229,13 @@
         <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -9463,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9474,13 +9471,13 @@
         <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F36">
         <v>1.75</v>
@@ -9501,7 +9498,7 @@
         <v>3.95</v>
       </c>
       <c r="L36">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M36">
         <v>1.08</v>
@@ -9525,10 +9522,10 @@
         <v>3.35</v>
       </c>
       <c r="T36">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U36">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V36">
         <v>1.2</v>
@@ -9591,58 +9588,58 @@
         <v>140</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS36">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW36">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA36">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE36">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH36">
         <v>3.35</v>
@@ -9687,7 +9684,7 @@
         <v>4.7</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW36">
         <v>8.4</v>
@@ -9699,13 +9696,13 @@
         <v>8.6</v>
       </c>
       <c r="BZ36">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
         <v>7.2</v>
       </c>
       <c r="CB36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9716,19 +9713,19 @@
         <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F37">
         <v>2.28</v>
       </c>
       <c r="G37">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H37">
         <v>2.58</v>
@@ -9752,7 +9749,7 @@
         <v>3.3</v>
       </c>
       <c r="O37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P37">
         <v>3.3</v>
@@ -9776,7 +9773,7 @@
         <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9833,52 +9830,52 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF37">
         <v>1.01</v>
@@ -9947,24 +9944,24 @@
         <v>1.04</v>
       </c>
       <c r="CB37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
         <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F38">
         <v>3.7</v>
@@ -10081,10 +10078,10 @@
         <v>6.6</v>
       </c>
       <c r="AR38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS38">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT38">
         <v>9</v>
@@ -10096,7 +10093,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX38">
         <v>21</v>
@@ -10111,7 +10108,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC38">
         <v>8.800000000000001</v>
@@ -10126,7 +10123,7 @@
         <v>9</v>
       </c>
       <c r="BG38">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH38">
         <v>2.78</v>
@@ -10189,7 +10186,7 @@
         <v>12.5</v>
       </c>
       <c r="CB38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10200,13 +10197,13 @@
         <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -10431,7 +10428,7 @@
         <v>1.04</v>
       </c>
       <c r="CB39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10442,13 +10439,13 @@
         <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F40">
         <v>1.68</v>
@@ -10673,24 +10670,24 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
         <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F41">
         <v>2.64</v>
@@ -10915,24 +10912,24 @@
         <v>1.04</v>
       </c>
       <c r="CB41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
         <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F42">
         <v>2.62</v>
@@ -11025,7 +11022,7 @@
         <v>90</v>
       </c>
       <c r="AJ42">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK42">
         <v>48</v>
@@ -11082,13 +11079,13 @@
         <v>6</v>
       </c>
       <c r="BC42">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD42">
         <v>6.2</v>
       </c>
       <c r="BE42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF42">
         <v>6</v>
@@ -11103,61 +11100,61 @@
         <v>2.22</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK42">
-        <v>1.56</v>
+        <v>2.92</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.56</v>
+        <v>3.55</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO42">
-        <v>1.56</v>
+        <v>3.55</v>
       </c>
       <c r="BP42">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ42">
-        <v>1.56</v>
+        <v>3.2</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU42">
-        <v>1.56</v>
+        <v>3.95</v>
       </c>
       <c r="BV42">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW42">
-        <v>1.51</v>
+        <v>3.3</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
       </c>
       <c r="CA42">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="CB42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11168,13 +11165,13 @@
         <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F43">
         <v>1.04</v>
@@ -11189,7 +11186,7 @@
         <v>990</v>
       </c>
       <c r="J43">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K43">
         <v>950</v>
@@ -11201,7 +11198,7 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O43">
         <v>1.02</v>
@@ -11210,13 +11207,13 @@
         <v>1.25</v>
       </c>
       <c r="Q43">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R43">
         <v>1.14</v>
       </c>
       <c r="S43">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
         <v>1.11</v>
@@ -11225,7 +11222,7 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W43">
         <v>1.02</v>
@@ -11285,52 +11282,52 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF43">
         <v>1.01</v>
@@ -11399,7 +11396,7 @@
         <v>1.04</v>
       </c>
       <c r="CB43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -658,7 +658,7 @@
     <t>Club Oriental de La Paz</t>
   </si>
   <si>
-    <t>2026-08-02 02:52:46</t>
+    <t>2026-08-02 05:07:19</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1252,7 @@
         <v>172</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
         <v>2.26</v>
@@ -1261,7 +1261,7 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -1270,22 +1270,22 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
         <v>1.46</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -1366,13 +1366,13 @@
         <v>9</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS2">
         <v>38</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1396,10 +1396,10 @@
         <v>42</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD2">
         <v>36</v>
@@ -1414,16 +1414,16 @@
         <v>42</v>
       </c>
       <c r="BH2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1459,19 +1459,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>214</v>
@@ -1497,16 +1497,16 @@
         <v>4.2</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>2.06</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
         <v>3.7</v>
@@ -1518,28 +1518,28 @@
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
         <v>1.29</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
         <v>1.94</v>
@@ -1557,19 +1557,19 @@
         <v>14</v>
       </c>
       <c r="AA3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
         <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF3">
         <v>38</v>
@@ -1596,10 +1596,10 @@
         <v>150</v>
       </c>
       <c r="AN3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3">
         <v>9.199999999999999</v>
@@ -1611,7 +1611,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
@@ -1623,7 +1623,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX3">
         <v>4.5</v>
@@ -1653,28 +1653,28 @@
         <v>4.8</v>
       </c>
       <c r="BG3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
         <v>3.25</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO3">
         <v>4.5</v>
@@ -1686,7 +1686,7 @@
         <v>8.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
         <v>8.800000000000001</v>
@@ -1698,10 +1698,10 @@
         <v>3.7</v>
       </c>
       <c r="BV3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
         <v>34</v>
@@ -1713,7 +1713,7 @@
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>214</v>
@@ -1742,7 +1742,7 @@
         <v>2.26</v>
       </c>
       <c r="H4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -1775,10 +1775,10 @@
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
         <v>2.04</v>
@@ -1814,7 +1814,7 @@
         <v>60</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG4">
         <v>13</v>
@@ -1853,31 +1853,31 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB4">
         <v>21</v>
@@ -1886,16 +1886,16 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF4">
         <v>15</v>
       </c>
       <c r="BG4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH4">
         <v>3.3</v>
@@ -1937,7 +1937,7 @@
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>34</v>
@@ -1978,16 +1978,16 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
+        <v>5.8</v>
+      </c>
+      <c r="I5">
         <v>6</v>
-      </c>
-      <c r="I5">
-        <v>6.4</v>
       </c>
       <c r="J5">
         <v>4.6</v>
@@ -2008,13 +2008,13 @@
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q5">
         <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S5">
         <v>2.34</v>
@@ -2026,22 +2026,22 @@
         <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
         <v>29</v>
       </c>
       <c r="Y5">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="Z5">
         <v>55</v>
       </c>
       <c r="AA5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -2050,19 +2050,19 @@
         <v>14</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5">
         <v>85</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>70</v>
@@ -2080,19 +2080,19 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
         <v>7.4</v>
@@ -2104,10 +2104,10 @@
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -2119,7 +2119,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
         <v>14</v>
@@ -2128,16 +2128,16 @@
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -2146,37 +2146,37 @@
         <v>3.65</v>
       </c>
       <c r="BJ5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS5">
         <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU5">
         <v>6.2</v>
@@ -2185,19 +2185,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="s">
         <v>214</v>
@@ -2226,7 +2226,7 @@
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I6">
         <v>990</v>
@@ -2253,7 +2253,7 @@
         <v>1.32</v>
       </c>
       <c r="Q6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R6">
         <v>1.18</v>
@@ -2268,10 +2268,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2462,19 +2462,19 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2501,7 +2501,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2719,7 +2719,7 @@
         <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2728,16 +2728,16 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="R8">
         <v>2.06</v>
@@ -2946,19 +2946,19 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.15</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2970,16 +2970,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="O9">
         <v>1.12</v>
       </c>
       <c r="P9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2994,10 +2994,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3209,7 +3209,7 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
         <v>1.24</v>
@@ -3550,7 +3550,7 @@
         <v>20</v>
       </c>
       <c r="AT11">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AU11">
         <v>7.2</v>
@@ -3580,7 +3580,7 @@
         <v>5</v>
       </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>29</v>
       </c>
       <c r="BE11">
         <v>5.4</v>
@@ -3672,7 +3672,7 @@
         <v>182</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G12">
         <v>2.02</v>
@@ -3681,7 +3681,7 @@
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3717,10 +3717,10 @@
         <v>1.89</v>
       </c>
       <c r="U12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
         <v>1.98</v>
@@ -3792,7 +3792,7 @@
         <v>5.1</v>
       </c>
       <c r="AT12">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3807,16 +3807,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA12">
         <v>5</v>
       </c>
       <c r="BB12">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
@@ -3914,7 +3914,7 @@
         <v>183</v>
       </c>
       <c r="F13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G13">
         <v>4.1</v>
@@ -3932,7 +3932,7 @@
         <v>3.9</v>
       </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M13">
         <v>1.07</v>
@@ -3947,13 +3947,13 @@
         <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
         <v>1.33</v>
       </c>
       <c r="S13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T13">
         <v>1.76</v>
@@ -4079,7 +4079,7 @@
         <v>3.5</v>
       </c>
       <c r="BI13">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ13">
         <v>10</v>
@@ -4189,13 +4189,13 @@
         <v>2.66</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R14">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S14">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T14">
         <v>1.55</v>
@@ -4216,7 +4216,7 @@
         <v>15</v>
       </c>
       <c r="Z14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA14">
         <v>27</v>
@@ -4237,7 +4237,7 @@
         <v>36</v>
       </c>
       <c r="AG14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
@@ -4246,7 +4246,7 @@
         <v>27</v>
       </c>
       <c r="AJ14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK14">
         <v>36</v>
@@ -4261,7 +4261,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP14">
         <v>20</v>
@@ -4300,7 +4300,7 @@
         <v>20</v>
       </c>
       <c r="BB14">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BC14">
         <v>7.6</v>
@@ -4309,7 +4309,7 @@
         <v>7.6</v>
       </c>
       <c r="BE14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF14">
         <v>16.5</v>
@@ -4640,19 +4640,19 @@
         <v>186</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G16">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H16">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="I16">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
         <v>3.8</v>
@@ -4673,121 +4673,121 @@
         <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S16">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U16">
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS16">
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA16">
         <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD16">
         <v>1.01</v>
@@ -4796,10 +4796,10 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
@@ -5617,7 +5617,7 @@
         <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J20">
         <v>2.84</v>
@@ -5656,7 +5656,7 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W20">
         <v>1.28</v>
@@ -5853,7 +5853,7 @@
         <v>1.04</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H21">
         <v>1.04</v>
@@ -5862,7 +5862,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5871,7 +5871,7 @@
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
         <v>1.3</v>
@@ -5880,7 +5880,7 @@
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q21">
         <v>1.16</v>
@@ -6095,7 +6095,7 @@
         <v>8.4</v>
       </c>
       <c r="G22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22">
         <v>1.42</v>
@@ -6104,7 +6104,7 @@
         <v>1.44</v>
       </c>
       <c r="J22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K22">
         <v>5.7</v>
@@ -6116,10 +6116,10 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
         <v>2.84</v>
@@ -6128,22 +6128,22 @@
         <v>1.5</v>
       </c>
       <c r="R22">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S22">
         <v>2.24</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
         <v>38</v>
@@ -6155,7 +6155,7 @@
         <v>11</v>
       </c>
       <c r="AA22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB22">
         <v>38</v>
@@ -6173,13 +6173,13 @@
         <v>80</v>
       </c>
       <c r="AG22">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AH22">
         <v>22</v>
       </c>
       <c r="AI22">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ22">
         <v>270</v>
@@ -6203,7 +6203,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR22">
         <v>9.6</v>
@@ -6212,7 +6212,7 @@
         <v>11</v>
       </c>
       <c r="AT22">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AU22">
         <v>11.5</v>
@@ -6239,7 +6239,7 @@
         <v>11.5</v>
       </c>
       <c r="BC22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD22">
         <v>10.5</v>
@@ -6340,16 +6340,16 @@
         <v>1.54</v>
       </c>
       <c r="H23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>5.1</v>
       </c>
       <c r="K23">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L23">
         <v>1.22</v>
@@ -6358,7 +6358,7 @@
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O23">
         <v>1.17</v>
@@ -6370,10 +6370,10 @@
         <v>1.5</v>
       </c>
       <c r="R23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S23">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T23">
         <v>1.68</v>
@@ -6385,10 +6385,10 @@
         <v>1.17</v>
       </c>
       <c r="W23">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X23">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y23">
         <v>38</v>
@@ -6436,22 +6436,22 @@
         <v>90</v>
       </c>
       <c r="AN23">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO23">
         <v>70</v>
       </c>
       <c r="AP23">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ23">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR23">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS23">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT23">
         <v>11.5</v>
@@ -6463,7 +6463,7 @@
         <v>20</v>
       </c>
       <c r="AW23">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX23">
         <v>10.5</v>
@@ -6472,13 +6472,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC23">
         <v>13</v>
@@ -6487,13 +6487,13 @@
         <v>19</v>
       </c>
       <c r="BE23">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF23">
         <v>4.8</v>
       </c>
       <c r="BG23">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH23">
         <v>4.9</v>
@@ -6526,7 +6526,7 @@
         <v>6.6</v>
       </c>
       <c r="BR23">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BS23">
         <v>8.6</v>
@@ -6585,7 +6585,7 @@
         <v>19</v>
       </c>
       <c r="I24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J24">
         <v>9.800000000000001</v>
@@ -6609,13 +6609,13 @@
         <v>3.6</v>
       </c>
       <c r="Q24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R24">
         <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T24">
         <v>2.04</v>
@@ -6714,10 +6714,10 @@
         <v>5.6</v>
       </c>
       <c r="AZ24">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BA24">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB24">
         <v>4.6</v>
@@ -6726,7 +6726,7 @@
         <v>5.6</v>
       </c>
       <c r="BD24">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE24">
         <v>8.199999999999999</v>
@@ -6821,19 +6821,19 @@
         <v>3.05</v>
       </c>
       <c r="G25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J25">
         <v>4.5</v>
       </c>
       <c r="K25">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6842,22 +6842,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P25">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="T25">
         <v>1.33</v>
@@ -6872,112 +6872,112 @@
         <v>1.44</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Y25">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="Z25">
         <v>34</v>
       </c>
       <c r="AA25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB25">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AC25">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AD25">
+        <v>14.5</v>
+      </c>
+      <c r="AE25">
+        <v>23</v>
+      </c>
+      <c r="AF25">
+        <v>46</v>
+      </c>
+      <c r="AG25">
         <v>17.5</v>
       </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>22</v>
-      </c>
       <c r="AH25">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK25">
         <v>36</v>
       </c>
       <c r="AL25">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO25">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP25">
-        <v>1.99</v>
+        <v>6.4</v>
       </c>
       <c r="AQ25">
         <v>18</v>
       </c>
       <c r="AR25">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS25">
-        <v>1.91</v>
+        <v>21</v>
       </c>
       <c r="AT25">
-        <v>1.91</v>
+        <v>6</v>
       </c>
       <c r="AU25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV25">
-        <v>1.79</v>
+        <v>11.5</v>
       </c>
       <c r="AW25">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="AX25">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="AY25">
-        <v>1.83</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="BA25">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="BB25">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="BC25">
         <v>19</v>
       </c>
       <c r="BD25">
-        <v>1.89</v>
+        <v>21</v>
       </c>
       <c r="BE25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BF25">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7060,7 +7060,7 @@
         <v>196</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G26">
         <v>2.34</v>
@@ -7069,7 +7069,7 @@
         <v>3.8</v>
       </c>
       <c r="I26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J26">
         <v>3.1</v>
@@ -7078,22 +7078,22 @@
         <v>3.2</v>
       </c>
       <c r="L26">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M26">
         <v>1.09</v>
       </c>
       <c r="N26">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O26">
         <v>1.41</v>
       </c>
       <c r="P26">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q26">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R26">
         <v>1.26</v>
@@ -7105,10 +7105,10 @@
         <v>1.88</v>
       </c>
       <c r="U26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
         <v>1.74</v>
@@ -7141,7 +7141,7 @@
         <v>14.5</v>
       </c>
       <c r="AG26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>20</v>
@@ -7174,10 +7174,10 @@
         <v>9.6</v>
       </c>
       <c r="AR26">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT26">
         <v>7</v>
@@ -7201,25 +7201,25 @@
         <v>16</v>
       </c>
       <c r="BA26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC26">
         <v>19.5</v>
       </c>
       <c r="BD26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF26">
         <v>17.5</v>
       </c>
       <c r="BG26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH26">
         <v>3.15</v>
@@ -7302,7 +7302,7 @@
         <v>197</v>
       </c>
       <c r="F27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
         <v>2.5</v>
@@ -7320,7 +7320,7 @@
         <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7335,7 +7335,7 @@
         <v>1.7</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
         <v>1.26</v>
@@ -7547,10 +7547,10 @@
         <v>2.22</v>
       </c>
       <c r="G28">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I28">
         <v>3.55</v>
@@ -7559,7 +7559,7 @@
         <v>3.75</v>
       </c>
       <c r="K28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L28">
         <v>1.29</v>
@@ -7589,13 +7589,13 @@
         <v>1.59</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X28">
         <v>24</v>
@@ -7822,7 +7822,7 @@
         <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S29">
         <v>2.66</v>
@@ -8028,7 +8028,7 @@
         <v>200</v>
       </c>
       <c r="F30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G30">
         <v>1.6</v>
@@ -8049,7 +8049,7 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
         <v>1.26</v>
@@ -8079,7 +8079,7 @@
         <v>1.06</v>
       </c>
       <c r="W30">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8285,10 +8285,10 @@
         <v>3.25</v>
       </c>
       <c r="K31">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -8512,22 +8512,22 @@
         <v>202</v>
       </c>
       <c r="F32">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G32">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H32">
         <v>4.5</v>
       </c>
       <c r="I32">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J32">
         <v>3.85</v>
       </c>
       <c r="K32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8539,7 +8539,7 @@
         <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
         <v>2.08</v>
@@ -8551,16 +8551,16 @@
         <v>1.42</v>
       </c>
       <c r="S32">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T32">
         <v>1.76</v>
       </c>
       <c r="U32">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W32">
         <v>2.12</v>
@@ -8754,22 +8754,22 @@
         <v>203</v>
       </c>
       <c r="F33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H33">
         <v>15.5</v>
       </c>
       <c r="I33">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="J33">
+        <v>8.4</v>
+      </c>
+      <c r="K33">
         <v>8.6</v>
-      </c>
-      <c r="K33">
-        <v>9</v>
       </c>
       <c r="L33">
         <v>1.2</v>
@@ -8778,7 +8778,7 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>1.13</v>
@@ -8787,28 +8787,28 @@
         <v>3.35</v>
       </c>
       <c r="Q33">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R33">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="S33">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T33">
         <v>1.9</v>
       </c>
       <c r="U33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V33">
         <v>1.06</v>
       </c>
       <c r="W33">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="X33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y33">
         <v>80</v>
@@ -8823,7 +8823,7 @@
         <v>12.5</v>
       </c>
       <c r="AC33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD33">
         <v>950</v>
@@ -8832,7 +8832,7 @@
         <v>260</v>
       </c>
       <c r="AF33">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
@@ -8853,7 +8853,7 @@
         <v>30</v>
       </c>
       <c r="AM33">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN33">
         <v>3.1</v>
@@ -8862,7 +8862,7 @@
         <v>250</v>
       </c>
       <c r="AP33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AQ33">
         <v>46</v>
@@ -8874,13 +8874,13 @@
         <v>14.5</v>
       </c>
       <c r="AT33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU33">
         <v>18.5</v>
       </c>
       <c r="AV33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW33">
         <v>13.5</v>
@@ -8889,13 +8889,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33">
         <v>30</v>
       </c>
       <c r="BA33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB33">
         <v>9.199999999999999</v>
@@ -8907,7 +8907,7 @@
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF33">
         <v>3</v>
@@ -8996,19 +8996,19 @@
         <v>204</v>
       </c>
       <c r="F34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G34">
         <v>990</v>
       </c>
       <c r="H34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I34">
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9722,37 +9722,37 @@
         <v>207</v>
       </c>
       <c r="F37">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G37">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H37">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I37">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J37">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L37">
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O37">
         <v>1.06</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q37">
         <v>1.29</v>
@@ -9773,7 +9773,7 @@
         <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9985,31 +9985,31 @@
         <v>1.56</v>
       </c>
       <c r="M38">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N38">
         <v>2.68</v>
       </c>
       <c r="O38">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q38">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S38">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T38">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U38">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V38">
         <v>1.7</v>
@@ -10018,31 +10018,31 @@
         <v>1.35</v>
       </c>
       <c r="X38">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z38">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA38">
         <v>34</v>
       </c>
       <c r="AB38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC38">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD38">
         <v>12</v>
       </c>
       <c r="AE38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF38">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG38">
         <v>16.5</v>
@@ -10054,16 +10054,16 @@
         <v>70</v>
       </c>
       <c r="AJ38">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AK38">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL38">
         <v>90</v>
       </c>
       <c r="AM38">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN38">
         <v>95</v>
@@ -10075,67 +10075,67 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR38">
         <v>11.5</v>
       </c>
       <c r="AS38">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AT38">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU38">
         <v>6.6</v>
       </c>
       <c r="AV38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW38">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AX38">
         <v>21</v>
       </c>
       <c r="AY38">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA38">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BB38">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BC38">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BD38">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BE38">
-        <v>9.6</v>
+        <v>48</v>
       </c>
       <c r="BF38">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BG38">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BH38">
         <v>2.78</v>
       </c>
       <c r="BI38">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="BJ38">
         <v>11</v>
       </c>
       <c r="BK38">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL38">
         <v>1000</v>
@@ -10147,10 +10147,10 @@
         <v>6.8</v>
       </c>
       <c r="BO38">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP38">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ38">
         <v>11.5</v>
@@ -10165,7 +10165,7 @@
         <v>5</v>
       </c>
       <c r="BU38">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BV38">
         <v>20</v>
@@ -10174,13 +10174,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX38">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
         <v>12</v>
       </c>
       <c r="BZ38">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA38">
         <v>12.5</v>
@@ -10466,7 +10466,7 @@
         <v>3.8</v>
       </c>
       <c r="L40">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M40">
         <v>1.11</v>
@@ -10478,7 +10478,7 @@
         <v>1.49</v>
       </c>
       <c r="P40">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q40">
         <v>2.46</v>
@@ -10514,10 +10514,10 @@
         <v>280</v>
       </c>
       <c r="AB40">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC40">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40">
         <v>32</v>
@@ -10526,31 +10526,31 @@
         <v>160</v>
       </c>
       <c r="AF40">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG40">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH40">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI40">
         <v>170</v>
       </c>
       <c r="AJ40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK40">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL40">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM40">
         <v>290</v>
       </c>
       <c r="AN40">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO40">
         <v>290</v>
@@ -10562,10 +10562,10 @@
         <v>12</v>
       </c>
       <c r="AR40">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AS40">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT40">
         <v>4.8</v>
@@ -10577,7 +10577,7 @@
         <v>20</v>
       </c>
       <c r="AW40">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX40">
         <v>7</v>
@@ -10586,10 +10586,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ40">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA40">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB40">
         <v>14</v>
@@ -10598,16 +10598,16 @@
         <v>18</v>
       </c>
       <c r="BD40">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE40">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF40">
         <v>13.5</v>
       </c>
       <c r="BG40">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH40">
         <v>2.9</v>
@@ -10619,7 +10619,7 @@
         <v>13</v>
       </c>
       <c r="BK40">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BL40">
         <v>1000</v>
@@ -10631,7 +10631,7 @@
         <v>4.2</v>
       </c>
       <c r="BO40">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BP40">
         <v>14</v>
@@ -10693,19 +10693,19 @@
         <v>2.64</v>
       </c>
       <c r="G41">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H41">
         <v>3.3</v>
       </c>
       <c r="I41">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J41">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="K41">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10714,13 +10714,13 @@
         <v>1.16</v>
       </c>
       <c r="N41">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O41">
         <v>1.66</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -10741,7 +10741,7 @@
         <v>1.37</v>
       </c>
       <c r="W41">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X41">
         <v>8.6</v>
@@ -10759,7 +10759,7 @@
         <v>7.6</v>
       </c>
       <c r="AC41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD41">
         <v>17</v>
@@ -10780,7 +10780,7 @@
         <v>120</v>
       </c>
       <c r="AJ41">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK41">
         <v>48</v>
@@ -10807,7 +10807,7 @@
         <v>18</v>
       </c>
       <c r="AS41">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT41">
         <v>6.2</v>
@@ -10819,7 +10819,7 @@
         <v>13.5</v>
       </c>
       <c r="AW41">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX41">
         <v>13.5</v>
@@ -10828,28 +10828,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ41">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA41">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB41">
         <v>40</v>
       </c>
       <c r="BC41">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD41">
+        <v>7.6</v>
+      </c>
+      <c r="BE41">
+        <v>8</v>
+      </c>
+      <c r="BF41">
         <v>7.2</v>
       </c>
-      <c r="BE41">
+      <c r="BG41">
         <v>7.6</v>
-      </c>
-      <c r="BF41">
-        <v>7</v>
-      </c>
-      <c r="BG41">
-        <v>7.2</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10932,22 +10932,22 @@
         <v>212</v>
       </c>
       <c r="F42">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G42">
         <v>2.74</v>
       </c>
       <c r="H42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I42">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J42">
         <v>3</v>
       </c>
       <c r="K42">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -10980,7 +10980,7 @@
         <v>1.78</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W42">
         <v>1.57</v>
@@ -11013,7 +11013,7 @@
         <v>17</v>
       </c>
       <c r="AG42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH42">
         <v>28</v>
@@ -11031,7 +11031,7 @@
         <v>80</v>
       </c>
       <c r="AM42">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN42">
         <v>55</v>
@@ -11049,7 +11049,7 @@
         <v>17.5</v>
       </c>
       <c r="AS42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT42">
         <v>6.8</v>
@@ -11061,7 +11061,7 @@
         <v>12.5</v>
       </c>
       <c r="AW42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX42">
         <v>14</v>
@@ -11073,7 +11073,7 @@
         <v>19</v>
       </c>
       <c r="BA42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB42">
         <v>6</v>
@@ -11082,7 +11082,7 @@
         <v>6</v>
       </c>
       <c r="BD42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE42">
         <v>6.6</v>
@@ -11091,7 +11091,7 @@
         <v>6</v>
       </c>
       <c r="BG42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH42">
         <v>3.15</v>
@@ -11186,7 +11186,7 @@
         <v>990</v>
       </c>
       <c r="J43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K43">
         <v>950</v>
@@ -11222,10 +11222,10 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -658,7 +658,7 @@
     <t>Club Oriental de La Paz</t>
   </si>
   <si>
-    <t>2026-08-02 05:07:19</t>
+    <t>2026-08-02 07:21:43</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1255,7 @@
         <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
         <v>4.2</v>
@@ -1303,7 +1303,7 @@
         <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>7.4</v>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="AM2">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN2">
         <v>38</v>
@@ -1375,7 +1375,7 @@
         <v>6</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>17.5</v>
@@ -1494,175 +1494,175 @@
         <v>173</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.46</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
         <v>4.1</v>
       </c>
       <c r="T3">
+        <v>1.87</v>
+      </c>
+      <c r="U3">
         <v>1.92</v>
       </c>
-      <c r="U3">
-        <v>1.93</v>
-      </c>
       <c r="V3">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="W3">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA3">
+        <v>32</v>
+      </c>
+      <c r="AB3">
+        <v>14.5</v>
+      </c>
+      <c r="AC3">
+        <v>8</v>
+      </c>
+      <c r="AD3">
+        <v>13</v>
+      </c>
+      <c r="AE3">
         <v>28</v>
       </c>
-      <c r="AB3">
+      <c r="AF3">
+        <v>28</v>
+      </c>
+      <c r="AG3">
+        <v>17</v>
+      </c>
+      <c r="AH3">
+        <v>23</v>
+      </c>
+      <c r="AI3">
+        <v>55</v>
+      </c>
+      <c r="AJ3">
+        <v>85</v>
+      </c>
+      <c r="AK3">
+        <v>60</v>
+      </c>
+      <c r="AL3">
+        <v>70</v>
+      </c>
+      <c r="AM3">
+        <v>140</v>
+      </c>
+      <c r="AN3">
+        <v>70</v>
+      </c>
+      <c r="AO3">
+        <v>26</v>
+      </c>
+      <c r="AP3">
+        <v>9</v>
+      </c>
+      <c r="AQ3">
+        <v>7.4</v>
+      </c>
+      <c r="AR3">
+        <v>10.5</v>
+      </c>
+      <c r="AS3">
+        <v>5.2</v>
+      </c>
+      <c r="AT3">
+        <v>9.6</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>9.6</v>
+      </c>
+      <c r="AW3">
+        <v>20</v>
+      </c>
+      <c r="AX3">
+        <v>20</v>
+      </c>
+      <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
         <v>16.5</v>
       </c>
-      <c r="AC3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>12.5</v>
-      </c>
-      <c r="AE3">
-        <v>27</v>
-      </c>
-      <c r="AF3">
-        <v>38</v>
-      </c>
-      <c r="AG3">
-        <v>21</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3">
-        <v>120</v>
-      </c>
-      <c r="AK3">
-        <v>75</v>
-      </c>
-      <c r="AL3">
-        <v>85</v>
-      </c>
-      <c r="AM3">
-        <v>150</v>
-      </c>
-      <c r="AN3">
-        <v>95</v>
-      </c>
-      <c r="AO3">
-        <v>21</v>
-      </c>
-      <c r="AP3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ3">
-        <v>6.2</v>
-      </c>
-      <c r="AR3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3">
-        <v>18.5</v>
-      </c>
-      <c r="AT3">
+      <c r="BA3">
+        <v>5.6</v>
+      </c>
+      <c r="BB3">
+        <v>5.8</v>
+      </c>
+      <c r="BC3">
+        <v>5.7</v>
+      </c>
+      <c r="BD3">
+        <v>5.7</v>
+      </c>
+      <c r="BE3">
+        <v>6</v>
+      </c>
+      <c r="BF3">
+        <v>5.7</v>
+      </c>
+      <c r="BG3">
+        <v>16.5</v>
+      </c>
+      <c r="BH3">
+        <v>3.2</v>
+      </c>
+      <c r="BI3">
+        <v>2.58</v>
+      </c>
+      <c r="BJ3">
         <v>10.5</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW3">
-        <v>17.5</v>
-      </c>
-      <c r="AX3">
-        <v>4.5</v>
-      </c>
-      <c r="AY3">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3">
-        <v>15.5</v>
-      </c>
-      <c r="BA3">
-        <v>4.6</v>
-      </c>
-      <c r="BB3">
-        <v>4.9</v>
-      </c>
-      <c r="BC3">
-        <v>4.8</v>
-      </c>
-      <c r="BD3">
-        <v>4.8</v>
-      </c>
-      <c r="BE3">
-        <v>4.9</v>
-      </c>
-      <c r="BF3">
-        <v>4.8</v>
-      </c>
-      <c r="BG3">
-        <v>13.5</v>
-      </c>
-      <c r="BH3">
-        <v>3.25</v>
-      </c>
-      <c r="BI3">
-        <v>2.62</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
       </c>
       <c r="BK3">
         <v>5.3</v>
@@ -1671,49 +1671,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BQ3">
         <v>8.4</v>
       </c>
       <c r="BR3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BU3">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BV3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX3">
+        <v>36</v>
+      </c>
+      <c r="BY3">
+        <v>8.4</v>
+      </c>
+      <c r="BZ3">
         <v>34</v>
       </c>
-      <c r="BY3">
-        <v>8</v>
-      </c>
-      <c r="BZ3">
-        <v>32</v>
-      </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>214</v>
@@ -1739,13 +1739,13 @@
         <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H4">
         <v>3.7</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1754,22 +1754,22 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
         <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1790,7 +1790,7 @@
         <v>1.79</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
         <v>15</v>
@@ -1802,10 +1802,10 @@
         <v>90</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>18.5</v>
@@ -1817,7 +1817,7 @@
         <v>14.5</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1832,13 +1832,13 @@
         <v>29</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>130</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4">
         <v>65</v>
@@ -1853,7 +1853,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
         <v>7.6</v>
@@ -1865,19 +1865,19 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>16</v>
       </c>
       <c r="BA4">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB4">
         <v>21</v>
@@ -1886,34 +1886,34 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
         <v>15</v>
       </c>
       <c r="BG4">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH4">
         <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4">
         <v>5.1</v>
@@ -1931,7 +1931,7 @@
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
@@ -1943,16 +1943,16 @@
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA4">
         <v>8</v>
@@ -1978,94 +1978,94 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
         <v>6</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R5">
         <v>1.7</v>
       </c>
       <c r="S5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T5">
         <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5">
         <v>150</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD5">
         <v>25</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>17</v>
@@ -2074,10 +2074,10 @@
         <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN5">
         <v>6.2</v>
@@ -2086,118 +2086,118 @@
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AR5">
-        <v>7.6</v>
+        <v>48</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU5">
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>9.4</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
+        <v>13.5</v>
+      </c>
+      <c r="BD5">
+        <v>22</v>
+      </c>
+      <c r="BE5">
+        <v>55</v>
+      </c>
+      <c r="BF5">
+        <v>5.5</v>
+      </c>
+      <c r="BG5">
+        <v>11</v>
+      </c>
+      <c r="BH5">
+        <v>4.5</v>
+      </c>
+      <c r="BI5">
+        <v>3.55</v>
+      </c>
+      <c r="BJ5">
+        <v>9.4</v>
+      </c>
+      <c r="BK5">
+        <v>6</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>14</v>
       </c>
-      <c r="BC5">
-        <v>13</v>
-      </c>
-      <c r="BD5">
-        <v>6.6</v>
-      </c>
-      <c r="BE5">
-        <v>7.8</v>
-      </c>
-      <c r="BF5">
-        <v>5.3</v>
-      </c>
-      <c r="BG5">
-        <v>7.6</v>
-      </c>
-      <c r="BH5">
-        <v>4.7</v>
-      </c>
-      <c r="BI5">
-        <v>3.65</v>
-      </c>
-      <c r="BJ5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK5">
+      <c r="BN5">
+        <v>4.6</v>
+      </c>
+      <c r="BO5">
+        <v>3.6</v>
+      </c>
+      <c r="BP5">
+        <v>10</v>
+      </c>
+      <c r="BQ5">
         <v>6.2</v>
       </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>13.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.7</v>
-      </c>
-      <c r="BO5">
-        <v>4.2</v>
-      </c>
-      <c r="BP5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ5">
-        <v>6.4</v>
-      </c>
       <c r="BR5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT5">
         <v>9.4</v>
       </c>
       <c r="BU5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>214</v>
@@ -2220,19 +2220,19 @@
         <v>176</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2268,10 +2268,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2462,19 +2462,19 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2483,19 +2483,19 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
         <v>1.3</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2510,10 +2510,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2731,7 +2731,7 @@
         <v>6.8</v>
       </c>
       <c r="O8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
         <v>3.4</v>
@@ -2740,10 +2740,10 @@
         <v>1.27</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
         <v>1.37</v>
@@ -2946,13 +2946,13 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="I9">
         <v>990</v>
@@ -2967,25 +2967,25 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>1.32</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="S9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2997,7 +2997,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3212,7 +3212,7 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
         <v>1.06</v>
@@ -3221,7 +3221,7 @@
         <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3490,7 +3490,7 @@
         <v>14.5</v>
       </c>
       <c r="Z11">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AA11">
         <v>36</v>
@@ -3574,16 +3574,16 @@
         <v>20</v>
       </c>
       <c r="BB11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD11">
         <v>29</v>
       </c>
       <c r="BE11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF11">
         <v>16</v>
@@ -3672,7 +3672,7 @@
         <v>182</v>
       </c>
       <c r="F12">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G12">
         <v>2.02</v>
@@ -3681,13 +3681,13 @@
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3720,7 +3720,7 @@
         <v>1.93</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
         <v>1.98</v>
@@ -3816,7 +3816,7 @@
         <v>5</v>
       </c>
       <c r="BB12">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
@@ -4159,13 +4159,13 @@
         <v>3.55</v>
       </c>
       <c r="G14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H14">
         <v>2.04</v>
       </c>
       <c r="I14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J14">
         <v>4.1</v>
@@ -4186,7 +4186,7 @@
         <v>1.19</v>
       </c>
       <c r="P14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q14">
         <v>1.55</v>
@@ -4195,7 +4195,7 @@
         <v>1.66</v>
       </c>
       <c r="S14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T14">
         <v>1.55</v>
@@ -4204,10 +4204,10 @@
         <v>2.66</v>
       </c>
       <c r="V14">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X14">
         <v>30</v>
@@ -4404,7 +4404,7 @@
         <v>3.4</v>
       </c>
       <c r="H15">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I15">
         <v>2.58</v>
@@ -4413,7 +4413,7 @@
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4428,10 +4428,10 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
         <v>1.42</v>
@@ -4440,10 +4440,10 @@
         <v>2.92</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
         <v>1.63</v>
@@ -4533,7 +4533,7 @@
         <v>16.5</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15">
         <v>11.5</v>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
       <c r="BF15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG15">
         <v>12</v>
@@ -4649,25 +4649,25 @@
         <v>2.88</v>
       </c>
       <c r="I16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P16">
         <v>1.87</v>
@@ -4676,25 +4676,25 @@
         <v>1.88</v>
       </c>
       <c r="R16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
         <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
         <v>15</v>
@@ -4709,7 +4709,7 @@
         <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD16">
         <v>16</v>
@@ -4736,31 +4736,31 @@
         <v>34</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM16">
         <v>110</v>
       </c>
       <c r="AN16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP16">
         <v>10.5</v>
       </c>
       <c r="AQ16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR16">
         <v>15</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU16">
         <v>6</v>
@@ -4769,7 +4769,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX16">
         <v>12.5</v>
@@ -4778,28 +4778,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG16">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
@@ -5405,7 +5405,7 @@
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T19">
         <v>1.71</v>
@@ -5486,13 +5486,13 @@
         <v>4.1</v>
       </c>
       <c r="AT19">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV19">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW19">
         <v>4</v>
@@ -5501,7 +5501,7 @@
         <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
         <v>13.5</v>
@@ -5516,7 +5516,7 @@
         <v>12</v>
       </c>
       <c r="BD19">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="BE19">
         <v>4</v>
@@ -5611,19 +5611,19 @@
         <v>3.15</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H20">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="I20">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="J20">
         <v>2.84</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5632,7 +5632,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O20">
         <v>1.31</v>
@@ -5641,10 +5641,10 @@
         <v>1.65</v>
       </c>
       <c r="Q20">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S20">
         <v>2.68</v>
@@ -5656,10 +5656,10 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5862,7 +5862,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5874,13 +5874,13 @@
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q21">
         <v>1.16</v>
@@ -6092,7 +6092,7 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>8.800000000000001</v>
@@ -6116,28 +6116,28 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
         <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q22">
         <v>1.5</v>
       </c>
       <c r="R22">
+        <v>1.77</v>
+      </c>
+      <c r="S22">
+        <v>2.22</v>
+      </c>
+      <c r="T22">
         <v>1.74</v>
       </c>
-      <c r="S22">
-        <v>2.24</v>
-      </c>
-      <c r="T22">
-        <v>1.75</v>
-      </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V22">
         <v>3.25</v>
@@ -6146,7 +6146,7 @@
         <v>1.12</v>
       </c>
       <c r="X22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y22">
         <v>13</v>
@@ -6155,7 +6155,7 @@
         <v>11</v>
       </c>
       <c r="AA22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB22">
         <v>38</v>
@@ -6167,13 +6167,13 @@
         <v>10.5</v>
       </c>
       <c r="AE22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF22">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH22">
         <v>22</v>
@@ -6182,13 +6182,13 @@
         <v>32</v>
       </c>
       <c r="AJ22">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
         <v>110</v>
@@ -6197,10 +6197,10 @@
         <v>110</v>
       </c>
       <c r="AO22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP22">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AQ22">
         <v>11.5</v>
@@ -6209,46 +6209,46 @@
         <v>9.6</v>
       </c>
       <c r="AS22">
+        <v>11.5</v>
+      </c>
+      <c r="AT22">
+        <v>32</v>
+      </c>
+      <c r="AU22">
         <v>11</v>
       </c>
-      <c r="AT22">
-        <v>27</v>
-      </c>
-      <c r="AU22">
-        <v>11.5</v>
-      </c>
       <c r="AV22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW22">
         <v>12.5</v>
       </c>
       <c r="AX22">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AY22">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AZ22">
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BB22">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BC22">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BD22">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BE22">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BF22">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BG22">
         <v>4.3</v>
@@ -6334,13 +6334,13 @@
         <v>193</v>
       </c>
       <c r="F23">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G23">
         <v>1.54</v>
       </c>
       <c r="H23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I23">
         <v>6.8</v>
@@ -6361,16 +6361,16 @@
         <v>6.4</v>
       </c>
       <c r="O23">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q23">
         <v>1.5</v>
       </c>
       <c r="R23">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S23">
         <v>2.26</v>
@@ -6379,7 +6379,7 @@
         <v>1.68</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
         <v>1.17</v>
@@ -6388,52 +6388,52 @@
         <v>2.84</v>
       </c>
       <c r="X23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z23">
-        <v>70</v>
+        <v>530</v>
       </c>
       <c r="AA23">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
         <v>13.5</v>
       </c>
       <c r="AC23">
+        <v>14.5</v>
+      </c>
+      <c r="AD23">
+        <v>26</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>12</v>
+      </c>
+      <c r="AG23">
+        <v>11</v>
+      </c>
+      <c r="AH23">
+        <v>23</v>
+      </c>
+      <c r="AI23">
+        <v>570</v>
+      </c>
+      <c r="AJ23">
+        <v>15.5</v>
+      </c>
+      <c r="AK23">
         <v>15</v>
       </c>
-      <c r="AD23">
+      <c r="AL23">
         <v>30</v>
       </c>
-      <c r="AE23">
-        <v>85</v>
-      </c>
-      <c r="AF23">
-        <v>14.5</v>
-      </c>
-      <c r="AG23">
-        <v>13</v>
-      </c>
-      <c r="AH23">
-        <v>24</v>
-      </c>
-      <c r="AI23">
-        <v>70</v>
-      </c>
-      <c r="AJ23">
-        <v>18</v>
-      </c>
-      <c r="AK23">
-        <v>18</v>
-      </c>
-      <c r="AL23">
-        <v>32</v>
-      </c>
       <c r="AM23">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
         <v>5.2</v>
@@ -6442,16 +6442,16 @@
         <v>70</v>
       </c>
       <c r="AP23">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AR23">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="AS23">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="AT23">
         <v>11.5</v>
@@ -6463,19 +6463,19 @@
         <v>20</v>
       </c>
       <c r="AW23">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AX23">
         <v>10.5</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA23">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BB23">
         <v>13</v>
@@ -6484,16 +6484,16 @@
         <v>13</v>
       </c>
       <c r="BD23">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE23">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BF23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG23">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BH23">
         <v>4.9</v>
@@ -6517,13 +6517,13 @@
         <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BP23">
         <v>9</v>
       </c>
       <c r="BQ23">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR23">
         <v>19</v>
@@ -6535,7 +6535,7 @@
         <v>10.5</v>
       </c>
       <c r="BU23">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6576,7 +6576,7 @@
         <v>194</v>
       </c>
       <c r="F24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G24">
         <v>1.16</v>
@@ -6600,22 +6600,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
         <v>1.09</v>
       </c>
       <c r="P24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q24">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R24">
         <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T24">
         <v>2.04</v>
@@ -6627,7 +6627,7 @@
         <v>1.03</v>
       </c>
       <c r="W24">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="X24">
         <v>70</v>
@@ -6699,7 +6699,7 @@
         <v>5.7</v>
       </c>
       <c r="AU24">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV24">
         <v>7.8</v>
@@ -6717,7 +6717,7 @@
         <v>9.4</v>
       </c>
       <c r="BA24">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB24">
         <v>4.6</v>
@@ -6917,7 +6917,7 @@
         <v>27</v>
       </c>
       <c r="AM25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN25">
         <v>11.5</v>
@@ -6926,7 +6926,7 @@
         <v>6.6</v>
       </c>
       <c r="AP25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ25">
         <v>18</v>
@@ -6962,7 +6962,7 @@
         <v>15</v>
       </c>
       <c r="BB25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC25">
         <v>19</v>
@@ -7078,7 +7078,7 @@
         <v>3.2</v>
       </c>
       <c r="L26">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M26">
         <v>1.09</v>
@@ -7132,7 +7132,7 @@
         <v>7.6</v>
       </c>
       <c r="AD26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE26">
         <v>60</v>
@@ -7141,13 +7141,13 @@
         <v>14.5</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
         <v>20</v>
       </c>
       <c r="AI26">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ26">
         <v>32</v>
@@ -7174,10 +7174,10 @@
         <v>9.6</v>
       </c>
       <c r="AR26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS26">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT26">
         <v>7</v>
@@ -7201,25 +7201,25 @@
         <v>16</v>
       </c>
       <c r="BA26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC26">
         <v>19.5</v>
       </c>
       <c r="BD26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE26">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF26">
         <v>17.5</v>
       </c>
       <c r="BG26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH26">
         <v>3.15</v>
@@ -7302,7 +7302,7 @@
         <v>197</v>
       </c>
       <c r="F27">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G27">
         <v>2.5</v>
@@ -7320,7 +7320,7 @@
         <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7335,7 +7335,7 @@
         <v>1.7</v>
       </c>
       <c r="Q27">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
         <v>1.26</v>
@@ -7550,16 +7550,16 @@
         <v>2.26</v>
       </c>
       <c r="H28">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
         <v>3.75</v>
       </c>
       <c r="K28">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L28">
         <v>1.29</v>
@@ -7583,7 +7583,7 @@
         <v>1.51</v>
       </c>
       <c r="S28">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T28">
         <v>1.59</v>
@@ -7613,7 +7613,7 @@
         <v>15</v>
       </c>
       <c r="AC28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD28">
         <v>15.5</v>
@@ -7628,7 +7628,7 @@
         <v>13</v>
       </c>
       <c r="AH28">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI28">
         <v>42</v>
@@ -7661,7 +7661,7 @@
         <v>20</v>
       </c>
       <c r="AS28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT28">
         <v>10</v>
@@ -7673,7 +7673,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7685,7 +7685,7 @@
         <v>13</v>
       </c>
       <c r="BA28">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB28">
         <v>20</v>
@@ -7694,10 +7694,10 @@
         <v>16</v>
       </c>
       <c r="BD28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
@@ -7795,13 +7795,13 @@
         <v>3.2</v>
       </c>
       <c r="I29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J29">
         <v>3.55</v>
       </c>
       <c r="K29">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7810,22 +7810,22 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.1</v>
+        <v>2.16</v>
       </c>
       <c r="O29">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="Q29">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R29">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T29">
         <v>1.66</v>
@@ -7834,7 +7834,7 @@
         <v>2.26</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.73</v>
@@ -8034,7 +8034,7 @@
         <v>1.6</v>
       </c>
       <c r="H30">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="I30">
         <v>990</v>
@@ -8076,10 +8076,10 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W30">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8288,7 +8288,7 @@
         <v>3.7</v>
       </c>
       <c r="L31">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -8512,7 +8512,7 @@
         <v>202</v>
       </c>
       <c r="F32">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G32">
         <v>1.88</v>
@@ -8763,10 +8763,10 @@
         <v>15.5</v>
       </c>
       <c r="I33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K33">
         <v>8.6</v>
@@ -8784,31 +8784,31 @@
         <v>1.13</v>
       </c>
       <c r="P33">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
         <v>1.39</v>
       </c>
       <c r="R33">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="T33">
         <v>1.9</v>
       </c>
       <c r="U33">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V33">
         <v>1.06</v>
       </c>
       <c r="W33">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="X33">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Y33">
         <v>80</v>
@@ -8820,25 +8820,25 @@
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC33">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD33">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AE33">
         <v>260</v>
       </c>
       <c r="AF33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI33">
         <v>180</v>
@@ -8847,16 +8847,16 @@
         <v>9.6</v>
       </c>
       <c r="AK33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM33">
         <v>170</v>
       </c>
       <c r="AN33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AO33">
         <v>250</v>
@@ -8865,37 +8865,37 @@
         <v>36</v>
       </c>
       <c r="AQ33">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS33">
         <v>14.5</v>
       </c>
       <c r="AT33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU33">
         <v>18.5</v>
       </c>
       <c r="AV33">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW33">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AX33">
         <v>8.800000000000001</v>
       </c>
       <c r="AY33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
         <v>30</v>
       </c>
       <c r="BA33">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB33">
         <v>9.199999999999999</v>
@@ -8907,13 +8907,13 @@
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF33">
         <v>3</v>
       </c>
       <c r="BG33">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8996,19 +8996,19 @@
         <v>204</v>
       </c>
       <c r="F34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G34">
         <v>990</v>
       </c>
       <c r="H34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I34">
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9725,7 +9725,7 @@
         <v>2.3</v>
       </c>
       <c r="G37">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H37">
         <v>2.6</v>
@@ -9773,7 +9773,7 @@
         <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9967,19 +9967,19 @@
         <v>3.7</v>
       </c>
       <c r="G38">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H38">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="I38">
         <v>2.42</v>
       </c>
       <c r="J38">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K38">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L38">
         <v>1.56</v>
@@ -9994,13 +9994,13 @@
         <v>1.54</v>
       </c>
       <c r="P38">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q38">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S38">
         <v>5.5</v>
@@ -10015,7 +10015,7 @@
         <v>1.7</v>
       </c>
       <c r="W38">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -10033,7 +10033,7 @@
         <v>11.5</v>
       </c>
       <c r="AC38">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD38">
         <v>12</v>
@@ -10045,7 +10045,7 @@
         <v>28</v>
       </c>
       <c r="AG38">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH38">
         <v>24</v>
@@ -10057,7 +10057,7 @@
         <v>90</v>
       </c>
       <c r="AK38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL38">
         <v>90</v>
@@ -10072,19 +10072,19 @@
         <v>34</v>
       </c>
       <c r="AP38">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ38">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR38">
         <v>11.5</v>
       </c>
       <c r="AS38">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU38">
         <v>6.6</v>
@@ -10099,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="AY38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ38">
         <v>21</v>
@@ -10108,13 +10108,13 @@
         <v>32</v>
       </c>
       <c r="BB38">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC38">
         <v>29</v>
       </c>
       <c r="BD38">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE38">
         <v>48</v>
@@ -10123,7 +10123,7 @@
         <v>34</v>
       </c>
       <c r="BG38">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BH38">
         <v>2.78</v>
@@ -10150,7 +10150,7 @@
         <v>5.3</v>
       </c>
       <c r="BP38">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ38">
         <v>11.5</v>
@@ -10448,19 +10448,19 @@
         <v>210</v>
       </c>
       <c r="F40">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="G40">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H40">
         <v>6</v>
       </c>
       <c r="I40">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J40">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K40">
         <v>3.8</v>
@@ -10472,61 +10472,61 @@
         <v>1.11</v>
       </c>
       <c r="N40">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O40">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P40">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q40">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R40">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S40">
         <v>5</v>
       </c>
       <c r="T40">
+        <v>2.34</v>
+      </c>
+      <c r="U40">
+        <v>1.65</v>
+      </c>
+      <c r="V40">
+        <v>1.18</v>
+      </c>
+      <c r="W40">
         <v>2.26</v>
       </c>
-      <c r="U40">
-        <v>1.64</v>
-      </c>
-      <c r="V40">
-        <v>1.16</v>
-      </c>
-      <c r="W40">
-        <v>2.2</v>
-      </c>
       <c r="X40">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y40">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z40">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AA40">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB40">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC40">
         <v>8.800000000000001</v>
       </c>
       <c r="AD40">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE40">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF40">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>11.5</v>
@@ -10535,79 +10535,79 @@
         <v>32</v>
       </c>
       <c r="AI40">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ40">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK40">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL40">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM40">
         <v>290</v>
       </c>
       <c r="AN40">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO40">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP40">
+        <v>8.4</v>
+      </c>
+      <c r="AQ40">
+        <v>13.5</v>
+      </c>
+      <c r="AR40">
+        <v>24</v>
+      </c>
+      <c r="AS40">
+        <v>46</v>
+      </c>
+      <c r="AT40">
+        <v>5.5</v>
+      </c>
+      <c r="AU40">
         <v>7.4</v>
       </c>
-      <c r="AQ40">
-        <v>12</v>
-      </c>
-      <c r="AR40">
-        <v>7</v>
-      </c>
-      <c r="AS40">
-        <v>7.8</v>
-      </c>
-      <c r="AT40">
-        <v>4.8</v>
-      </c>
-      <c r="AU40">
-        <v>6.6</v>
-      </c>
       <c r="AV40">
+        <v>18</v>
+      </c>
+      <c r="AW40">
+        <v>40</v>
+      </c>
+      <c r="AX40">
+        <v>7.6</v>
+      </c>
+      <c r="AY40">
+        <v>9.4</v>
+      </c>
+      <c r="AZ40">
+        <v>25</v>
+      </c>
+      <c r="BA40">
+        <v>44</v>
+      </c>
+      <c r="BB40">
+        <v>15.5</v>
+      </c>
+      <c r="BC40">
         <v>20</v>
       </c>
-      <c r="AW40">
-        <v>7.8</v>
-      </c>
-      <c r="AX40">
-        <v>7</v>
-      </c>
-      <c r="AY40">
-        <v>8.4</v>
-      </c>
-      <c r="AZ40">
-        <v>6.4</v>
-      </c>
-      <c r="BA40">
-        <v>7.8</v>
-      </c>
-      <c r="BB40">
-        <v>14</v>
-      </c>
-      <c r="BC40">
-        <v>18</v>
-      </c>
       <c r="BD40">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BE40">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BF40">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG40">
-        <v>7.8</v>
+        <v>48</v>
       </c>
       <c r="BH40">
         <v>2.9</v>
@@ -10693,19 +10693,19 @@
         <v>2.64</v>
       </c>
       <c r="G41">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H41">
         <v>3.3</v>
       </c>
       <c r="I41">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J41">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10714,52 +10714,52 @@
         <v>1.16</v>
       </c>
       <c r="N41">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O41">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="P41">
         <v>1.43</v>
       </c>
       <c r="Q41">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
         <v>1.15</v>
       </c>
       <c r="S41">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="T41">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U41">
         <v>1.66</v>
       </c>
       <c r="V41">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
         <v>1.54</v>
       </c>
       <c r="X41">
+        <v>7</v>
+      </c>
+      <c r="Y41">
         <v>8.6</v>
       </c>
-      <c r="Y41">
-        <v>9</v>
-      </c>
       <c r="Z41">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA41">
         <v>85</v>
       </c>
       <c r="AB41">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC41">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD41">
         <v>17</v>
@@ -10768,7 +10768,7 @@
         <v>75</v>
       </c>
       <c r="AF41">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG41">
         <v>14.5</v>
@@ -10777,10 +10777,10 @@
         <v>28</v>
       </c>
       <c r="AI41">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AK41">
         <v>48</v>
@@ -10795,61 +10795,61 @@
         <v>65</v>
       </c>
       <c r="AO41">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP41">
         <v>6.4</v>
       </c>
       <c r="AQ41">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR41">
         <v>18</v>
       </c>
       <c r="AS41">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AT41">
+        <v>6.4</v>
+      </c>
+      <c r="AU41">
         <v>6.2</v>
       </c>
-      <c r="AU41">
-        <v>6</v>
-      </c>
       <c r="AV41">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW41">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AX41">
         <v>13.5</v>
       </c>
       <c r="AY41">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ41">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BA41">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BB41">
         <v>40</v>
       </c>
       <c r="BC41">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BD41">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BE41">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BF41">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BG41">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10938,7 +10938,7 @@
         <v>2.74</v>
       </c>
       <c r="H42">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I42">
         <v>3.45</v>
@@ -10956,13 +10956,13 @@
         <v>1.12</v>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O42">
         <v>1.53</v>
       </c>
       <c r="P42">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -10980,7 +10980,7 @@
         <v>1.78</v>
       </c>
       <c r="V42">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
         <v>1.57</v>
@@ -11016,7 +11016,7 @@
         <v>15.5</v>
       </c>
       <c r="AH42">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI42">
         <v>90</v>
@@ -11076,7 +11076,7 @@
         <v>6.4</v>
       </c>
       <c r="BB42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC42">
         <v>6</v>
@@ -11085,10 +11085,10 @@
         <v>6.4</v>
       </c>
       <c r="BE42">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG42">
         <v>6.4</v>
@@ -11186,7 +11186,7 @@
         <v>990</v>
       </c>
       <c r="J43">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K43">
         <v>950</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="222">
   <si>
     <t>League</t>
   </si>
@@ -304,21 +304,24 @@
     <t>Serbian Super League</t>
   </si>
   <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
-    <t>Polish Ekstraklasa</t>
+    <t>Danish Superliga</t>
   </si>
   <si>
     <t>Polish I Liga</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>Argentinian Primera C</t>
+  </si>
+  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
+    <t>Brazilian Campeonato Women</t>
+  </si>
+  <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
@@ -385,6 +391,9 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:15:00</t>
   </si>
   <si>
@@ -475,33 +484,36 @@
     <t>Vojvodina</t>
   </si>
   <si>
+    <t>Cracovia Krakow</t>
+  </si>
+  <si>
     <t>Ranheim IL</t>
   </si>
   <si>
-    <t>Cracovia Krakow</t>
+    <t>OB</t>
   </si>
   <si>
     <t>Chrobry Glogow</t>
   </si>
   <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>Orebro</t>
   </si>
   <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>CSD Yupanqui</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>Celtic</t>
+  </si>
+  <si>
     <t>FCSB</t>
   </si>
   <si>
-    <t>Celtic</t>
-  </si>
-  <si>
     <t>Defensores de Puerto Vi</t>
   </si>
   <si>
@@ -517,18 +529,21 @@
     <t>Sarmiento de Junin</t>
   </si>
   <si>
+    <t>CR Flamengo (W)</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
     <t>Defensor Sporting</t>
   </si>
   <si>
     <t>CA Platense</t>
   </si>
   <si>
-    <t>Velez Sarsfield</t>
-  </si>
-  <si>
     <t>Paysandu FC</t>
   </si>
   <si>
@@ -601,33 +616,36 @@
     <t>Macva Sabac</t>
   </si>
   <si>
+    <t>Pogon Szczecin</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Pogon Szczecin</t>
+    <t>SonderjyskE</t>
   </si>
   <si>
     <t>Odra Opole</t>
   </si>
   <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
     <t>Varnamo</t>
   </si>
   <si>
     <t>FC Arlanda</t>
   </si>
   <si>
+    <t>Canuelas</t>
+  </si>
+  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Dundee</t>
+  </si>
+  <si>
     <t>Farul Constanta</t>
   </si>
   <si>
-    <t>Dundee</t>
-  </si>
-  <si>
     <t>Sarmiento de Resistenci</t>
   </si>
   <si>
@@ -643,22 +661,25 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
+    <t>Corinthians (W)</t>
+  </si>
+  <si>
     <t>Nacional (Par)</t>
   </si>
   <si>
+    <t>CA Independiente</t>
+  </si>
+  <si>
     <t>Cerro</t>
   </si>
   <si>
     <t>Talleres</t>
   </si>
   <si>
-    <t>CA Independiente</t>
-  </si>
-  <si>
     <t>Club Oriental de La Paz</t>
   </si>
   <si>
-    <t>2026-08-02 07:21:43</t>
+    <t>2026-08-02 09:44:41</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB43"/>
+  <dimension ref="A1:CB45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1240,16 +1261,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F2">
         <v>2.2</v>
@@ -1261,7 +1282,7 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -1273,16 +1294,16 @@
         <v>1.66</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
         <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
@@ -1294,10 +1315,10 @@
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
         <v>1.29</v>
@@ -1306,7 +1327,7 @@
         <v>1.8</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1315,7 +1336,7 @@
         <v>30</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
         <v>6.6</v>
@@ -1363,13 +1384,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>24</v>
       </c>
       <c r="AS2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1384,7 +1405,7 @@
         <v>65</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1396,7 +1417,7 @@
         <v>42</v>
       </c>
       <c r="BB2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC2">
         <v>27</v>
@@ -1405,76 +1426,76 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>29</v>
       </c>
       <c r="BG2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
         <v>3.6</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1482,28 +1503,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F3">
         <v>3.65</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1521,7 +1542,7 @@
         <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
         <v>1.75</v>
@@ -1539,7 +1560,7 @@
         <v>1.87</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V3">
         <v>1.79</v>
@@ -1560,13 +1581,13 @@
         <v>32</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
         <v>8</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE3">
         <v>28</v>
@@ -1587,7 +1608,7 @@
         <v>85</v>
       </c>
       <c r="AK3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL3">
         <v>70</v>
@@ -1596,10 +1617,10 @@
         <v>140</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3">
         <v>9</v>
@@ -1611,7 +1632,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1635,22 +1656,22 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
         <v>16.5</v>
@@ -1659,7 +1680,7 @@
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
@@ -1695,7 +1716,7 @@
         <v>5.1</v>
       </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV3">
         <v>18</v>
@@ -1716,7 +1737,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1724,34 +1745,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H4">
         <v>3.7</v>
       </c>
       <c r="I4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.46</v>
@@ -1778,16 +1799,16 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1958,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="CB4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1966,16 +1987,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F5">
         <v>1.61</v>
@@ -2008,7 +2029,7 @@
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q5">
         <v>1.55</v>
@@ -2032,22 +2053,22 @@
         <v>2.58</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA5">
         <v>150</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>25</v>
@@ -2068,7 +2089,7 @@
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AK5">
         <v>15.5</v>
@@ -2077,28 +2098,28 @@
         <v>25</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
         <v>27</v>
       </c>
       <c r="AR5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AS5">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2134,10 +2155,10 @@
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
@@ -2155,7 +2176,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN5">
         <v>4.6</v>
@@ -2164,7 +2185,7 @@
         <v>3.6</v>
       </c>
       <c r="BP5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
         <v>6.2</v>
@@ -2173,7 +2194,7 @@
         <v>20</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5">
         <v>9.4</v>
@@ -2185,22 +2206,22 @@
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
         <v>13</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2208,16 +2229,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F6">
         <v>1.1</v>
@@ -2226,13 +2247,13 @@
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2244,22 +2265,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O6">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2271,7 +2292,7 @@
         <v>1.09</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2442,7 +2463,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2450,31 +2471,31 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F7">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2486,13 +2507,13 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="O7">
         <v>1.08</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
         <v>1.08</v>
@@ -2507,13 +2528,13 @@
         <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2684,7 +2705,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2692,16 +2713,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F8">
         <v>2.02</v>
@@ -2731,7 +2752,7 @@
         <v>6.8</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
         <v>3.4</v>
@@ -2743,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="T8">
         <v>1.37</v>
@@ -2926,7 +2947,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2934,16 +2955,16 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2952,13 +2973,13 @@
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2976,13 +2997,13 @@
         <v>1.1</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.92</v>
       </c>
       <c r="Q9">
         <v>1.1</v>
       </c>
       <c r="R9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S9">
         <v>1.1</v>
@@ -2997,7 +3018,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3168,7 +3189,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3176,16 +3197,16 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3194,7 +3215,7 @@
         <v>1.28</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="I10">
         <v>990</v>
@@ -3203,7 +3224,7 @@
         <v>1.05</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3410,7 +3431,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3418,22 +3439,22 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F11">
         <v>3.15</v>
       </c>
       <c r="G11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H11">
         <v>2.12</v>
@@ -3451,7 +3472,7 @@
         <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
         <v>5.2</v>
@@ -3460,7 +3481,7 @@
         <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q11">
         <v>1.58</v>
@@ -3481,7 +3502,7 @@
         <v>1.78</v>
       </c>
       <c r="W11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X11">
         <v>29</v>
@@ -3496,7 +3517,7 @@
         <v>36</v>
       </c>
       <c r="AB11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC11">
         <v>12</v>
@@ -3520,7 +3541,7 @@
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK11">
         <v>42</v>
@@ -3574,7 +3595,7 @@
         <v>20</v>
       </c>
       <c r="BB11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC11">
         <v>5.1</v>
@@ -3583,7 +3604,7 @@
         <v>29</v>
       </c>
       <c r="BE11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF11">
         <v>16</v>
@@ -3652,7 +3673,7 @@
         <v>7.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3660,19 +3681,19 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G12">
         <v>2.02</v>
@@ -3681,7 +3702,7 @@
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -3720,7 +3741,7 @@
         <v>1.93</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
         <v>1.98</v>
@@ -3894,7 +3915,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3902,19 +3923,19 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
         <v>4.1</v>
@@ -3923,16 +3944,16 @@
         <v>2.06</v>
       </c>
       <c r="I13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
         <v>3.9</v>
       </c>
       <c r="L13">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
         <v>1.07</v>
@@ -3944,7 +3965,7 @@
         <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q13">
         <v>1.94</v>
@@ -3953,16 +3974,16 @@
         <v>1.33</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U13">
         <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W13">
         <v>1.33</v>
@@ -4025,34 +4046,34 @@
         <v>3.4</v>
       </c>
       <c r="AQ13">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AR13">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT13">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU13">
-        <v>2.98</v>
+        <v>6</v>
       </c>
       <c r="AV13">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AW13">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="AX13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY13">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>3.55</v>
+        <v>15</v>
       </c>
       <c r="BA13">
         <v>3.9</v>
@@ -4073,7 +4094,7 @@
         <v>4</v>
       </c>
       <c r="BG13">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="BH13">
         <v>3.5</v>
@@ -4136,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4144,22 +4165,22 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G14">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H14">
         <v>2.04</v>
@@ -4186,7 +4207,7 @@
         <v>1.19</v>
       </c>
       <c r="P14">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q14">
         <v>1.55</v>
@@ -4195,13 +4216,13 @@
         <v>1.66</v>
       </c>
       <c r="S14">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T14">
         <v>1.55</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V14">
         <v>1.94</v>
@@ -4219,7 +4240,7 @@
         <v>19</v>
       </c>
       <c r="AA14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB14">
         <v>21</v>
@@ -4243,13 +4264,13 @@
         <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ14">
         <v>65</v>
       </c>
       <c r="AK14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL14">
         <v>36</v>
@@ -4261,7 +4282,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AP14">
         <v>20</v>
@@ -4273,10 +4294,10 @@
         <v>14.5</v>
       </c>
       <c r="AS14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU14">
         <v>9</v>
@@ -4288,31 +4309,31 @@
         <v>16.5</v>
       </c>
       <c r="AX14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY14">
         <v>13.5</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA14">
         <v>20</v>
       </c>
       <c r="BB14">
+        <v>9</v>
+      </c>
+      <c r="BC14">
+        <v>25</v>
+      </c>
+      <c r="BD14">
+        <v>26</v>
+      </c>
+      <c r="BE14">
         <v>8.6</v>
       </c>
-      <c r="BC14">
-        <v>7.6</v>
-      </c>
-      <c r="BD14">
-        <v>7.6</v>
-      </c>
-      <c r="BE14">
-        <v>8.4</v>
-      </c>
       <c r="BF14">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG14">
         <v>8.199999999999999</v>
@@ -4378,7 +4399,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4386,34 +4407,34 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F15">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H15">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I15">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4428,13 +4449,13 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
         <v>2.92</v>
@@ -4446,40 +4467,40 @@
         <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="W15">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X15">
         <v>22</v>
       </c>
       <c r="Y15">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC15">
         <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH15">
         <v>19.5</v>
@@ -4488,76 +4509,76 @@
         <v>42</v>
       </c>
       <c r="AJ15">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK15">
         <v>40</v>
       </c>
       <c r="AL15">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM15">
         <v>90</v>
       </c>
       <c r="AN15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU15">
         <v>6.4</v>
       </c>
       <c r="AV15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AX15">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
         <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BB15">
         <v>3.95</v>
       </c>
       <c r="BC15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD15">
         <v>3.9</v>
       </c>
       <c r="BE15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH15">
         <v>3.9</v>
@@ -4578,31 +4599,31 @@
         <v>9</v>
       </c>
       <c r="BN15">
+        <v>6.6</v>
+      </c>
+      <c r="BO15">
+        <v>4.7</v>
+      </c>
+      <c r="BP15">
+        <v>23</v>
+      </c>
+      <c r="BQ15">
         <v>6.8</v>
       </c>
-      <c r="BO15">
-        <v>4.8</v>
-      </c>
-      <c r="BP15">
-        <v>24</v>
-      </c>
-      <c r="BQ15">
-        <v>7</v>
-      </c>
       <c r="BR15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS15">
         <v>7.6</v>
       </c>
       <c r="BT15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW15">
         <v>6.4</v>
@@ -4620,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4628,16 +4649,16 @@
         <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F16">
         <v>2.46</v>
@@ -4862,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4870,16 +4891,16 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F17">
         <v>1.36</v>
@@ -4903,7 +4924,7 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>3.85</v>
@@ -5104,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5112,16 +5133,16 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F18">
         <v>1.66</v>
@@ -5346,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5354,16 +5375,16 @@
         <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F19">
         <v>1.65</v>
@@ -5405,7 +5426,7 @@
         <v>1.47</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
         <v>1.71</v>
@@ -5588,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5596,34 +5617,34 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G20">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="H20">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="I20">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="J20">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="K20">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5632,7 +5653,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
         <v>1.31</v>
@@ -5656,10 +5677,10 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W20">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5830,7 +5851,7 @@
         <v>1.34</v>
       </c>
       <c r="CB20" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5838,31 +5859,31 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G21">
         <v>990</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I21">
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5901,7 +5922,7 @@
         <v>1.02</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6072,7 +6093,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6080,31 +6101,31 @@
         <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F22">
         <v>8</v>
       </c>
       <c r="G22">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H22">
         <v>1.42</v>
       </c>
       <c r="I22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K22">
         <v>5.7</v>
@@ -6122,28 +6143,28 @@
         <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q22">
         <v>1.5</v>
       </c>
       <c r="R22">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S22">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T22">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U22">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V22">
         <v>3.25</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>36</v>
@@ -6152,7 +6173,7 @@
         <v>13</v>
       </c>
       <c r="Z22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA22">
         <v>13</v>
@@ -6179,7 +6200,7 @@
         <v>22</v>
       </c>
       <c r="AI22">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
         <v>1000</v>
@@ -6197,7 +6218,7 @@
         <v>110</v>
       </c>
       <c r="AO22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AP22">
         <v>21</v>
@@ -6209,7 +6230,7 @@
         <v>9.6</v>
       </c>
       <c r="AS22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT22">
         <v>32</v>
@@ -6233,7 +6254,7 @@
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB22">
         <v>48</v>
@@ -6251,7 +6272,7 @@
         <v>36</v>
       </c>
       <c r="BG22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH22">
         <v>4.9</v>
@@ -6314,7 +6335,7 @@
         <v>6</v>
       </c>
       <c r="CB22" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6322,28 +6343,28 @@
         <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F23">
         <v>1.52</v>
       </c>
       <c r="G23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H23">
         <v>6.4</v>
       </c>
       <c r="I23">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J23">
         <v>5.1</v>
@@ -6385,7 +6406,7 @@
         <v>1.17</v>
       </c>
       <c r="W23">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X23">
         <v>36</v>
@@ -6424,7 +6445,7 @@
         <v>570</v>
       </c>
       <c r="AJ23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK23">
         <v>15</v>
@@ -6517,7 +6538,7 @@
         <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP23">
         <v>9</v>
@@ -6535,7 +6556,7 @@
         <v>10.5</v>
       </c>
       <c r="BU23">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6553,10 +6574,10 @@
         <v>11</v>
       </c>
       <c r="CA23">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="CB23" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6564,16 +6585,16 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F24">
         <v>1.12</v>
@@ -6606,7 +6627,7 @@
         <v>1.09</v>
       </c>
       <c r="P24">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q24">
         <v>1.33</v>
@@ -6726,7 +6747,7 @@
         <v>5.6</v>
       </c>
       <c r="BD24">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE24">
         <v>8.199999999999999</v>
@@ -6798,7 +6819,7 @@
         <v>3.95</v>
       </c>
       <c r="CB24" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6806,241 +6827,241 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F25">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="G25">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="H25">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="I25">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J25">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N25">
+        <v>3.1</v>
+      </c>
+      <c r="O25">
+        <v>1.41</v>
+      </c>
+      <c r="P25">
+        <v>1.68</v>
+      </c>
+      <c r="Q25">
+        <v>2.24</v>
+      </c>
+      <c r="R25">
+        <v>1.27</v>
+      </c>
+      <c r="S25">
+        <v>4.1</v>
+      </c>
+      <c r="T25">
+        <v>1.88</v>
+      </c>
+      <c r="U25">
+        <v>1.98</v>
+      </c>
+      <c r="V25">
+        <v>1.32</v>
+      </c>
+      <c r="W25">
+        <v>1.74</v>
+      </c>
+      <c r="X25">
+        <v>13</v>
+      </c>
+      <c r="Y25">
+        <v>13.5</v>
+      </c>
+      <c r="Z25">
+        <v>29</v>
+      </c>
+      <c r="AA25">
+        <v>100</v>
+      </c>
+      <c r="AB25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC25">
+        <v>7.6</v>
+      </c>
+      <c r="AD25">
+        <v>18</v>
+      </c>
+      <c r="AE25">
+        <v>60</v>
+      </c>
+      <c r="AF25">
+        <v>14.5</v>
+      </c>
+      <c r="AG25">
+        <v>11.5</v>
+      </c>
+      <c r="AH25">
+        <v>20</v>
+      </c>
+      <c r="AI25">
+        <v>70</v>
+      </c>
+      <c r="AJ25">
+        <v>32</v>
+      </c>
+      <c r="AK25">
+        <v>29</v>
+      </c>
+      <c r="AL25">
+        <v>48</v>
+      </c>
+      <c r="AM25">
+        <v>150</v>
+      </c>
+      <c r="AN25">
+        <v>25</v>
+      </c>
+      <c r="AO25">
+        <v>65</v>
+      </c>
+      <c r="AP25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ25">
+        <v>9.6</v>
+      </c>
+      <c r="AR25">
+        <v>6.4</v>
+      </c>
+      <c r="AS25">
+        <v>7.6</v>
+      </c>
+      <c r="AT25">
+        <v>7</v>
+      </c>
+      <c r="AU25">
+        <v>6.2</v>
+      </c>
+      <c r="AV25">
+        <v>12.5</v>
+      </c>
+      <c r="AW25">
+        <v>38</v>
+      </c>
+      <c r="AX25">
         <v>10</v>
       </c>
-      <c r="O25">
-        <v>1.09</v>
-      </c>
-      <c r="P25">
-        <v>3.9</v>
-      </c>
-      <c r="Q25">
-        <v>1.29</v>
-      </c>
-      <c r="R25">
-        <v>2.18</v>
-      </c>
-      <c r="S25">
-        <v>1.69</v>
-      </c>
-      <c r="T25">
-        <v>1.33</v>
-      </c>
-      <c r="U25">
-        <v>3.4</v>
-      </c>
-      <c r="V25">
-        <v>1.83</v>
-      </c>
-      <c r="W25">
-        <v>1.44</v>
-      </c>
-      <c r="X25">
-        <v>70</v>
-      </c>
-      <c r="Y25">
-        <v>36</v>
-      </c>
-      <c r="Z25">
-        <v>34</v>
-      </c>
-      <c r="AA25">
-        <v>34</v>
-      </c>
-      <c r="AB25">
-        <v>36</v>
-      </c>
-      <c r="AC25">
-        <v>15.5</v>
-      </c>
-      <c r="AD25">
-        <v>14.5</v>
-      </c>
-      <c r="AE25">
-        <v>23</v>
-      </c>
-      <c r="AF25">
-        <v>46</v>
-      </c>
-      <c r="AG25">
-        <v>17.5</v>
-      </c>
-      <c r="AH25">
-        <v>15</v>
-      </c>
-      <c r="AI25">
-        <v>25</v>
-      </c>
-      <c r="AJ25">
-        <v>70</v>
-      </c>
-      <c r="AK25">
-        <v>36</v>
-      </c>
-      <c r="AL25">
-        <v>27</v>
-      </c>
-      <c r="AM25">
-        <v>40</v>
-      </c>
-      <c r="AN25">
-        <v>11.5</v>
-      </c>
-      <c r="AO25">
-        <v>6.6</v>
-      </c>
-      <c r="AP25">
-        <v>6.6</v>
-      </c>
-      <c r="AQ25">
-        <v>18</v>
-      </c>
-      <c r="AR25">
-        <v>21</v>
-      </c>
-      <c r="AS25">
-        <v>21</v>
-      </c>
-      <c r="AT25">
-        <v>6</v>
-      </c>
-      <c r="AU25">
-        <v>12</v>
-      </c>
-      <c r="AV25">
-        <v>11.5</v>
-      </c>
-      <c r="AW25">
-        <v>13.5</v>
-      </c>
-      <c r="AX25">
-        <v>6.2</v>
-      </c>
       <c r="AY25">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA25">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="BB25">
         <v>6.6</v>
       </c>
       <c r="BC25">
+        <v>19.5</v>
+      </c>
+      <c r="BD25">
+        <v>7</v>
+      </c>
+      <c r="BE25">
+        <v>8</v>
+      </c>
+      <c r="BF25">
+        <v>17.5</v>
+      </c>
+      <c r="BG25">
+        <v>7.4</v>
+      </c>
+      <c r="BH25">
+        <v>3.15</v>
+      </c>
+      <c r="BI25">
+        <v>2.46</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>5.4</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN25">
+        <v>5.2</v>
+      </c>
+      <c r="BO25">
+        <v>3.85</v>
+      </c>
+      <c r="BP25">
         <v>19</v>
       </c>
-      <c r="BD25">
-        <v>21</v>
-      </c>
-      <c r="BE25">
-        <v>6</v>
-      </c>
-      <c r="BF25">
+      <c r="BQ25">
+        <v>6.8</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG25">
-        <v>5.4</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.04</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.04</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.04</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.04</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.04</v>
-      </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7048,241 +7069,241 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F26">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="G26">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="H26">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="I26">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J26">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="K26">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>10</v>
+      </c>
+      <c r="O26">
         <v>1.09</v>
       </c>
-      <c r="N26">
-        <v>3.1</v>
-      </c>
-      <c r="O26">
-        <v>1.41</v>
-      </c>
       <c r="P26">
-        <v>1.68</v>
+        <v>3.9</v>
       </c>
       <c r="Q26">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="R26">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>1.69</v>
       </c>
       <c r="T26">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="U26">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="V26">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="W26">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="X26">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="Y26">
+        <v>36</v>
+      </c>
+      <c r="Z26">
+        <v>34</v>
+      </c>
+      <c r="AA26">
+        <v>34</v>
+      </c>
+      <c r="AB26">
+        <v>36</v>
+      </c>
+      <c r="AC26">
+        <v>15.5</v>
+      </c>
+      <c r="AD26">
+        <v>14.5</v>
+      </c>
+      <c r="AE26">
+        <v>23</v>
+      </c>
+      <c r="AF26">
+        <v>46</v>
+      </c>
+      <c r="AG26">
+        <v>17.5</v>
+      </c>
+      <c r="AH26">
+        <v>15</v>
+      </c>
+      <c r="AI26">
+        <v>25</v>
+      </c>
+      <c r="AJ26">
+        <v>70</v>
+      </c>
+      <c r="AK26">
+        <v>36</v>
+      </c>
+      <c r="AL26">
+        <v>27</v>
+      </c>
+      <c r="AM26">
+        <v>40</v>
+      </c>
+      <c r="AN26">
+        <v>11.5</v>
+      </c>
+      <c r="AO26">
+        <v>6.6</v>
+      </c>
+      <c r="AP26">
+        <v>6.6</v>
+      </c>
+      <c r="AQ26">
+        <v>18</v>
+      </c>
+      <c r="AR26">
+        <v>21</v>
+      </c>
+      <c r="AS26">
+        <v>21</v>
+      </c>
+      <c r="AT26">
+        <v>6</v>
+      </c>
+      <c r="AU26">
+        <v>12</v>
+      </c>
+      <c r="AV26">
+        <v>11.5</v>
+      </c>
+      <c r="AW26">
         <v>13.5</v>
       </c>
-      <c r="Z26">
-        <v>29</v>
-      </c>
-      <c r="AA26">
-        <v>100</v>
-      </c>
-      <c r="AB26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC26">
-        <v>7.6</v>
-      </c>
-      <c r="AD26">
-        <v>18</v>
-      </c>
-      <c r="AE26">
-        <v>60</v>
-      </c>
-      <c r="AF26">
-        <v>14.5</v>
-      </c>
-      <c r="AG26">
-        <v>11.5</v>
-      </c>
-      <c r="AH26">
-        <v>20</v>
-      </c>
-      <c r="AI26">
-        <v>70</v>
-      </c>
-      <c r="AJ26">
-        <v>32</v>
-      </c>
-      <c r="AK26">
-        <v>29</v>
-      </c>
-      <c r="AL26">
-        <v>48</v>
-      </c>
-      <c r="AM26">
-        <v>150</v>
-      </c>
-      <c r="AN26">
-        <v>25</v>
-      </c>
-      <c r="AO26">
-        <v>65</v>
-      </c>
-      <c r="AP26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ26">
-        <v>9.6</v>
-      </c>
-      <c r="AR26">
-        <v>6.4</v>
-      </c>
-      <c r="AS26">
-        <v>7.6</v>
-      </c>
-      <c r="AT26">
-        <v>7</v>
-      </c>
-      <c r="AU26">
+      <c r="AX26">
         <v>6.2</v>
       </c>
-      <c r="AV26">
-        <v>12.5</v>
-      </c>
-      <c r="AW26">
-        <v>38</v>
-      </c>
-      <c r="AX26">
-        <v>10</v>
-      </c>
       <c r="AY26">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA26">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BB26">
         <v>6.6</v>
       </c>
       <c r="BC26">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD26">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BE26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BF26">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH26">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7290,241 +7311,241 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="H27">
         <v>3.35</v>
       </c>
       <c r="I27">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L27">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="M27">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N27">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="O27">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="P27">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="R27">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S27">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="T27">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="X27">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y27">
+        <v>18</v>
+      </c>
+      <c r="Z27">
+        <v>32</v>
+      </c>
+      <c r="AA27">
+        <v>65</v>
+      </c>
+      <c r="AB27">
+        <v>15</v>
+      </c>
+      <c r="AC27">
+        <v>9.4</v>
+      </c>
+      <c r="AD27">
+        <v>15.5</v>
+      </c>
+      <c r="AE27">
+        <v>36</v>
+      </c>
+      <c r="AF27">
+        <v>17</v>
+      </c>
+      <c r="AG27">
+        <v>13</v>
+      </c>
+      <c r="AH27">
+        <v>17.5</v>
+      </c>
+      <c r="AI27">
+        <v>42</v>
+      </c>
+      <c r="AJ27">
+        <v>29</v>
+      </c>
+      <c r="AK27">
+        <v>25</v>
+      </c>
+      <c r="AL27">
+        <v>32</v>
+      </c>
+      <c r="AM27">
+        <v>75</v>
+      </c>
+      <c r="AN27">
         <v>14</v>
       </c>
-      <c r="Z27">
-        <v>29</v>
-      </c>
-      <c r="AA27">
-        <v>85</v>
-      </c>
-      <c r="AB27">
+      <c r="AO27">
+        <v>27</v>
+      </c>
+      <c r="AP27">
+        <v>16</v>
+      </c>
+      <c r="AQ27">
+        <v>13</v>
+      </c>
+      <c r="AR27">
+        <v>20</v>
+      </c>
+      <c r="AS27">
+        <v>6.2</v>
+      </c>
+      <c r="AT27">
         <v>10</v>
       </c>
-      <c r="AC27">
-        <v>8.6</v>
-      </c>
-      <c r="AD27">
-        <v>18</v>
-      </c>
-      <c r="AE27">
-        <v>60</v>
-      </c>
-      <c r="AF27">
-        <v>15</v>
-      </c>
-      <c r="AG27">
-        <v>13.5</v>
-      </c>
-      <c r="AH27">
-        <v>20</v>
-      </c>
-      <c r="AI27">
-        <v>70</v>
-      </c>
-      <c r="AJ27">
-        <v>38</v>
-      </c>
-      <c r="AK27">
-        <v>34</v>
-      </c>
-      <c r="AL27">
-        <v>55</v>
-      </c>
-      <c r="AM27">
-        <v>140</v>
-      </c>
-      <c r="AN27">
-        <v>29</v>
-      </c>
-      <c r="AO27">
-        <v>65</v>
-      </c>
-      <c r="AP27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR27">
-        <v>21</v>
-      </c>
-      <c r="AS27">
-        <v>5.1</v>
-      </c>
-      <c r="AT27">
-        <v>6.8</v>
-      </c>
       <c r="AU27">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV27">
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27">
+        <v>13</v>
+      </c>
+      <c r="BA27">
+        <v>5.9</v>
+      </c>
+      <c r="BB27">
+        <v>20</v>
+      </c>
+      <c r="BC27">
         <v>16</v>
       </c>
-      <c r="BA27">
-        <v>5</v>
-      </c>
-      <c r="BB27">
-        <v>4.7</v>
-      </c>
-      <c r="BC27">
-        <v>21</v>
-      </c>
       <c r="BD27">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE27">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF27">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG27">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BH27">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="BI27">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="BJ27">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK27">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN27">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO27">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP27">
+        <v>15.5</v>
+      </c>
+      <c r="BQ27">
+        <v>6.2</v>
+      </c>
+      <c r="BR27">
+        <v>25</v>
+      </c>
+      <c r="BS27">
+        <v>7.2</v>
+      </c>
+      <c r="BT27">
+        <v>7.2</v>
+      </c>
+      <c r="BU27">
+        <v>5.4</v>
+      </c>
+      <c r="BV27">
+        <v>25</v>
+      </c>
+      <c r="BW27">
+        <v>7.2</v>
+      </c>
+      <c r="BX27">
+        <v>32</v>
+      </c>
+      <c r="BY27">
+        <v>7.8</v>
+      </c>
+      <c r="BZ27">
         <v>19</v>
       </c>
-      <c r="BQ27">
-        <v>6.8</v>
-      </c>
-      <c r="BR27">
-        <v>36</v>
-      </c>
-      <c r="BS27">
-        <v>8</v>
-      </c>
-      <c r="BT27">
-        <v>7</v>
-      </c>
-      <c r="BU27">
-        <v>5.2</v>
-      </c>
-      <c r="BV27">
-        <v>32</v>
-      </c>
-      <c r="BW27">
-        <v>7.8</v>
-      </c>
-      <c r="BX27">
-        <v>48</v>
-      </c>
-      <c r="BY27">
-        <v>8.6</v>
-      </c>
-      <c r="BZ27">
-        <v>0</v>
-      </c>
       <c r="CA27">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="CB27" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7532,241 +7553,241 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F28">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G28">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="H28">
         <v>3.35</v>
       </c>
       <c r="I28">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="J28">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L28">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N28">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="O28">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="Q28">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="R28">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="S28">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="X28">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="Y28">
+        <v>14</v>
+      </c>
+      <c r="Z28">
+        <v>29</v>
+      </c>
+      <c r="AA28">
+        <v>85</v>
+      </c>
+      <c r="AB28">
+        <v>10</v>
+      </c>
+      <c r="AC28">
+        <v>8.6</v>
+      </c>
+      <c r="AD28">
         <v>18</v>
       </c>
-      <c r="Z28">
-        <v>32</v>
-      </c>
-      <c r="AA28">
+      <c r="AE28">
+        <v>60</v>
+      </c>
+      <c r="AF28">
+        <v>15</v>
+      </c>
+      <c r="AG28">
+        <v>13.5</v>
+      </c>
+      <c r="AH28">
+        <v>20</v>
+      </c>
+      <c r="AI28">
+        <v>70</v>
+      </c>
+      <c r="AJ28">
+        <v>38</v>
+      </c>
+      <c r="AK28">
+        <v>34</v>
+      </c>
+      <c r="AL28">
+        <v>55</v>
+      </c>
+      <c r="AM28">
+        <v>140</v>
+      </c>
+      <c r="AN28">
+        <v>29</v>
+      </c>
+      <c r="AO28">
         <v>65</v>
       </c>
-      <c r="AB28">
-        <v>15</v>
-      </c>
-      <c r="AC28">
-        <v>9.4</v>
-      </c>
-      <c r="AD28">
-        <v>15.5</v>
-      </c>
-      <c r="AE28">
-        <v>36</v>
-      </c>
-      <c r="AF28">
-        <v>17</v>
-      </c>
-      <c r="AG28">
-        <v>13</v>
-      </c>
-      <c r="AH28">
-        <v>17.5</v>
-      </c>
-      <c r="AI28">
-        <v>42</v>
-      </c>
-      <c r="AJ28">
-        <v>29</v>
-      </c>
-      <c r="AK28">
-        <v>25</v>
-      </c>
-      <c r="AL28">
-        <v>32</v>
-      </c>
-      <c r="AM28">
-        <v>75</v>
-      </c>
-      <c r="AN28">
-        <v>14</v>
-      </c>
-      <c r="AO28">
-        <v>27</v>
-      </c>
       <c r="AP28">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ28">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS28">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT28">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AU28">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV28">
         <v>11.5</v>
       </c>
       <c r="AW28">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AX28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28">
+        <v>16</v>
+      </c>
+      <c r="BA28">
+        <v>5</v>
+      </c>
+      <c r="BB28">
+        <v>4.7</v>
+      </c>
+      <c r="BC28">
+        <v>21</v>
+      </c>
+      <c r="BD28">
+        <v>4.9</v>
+      </c>
+      <c r="BE28">
+        <v>5.2</v>
+      </c>
+      <c r="BF28">
+        <v>18.5</v>
+      </c>
+      <c r="BG28">
+        <v>5</v>
+      </c>
+      <c r="BH28">
+        <v>3.2</v>
+      </c>
+      <c r="BI28">
+        <v>2.74</v>
+      </c>
+      <c r="BJ28">
+        <v>10.5</v>
+      </c>
+      <c r="BK28">
+        <v>8</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN28">
+        <v>5.3</v>
+      </c>
+      <c r="BO28">
+        <v>4</v>
+      </c>
+      <c r="BP28">
+        <v>19</v>
+      </c>
+      <c r="BQ28">
+        <v>6.8</v>
+      </c>
+      <c r="BR28">
+        <v>36</v>
+      </c>
+      <c r="BS28">
+        <v>8</v>
+      </c>
+      <c r="BT28">
+        <v>7</v>
+      </c>
+      <c r="BU28">
+        <v>5.2</v>
+      </c>
+      <c r="BV28">
+        <v>32</v>
+      </c>
+      <c r="BW28">
+        <v>7.8</v>
+      </c>
+      <c r="BX28">
+        <v>48</v>
+      </c>
+      <c r="BY28">
         <v>8.6</v>
       </c>
-      <c r="AZ28">
-        <v>13</v>
-      </c>
-      <c r="BA28">
-        <v>5.9</v>
-      </c>
-      <c r="BB28">
-        <v>20</v>
-      </c>
-      <c r="BC28">
-        <v>16</v>
-      </c>
-      <c r="BD28">
-        <v>5.6</v>
-      </c>
-      <c r="BE28">
-        <v>6.2</v>
-      </c>
-      <c r="BF28">
-        <v>9.4</v>
-      </c>
-      <c r="BG28">
-        <v>19.5</v>
-      </c>
-      <c r="BH28">
-        <v>4.2</v>
-      </c>
-      <c r="BI28">
-        <v>3.3</v>
-      </c>
-      <c r="BJ28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK28">
-        <v>4.8</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN28">
-        <v>5.6</v>
-      </c>
-      <c r="BO28">
-        <v>4.3</v>
-      </c>
-      <c r="BP28">
-        <v>15.5</v>
-      </c>
-      <c r="BQ28">
-        <v>6.2</v>
-      </c>
-      <c r="BR28">
-        <v>25</v>
-      </c>
-      <c r="BS28">
-        <v>7.2</v>
-      </c>
-      <c r="BT28">
-        <v>7.2</v>
-      </c>
-      <c r="BU28">
-        <v>5.4</v>
-      </c>
-      <c r="BV28">
-        <v>25</v>
-      </c>
-      <c r="BW28">
-        <v>7.2</v>
-      </c>
-      <c r="BX28">
-        <v>32</v>
-      </c>
-      <c r="BY28">
-        <v>7.8</v>
-      </c>
       <c r="BZ28">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA28">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7774,16 +7795,16 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F29">
         <v>2.16</v>
@@ -7822,7 +7843,7 @@
         <v>1.76</v>
       </c>
       <c r="R29">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S29">
         <v>2.8</v>
@@ -8008,7 +8029,7 @@
         <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8016,22 +8037,22 @@
         <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F30">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G30">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H30">
         <v>2.98</v>
@@ -8250,7 +8271,7 @@
         <v>1.04</v>
       </c>
       <c r="CB30" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8258,518 +8279,518 @@
         <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="G31">
-        <v>3.4</v>
+        <v>990</v>
       </c>
       <c r="H31">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="I31">
-        <v>2.6</v>
+        <v>990</v>
       </c>
       <c r="J31">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L31">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>1.24</v>
       </c>
       <c r="O31">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P31">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q31">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="S31">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="T31">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="W31">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP31">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV31">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F32">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="H32">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="I32">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J32">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="K32">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O32">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P32">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="Q32">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="R32">
+        <v>1.33</v>
+      </c>
+      <c r="S32">
+        <v>3.4</v>
+      </c>
+      <c r="T32">
+        <v>1.74</v>
+      </c>
+      <c r="U32">
+        <v>2.1</v>
+      </c>
+      <c r="V32">
+        <v>1.64</v>
+      </c>
+      <c r="W32">
         <v>1.42</v>
       </c>
-      <c r="S32">
-        <v>3</v>
-      </c>
-      <c r="T32">
-        <v>1.76</v>
-      </c>
-      <c r="U32">
-        <v>2.14</v>
-      </c>
-      <c r="V32">
-        <v>1.24</v>
-      </c>
-      <c r="W32">
-        <v>2.12</v>
-      </c>
       <c r="X32">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y32">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z32">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="AA32">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="AB32">
+        <v>13</v>
+      </c>
+      <c r="AC32">
+        <v>8.4</v>
+      </c>
+      <c r="AD32">
+        <v>12.5</v>
+      </c>
+      <c r="AE32">
+        <v>29</v>
+      </c>
+      <c r="AF32">
+        <v>23</v>
+      </c>
+      <c r="AG32">
+        <v>14.5</v>
+      </c>
+      <c r="AH32">
+        <v>18</v>
+      </c>
+      <c r="AI32">
+        <v>42</v>
+      </c>
+      <c r="AJ32">
+        <v>75</v>
+      </c>
+      <c r="AK32">
+        <v>38</v>
+      </c>
+      <c r="AL32">
+        <v>50</v>
+      </c>
+      <c r="AM32">
+        <v>120</v>
+      </c>
+      <c r="AN32">
+        <v>36</v>
+      </c>
+      <c r="AO32">
+        <v>27</v>
+      </c>
+      <c r="AP32">
         <v>10</v>
       </c>
-      <c r="AC32">
-        <v>9.4</v>
-      </c>
-      <c r="AD32">
-        <v>970</v>
-      </c>
-      <c r="AE32">
-        <v>75</v>
-      </c>
-      <c r="AF32">
-        <v>12</v>
-      </c>
-      <c r="AG32">
+      <c r="AQ32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR32">
+        <v>13.5</v>
+      </c>
+      <c r="AS32">
+        <v>6.4</v>
+      </c>
+      <c r="AT32">
         <v>10.5</v>
       </c>
-      <c r="AH32">
-        <v>19</v>
-      </c>
-      <c r="AI32">
-        <v>75</v>
-      </c>
-      <c r="AJ32">
-        <v>20</v>
-      </c>
-      <c r="AK32">
-        <v>970</v>
-      </c>
-      <c r="AL32">
-        <v>34</v>
-      </c>
-      <c r="AM32">
-        <v>110</v>
-      </c>
-      <c r="AN32">
-        <v>13</v>
-      </c>
-      <c r="AO32">
-        <v>75</v>
-      </c>
-      <c r="AP32">
-        <v>13</v>
-      </c>
-      <c r="AQ32">
-        <v>16</v>
-      </c>
-      <c r="AR32">
+      <c r="AU32">
         <v>6.8</v>
       </c>
-      <c r="AS32">
-        <v>7.6</v>
-      </c>
-      <c r="AT32">
-        <v>7.2</v>
-      </c>
-      <c r="AU32">
-        <v>8</v>
-      </c>
       <c r="AV32">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AW32">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX32">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AY32">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ32">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA32">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB32">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BC32">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD32">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE32">
         <v>7.4</v>
       </c>
       <c r="BF32">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BG32">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI32">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO32">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ32">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS32">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU32">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW32">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY32">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB32" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G33">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J33">
+        <v>8</v>
+      </c>
+      <c r="K33">
         <v>8.199999999999999</v>
-      </c>
-      <c r="K33">
-        <v>8.6</v>
       </c>
       <c r="L33">
         <v>1.2</v>
@@ -8781,7 +8802,7 @@
         <v>8</v>
       </c>
       <c r="O33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P33">
         <v>3.3</v>
@@ -8790,7 +8811,7 @@
         <v>1.39</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S33">
         <v>1.98</v>
@@ -8799,16 +8820,16 @@
         <v>1.9</v>
       </c>
       <c r="U33">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V33">
         <v>1.06</v>
       </c>
       <c r="W33">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="X33">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y33">
         <v>80</v>
@@ -8820,31 +8841,31 @@
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC33">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AD33">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AE33">
         <v>260</v>
       </c>
       <c r="AF33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG33">
         <v>12</v>
       </c>
       <c r="AH33">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI33">
         <v>180</v>
       </c>
       <c r="AJ33">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK33">
         <v>13</v>
@@ -8865,37 +8886,37 @@
         <v>36</v>
       </c>
       <c r="AQ33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AR33">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS33">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT33">
         <v>12</v>
       </c>
       <c r="AU33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AV33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY33">
         <v>11</v>
       </c>
       <c r="AZ33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA33">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BB33">
         <v>9.199999999999999</v>
@@ -8907,13 +8928,13 @@
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF33">
         <v>3</v>
       </c>
       <c r="BG33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8976,186 +8997,186 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F34">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="G34">
-        <v>990</v>
+        <v>1.88</v>
       </c>
       <c r="H34">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="I34">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="J34">
-        <v>1.2</v>
+        <v>3.85</v>
       </c>
       <c r="K34">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L34">
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="O34">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q34">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="R34">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="T34">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U34">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V34">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU34">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV34">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW34">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA34">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9218,7 +9239,7 @@
         <v>1.04</v>
       </c>
       <c r="CB34" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9226,34 +9247,34 @@
         <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9265,19 +9286,19 @@
         <v>1.25</v>
       </c>
       <c r="O35">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P35">
         <v>1.25</v>
       </c>
       <c r="Q35">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="R35">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
         <v>1.11</v>
@@ -9286,10 +9307,10 @@
         <v>1.11</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W35">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9454,843 +9475,843 @@
         <v>1.04</v>
       </c>
       <c r="BZ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F36">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N36">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O36">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q36">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="R36">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S36">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U36">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W36">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X36">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y36">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z36">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA36">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB36">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC36">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD36">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE36">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF36">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG36">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI36">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK36">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL36">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM36">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO36">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP36">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX36">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB36">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC36">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE36">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF36">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH36">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN36">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP36">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR36">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT36">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV36">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA36">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F37">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="G37">
-        <v>2.54</v>
+        <v>1.93</v>
       </c>
       <c r="H37">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="I37">
+        <v>6.2</v>
+      </c>
+      <c r="J37">
+        <v>3.45</v>
+      </c>
+      <c r="K37">
+        <v>3.95</v>
+      </c>
+      <c r="L37">
+        <v>1.42</v>
+      </c>
+      <c r="M37">
+        <v>1.08</v>
+      </c>
+      <c r="N37">
+        <v>3.2</v>
+      </c>
+      <c r="O37">
+        <v>1.35</v>
+      </c>
+      <c r="P37">
+        <v>1.75</v>
+      </c>
+      <c r="Q37">
+        <v>2.02</v>
+      </c>
+      <c r="R37">
+        <v>1.28</v>
+      </c>
+      <c r="S37">
+        <v>3.35</v>
+      </c>
+      <c r="T37">
+        <v>1.91</v>
+      </c>
+      <c r="U37">
+        <v>1.87</v>
+      </c>
+      <c r="V37">
+        <v>1.2</v>
+      </c>
+      <c r="W37">
+        <v>2.06</v>
+      </c>
+      <c r="X37">
+        <v>15.5</v>
+      </c>
+      <c r="Y37">
+        <v>17</v>
+      </c>
+      <c r="Z37">
+        <v>50</v>
+      </c>
+      <c r="AA37">
+        <v>180</v>
+      </c>
+      <c r="AB37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD37">
+        <v>23</v>
+      </c>
+      <c r="AE37">
+        <v>100</v>
+      </c>
+      <c r="AF37">
+        <v>13</v>
+      </c>
+      <c r="AG37">
+        <v>12.5</v>
+      </c>
+      <c r="AH37">
+        <v>23</v>
+      </c>
+      <c r="AI37">
+        <v>110</v>
+      </c>
+      <c r="AJ37">
+        <v>24</v>
+      </c>
+      <c r="AK37">
+        <v>22</v>
+      </c>
+      <c r="AL37">
+        <v>55</v>
+      </c>
+      <c r="AM37">
+        <v>170</v>
+      </c>
+      <c r="AN37">
+        <v>17.5</v>
+      </c>
+      <c r="AO37">
+        <v>140</v>
+      </c>
+      <c r="AP37">
+        <v>4.1</v>
+      </c>
+      <c r="AQ37">
+        <v>4.2</v>
+      </c>
+      <c r="AR37">
+        <v>5</v>
+      </c>
+      <c r="AS37">
+        <v>5.4</v>
+      </c>
+      <c r="AT37">
+        <v>3.3</v>
+      </c>
+      <c r="AU37">
+        <v>3.4</v>
+      </c>
+      <c r="AV37">
+        <v>4.5</v>
+      </c>
+      <c r="AW37">
+        <v>5.3</v>
+      </c>
+      <c r="AX37">
+        <v>3.9</v>
+      </c>
+      <c r="AY37">
+        <v>3.85</v>
+      </c>
+      <c r="AZ37">
+        <v>4.5</v>
+      </c>
+      <c r="BA37">
+        <v>5.3</v>
+      </c>
+      <c r="BB37">
+        <v>4.5</v>
+      </c>
+      <c r="BC37">
+        <v>4.4</v>
+      </c>
+      <c r="BD37">
+        <v>5.1</v>
+      </c>
+      <c r="BE37">
+        <v>5.4</v>
+      </c>
+      <c r="BF37">
+        <v>4.2</v>
+      </c>
+      <c r="BG37">
+        <v>5.4</v>
+      </c>
+      <c r="BH37">
+        <v>3.35</v>
+      </c>
+      <c r="BI37">
+        <v>2.84</v>
+      </c>
+      <c r="BJ37">
+        <v>11.5</v>
+      </c>
+      <c r="BK37">
+        <v>5.3</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>6.6</v>
+      </c>
+      <c r="BN37">
+        <v>4.5</v>
+      </c>
+      <c r="BO37">
         <v>3.05</v>
       </c>
-      <c r="J37">
-        <v>4</v>
-      </c>
-      <c r="K37">
-        <v>5.6</v>
-      </c>
-      <c r="L37">
-        <v>1.01</v>
-      </c>
-      <c r="M37">
-        <v>1.02</v>
-      </c>
-      <c r="N37">
-        <v>3.35</v>
-      </c>
-      <c r="O37">
-        <v>1.06</v>
-      </c>
-      <c r="P37">
-        <v>3.35</v>
-      </c>
-      <c r="Q37">
-        <v>1.29</v>
-      </c>
-      <c r="R37">
-        <v>2.06</v>
-      </c>
-      <c r="S37">
-        <v>1.72</v>
-      </c>
-      <c r="T37">
-        <v>1.11</v>
-      </c>
-      <c r="U37">
-        <v>1.11</v>
-      </c>
-      <c r="V37">
-        <v>1.48</v>
-      </c>
-      <c r="W37">
-        <v>1.64</v>
-      </c>
-      <c r="X37">
-        <v>1000</v>
-      </c>
-      <c r="Y37">
-        <v>1000</v>
-      </c>
-      <c r="Z37">
-        <v>1000</v>
-      </c>
-      <c r="AA37">
-        <v>1000</v>
-      </c>
-      <c r="AB37">
-        <v>1000</v>
-      </c>
-      <c r="AC37">
-        <v>1000</v>
-      </c>
-      <c r="AD37">
-        <v>1000</v>
-      </c>
-      <c r="AE37">
-        <v>1000</v>
-      </c>
-      <c r="AF37">
-        <v>1000</v>
-      </c>
-      <c r="AG37">
-        <v>1000</v>
-      </c>
-      <c r="AH37">
-        <v>1000</v>
-      </c>
-      <c r="AI37">
-        <v>1000</v>
-      </c>
-      <c r="AJ37">
-        <v>1000</v>
-      </c>
-      <c r="AK37">
-        <v>1000</v>
-      </c>
-      <c r="AL37">
-        <v>1000</v>
-      </c>
-      <c r="AM37">
-        <v>1000</v>
-      </c>
-      <c r="AN37">
-        <v>1000</v>
-      </c>
-      <c r="AO37">
-        <v>1000</v>
-      </c>
-      <c r="AP37">
-        <v>1.01</v>
-      </c>
-      <c r="AQ37">
-        <v>1.01</v>
-      </c>
-      <c r="AR37">
-        <v>1.01</v>
-      </c>
-      <c r="AS37">
-        <v>1.01</v>
-      </c>
-      <c r="AT37">
-        <v>1.01</v>
-      </c>
-      <c r="AU37">
-        <v>1.01</v>
-      </c>
-      <c r="AV37">
-        <v>1.01</v>
-      </c>
-      <c r="AW37">
-        <v>1.01</v>
-      </c>
-      <c r="AX37">
-        <v>1.01</v>
-      </c>
-      <c r="AY37">
-        <v>1.01</v>
-      </c>
-      <c r="AZ37">
-        <v>1.01</v>
-      </c>
-      <c r="BA37">
-        <v>1.01</v>
-      </c>
-      <c r="BB37">
-        <v>1.01</v>
-      </c>
-      <c r="BC37">
-        <v>1.01</v>
-      </c>
-      <c r="BD37">
-        <v>1.01</v>
-      </c>
-      <c r="BE37">
-        <v>1.01</v>
-      </c>
-      <c r="BF37">
-        <v>1.01</v>
-      </c>
-      <c r="BG37">
-        <v>1.01</v>
-      </c>
-      <c r="BH37">
-        <v>1000</v>
-      </c>
-      <c r="BI37">
-        <v>1.04</v>
-      </c>
-      <c r="BJ37">
-        <v>1000</v>
-      </c>
-      <c r="BK37">
-        <v>1.04</v>
-      </c>
-      <c r="BL37">
-        <v>1000</v>
-      </c>
-      <c r="BM37">
-        <v>1.04</v>
-      </c>
-      <c r="BN37">
-        <v>1000</v>
-      </c>
-      <c r="BO37">
-        <v>1.04</v>
-      </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ37">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS37">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU37">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW37">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB37" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F38">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="G38">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="H38">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="I38">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="J38">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="K38">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="L38">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N38">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="P38">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="R38">
-        <v>1.2</v>
+        <v>2.08</v>
       </c>
       <c r="S38">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="T38">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U38">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V38">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W38">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y38">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z38">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA38">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC38">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD38">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE38">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF38">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG38">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH38">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI38">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK38">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL38">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM38">
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO38">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP38">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR38">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS38">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT38">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU38">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV38">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW38">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX38">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY38">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA38">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB38">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC38">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD38">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE38">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF38">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG38">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH38">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ38">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK38">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN38">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP38">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR38">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS38">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT38">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU38">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV38">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW38">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N39">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O39">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="P39">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q39">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="T39">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U39">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V39">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI39">
         <v>1000</v>
@@ -10299,557 +10320,557 @@
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM39">
         <v>1000</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI39">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK39">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO39">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ39">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU39">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW39">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB39" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F40">
-        <v>1.72</v>
+        <v>2.96</v>
       </c>
       <c r="G40">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="I40">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J40">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K40">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="L40">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
+        <v>1.01</v>
+      </c>
+      <c r="N40">
+        <v>3.75</v>
+      </c>
+      <c r="O40">
+        <v>1.28</v>
+      </c>
+      <c r="P40">
+        <v>1.9</v>
+      </c>
+      <c r="Q40">
+        <v>1.84</v>
+      </c>
+      <c r="R40">
+        <v>1.18</v>
+      </c>
+      <c r="S40">
+        <v>1.01</v>
+      </c>
+      <c r="T40">
         <v>1.11</v>
       </c>
-      <c r="N40">
-        <v>2.76</v>
-      </c>
-      <c r="O40">
-        <v>1.5</v>
-      </c>
-      <c r="P40">
-        <v>1.59</v>
-      </c>
-      <c r="Q40">
-        <v>2.48</v>
-      </c>
-      <c r="R40">
-        <v>1.21</v>
-      </c>
-      <c r="S40">
-        <v>5</v>
-      </c>
-      <c r="T40">
-        <v>2.34</v>
-      </c>
       <c r="U40">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="W40">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="X40">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y40">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z40">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA40">
         <v>1000</v>
       </c>
       <c r="AB40">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC40">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD40">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE40">
         <v>1000</v>
       </c>
       <c r="AF40">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG40">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH40">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI40">
         <v>1000</v>
       </c>
       <c r="AJ40">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK40">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL40">
         <v>1000</v>
       </c>
       <c r="AM40">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN40">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO40">
         <v>1000</v>
       </c>
       <c r="AP40">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR40">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS40">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AT40">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU40">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV40">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW40">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX40">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY40">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BA40">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB40">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC40">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD40">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE40">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF40">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG40">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BH40">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="BI40">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="BJ40">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
-        <v>5.8</v>
+        <v>1.31</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>10</v>
+        <v>1.31</v>
       </c>
       <c r="BN40">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
-        <v>3.25</v>
+        <v>1.31</v>
       </c>
       <c r="BP40">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>5.9</v>
+        <v>1.31</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>8.199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="BT40">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU40">
-        <v>5.2</v>
+        <v>1.31</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>9.199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>9.4</v>
+        <v>1.31</v>
       </c>
       <c r="BZ40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA40">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F41">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N41">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O41">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="P41">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
-        <v>3.1</v>
+        <v>1.41</v>
       </c>
       <c r="R41">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S41">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="U41">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W41">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y41">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z41">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA41">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB41">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC41">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD41">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE41">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF41">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG41">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH41">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI41">
         <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK41">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL41">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO41">
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG41">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10912,7 +10933,7 @@
         <v>1.04</v>
       </c>
       <c r="CB41" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -10920,34 +10941,34 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F42">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G42">
         <v>2.74</v>
       </c>
       <c r="H42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I42">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J42">
         <v>3</v>
       </c>
       <c r="K42">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -10956,13 +10977,13 @@
         <v>1.12</v>
       </c>
       <c r="N42">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
         <v>1.53</v>
       </c>
       <c r="P42">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -10974,13 +10995,13 @@
         <v>5.2</v>
       </c>
       <c r="T42">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U42">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
         <v>1.57</v>
@@ -10995,7 +11016,7 @@
         <v>25</v>
       </c>
       <c r="AA42">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB42">
         <v>8.199999999999999</v>
@@ -11037,7 +11058,7 @@
         <v>55</v>
       </c>
       <c r="AO42">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP42">
         <v>7.8</v>
@@ -11061,7 +11082,7 @@
         <v>12.5</v>
       </c>
       <c r="AW42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX42">
         <v>14</v>
@@ -11073,16 +11094,16 @@
         <v>19</v>
       </c>
       <c r="BA42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB42">
         <v>6.2</v>
       </c>
       <c r="BC42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE42">
         <v>6.8</v>
@@ -11154,249 +11175,733 @@
         <v>3.4</v>
       </c>
       <c r="CB42" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F43">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="G43">
+        <v>1.79</v>
+      </c>
+      <c r="H43">
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>6.6</v>
+      </c>
+      <c r="J43">
+        <v>3.45</v>
+      </c>
+      <c r="K43">
+        <v>3.8</v>
+      </c>
+      <c r="L43">
+        <v>1.52</v>
+      </c>
+      <c r="M43">
+        <v>1.11</v>
+      </c>
+      <c r="N43">
+        <v>2.76</v>
+      </c>
+      <c r="O43">
+        <v>1.5</v>
+      </c>
+      <c r="P43">
+        <v>1.59</v>
+      </c>
+      <c r="Q43">
+        <v>2.48</v>
+      </c>
+      <c r="R43">
+        <v>1.21</v>
+      </c>
+      <c r="S43">
+        <v>5</v>
+      </c>
+      <c r="T43">
+        <v>2.34</v>
+      </c>
+      <c r="U43">
+        <v>1.65</v>
+      </c>
+      <c r="V43">
+        <v>1.18</v>
+      </c>
+      <c r="W43">
+        <v>2.26</v>
+      </c>
+      <c r="X43">
+        <v>10</v>
+      </c>
+      <c r="Y43">
+        <v>16</v>
+      </c>
+      <c r="Z43">
+        <v>50</v>
+      </c>
+      <c r="AA43">
+        <v>1000</v>
+      </c>
+      <c r="AB43">
+        <v>6.2</v>
+      </c>
+      <c r="AC43">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD43">
+        <v>30</v>
+      </c>
+      <c r="AE43">
+        <v>1000</v>
+      </c>
+      <c r="AF43">
+        <v>9</v>
+      </c>
+      <c r="AG43">
+        <v>11.5</v>
+      </c>
+      <c r="AH43">
+        <v>32</v>
+      </c>
+      <c r="AI43">
+        <v>1000</v>
+      </c>
+      <c r="AJ43">
+        <v>18.5</v>
+      </c>
+      <c r="AK43">
+        <v>26</v>
+      </c>
+      <c r="AL43">
+        <v>1000</v>
+      </c>
+      <c r="AM43">
+        <v>290</v>
+      </c>
+      <c r="AN43">
+        <v>18</v>
+      </c>
+      <c r="AO43">
+        <v>1000</v>
+      </c>
+      <c r="AP43">
+        <v>8.4</v>
+      </c>
+      <c r="AQ43">
+        <v>13.5</v>
+      </c>
+      <c r="AR43">
+        <v>24</v>
+      </c>
+      <c r="AS43">
+        <v>46</v>
+      </c>
+      <c r="AT43">
+        <v>5.5</v>
+      </c>
+      <c r="AU43">
+        <v>7.4</v>
+      </c>
+      <c r="AV43">
+        <v>18</v>
+      </c>
+      <c r="AW43">
+        <v>40</v>
+      </c>
+      <c r="AX43">
+        <v>7.6</v>
+      </c>
+      <c r="AY43">
+        <v>9.4</v>
+      </c>
+      <c r="AZ43">
+        <v>25</v>
+      </c>
+      <c r="BA43">
+        <v>44</v>
+      </c>
+      <c r="BB43">
+        <v>15.5</v>
+      </c>
+      <c r="BC43">
+        <v>20</v>
+      </c>
+      <c r="BD43">
+        <v>46</v>
+      </c>
+      <c r="BE43">
+        <v>50</v>
+      </c>
+      <c r="BF43">
+        <v>15</v>
+      </c>
+      <c r="BG43">
+        <v>48</v>
+      </c>
+      <c r="BH43">
+        <v>2.9</v>
+      </c>
+      <c r="BI43">
+        <v>2.52</v>
+      </c>
+      <c r="BJ43">
+        <v>13</v>
+      </c>
+      <c r="BK43">
+        <v>5.8</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>10</v>
+      </c>
+      <c r="BN43">
+        <v>4.2</v>
+      </c>
+      <c r="BO43">
+        <v>3.25</v>
+      </c>
+      <c r="BP43">
+        <v>14</v>
+      </c>
+      <c r="BQ43">
+        <v>5.9</v>
+      </c>
+      <c r="BR43">
+        <v>1000</v>
+      </c>
+      <c r="BS43">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT43">
+        <v>10.5</v>
+      </c>
+      <c r="BU43">
+        <v>5.2</v>
+      </c>
+      <c r="BV43">
+        <v>1000</v>
+      </c>
+      <c r="BW43">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX43">
+        <v>1000</v>
+      </c>
+      <c r="BY43">
+        <v>9.4</v>
+      </c>
+      <c r="BZ43">
+        <v>1000</v>
+      </c>
+      <c r="CA43">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:80">
+      <c r="A44" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44">
+        <v>2.66</v>
+      </c>
+      <c r="G44">
+        <v>2.8</v>
+      </c>
+      <c r="H44">
+        <v>3.3</v>
+      </c>
+      <c r="I44">
+        <v>3.55</v>
+      </c>
+      <c r="J44">
+        <v>2.88</v>
+      </c>
+      <c r="K44">
+        <v>2.96</v>
+      </c>
+      <c r="L44">
+        <v>1.01</v>
+      </c>
+      <c r="M44">
+        <v>1.16</v>
+      </c>
+      <c r="N44">
+        <v>2.34</v>
+      </c>
+      <c r="O44">
+        <v>1.68</v>
+      </c>
+      <c r="P44">
+        <v>1.43</v>
+      </c>
+      <c r="Q44">
+        <v>3.1</v>
+      </c>
+      <c r="R44">
+        <v>1.15</v>
+      </c>
+      <c r="S44">
+        <v>7</v>
+      </c>
+      <c r="T44">
+        <v>2.34</v>
+      </c>
+      <c r="U44">
+        <v>1.66</v>
+      </c>
+      <c r="V44">
+        <v>1.39</v>
+      </c>
+      <c r="W44">
+        <v>1.55</v>
+      </c>
+      <c r="X44">
+        <v>7.2</v>
+      </c>
+      <c r="Y44">
+        <v>8.6</v>
+      </c>
+      <c r="Z44">
+        <v>22</v>
+      </c>
+      <c r="AA44">
+        <v>85</v>
+      </c>
+      <c r="AB44">
+        <v>7.2</v>
+      </c>
+      <c r="AC44">
+        <v>7</v>
+      </c>
+      <c r="AD44">
+        <v>17</v>
+      </c>
+      <c r="AE44">
+        <v>75</v>
+      </c>
+      <c r="AF44">
+        <v>15.5</v>
+      </c>
+      <c r="AG44">
+        <v>14.5</v>
+      </c>
+      <c r="AH44">
+        <v>28</v>
+      </c>
+      <c r="AI44">
+        <v>1000</v>
+      </c>
+      <c r="AJ44">
+        <v>50</v>
+      </c>
+      <c r="AK44">
+        <v>48</v>
+      </c>
+      <c r="AL44">
+        <v>1000</v>
+      </c>
+      <c r="AM44">
+        <v>300</v>
+      </c>
+      <c r="AN44">
+        <v>65</v>
+      </c>
+      <c r="AO44">
+        <v>1000</v>
+      </c>
+      <c r="AP44">
+        <v>6.4</v>
+      </c>
+      <c r="AQ44">
+        <v>7.6</v>
+      </c>
+      <c r="AR44">
+        <v>18</v>
+      </c>
+      <c r="AS44">
+        <v>32</v>
+      </c>
+      <c r="AT44">
+        <v>6.4</v>
+      </c>
+      <c r="AU44">
+        <v>6.2</v>
+      </c>
+      <c r="AV44">
+        <v>14.5</v>
+      </c>
+      <c r="AW44">
+        <v>30</v>
+      </c>
+      <c r="AX44">
+        <v>13.5</v>
+      </c>
+      <c r="AY44">
+        <v>12.5</v>
+      </c>
+      <c r="AZ44">
+        <v>19.5</v>
+      </c>
+      <c r="BA44">
+        <v>40</v>
+      </c>
+      <c r="BB44">
+        <v>40</v>
+      </c>
+      <c r="BC44">
+        <v>25</v>
+      </c>
+      <c r="BD44">
+        <v>38</v>
+      </c>
+      <c r="BE44">
+        <v>50</v>
+      </c>
+      <c r="BF44">
+        <v>42</v>
+      </c>
+      <c r="BG44">
+        <v>36</v>
+      </c>
+      <c r="BH44">
+        <v>2.56</v>
+      </c>
+      <c r="BI44">
+        <v>2.08</v>
+      </c>
+      <c r="BJ44">
+        <v>12.5</v>
+      </c>
+      <c r="BK44">
+        <v>6</v>
+      </c>
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
+        <v>11</v>
+      </c>
+      <c r="BN44">
+        <v>5.6</v>
+      </c>
+      <c r="BO44">
+        <v>4.1</v>
+      </c>
+      <c r="BP44">
+        <v>28</v>
+      </c>
+      <c r="BQ44">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR44">
+        <v>60</v>
+      </c>
+      <c r="BS44">
+        <v>9.6</v>
+      </c>
+      <c r="BT44">
+        <v>6.6</v>
+      </c>
+      <c r="BU44">
+        <v>4.7</v>
+      </c>
+      <c r="BV44">
+        <v>36</v>
+      </c>
+      <c r="BW44">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX44">
+        <v>1000</v>
+      </c>
+      <c r="BY44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ44">
+        <v>70</v>
+      </c>
+      <c r="CA44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:80">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45">
+        <v>1.11</v>
+      </c>
+      <c r="G45">
         <v>990</v>
       </c>
-      <c r="H43">
-        <v>1.04</v>
-      </c>
-      <c r="I43">
+      <c r="H45">
+        <v>1.11</v>
+      </c>
+      <c r="I45">
         <v>990</v>
       </c>
-      <c r="J43">
-        <v>1.16</v>
-      </c>
-      <c r="K43">
+      <c r="J45">
+        <v>1.22</v>
+      </c>
+      <c r="K45">
         <v>950</v>
       </c>
-      <c r="L43">
-        <v>1.01</v>
-      </c>
-      <c r="M43">
-        <v>1.01</v>
-      </c>
-      <c r="N43">
-        <v>1.25</v>
-      </c>
-      <c r="O43">
+      <c r="L45">
+        <v>1.01</v>
+      </c>
+      <c r="M45">
+        <v>1.01</v>
+      </c>
+      <c r="N45">
+        <v>1.26</v>
+      </c>
+      <c r="O45">
         <v>1.02</v>
       </c>
-      <c r="P43">
-        <v>1.25</v>
-      </c>
-      <c r="Q43">
+      <c r="P45">
+        <v>1.26</v>
+      </c>
+      <c r="Q45">
         <v>1.42</v>
       </c>
-      <c r="R43">
-        <v>1.14</v>
-      </c>
-      <c r="S43">
+      <c r="R45">
+        <v>1.15</v>
+      </c>
+      <c r="S45">
         <v>1.41</v>
       </c>
-      <c r="T43">
+      <c r="T45">
         <v>1.11</v>
       </c>
-      <c r="U43">
+      <c r="U45">
         <v>1.11</v>
       </c>
-      <c r="V43">
-        <v>1.01</v>
-      </c>
-      <c r="W43">
-        <v>1.01</v>
-      </c>
-      <c r="X43">
-        <v>1000</v>
-      </c>
-      <c r="Y43">
-        <v>1000</v>
-      </c>
-      <c r="Z43">
-        <v>1000</v>
-      </c>
-      <c r="AA43">
-        <v>1000</v>
-      </c>
-      <c r="AB43">
-        <v>1000</v>
-      </c>
-      <c r="AC43">
-        <v>1000</v>
-      </c>
-      <c r="AD43">
-        <v>1000</v>
-      </c>
-      <c r="AE43">
-        <v>1000</v>
-      </c>
-      <c r="AF43">
-        <v>1000</v>
-      </c>
-      <c r="AG43">
-        <v>1000</v>
-      </c>
-      <c r="AH43">
-        <v>1000</v>
-      </c>
-      <c r="AI43">
-        <v>1000</v>
-      </c>
-      <c r="AJ43">
-        <v>1000</v>
-      </c>
-      <c r="AK43">
-        <v>1000</v>
-      </c>
-      <c r="AL43">
-        <v>1000</v>
-      </c>
-      <c r="AM43">
-        <v>1000</v>
-      </c>
-      <c r="AN43">
-        <v>1000</v>
-      </c>
-      <c r="AO43">
-        <v>1000</v>
-      </c>
-      <c r="AP43">
-        <v>1.01</v>
-      </c>
-      <c r="AQ43">
-        <v>1.01</v>
-      </c>
-      <c r="AR43">
-        <v>1.01</v>
-      </c>
-      <c r="AS43">
-        <v>1.01</v>
-      </c>
-      <c r="AT43">
-        <v>1.01</v>
-      </c>
-      <c r="AU43">
-        <v>1.01</v>
-      </c>
-      <c r="AV43">
-        <v>1.01</v>
-      </c>
-      <c r="AW43">
-        <v>1.01</v>
-      </c>
-      <c r="AX43">
-        <v>1.01</v>
-      </c>
-      <c r="AY43">
-        <v>1.01</v>
-      </c>
-      <c r="AZ43">
-        <v>1.01</v>
-      </c>
-      <c r="BA43">
-        <v>1.01</v>
-      </c>
-      <c r="BB43">
-        <v>1.01</v>
-      </c>
-      <c r="BC43">
-        <v>1.01</v>
-      </c>
-      <c r="BD43">
-        <v>1.01</v>
-      </c>
-      <c r="BE43">
-        <v>1.01</v>
-      </c>
-      <c r="BF43">
-        <v>1.01</v>
-      </c>
-      <c r="BG43">
-        <v>1.01</v>
-      </c>
-      <c r="BH43">
-        <v>1000</v>
-      </c>
-      <c r="BI43">
-        <v>1.04</v>
-      </c>
-      <c r="BJ43">
-        <v>1000</v>
-      </c>
-      <c r="BK43">
-        <v>1.04</v>
-      </c>
-      <c r="BL43">
-        <v>1000</v>
-      </c>
-      <c r="BM43">
-        <v>1.04</v>
-      </c>
-      <c r="BN43">
-        <v>1000</v>
-      </c>
-      <c r="BO43">
-        <v>1.04</v>
-      </c>
-      <c r="BP43">
-        <v>1000</v>
-      </c>
-      <c r="BQ43">
-        <v>1.04</v>
-      </c>
-      <c r="BR43">
-        <v>1000</v>
-      </c>
-      <c r="BS43">
-        <v>1.04</v>
-      </c>
-      <c r="BT43">
-        <v>1000</v>
-      </c>
-      <c r="BU43">
-        <v>1.04</v>
-      </c>
-      <c r="BV43">
-        <v>1000</v>
-      </c>
-      <c r="BW43">
-        <v>1.04</v>
-      </c>
-      <c r="BX43">
-        <v>1000</v>
-      </c>
-      <c r="BY43">
-        <v>1.04</v>
-      </c>
-      <c r="BZ43">
-        <v>1000</v>
-      </c>
-      <c r="CA43">
-        <v>1.04</v>
-      </c>
-      <c r="CB43" t="s">
-        <v>214</v>
+      <c r="V45">
+        <v>1.02</v>
+      </c>
+      <c r="W45">
+        <v>1.02</v>
+      </c>
+      <c r="X45">
+        <v>1000</v>
+      </c>
+      <c r="Y45">
+        <v>1000</v>
+      </c>
+      <c r="Z45">
+        <v>1000</v>
+      </c>
+      <c r="AA45">
+        <v>1000</v>
+      </c>
+      <c r="AB45">
+        <v>1000</v>
+      </c>
+      <c r="AC45">
+        <v>1000</v>
+      </c>
+      <c r="AD45">
+        <v>1000</v>
+      </c>
+      <c r="AE45">
+        <v>1000</v>
+      </c>
+      <c r="AF45">
+        <v>1000</v>
+      </c>
+      <c r="AG45">
+        <v>1000</v>
+      </c>
+      <c r="AH45">
+        <v>1000</v>
+      </c>
+      <c r="AI45">
+        <v>1000</v>
+      </c>
+      <c r="AJ45">
+        <v>1000</v>
+      </c>
+      <c r="AK45">
+        <v>1000</v>
+      </c>
+      <c r="AL45">
+        <v>1000</v>
+      </c>
+      <c r="AM45">
+        <v>1000</v>
+      </c>
+      <c r="AN45">
+        <v>1000</v>
+      </c>
+      <c r="AO45">
+        <v>1000</v>
+      </c>
+      <c r="AP45">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45">
+        <v>1.01</v>
+      </c>
+      <c r="AR45">
+        <v>1.01</v>
+      </c>
+      <c r="AS45">
+        <v>1.01</v>
+      </c>
+      <c r="AT45">
+        <v>1.01</v>
+      </c>
+      <c r="AU45">
+        <v>1.01</v>
+      </c>
+      <c r="AV45">
+        <v>1.01</v>
+      </c>
+      <c r="AW45">
+        <v>1.01</v>
+      </c>
+      <c r="AX45">
+        <v>1.01</v>
+      </c>
+      <c r="AY45">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45">
+        <v>1.01</v>
+      </c>
+      <c r="BA45">
+        <v>1.01</v>
+      </c>
+      <c r="BB45">
+        <v>1.01</v>
+      </c>
+      <c r="BC45">
+        <v>1.01</v>
+      </c>
+      <c r="BD45">
+        <v>1.01</v>
+      </c>
+      <c r="BE45">
+        <v>1.01</v>
+      </c>
+      <c r="BF45">
+        <v>1.01</v>
+      </c>
+      <c r="BG45">
+        <v>1.01</v>
+      </c>
+      <c r="BH45">
+        <v>1000</v>
+      </c>
+      <c r="BI45">
+        <v>1.04</v>
+      </c>
+      <c r="BJ45">
+        <v>1000</v>
+      </c>
+      <c r="BK45">
+        <v>1.04</v>
+      </c>
+      <c r="BL45">
+        <v>1000</v>
+      </c>
+      <c r="BM45">
+        <v>1.04</v>
+      </c>
+      <c r="BN45">
+        <v>1000</v>
+      </c>
+      <c r="BO45">
+        <v>1.04</v>
+      </c>
+      <c r="BP45">
+        <v>1000</v>
+      </c>
+      <c r="BQ45">
+        <v>1.04</v>
+      </c>
+      <c r="BR45">
+        <v>1000</v>
+      </c>
+      <c r="BS45">
+        <v>1.04</v>
+      </c>
+      <c r="BT45">
+        <v>1000</v>
+      </c>
+      <c r="BU45">
+        <v>1.04</v>
+      </c>
+      <c r="BV45">
+        <v>1000</v>
+      </c>
+      <c r="BW45">
+        <v>1.04</v>
+      </c>
+      <c r="BX45">
+        <v>1000</v>
+      </c>
+      <c r="BY45">
+        <v>1.04</v>
+      </c>
+      <c r="BZ45">
+        <v>1000</v>
+      </c>
+      <c r="CA45">
+        <v>1.04</v>
+      </c>
+      <c r="CB45" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -733,7 +733,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-02 14:21:57</t>
+    <t>2026-08-02 16:32:47</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1333,7 @@
         <v>2.26</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
         <v>4.5</v>
@@ -1360,7 +1360,7 @@
         <v>1.48</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
         <v>1.17</v>
@@ -1372,7 +1372,7 @@
         <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
         <v>1.29</v>
@@ -1387,13 +1387,13 @@
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA2">
         <v>120</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
@@ -1405,7 +1405,7 @@
         <v>95</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1414,7 +1414,7 @@
         <v>29</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>30</v>
@@ -1444,13 +1444,13 @@
         <v>25</v>
       </c>
       <c r="AS2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT2">
         <v>6</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>18</v>
@@ -1468,10 +1468,10 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
         <v>30</v>
@@ -1480,13 +1480,13 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH2">
         <v>2.54</v>
@@ -1569,7 +1569,7 @@
         <v>190</v>
       </c>
       <c r="F3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G3">
         <v>4.1</v>
@@ -1593,16 +1593,16 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
         <v>1.28</v>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
         <v>14</v>
@@ -1641,10 +1641,10 @@
         <v>8</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF3">
         <v>28</v>
@@ -1665,7 +1665,7 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM3">
         <v>150</v>
@@ -1686,7 +1686,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1722,10 +1722,10 @@
         <v>44</v>
       </c>
       <c r="BE3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG3">
         <v>16.5</v>
@@ -1734,7 +1734,7 @@
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1749,10 +1749,10 @@
         <v>9.6</v>
       </c>
       <c r="BN3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>36</v>
@@ -1770,10 +1770,10 @@
         <v>5.1</v>
       </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW3">
         <v>6.4</v>
@@ -1785,10 +1785,10 @@
         <v>8</v>
       </c>
       <c r="BZ3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>239</v>
@@ -1811,22 +1811,22 @@
         <v>191</v>
       </c>
       <c r="F4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
         <v>2.28</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.46</v>
@@ -1838,13 +1838,13 @@
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1877,7 +1877,7 @@
         <v>80</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1892,16 +1892,16 @@
         <v>14</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
         <v>65</v>
       </c>
       <c r="AJ4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1937,7 +1937,7 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW4">
         <v>34</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="BB4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4">
         <v>23</v>
@@ -1982,13 +1982,13 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
         <v>5.1</v>
@@ -1997,19 +1997,19 @@
         <v>3.95</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
         <v>5.5</v>
@@ -2018,19 +2018,19 @@
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="s">
         <v>239</v>
@@ -2059,10 +2059,10 @@
         <v>1.56</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>4.9</v>
@@ -2080,28 +2080,28 @@
         <v>6.2</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
         <v>2.74</v>
       </c>
       <c r="Q5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R5">
         <v>1.71</v>
       </c>
       <c r="S5">
+        <v>2.34</v>
+      </c>
+      <c r="T5">
+        <v>1.68</v>
+      </c>
+      <c r="U5">
         <v>2.36</v>
       </c>
-      <c r="T5">
-        <v>1.67</v>
-      </c>
-      <c r="U5">
-        <v>2.38</v>
-      </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
         <v>2.78</v>
@@ -2122,7 +2122,7 @@
         <v>13</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD5">
         <v>24</v>
@@ -2137,7 +2137,7 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -2149,10 +2149,10 @@
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN5">
         <v>5.6</v>
@@ -2161,7 +2161,7 @@
         <v>60</v>
       </c>
       <c r="AP5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ5">
         <v>27</v>
@@ -2170,7 +2170,7 @@
         <v>50</v>
       </c>
       <c r="AS5">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2179,7 +2179,7 @@
         <v>10.5</v>
       </c>
       <c r="AV5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW5">
         <v>60</v>
@@ -2197,25 +2197,25 @@
         <v>50</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC5">
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE5">
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI5">
         <v>3.7</v>
@@ -2224,55 +2224,55 @@
         <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR5">
         <v>19.5</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV5">
         <v>44</v>
       </c>
       <c r="BW5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5">
         <v>12</v>
       </c>
       <c r="CA5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>239</v>
@@ -2295,25 +2295,25 @@
         <v>193</v>
       </c>
       <c r="F6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G6">
         <v>1.35</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
         <v>1.02</v>
@@ -2325,19 +2325,19 @@
         <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
         <v>1.73</v>
@@ -2346,16 +2346,16 @@
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2364,25 +2364,25 @@
         <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE6">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AF6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI6">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ6">
         <v>12</v>
@@ -2391,70 +2391,70 @@
         <v>16</v>
       </c>
       <c r="AL6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM6">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN6">
         <v>5</v>
       </c>
       <c r="AO6">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AP6">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR6">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT6">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AU6">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AW6">
+        <v>5.8</v>
+      </c>
+      <c r="AX6">
+        <v>6.2</v>
+      </c>
+      <c r="AY6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6">
         <v>5.1</v>
       </c>
-      <c r="AX6">
-        <v>3.4</v>
-      </c>
-      <c r="AY6">
+      <c r="BA6">
+        <v>5.7</v>
+      </c>
+      <c r="BB6">
+        <v>7.4</v>
+      </c>
+      <c r="BC6">
+        <v>11.5</v>
+      </c>
+      <c r="BD6">
+        <v>29</v>
+      </c>
+      <c r="BE6">
+        <v>5.7</v>
+      </c>
+      <c r="BF6">
         <v>3.75</v>
       </c>
-      <c r="AZ6">
-        <v>4.5</v>
-      </c>
-      <c r="BA6">
-        <v>5.1</v>
-      </c>
-      <c r="BB6">
-        <v>3.65</v>
-      </c>
-      <c r="BC6">
-        <v>3.95</v>
-      </c>
-      <c r="BD6">
-        <v>4.7</v>
-      </c>
-      <c r="BE6">
-        <v>5.1</v>
-      </c>
-      <c r="BF6">
-        <v>2.56</v>
-      </c>
       <c r="BG6">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2540,7 +2540,7 @@
         <v>3.35</v>
       </c>
       <c r="G7">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H7">
         <v>2.16</v>
@@ -2555,7 +2555,7 @@
         <v>3.65</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2564,7 +2564,7 @@
         <v>2.84</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P7">
         <v>1.63</v>
@@ -2576,19 +2576,19 @@
         <v>1.23</v>
       </c>
       <c r="S7">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U7">
         <v>1.86</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2615,7 +2615,7 @@
         <v>32</v>
       </c>
       <c r="AF7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG7">
         <v>17</v>
@@ -2624,7 +2624,7 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
         <v>100</v>
@@ -2642,121 +2642,121 @@
         <v>85</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7">
+        <v>5.4</v>
+      </c>
+      <c r="AR7">
+        <v>4.6</v>
+      </c>
+      <c r="AS7">
+        <v>5.6</v>
+      </c>
+      <c r="AT7">
+        <v>4.3</v>
+      </c>
+      <c r="AU7">
         <v>3.6</v>
       </c>
-      <c r="AR7">
-        <v>4.4</v>
-      </c>
-      <c r="AS7">
+      <c r="AV7">
+        <v>4.3</v>
+      </c>
+      <c r="AW7">
+        <v>5.5</v>
+      </c>
+      <c r="AX7">
         <v>5.3</v>
       </c>
-      <c r="AT7">
-        <v>4.1</v>
-      </c>
-      <c r="AU7">
-        <v>3.5</v>
-      </c>
-      <c r="AV7">
-        <v>4.1</v>
-      </c>
-      <c r="AW7">
-        <v>5.2</v>
-      </c>
-      <c r="AX7">
-        <v>5.2</v>
-      </c>
       <c r="AY7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ7">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA7">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC7">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE7">
+        <v>6.4</v>
+      </c>
+      <c r="BF7">
         <v>6</v>
       </c>
-      <c r="BF7">
-        <v>5.8</v>
-      </c>
       <c r="BG7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH7">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>1.54</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="BN7">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ7">
-        <v>7.4</v>
+        <v>1.66</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>1.68</v>
       </c>
       <c r="BT7">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>3.35</v>
+        <v>1.38</v>
       </c>
       <c r="BV7">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="BW7">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>1.67</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>1.67</v>
       </c>
       <c r="CB7" t="s">
         <v>239</v>
@@ -2779,7 +2779,7 @@
         <v>195</v>
       </c>
       <c r="F8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>2.2</v>
@@ -2791,7 +2791,7 @@
         <v>3.4</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -2944,7 +2944,7 @@
         <v>6.2</v>
       </c>
       <c r="BI8">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BJ8">
         <v>8.199999999999999</v>
@@ -3051,7 +3051,7 @@
         <v>1.14</v>
       </c>
       <c r="P9">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q9">
         <v>1.43</v>
@@ -3060,7 +3060,7 @@
         <v>1.87</v>
       </c>
       <c r="S9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T9">
         <v>1.83</v>
@@ -3075,7 +3075,7 @@
         <v>3.9</v>
       </c>
       <c r="X9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y9">
         <v>950</v>
@@ -3087,7 +3087,7 @@
         <v>440</v>
       </c>
       <c r="AB9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>16.5</v>
@@ -3129,16 +3129,16 @@
         <v>180</v>
       </c>
       <c r="AP9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT9">
         <v>9.4</v>
@@ -3147,10 +3147,10 @@
         <v>11.5</v>
       </c>
       <c r="AV9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9">
         <v>7.6</v>
@@ -3162,7 +3162,7 @@
         <v>19.5</v>
       </c>
       <c r="BA9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB9">
         <v>8.199999999999999</v>
@@ -3171,16 +3171,16 @@
         <v>10</v>
       </c>
       <c r="BD9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
@@ -3192,13 +3192,13 @@
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9">
         <v>4.3</v>
@@ -3216,10 +3216,10 @@
         <v>20</v>
       </c>
       <c r="BS9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU9">
         <v>6</v>
@@ -3228,19 +3228,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>9</v>
       </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="s">
         <v>239</v>
@@ -3308,13 +3308,13 @@
         <v>1.71</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
         <v>1.22</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X10">
         <v>22</v>
@@ -3440,7 +3440,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10">
         <v>4.8</v>
@@ -3452,16 +3452,16 @@
         <v>12.5</v>
       </c>
       <c r="BQ10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR10">
         <v>25</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU10">
         <v>4.6</v>
@@ -3470,13 +3470,13 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10">
         <v>19</v>
@@ -3505,58 +3505,58 @@
         <v>198</v>
       </c>
       <c r="F11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M11">
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P11">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="S11">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T11">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U11">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X11">
         <v>42</v>
@@ -3583,7 +3583,7 @@
         <v>510</v>
       </c>
       <c r="AF11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG11">
         <v>16</v>
@@ -3616,10 +3616,10 @@
         <v>5.6</v>
       </c>
       <c r="AQ11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS11">
         <v>6.4</v>
@@ -3634,7 +3634,7 @@
         <v>6</v>
       </c>
       <c r="AW11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX11">
         <v>6.2</v>
@@ -3643,10 +3643,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB11">
         <v>6.2</v>
@@ -3655,13 +3655,13 @@
         <v>10.5</v>
       </c>
       <c r="BD11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="BG11">
         <v>6.4</v>
@@ -3750,52 +3750,52 @@
         <v>3.15</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
         <v>2.12</v>
       </c>
       <c r="I12">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M12">
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R12">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S12">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="T12">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W12">
         <v>1.4</v>
@@ -3804,7 +3804,7 @@
         <v>29</v>
       </c>
       <c r="Y12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z12">
         <v>22</v>
@@ -3813,7 +3813,7 @@
         <v>36</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC12">
         <v>12</v>
@@ -3822,16 +3822,16 @@
         <v>12</v>
       </c>
       <c r="AE12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF12">
         <v>36</v>
       </c>
       <c r="AG12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH12">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
         <v>36</v>
@@ -3843,7 +3843,7 @@
         <v>42</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM12">
         <v>70</v>
@@ -3870,7 +3870,7 @@
         <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>8.4</v>
@@ -3891,28 +3891,28 @@
         <v>20</v>
       </c>
       <c r="BB12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD12">
         <v>29</v>
       </c>
       <c r="BE12">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF12">
         <v>16</v>
       </c>
       <c r="BG12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
@@ -3924,13 +3924,13 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN12">
         <v>7</v>
       </c>
       <c r="BO12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP12">
         <v>34</v>
@@ -3939,10 +3939,10 @@
         <v>9</v>
       </c>
       <c r="BR12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
         <v>5.5</v>
@@ -3954,7 +3954,7 @@
         <v>14.5</v>
       </c>
       <c r="BW12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX12">
         <v>34</v>
@@ -3966,7 +3966,7 @@
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="s">
         <v>239</v>
@@ -3989,7 +3989,7 @@
         <v>200</v>
       </c>
       <c r="F13">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G13">
         <v>2.02</v>
@@ -4001,13 +4001,13 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -4040,7 +4040,7 @@
         <v>1.25</v>
       </c>
       <c r="W13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X13">
         <v>14.5</v>
@@ -4151,64 +4151,64 @@
         <v>5.2</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB13" t="s">
         <v>239</v>
@@ -4231,25 +4231,25 @@
         <v>201</v>
       </c>
       <c r="F14">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="G14">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="H14">
+        <v>1.92</v>
+      </c>
+      <c r="I14">
         <v>2.08</v>
-      </c>
-      <c r="I14">
-        <v>2.28</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M14">
         <v>1.07</v>
@@ -4264,37 +4264,37 @@
         <v>1.86</v>
       </c>
       <c r="Q14">
+        <v>1.96</v>
+      </c>
+      <c r="R14">
+        <v>1.33</v>
+      </c>
+      <c r="S14">
+        <v>3.5</v>
+      </c>
+      <c r="T14">
+        <v>1.81</v>
+      </c>
+      <c r="U14">
         <v>2</v>
       </c>
-      <c r="R14">
-        <v>1.32</v>
-      </c>
-      <c r="S14">
-        <v>3.55</v>
-      </c>
-      <c r="T14">
-        <v>1.78</v>
-      </c>
-      <c r="U14">
-        <v>2.06</v>
-      </c>
       <c r="V14">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="W14">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="X14">
         <v>16</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AB14">
         <v>16.5</v>
@@ -4303,10 +4303,10 @@
         <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF14">
         <v>34</v>
@@ -4321,7 +4321,7 @@
         <v>46</v>
       </c>
       <c r="AJ14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AK14">
         <v>60</v>
@@ -4333,10 +4333,10 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AO14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP14">
         <v>11.5</v>
@@ -4345,25 +4345,25 @@
         <v>7</v>
       </c>
       <c r="AR14">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AS14">
-        <v>3.95</v>
+        <v>18</v>
       </c>
       <c r="AT14">
         <v>11.5</v>
       </c>
       <c r="AU14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
         <v>8</v>
       </c>
       <c r="AW14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX14">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AY14">
         <v>13</v>
@@ -4372,79 +4372,79 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB14">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC14">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD14">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE14">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF14">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG14">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI14">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BQ14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BS14">
         <v>8.6</v>
       </c>
       <c r="BT14">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BU14">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BV14">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4473,166 +4473,166 @@
         <v>202</v>
       </c>
       <c r="F15">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="G15">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="H15">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
         <v>4.3</v>
       </c>
       <c r="K15">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P15">
         <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W15">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH15">
         <v>4.5</v>
@@ -4644,55 +4644,55 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="CB15" t="s">
         <v>239</v>
@@ -4715,10 +4715,10 @@
         <v>203</v>
       </c>
       <c r="F16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H16">
         <v>2.04</v>
@@ -4730,13 +4730,13 @@
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.25</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>5.8</v>
@@ -4748,25 +4748,25 @@
         <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R16">
         <v>1.66</v>
       </c>
       <c r="S16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U16">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V16">
         <v>1.92</v>
       </c>
       <c r="W16">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X16">
         <v>30</v>
@@ -4775,55 +4775,55 @@
         <v>15</v>
       </c>
       <c r="Z16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA16">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AB16">
         <v>21</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE16">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AF16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH16">
         <v>16</v>
       </c>
       <c r="AI16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AJ16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
         <v>38</v>
       </c>
       <c r="AL16">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>520</v>
       </c>
       <c r="AN16">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AO16">
         <v>9.4</v>
       </c>
       <c r="AP16">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AQ16">
         <v>13</v>
@@ -4832,10 +4832,10 @@
         <v>14.5</v>
       </c>
       <c r="AS16">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AT16">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4847,52 +4847,52 @@
         <v>16.5</v>
       </c>
       <c r="AX16">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="AY16">
         <v>13.5</v>
       </c>
       <c r="AZ16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BA16">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB16">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BC16">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD16">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BE16">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BF16">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH16">
         <v>4.4</v>
       </c>
       <c r="BI16">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN16">
         <v>7.2</v>
@@ -4904,13 +4904,13 @@
         <v>25</v>
       </c>
       <c r="BQ16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16">
         <v>5.3</v>
@@ -4922,19 +4922,19 @@
         <v>13.5</v>
       </c>
       <c r="BW16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX16">
         <v>22</v>
       </c>
       <c r="BY16">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB16" t="s">
         <v>239</v>
@@ -4957,7 +4957,7 @@
         <v>204</v>
       </c>
       <c r="F17">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G17">
         <v>3.2</v>
@@ -5008,7 +5008,7 @@
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X17">
         <v>22</v>
@@ -5050,7 +5050,7 @@
         <v>55</v>
       </c>
       <c r="AK17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL17">
         <v>46</v>
@@ -5080,7 +5080,7 @@
         <v>11.5</v>
       </c>
       <c r="AU17">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV17">
         <v>8.800000000000001</v>
@@ -5110,7 +5110,7 @@
         <v>4.1</v>
       </c>
       <c r="BE17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF17">
         <v>19.5</v>
@@ -5202,7 +5202,7 @@
         <v>2.46</v>
       </c>
       <c r="G18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H18">
         <v>2.92</v>
@@ -5250,7 +5250,7 @@
         <v>1.45</v>
       </c>
       <c r="W18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X18">
         <v>17.5</v>
@@ -5465,10 +5465,10 @@
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P19">
         <v>2.22</v>
@@ -5477,10 +5477,10 @@
         <v>1.69</v>
       </c>
       <c r="R19">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
         <v>1.91</v>
@@ -5495,112 +5495,112 @@
         <v>3</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5689,13 +5689,13 @@
         <v>1.74</v>
       </c>
       <c r="H20">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
         <v>4.3</v>
@@ -5707,7 +5707,7 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
         <v>1.33</v>
@@ -5731,7 +5731,7 @@
         <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W20">
         <v>2.36</v>
@@ -5746,7 +5746,7 @@
         <v>60</v>
       </c>
       <c r="AA20">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB20">
         <v>9.4</v>
@@ -5788,7 +5788,7 @@
         <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP20">
         <v>10.5</v>
@@ -5836,7 +5836,7 @@
         <v>4</v>
       </c>
       <c r="BE20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF20">
         <v>9.800000000000001</v>
@@ -5928,7 +5928,7 @@
         <v>1.66</v>
       </c>
       <c r="G21">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H21">
         <v>4.9</v>
@@ -5937,7 +5937,7 @@
         <v>5.9</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>4.7</v>
@@ -5958,13 +5958,13 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R21">
         <v>1.48</v>
       </c>
       <c r="S21">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T21">
         <v>1.72</v>
@@ -5973,7 +5973,7 @@
         <v>2.16</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
         <v>2.26</v>
@@ -6057,7 +6057,7 @@
         <v>4</v>
       </c>
       <c r="AX21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
@@ -6081,7 +6081,7 @@
         <v>4</v>
       </c>
       <c r="BF21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG21">
         <v>4</v>
@@ -6173,19 +6173,19 @@
         <v>3.65</v>
       </c>
       <c r="H22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I22">
         <v>2.5</v>
       </c>
       <c r="J22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K22">
         <v>3.45</v>
       </c>
       <c r="L22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -6200,7 +6200,7 @@
         <v>1.84</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R22">
         <v>1.32</v>
@@ -6218,7 +6218,7 @@
         <v>1.66</v>
       </c>
       <c r="W22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X22">
         <v>16</v>
@@ -6275,37 +6275,37 @@
         <v>25</v>
       </c>
       <c r="AP22">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AQ22">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR22">
-        <v>3.55</v>
+        <v>13</v>
       </c>
       <c r="AS22">
         <v>3.95</v>
       </c>
       <c r="AT22">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU22">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW22">
         <v>3.85</v>
       </c>
       <c r="AX22">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AY22">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AZ22">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="BA22">
         <v>4</v>
@@ -6326,7 +6326,7 @@
         <v>4</v>
       </c>
       <c r="BG22">
-        <v>3.75</v>
+        <v>18.5</v>
       </c>
       <c r="BH22">
         <v>3.35</v>
@@ -6409,19 +6409,19 @@
         <v>210</v>
       </c>
       <c r="F23">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G23">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K23">
         <v>4.7</v>
@@ -6433,67 +6433,67 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P23">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R23">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S23">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T23">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W23">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="X23">
         <v>29</v>
       </c>
       <c r="Y23">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z23">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA23">
         <v>75</v>
       </c>
       <c r="AB23">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE23">
         <v>44</v>
       </c>
       <c r="AF23">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH23">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI23">
         <v>46</v>
@@ -6502,7 +6502,7 @@
         <v>27</v>
       </c>
       <c r="AK23">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL23">
         <v>32</v>
@@ -6511,61 +6511,61 @@
         <v>70</v>
       </c>
       <c r="AN23">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AP23">
+        <v>6.6</v>
+      </c>
+      <c r="AQ23">
+        <v>6.4</v>
+      </c>
+      <c r="AR23">
+        <v>21</v>
+      </c>
+      <c r="AS23">
+        <v>7.8</v>
+      </c>
+      <c r="AT23">
+        <v>5.4</v>
+      </c>
+      <c r="AU23">
         <v>4.8</v>
       </c>
-      <c r="AQ23">
-        <v>4.6</v>
-      </c>
-      <c r="AR23">
+      <c r="AV23">
+        <v>5.8</v>
+      </c>
+      <c r="AW23">
+        <v>7.2</v>
+      </c>
+      <c r="AX23">
+        <v>12.5</v>
+      </c>
+      <c r="AY23">
         <v>4.9</v>
       </c>
-      <c r="AS23">
-        <v>5.3</v>
-      </c>
-      <c r="AT23">
-        <v>4.2</v>
-      </c>
-      <c r="AU23">
-        <v>3.85</v>
-      </c>
-      <c r="AV23">
-        <v>4.3</v>
-      </c>
-      <c r="AW23">
-        <v>5.1</v>
-      </c>
-      <c r="AX23">
-        <v>4.3</v>
-      </c>
-      <c r="AY23">
-        <v>3.95</v>
-      </c>
       <c r="AZ23">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA23">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB23">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="BC23">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD23">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF23">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG23">
         <v>20</v>
@@ -6574,7 +6574,7 @@
         <v>4.6</v>
       </c>
       <c r="BI23">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BJ23">
         <v>9.199999999999999</v>
@@ -6592,31 +6592,31 @@
         <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR23">
         <v>22</v>
       </c>
       <c r="BS23">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT23">
         <v>8</v>
       </c>
       <c r="BU23">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX23">
         <v>34</v>
@@ -6657,7 +6657,7 @@
         <v>8.6</v>
       </c>
       <c r="H24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I24">
         <v>1.42</v>
@@ -6669,13 +6669,13 @@
         <v>5.9</v>
       </c>
       <c r="L24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M24">
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O24">
         <v>1.16</v>
@@ -6690,13 +6690,13 @@
         <v>1.76</v>
       </c>
       <c r="S24">
+        <v>2.22</v>
+      </c>
+      <c r="T24">
+        <v>1.75</v>
+      </c>
+      <c r="U24">
         <v>2.24</v>
-      </c>
-      <c r="T24">
-        <v>1.74</v>
-      </c>
-      <c r="U24">
-        <v>2.26</v>
       </c>
       <c r="V24">
         <v>3.35</v>
@@ -6705,7 +6705,7 @@
         <v>1.13</v>
       </c>
       <c r="X24">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y24">
         <v>13</v>
@@ -6729,7 +6729,7 @@
         <v>13.5</v>
       </c>
       <c r="AF24">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
         <v>30</v>
@@ -6738,7 +6738,7 @@
         <v>23</v>
       </c>
       <c r="AI24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ24">
         <v>270</v>
@@ -6747,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="AL24">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
         <v>100</v>
@@ -6759,13 +6759,13 @@
         <v>4.6</v>
       </c>
       <c r="AP24">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS24">
         <v>11.5</v>
@@ -6795,7 +6795,7 @@
         <v>23</v>
       </c>
       <c r="BB24">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BC24">
         <v>38</v>
@@ -6810,7 +6810,7 @@
         <v>65</v>
       </c>
       <c r="BG24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH24">
         <v>4.9</v>
@@ -6834,7 +6834,7 @@
         <v>12</v>
       </c>
       <c r="BO24">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BP24">
         <v>60</v>
@@ -6899,16 +6899,16 @@
         <v>1.52</v>
       </c>
       <c r="H25">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I25">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J25">
         <v>5.1</v>
       </c>
       <c r="K25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L25">
         <v>1.22</v>
@@ -6926,10 +6926,10 @@
         <v>2.84</v>
       </c>
       <c r="Q25">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R25">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S25">
         <v>2.24</v>
@@ -6938,16 +6938,16 @@
         <v>1.67</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W25">
         <v>2.92</v>
       </c>
       <c r="X25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y25">
         <v>36</v>
@@ -6956,7 +6956,7 @@
         <v>1000</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB25">
         <v>13.5</v>
@@ -6968,7 +6968,7 @@
         <v>27</v>
       </c>
       <c r="AE25">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF25">
         <v>12</v>
@@ -6980,16 +6980,16 @@
         <v>19.5</v>
       </c>
       <c r="AI25">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
         <v>15</v>
       </c>
       <c r="AK25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM25">
         <v>85</v>
@@ -7001,10 +7001,10 @@
         <v>65</v>
       </c>
       <c r="AP25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AR25">
         <v>55</v>
@@ -7013,7 +7013,7 @@
         <v>46</v>
       </c>
       <c r="AT25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU25">
         <v>11</v>
@@ -7025,28 +7025,28 @@
         <v>34</v>
       </c>
       <c r="AX25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY25">
         <v>9.4</v>
       </c>
       <c r="AZ25">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA25">
         <v>55</v>
       </c>
       <c r="BB25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC25">
         <v>12.5</v>
       </c>
       <c r="BD25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE25">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF25">
         <v>4.9</v>
@@ -7177,10 +7177,10 @@
         <v>1.75</v>
       </c>
       <c r="T26">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V26">
         <v>1.03</v>
@@ -7249,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="AR26">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS26">
         <v>8.800000000000001</v>
@@ -7270,7 +7270,7 @@
         <v>5</v>
       </c>
       <c r="AY26">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ26">
         <v>7.4</v>
@@ -7279,10 +7279,10 @@
         <v>8.4</v>
       </c>
       <c r="BB26">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC26">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD26">
         <v>7.4</v>
@@ -7318,7 +7318,7 @@
         <v>4.4</v>
       </c>
       <c r="BO26">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BP26">
         <v>6.2</v>
@@ -7383,19 +7383,19 @@
         <v>2.48</v>
       </c>
       <c r="H27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I27">
         <v>3.95</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K27">
         <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7407,7 +7407,7 @@
         <v>1.39</v>
       </c>
       <c r="P27">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q27">
         <v>2.16</v>
@@ -7619,7 +7619,7 @@
         <v>215</v>
       </c>
       <c r="F28">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G28">
         <v>2.34</v>
@@ -7631,10 +7631,10 @@
         <v>4.1</v>
       </c>
       <c r="J28">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L28">
         <v>1.39</v>
@@ -7658,7 +7658,7 @@
         <v>1.27</v>
       </c>
       <c r="S28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T28">
         <v>1.88</v>
@@ -7694,7 +7694,7 @@
         <v>18</v>
       </c>
       <c r="AE28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF28">
         <v>14.5</v>
@@ -7763,7 +7763,7 @@
         <v>7.6</v>
       </c>
       <c r="BB28">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC28">
         <v>19.5</v>
@@ -7772,7 +7772,7 @@
         <v>7.2</v>
       </c>
       <c r="BE28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28">
         <v>17.5</v>
@@ -7820,7 +7820,7 @@
         <v>7</v>
       </c>
       <c r="BU28">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7861,22 +7861,22 @@
         <v>216</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G29">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="H29">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="I29">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="J29">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7885,142 +7885,142 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>2.56</v>
       </c>
       <c r="O29">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P29">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q29">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="S29">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="T29">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="U29">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="V29">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="W29">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="X29">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8112,37 +8112,37 @@
         <v>3.45</v>
       </c>
       <c r="I30">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J30">
         <v>3.8</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R30">
         <v>1.54</v>
       </c>
       <c r="S30">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T30">
         <v>1.59</v>
@@ -8151,7 +8151,7 @@
         <v>2.54</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
         <v>1.81</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="AA30">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB30">
         <v>14</v>
@@ -8214,7 +8214,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR30">
         <v>23</v>
@@ -8265,22 +8265,22 @@
         <v>22</v>
       </c>
       <c r="BH30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI30">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BJ30">
         <v>9.199999999999999</v>
       </c>
       <c r="BK30">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN30">
         <v>5.6</v>
@@ -8292,13 +8292,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ30">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR30">
         <v>25</v>
       </c>
       <c r="BS30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT30">
         <v>7.2</v>
@@ -8310,19 +8310,19 @@
         <v>25</v>
       </c>
       <c r="BW30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX30">
         <v>32</v>
       </c>
       <c r="BY30">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA30">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB30" t="s">
         <v>239</v>
@@ -8345,22 +8345,22 @@
         <v>218</v>
       </c>
       <c r="F31">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G31">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H31">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I31">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J31">
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L31">
         <v>1.32</v>
@@ -8369,7 +8369,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O31">
         <v>1.26</v>
@@ -8390,13 +8390,13 @@
         <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X31">
         <v>19.5</v>
@@ -8405,7 +8405,7 @@
         <v>15.5</v>
       </c>
       <c r="Z31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA31">
         <v>85</v>
@@ -8423,19 +8423,19 @@
         <v>38</v>
       </c>
       <c r="AF31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG31">
         <v>12</v>
       </c>
       <c r="AH31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI31">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK31">
         <v>24</v>
@@ -8447,7 +8447,7 @@
         <v>100</v>
       </c>
       <c r="AN31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO31">
         <v>34</v>
@@ -8459,10 +8459,10 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT31">
         <v>9.6</v>
@@ -8489,13 +8489,13 @@
         <v>7.4</v>
       </c>
       <c r="BB31">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC31">
         <v>19.5</v>
       </c>
       <c r="BD31">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE31">
         <v>8</v>
@@ -8504,7 +8504,7 @@
         <v>12</v>
       </c>
       <c r="BG31">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8587,226 +8587,226 @@
         <v>219</v>
       </c>
       <c r="F32">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="G32">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="H32">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="I32">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L32">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O32">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P32">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="R32">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S32">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="T32">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V32">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W32">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="X32">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y32">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA32">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB32">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC32">
+        <v>12</v>
+      </c>
+      <c r="AD32">
+        <v>28</v>
+      </c>
+      <c r="AE32">
+        <v>80</v>
+      </c>
+      <c r="AF32">
+        <v>14</v>
+      </c>
+      <c r="AG32">
+        <v>12</v>
+      </c>
+      <c r="AH32">
+        <v>18.5</v>
+      </c>
+      <c r="AI32">
+        <v>75</v>
+      </c>
+      <c r="AJ32">
+        <v>17.5</v>
+      </c>
+      <c r="AK32">
+        <v>16.5</v>
+      </c>
+      <c r="AL32">
+        <v>29</v>
+      </c>
+      <c r="AM32">
+        <v>85</v>
+      </c>
+      <c r="AN32">
+        <v>7.2</v>
+      </c>
+      <c r="AO32">
+        <v>70</v>
+      </c>
+      <c r="AP32">
+        <v>19.5</v>
+      </c>
+      <c r="AQ32">
+        <v>5.1</v>
+      </c>
+      <c r="AR32">
+        <v>5.6</v>
+      </c>
+      <c r="AS32">
+        <v>5.9</v>
+      </c>
+      <c r="AT32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV32">
+        <v>19.5</v>
+      </c>
+      <c r="AW32">
+        <v>5.7</v>
+      </c>
+      <c r="AX32">
+        <v>10</v>
+      </c>
+      <c r="AY32">
+        <v>8</v>
+      </c>
+      <c r="AZ32">
+        <v>14.5</v>
+      </c>
+      <c r="BA32">
+        <v>5.7</v>
+      </c>
+      <c r="BB32">
+        <v>14</v>
+      </c>
+      <c r="BC32">
         <v>13</v>
       </c>
-      <c r="AD32">
-        <v>24</v>
-      </c>
-      <c r="AE32">
-        <v>65</v>
-      </c>
-      <c r="AF32">
+      <c r="BD32">
+        <v>5</v>
+      </c>
+      <c r="BE32">
+        <v>5.7</v>
+      </c>
+      <c r="BF32">
+        <v>5.9</v>
+      </c>
+      <c r="BG32">
+        <v>5.6</v>
+      </c>
+      <c r="BH32">
+        <v>4.6</v>
+      </c>
+      <c r="BI32">
+        <v>3.6</v>
+      </c>
+      <c r="BJ32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK32">
+        <v>4.8</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>8.6</v>
+      </c>
+      <c r="BN32">
+        <v>4.8</v>
+      </c>
+      <c r="BO32">
+        <v>3.95</v>
+      </c>
+      <c r="BP32">
+        <v>11</v>
+      </c>
+      <c r="BQ32">
+        <v>5</v>
+      </c>
+      <c r="BR32">
+        <v>22</v>
+      </c>
+      <c r="BS32">
+        <v>6.6</v>
+      </c>
+      <c r="BT32">
+        <v>9.6</v>
+      </c>
+      <c r="BU32">
+        <v>4.7</v>
+      </c>
+      <c r="BV32">
+        <v>42</v>
+      </c>
+      <c r="BW32">
+        <v>7.6</v>
+      </c>
+      <c r="BX32">
+        <v>44</v>
+      </c>
+      <c r="BY32">
+        <v>7.6</v>
+      </c>
+      <c r="BZ32">
         <v>14.5</v>
       </c>
-      <c r="AG32">
-        <v>12.5</v>
-      </c>
-      <c r="AH32">
-        <v>20</v>
-      </c>
-      <c r="AI32">
-        <v>60</v>
-      </c>
-      <c r="AJ32">
-        <v>20</v>
-      </c>
-      <c r="AK32">
-        <v>17</v>
-      </c>
-      <c r="AL32">
-        <v>28</v>
-      </c>
-      <c r="AM32">
-        <v>75</v>
-      </c>
-      <c r="AN32">
-        <v>6.8</v>
-      </c>
-      <c r="AO32">
-        <v>50</v>
-      </c>
-      <c r="AP32">
-        <v>4.9</v>
-      </c>
-      <c r="AQ32">
-        <v>4.9</v>
-      </c>
-      <c r="AR32">
-        <v>5.2</v>
-      </c>
-      <c r="AS32">
-        <v>5.5</v>
-      </c>
-      <c r="AT32">
-        <v>4.1</v>
-      </c>
-      <c r="AU32">
-        <v>4</v>
-      </c>
-      <c r="AV32">
-        <v>4.6</v>
-      </c>
-      <c r="AW32">
-        <v>5.3</v>
-      </c>
-      <c r="AX32">
-        <v>4.1</v>
-      </c>
-      <c r="AY32">
-        <v>3.95</v>
-      </c>
-      <c r="AZ32">
-        <v>4.5</v>
-      </c>
-      <c r="BA32">
-        <v>5.2</v>
-      </c>
-      <c r="BB32">
-        <v>4.5</v>
-      </c>
-      <c r="BC32">
-        <v>4.3</v>
-      </c>
-      <c r="BD32">
-        <v>4.8</v>
-      </c>
-      <c r="BE32">
-        <v>5.3</v>
-      </c>
-      <c r="BF32">
-        <v>3.1</v>
-      </c>
-      <c r="BG32">
-        <v>5.2</v>
-      </c>
-      <c r="BH32">
-        <v>1000</v>
-      </c>
-      <c r="BI32">
-        <v>1.04</v>
-      </c>
-      <c r="BJ32">
-        <v>1000</v>
-      </c>
-      <c r="BK32">
-        <v>1.04</v>
-      </c>
-      <c r="BL32">
-        <v>1000</v>
-      </c>
-      <c r="BM32">
-        <v>1.04</v>
-      </c>
-      <c r="BN32">
-        <v>1000</v>
-      </c>
-      <c r="BO32">
-        <v>1.04</v>
-      </c>
-      <c r="BP32">
-        <v>1000</v>
-      </c>
-      <c r="BQ32">
-        <v>1.04</v>
-      </c>
-      <c r="BR32">
-        <v>1000</v>
-      </c>
-      <c r="BS32">
-        <v>1.04</v>
-      </c>
-      <c r="BT32">
-        <v>1000</v>
-      </c>
-      <c r="BU32">
-        <v>1.04</v>
-      </c>
-      <c r="BV32">
-        <v>1000</v>
-      </c>
-      <c r="BW32">
-        <v>1.04</v>
-      </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
-        <v>1.04</v>
-      </c>
-      <c r="BZ32">
-        <v>1000</v>
-      </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB32" t="s">
         <v>239</v>
@@ -8829,13 +8829,13 @@
         <v>220</v>
       </c>
       <c r="F33">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="I33">
         <v>2.72</v>
@@ -8844,37 +8844,37 @@
         <v>2.54</v>
       </c>
       <c r="K33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M33">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N33">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="O33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P33">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q33">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S33">
         <v>1.05</v>
       </c>
       <c r="T33">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="U33">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V33">
         <v>1.58</v>
@@ -8883,166 +8883,166 @@
         <v>1.25</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y33">
+        <v>6.8</v>
+      </c>
+      <c r="Z33">
+        <v>15</v>
+      </c>
+      <c r="AA33">
+        <v>44</v>
+      </c>
+      <c r="AB33">
+        <v>11.5</v>
+      </c>
+      <c r="AC33">
         <v>7.6</v>
       </c>
-      <c r="Z33">
-        <v>1000</v>
-      </c>
-      <c r="AA33">
-        <v>1000</v>
-      </c>
-      <c r="AB33">
-        <v>1000</v>
-      </c>
-      <c r="AC33">
-        <v>8.6</v>
-      </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF33">
         <v>36</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH33">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP33">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AQ33">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="AR33">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="AS33">
-        <v>1.44</v>
+        <v>5.4</v>
       </c>
       <c r="AT33">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="AU33">
-        <v>1.23</v>
+        <v>3.4</v>
       </c>
       <c r="AV33">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="AW33">
-        <v>1.44</v>
+        <v>5.4</v>
       </c>
       <c r="AX33">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="AY33">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="AZ33">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="BA33">
-        <v>1.44</v>
+        <v>5.7</v>
       </c>
       <c r="BB33">
-        <v>1.44</v>
+        <v>5.8</v>
       </c>
       <c r="BC33">
-        <v>1.44</v>
+        <v>5.7</v>
       </c>
       <c r="BD33">
-        <v>1.44</v>
+        <v>5.9</v>
       </c>
       <c r="BE33">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="BF33">
-        <v>1.44</v>
+        <v>5.9</v>
       </c>
       <c r="BG33">
-        <v>1.44</v>
+        <v>5.5</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI33">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK33">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO33">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU33">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW33">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BZ33">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9098,13 +9098,13 @@
         <v>1.26</v>
       </c>
       <c r="O34">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P34">
         <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="R34">
         <v>1.12</v>
@@ -9313,22 +9313,22 @@
         <v>222</v>
       </c>
       <c r="F35">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>3.4</v>
       </c>
       <c r="H35">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I35">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L35">
         <v>1.34</v>
@@ -9337,16 +9337,16 @@
         <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35">
         <v>1.33</v>
       </c>
       <c r="P35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R35">
         <v>1.33</v>
@@ -9355,10 +9355,10 @@
         <v>3.4</v>
       </c>
       <c r="T35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U35">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V35">
         <v>1.62</v>
@@ -9555,19 +9555,19 @@
         <v>223</v>
       </c>
       <c r="F36">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="G36">
         <v>990</v>
       </c>
       <c r="H36">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="I36">
         <v>990</v>
       </c>
       <c r="J36">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="K36">
         <v>950</v>
@@ -9579,16 +9579,16 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O36">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P36">
         <v>1.25</v>
       </c>
       <c r="Q36">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="R36">
         <v>1.12</v>
@@ -9603,10 +9603,10 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W36">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9797,7 +9797,7 @@
         <v>224</v>
       </c>
       <c r="F37">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G37">
         <v>1.88</v>
@@ -9827,10 +9827,10 @@
         <v>1.27</v>
       </c>
       <c r="P37">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R37">
         <v>1.43</v>
@@ -9959,10 +9959,10 @@
         <v>7.6</v>
       </c>
       <c r="BH37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI37">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ37">
         <v>9.6</v>
@@ -9974,49 +9974,49 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN37">
         <v>4.6</v>
       </c>
       <c r="BO37">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP37">
         <v>12.5</v>
       </c>
       <c r="BQ37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT37">
         <v>8.199999999999999</v>
       </c>
       <c r="BU37">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV37">
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB37" t="s">
         <v>239</v>
@@ -10039,10 +10039,10 @@
         <v>225</v>
       </c>
       <c r="F38">
+        <v>1.22</v>
+      </c>
+      <c r="G38">
         <v>1.23</v>
-      </c>
-      <c r="G38">
-        <v>1.24</v>
       </c>
       <c r="H38">
         <v>15</v>
@@ -10054,7 +10054,7 @@
         <v>8</v>
       </c>
       <c r="K38">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L38">
         <v>1.2</v>
@@ -10063,22 +10063,22 @@
         <v>1.02</v>
       </c>
       <c r="N38">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O38">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R38">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="T38">
         <v>1.9</v>
@@ -10093,31 +10093,31 @@
         <v>5.2</v>
       </c>
       <c r="X38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y38">
         <v>80</v>
       </c>
       <c r="Z38">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA38">
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC38">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AD38">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AE38">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF38">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AG38">
         <v>12</v>
@@ -10126,97 +10126,97 @@
         <v>44</v>
       </c>
       <c r="AI38">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AK38">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AL38">
         <v>32</v>
       </c>
       <c r="AM38">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN38">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AO38">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AQ38">
         <v>46</v>
       </c>
       <c r="AR38">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AS38">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AT38">
         <v>12</v>
       </c>
       <c r="AU38">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV38">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AW38">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX38">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY38">
         <v>11</v>
       </c>
       <c r="AZ38">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA38">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BB38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE38">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BF38">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BG38">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH38">
         <v>5.6</v>
       </c>
       <c r="BI38">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BJ38">
         <v>12</v>
       </c>
       <c r="BK38">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN38">
         <v>4.2</v>
@@ -10228,31 +10228,31 @@
         <v>6.6</v>
       </c>
       <c r="BQ38">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR38">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS38">
         <v>8.4</v>
       </c>
       <c r="BT38">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BU38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
+        <v>13.5</v>
+      </c>
+      <c r="BX38">
+        <v>100</v>
+      </c>
+      <c r="BY38">
         <v>13</v>
-      </c>
-      <c r="BX38">
-        <v>1000</v>
-      </c>
-      <c r="BY38">
-        <v>12.5</v>
       </c>
       <c r="BZ38">
         <v>0</v>
@@ -10287,10 +10287,10 @@
         <v>3.65</v>
       </c>
       <c r="H39">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I39">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J39">
         <v>3</v>
@@ -10299,7 +10299,7 @@
         <v>3.3</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M39">
         <v>1.12</v>
@@ -10308,10 +10308,10 @@
         <v>2.56</v>
       </c>
       <c r="O39">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -10329,10 +10329,10 @@
         <v>1.78</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W39">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X39">
         <v>10.5</v>
@@ -10398,7 +10398,7 @@
         <v>11.5</v>
       </c>
       <c r="AS39">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="AT39">
         <v>7.2</v>
@@ -10407,19 +10407,19 @@
         <v>6</v>
       </c>
       <c r="AV39">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW39">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="AX39">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AY39">
         <v>11</v>
       </c>
       <c r="AZ39">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA39">
         <v>5.8</v>
@@ -10443,64 +10443,64 @@
         <v>5.6</v>
       </c>
       <c r="BH39">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BI39">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK39">
-        <v>1.47</v>
+        <v>5.6</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.47</v>
+        <v>10.5</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO39">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ39">
-        <v>1.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.47</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU39">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW39">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY39">
-        <v>1.47</v>
+        <v>9</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.47</v>
+        <v>9</v>
       </c>
       <c r="CB39" t="s">
         <v>239</v>
@@ -10523,220 +10523,220 @@
         <v>227</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M40">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N40">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O40">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P40">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>1.34</v>
+        <v>2.08</v>
       </c>
       <c r="R40">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S40">
-        <v>1.34</v>
+        <v>3.9</v>
       </c>
       <c r="T40">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U40">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V40">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W40">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="X40">
         <v>1000</v>
       </c>
       <c r="Y40">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z40">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA40">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB40">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD40">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE40">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF40">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG40">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH40">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ40">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM40">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO40">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ40">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR40">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS40">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT40">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU40">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW40">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX40">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY40">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ40">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA40">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB40">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC40">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD40">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE40">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BF40">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG40">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI40">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ40">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK40">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BN40">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO40">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP40">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ40">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT40">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU40">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>228</v>
       </c>
       <c r="F41">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G41">
         <v>1.94</v>
@@ -10777,10 +10777,10 @@
         <v>6.2</v>
       </c>
       <c r="J41">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K41">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L41">
         <v>1.42</v>
@@ -10792,10 +10792,10 @@
         <v>3.2</v>
       </c>
       <c r="O41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P41">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q41">
         <v>2.04</v>
@@ -10852,7 +10852,7 @@
         <v>23</v>
       </c>
       <c r="AI41">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ41">
         <v>25</v>
@@ -10876,22 +10876,22 @@
         <v>9.4</v>
       </c>
       <c r="AQ41">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR41">
-        <v>28</v>
+        <v>5.2</v>
       </c>
       <c r="AS41">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT41">
         <v>6.6</v>
       </c>
       <c r="AU41">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV41">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AW41">
         <v>5.4</v>
@@ -10900,13 +10900,13 @@
         <v>7.8</v>
       </c>
       <c r="AY41">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ41">
         <v>15.5</v>
       </c>
       <c r="BA41">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB41">
         <v>14.5</v>
@@ -10915,10 +10915,10 @@
         <v>15</v>
       </c>
       <c r="BD41">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE41">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF41">
         <v>10.5</v>
@@ -10975,7 +10975,7 @@
         <v>8.4</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY41">
         <v>8.6</v>
@@ -11007,13 +11007,13 @@
         <v>229</v>
       </c>
       <c r="F42">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G42">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H42">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I42">
         <v>2.9</v>
@@ -11031,28 +11031,28 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42">
         <v>1.09</v>
       </c>
       <c r="P42">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R42">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="T42">
         <v>1.33</v>
       </c>
       <c r="U42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V42">
         <v>1.52</v>
@@ -11103,28 +11103,28 @@
         <v>25</v>
       </c>
       <c r="AL42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM42">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN42">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO42">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP42">
+        <v>5.2</v>
+      </c>
+      <c r="AQ42">
         <v>4.9</v>
       </c>
-      <c r="AQ42">
-        <v>4.6</v>
-      </c>
       <c r="AR42">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS42">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT42">
         <v>21</v>
@@ -11151,7 +11151,7 @@
         <v>18</v>
       </c>
       <c r="BB42">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC42">
         <v>16</v>
@@ -11160,7 +11160,7 @@
         <v>16.5</v>
       </c>
       <c r="BE42">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF42">
         <v>5.9</v>
@@ -11249,7 +11249,7 @@
         <v>230</v>
       </c>
       <c r="F43">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G43">
         <v>3.9</v>
@@ -11258,7 +11258,7 @@
         <v>2.36</v>
       </c>
       <c r="I43">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J43">
         <v>3.1</v>
@@ -11270,7 +11270,7 @@
         <v>1.56</v>
       </c>
       <c r="M43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N43">
         <v>2.68</v>
@@ -11279,16 +11279,16 @@
         <v>1.54</v>
       </c>
       <c r="P43">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q43">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R43">
         <v>1.19</v>
       </c>
       <c r="S43">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T43">
         <v>2.14</v>
@@ -11297,7 +11297,7 @@
         <v>1.78</v>
       </c>
       <c r="V43">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
         <v>1.35</v>
@@ -11312,7 +11312,7 @@
         <v>13.5</v>
       </c>
       <c r="AA43">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB43">
         <v>10.5</v>
@@ -11324,7 +11324,7 @@
         <v>12.5</v>
       </c>
       <c r="AE43">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF43">
         <v>25</v>
@@ -11372,7 +11372,7 @@
         <v>9.4</v>
       </c>
       <c r="AU43">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV43">
         <v>11</v>
@@ -11390,7 +11390,7 @@
         <v>21</v>
       </c>
       <c r="BA43">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB43">
         <v>34</v>
@@ -11432,10 +11432,10 @@
         <v>6.8</v>
       </c>
       <c r="BO43">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP43">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BQ43">
         <v>11.5</v>
@@ -11450,7 +11450,7 @@
         <v>5</v>
       </c>
       <c r="BU43">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BV43">
         <v>21</v>
@@ -11465,7 +11465,7 @@
         <v>12</v>
       </c>
       <c r="BZ43">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA43">
         <v>12.5</v>
@@ -11494,19 +11494,19 @@
         <v>2.36</v>
       </c>
       <c r="G44">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="H44">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="I44">
+        <v>4.2</v>
+      </c>
+      <c r="J44">
+        <v>2.4</v>
+      </c>
+      <c r="K44">
         <v>4.4</v>
-      </c>
-      <c r="J44">
-        <v>1.3</v>
-      </c>
-      <c r="K44">
-        <v>4.8</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11515,19 +11515,19 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O44">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="P44">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q44">
         <v>2.46</v>
       </c>
       <c r="R44">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S44">
         <v>2.98</v>
@@ -11539,10 +11539,10 @@
         <v>1.11</v>
       </c>
       <c r="V44">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11736,25 +11736,25 @@
         <v>3</v>
       </c>
       <c r="G45">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H45">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I45">
         <v>2.68</v>
       </c>
       <c r="J45">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="K45">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L45">
         <v>1.38</v>
       </c>
       <c r="M45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N45">
         <v>3.4</v>
@@ -11784,19 +11784,19 @@
         <v>1.59</v>
       </c>
       <c r="W45">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X45">
         <v>18</v>
       </c>
       <c r="Y45">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z45">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA45">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB45">
         <v>16</v>
@@ -11823,10 +11823,10 @@
         <v>46</v>
       </c>
       <c r="AJ45">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK45">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL45">
         <v>60</v>
@@ -11835,91 +11835,91 @@
         <v>110</v>
       </c>
       <c r="AN45">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO45">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP45">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="AQ45">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="AR45">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AS45">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="AT45">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="AU45">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="AV45">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AW45">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="AX45">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="AY45">
-        <v>2.46</v>
+        <v>3.45</v>
       </c>
       <c r="AZ45">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="BA45">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="BB45">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="BC45">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="BD45">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="BE45">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF45">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG45">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="BH45">
         <v>3.6</v>
       </c>
       <c r="BI45">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ45">
         <v>9.800000000000001</v>
       </c>
       <c r="BK45">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BN45">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO45">
         <v>4</v>
       </c>
       <c r="BP45">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ45">
         <v>7.2</v>
@@ -11928,25 +11928,25 @@
         <v>40</v>
       </c>
       <c r="BS45">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BT45">
         <v>5.5</v>
       </c>
       <c r="BU45">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV45">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW45">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX45">
         <v>32</v>
       </c>
       <c r="BY45">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -12217,19 +12217,19 @@
         <v>234</v>
       </c>
       <c r="F47">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="G47">
         <v>990</v>
       </c>
       <c r="H47">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I47">
         <v>990</v>
       </c>
       <c r="J47">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12241,13 +12241,13 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P47">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q47">
         <v>1.42</v>
@@ -12265,10 +12265,10 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12471,7 +12471,7 @@
         <v>3.5</v>
       </c>
       <c r="J48">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K48">
         <v>2.96</v>
@@ -12486,25 +12486,25 @@
         <v>2.34</v>
       </c>
       <c r="O48">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P48">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q48">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S48">
         <v>7</v>
       </c>
       <c r="T48">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U48">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V48">
         <v>1.4</v>
@@ -12519,7 +12519,7 @@
         <v>8.6</v>
       </c>
       <c r="Z48">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA48">
         <v>85</v>
@@ -12528,7 +12528,7 @@
         <v>7.2</v>
       </c>
       <c r="AC48">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD48">
         <v>17</v>
@@ -12567,10 +12567,10 @@
         <v>1000</v>
       </c>
       <c r="AP48">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ48">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR48">
         <v>18</v>
@@ -12597,7 +12597,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ48">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA48">
         <v>40</v>
@@ -12701,37 +12701,37 @@
         <v>236</v>
       </c>
       <c r="F49">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G49">
         <v>2.8</v>
       </c>
       <c r="H49">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I49">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J49">
         <v>3.05</v>
       </c>
       <c r="K49">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L49">
         <v>1.48</v>
       </c>
       <c r="M49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N49">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O49">
         <v>1.55</v>
       </c>
       <c r="P49">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q49">
         <v>2.62</v>
@@ -12740,19 +12740,19 @@
         <v>1.2</v>
       </c>
       <c r="S49">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T49">
         <v>2.12</v>
       </c>
       <c r="U49">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X49">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>21</v>
       </c>
       <c r="AA49">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="AB49">
         <v>8.199999999999999</v>
@@ -12776,13 +12776,13 @@
         <v>15.5</v>
       </c>
       <c r="AE49">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="AF49">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG49">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH49">
         <v>24</v>
@@ -12791,10 +12791,10 @@
         <v>1000</v>
       </c>
       <c r="AJ49">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AK49">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AL49">
         <v>1000</v>
@@ -12803,31 +12803,31 @@
         <v>1000</v>
       </c>
       <c r="AN49">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AO49">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AP49">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ49">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR49">
         <v>17.5</v>
       </c>
       <c r="AS49">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT49">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU49">
         <v>6.4</v>
       </c>
       <c r="AV49">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW49">
         <v>26</v>
@@ -12836,13 +12836,13 @@
         <v>14</v>
       </c>
       <c r="AY49">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ49">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA49">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB49">
         <v>24</v>
@@ -12851,13 +12851,13 @@
         <v>23</v>
       </c>
       <c r="BD49">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE49">
         <v>46</v>
       </c>
       <c r="BF49">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BG49">
         <v>29</v>
@@ -12866,13 +12866,13 @@
         <v>2.78</v>
       </c>
       <c r="BI49">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ49">
         <v>11.5</v>
       </c>
       <c r="BK49">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL49">
         <v>1000</v>
@@ -12943,13 +12943,13 @@
         <v>237</v>
       </c>
       <c r="F50">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G50">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I50">
         <v>7.2</v>
@@ -12958,10 +12958,10 @@
         <v>3.35</v>
       </c>
       <c r="K50">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L50">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M50">
         <v>1.11</v>
@@ -12985,7 +12985,7 @@
         <v>5</v>
       </c>
       <c r="T50">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U50">
         <v>1.66</v>
@@ -12994,13 +12994,13 @@
         <v>1.16</v>
       </c>
       <c r="W50">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X50">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y50">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z50">
         <v>60</v>
@@ -13063,13 +13063,13 @@
         <v>46</v>
       </c>
       <c r="AT50">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU50">
         <v>7.4</v>
       </c>
       <c r="AV50">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW50">
         <v>40</v>
@@ -13081,7 +13081,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ50">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA50">
         <v>44</v>
@@ -13191,16 +13191,16 @@
         <v>2.12</v>
       </c>
       <c r="H51">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I51">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J51">
         <v>3.3</v>
       </c>
       <c r="K51">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13209,7 +13209,7 @@
         <v>1.08</v>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O51">
         <v>1.37</v>
@@ -13218,7 +13218,7 @@
         <v>1.73</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R51">
         <v>1.27</v>
@@ -13233,7 +13233,7 @@
         <v>1.9</v>
       </c>
       <c r="V51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W51">
         <v>1.89</v>
@@ -13254,7 +13254,7 @@
         <v>9.6</v>
       </c>
       <c r="AC51">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD51">
         <v>23</v>
@@ -13293,58 +13293,58 @@
         <v>100</v>
       </c>
       <c r="AP51">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AQ51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR51">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS51">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT51">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AU51">
         <v>3</v>
       </c>
       <c r="AV51">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AW51">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX51">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AY51">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AZ51">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BA51">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB51">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BC51">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD51">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE51">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF51">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BG51">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH51">
         <v>3.9</v>
@@ -13356,55 +13356,55 @@
         <v>1000</v>
       </c>
       <c r="BK51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BL51">
         <v>1000</v>
       </c>
       <c r="BM51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BN51">
         <v>1000</v>
       </c>
       <c r="BO51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BP51">
         <v>1000</v>
       </c>
       <c r="BQ51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BR51">
         <v>1000</v>
       </c>
       <c r="BS51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BT51">
         <v>1000</v>
       </c>
       <c r="BU51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BV51">
         <v>1000</v>
       </c>
       <c r="BW51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BX51">
         <v>1000</v>
       </c>
       <c r="BY51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BZ51">
         <v>1000</v>
       </c>
       <c r="CA51">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="CB51" t="s">
         <v>239</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="241">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Costa Rican Primera Division</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
-    <t>Costa Rican Primera Division</t>
-  </si>
-  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -361,6 +361,9 @@
     <t>2026-08-03</t>
   </si>
   <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
     <t>00:30:00</t>
   </si>
   <si>
@@ -433,12 +436,12 @@
     <t>22:30:00</t>
   </si>
   <si>
+    <t>Inter San Carlos</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
-    <t>Inter San Carlos</t>
-  </si>
-  <si>
     <t>Santa Fe</t>
   </si>
   <si>
@@ -583,12 +586,12 @@
     <t>Caracas</t>
   </si>
   <si>
+    <t>Cs Herediano</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Cs Herediano</t>
-  </si>
-  <si>
     <t>Once Caldas</t>
   </si>
   <si>
@@ -733,7 +736,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-02 16:32:47</t>
+    <t>2026-08-02 18:42:52</t>
   </si>
 </sst>
 </file>
@@ -1321,235 +1324,235 @@
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F2">
+        <v>3.7</v>
+      </c>
+      <c r="G2">
+        <v>4.1</v>
+      </c>
+      <c r="H2">
+        <v>2.18</v>
+      </c>
+      <c r="I2">
+        <v>2.3</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.47</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.25</v>
+      </c>
+      <c r="O2">
+        <v>1.43</v>
+      </c>
+      <c r="P2">
+        <v>1.74</v>
+      </c>
+      <c r="Q2">
         <v>2.22</v>
       </c>
-      <c r="G2">
-        <v>2.26</v>
-      </c>
-      <c r="H2">
-        <v>4.3</v>
-      </c>
-      <c r="I2">
-        <v>4.5</v>
-      </c>
-      <c r="J2">
-        <v>3.05</v>
-      </c>
-      <c r="K2">
-        <v>3.15</v>
-      </c>
-      <c r="L2">
-        <v>1.66</v>
-      </c>
-      <c r="M2">
-        <v>1.15</v>
-      </c>
-      <c r="N2">
-        <v>2.48</v>
-      </c>
-      <c r="O2">
-        <v>1.64</v>
-      </c>
-      <c r="P2">
-        <v>1.48</v>
-      </c>
-      <c r="Q2">
-        <v>2.98</v>
-      </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
+        <v>4.2</v>
+      </c>
+      <c r="T2">
+        <v>1.94</v>
+      </c>
+      <c r="U2">
+        <v>1.98</v>
+      </c>
+      <c r="V2">
+        <v>1.76</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>12</v>
+      </c>
+      <c r="Y2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z2">
+        <v>13.5</v>
+      </c>
+      <c r="AA2">
+        <v>29</v>
+      </c>
+      <c r="AB2">
+        <v>13</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>27</v>
+      </c>
+      <c r="AF2">
+        <v>28</v>
+      </c>
+      <c r="AG2">
+        <v>16.5</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>46</v>
+      </c>
+      <c r="AJ2">
+        <v>85</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>85</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>80</v>
+      </c>
+      <c r="AO2">
+        <v>23</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>7.4</v>
+      </c>
+      <c r="AR2">
+        <v>11.5</v>
+      </c>
+      <c r="AS2">
+        <v>23</v>
+      </c>
+      <c r="AT2">
+        <v>10.5</v>
+      </c>
+      <c r="AU2">
         <v>6.6</v>
       </c>
-      <c r="T2">
-        <v>2.36</v>
-      </c>
-      <c r="U2">
-        <v>1.68</v>
-      </c>
-      <c r="V2">
-        <v>1.29</v>
-      </c>
-      <c r="W2">
-        <v>1.79</v>
-      </c>
-      <c r="X2">
-        <v>7.6</v>
-      </c>
-      <c r="Y2">
-        <v>10.5</v>
-      </c>
-      <c r="Z2">
-        <v>30</v>
-      </c>
-      <c r="AA2">
-        <v>120</v>
-      </c>
-      <c r="AB2">
-        <v>6.6</v>
-      </c>
-      <c r="AC2">
+      <c r="AV2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2">
+        <v>21</v>
+      </c>
+      <c r="AX2">
+        <v>22</v>
+      </c>
+      <c r="AY2">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
+        <v>32</v>
+      </c>
+      <c r="BB2">
+        <v>50</v>
+      </c>
+      <c r="BC2">
+        <v>32</v>
+      </c>
+      <c r="BD2">
+        <v>42</v>
+      </c>
+      <c r="BE2">
+        <v>11</v>
+      </c>
+      <c r="BF2">
+        <v>40</v>
+      </c>
+      <c r="BG2">
+        <v>18.5</v>
+      </c>
+      <c r="BH2">
+        <v>3.2</v>
+      </c>
+      <c r="BI2">
+        <v>2.58</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>5.3</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>9.6</v>
+      </c>
+      <c r="BN2">
         <v>7.2</v>
       </c>
-      <c r="AD2">
-        <v>22</v>
-      </c>
-      <c r="AE2">
-        <v>95</v>
-      </c>
-      <c r="AF2">
-        <v>12</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>120</v>
-      </c>
-      <c r="AJ2">
-        <v>30</v>
-      </c>
-      <c r="AK2">
-        <v>38</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>250</v>
-      </c>
-      <c r="AN2">
+      <c r="BO2">
+        <v>6</v>
+      </c>
+      <c r="BP2">
         <v>36</v>
       </c>
-      <c r="AO2">
-        <v>160</v>
-      </c>
-      <c r="AP2">
-        <v>6.8</v>
-      </c>
-      <c r="AQ2">
-        <v>9.6</v>
-      </c>
-      <c r="AR2">
-        <v>25</v>
-      </c>
-      <c r="AS2">
-        <v>60</v>
-      </c>
-      <c r="AT2">
-        <v>6</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
+      <c r="BQ2">
+        <v>8</v>
+      </c>
+      <c r="BR2">
+        <v>50</v>
+      </c>
+      <c r="BS2">
+        <v>8.4</v>
+      </c>
+      <c r="BT2">
+        <v>5.1</v>
+      </c>
+      <c r="BU2">
+        <v>4.2</v>
+      </c>
+      <c r="BV2">
         <v>18</v>
       </c>
-      <c r="AW2">
-        <v>65</v>
-      </c>
-      <c r="AX2">
-        <v>10.5</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>26</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>19.5</v>
-      </c>
-      <c r="BC2">
-        <v>30</v>
-      </c>
-      <c r="BD2">
+      <c r="BW2">
+        <v>6.4</v>
+      </c>
+      <c r="BX2">
         <v>36</v>
       </c>
-      <c r="BE2">
-        <v>85</v>
-      </c>
-      <c r="BF2">
-        <v>30</v>
-      </c>
-      <c r="BG2">
-        <v>42</v>
-      </c>
-      <c r="BH2">
-        <v>2.54</v>
-      </c>
-      <c r="BI2">
-        <v>2.4</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>7.4</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>17</v>
-      </c>
-      <c r="BN2">
-        <v>4.6</v>
-      </c>
-      <c r="BO2">
-        <v>4</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>9.4</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>13</v>
-      </c>
-      <c r="BT2">
-        <v>7.8</v>
-      </c>
-      <c r="BU2">
-        <v>5.4</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>13</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
       <c r="BY2">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1560,238 +1563,238 @@
         <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F3">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
-        <v>2.28</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z3">
+        <v>29</v>
+      </c>
+      <c r="AA3">
+        <v>120</v>
+      </c>
+      <c r="AB3">
+        <v>6.6</v>
+      </c>
+      <c r="AC3">
+        <v>7.2</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>95</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>29</v>
+      </c>
+      <c r="AI3">
+        <v>130</v>
+      </c>
+      <c r="AJ3">
+        <v>30</v>
+      </c>
+      <c r="AK3">
+        <v>38</v>
+      </c>
+      <c r="AL3">
+        <v>75</v>
+      </c>
+      <c r="AM3">
+        <v>250</v>
+      </c>
+      <c r="AN3">
+        <v>36</v>
+      </c>
+      <c r="AO3">
+        <v>160</v>
+      </c>
+      <c r="AP3">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3">
+        <v>9.6</v>
+      </c>
+      <c r="AR3">
+        <v>25</v>
+      </c>
+      <c r="AS3">
+        <v>65</v>
+      </c>
+      <c r="AT3">
+        <v>6</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>18</v>
+      </c>
+      <c r="AW3">
+        <v>65</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>26</v>
+      </c>
+      <c r="BA3">
+        <v>95</v>
+      </c>
+      <c r="BB3">
+        <v>27</v>
+      </c>
+      <c r="BC3">
+        <v>30</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>55</v>
+      </c>
+      <c r="BF3">
+        <v>30</v>
+      </c>
+      <c r="BG3">
+        <v>42</v>
+      </c>
+      <c r="BH3">
+        <v>2.54</v>
+      </c>
+      <c r="BI3">
+        <v>2.4</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>7.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>17.5</v>
+      </c>
+      <c r="BN3">
+        <v>4.6</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>19.5</v>
+      </c>
+      <c r="BQ3">
+        <v>9.4</v>
+      </c>
+      <c r="BR3">
+        <v>48</v>
+      </c>
+      <c r="BS3">
+        <v>13.5</v>
+      </c>
+      <c r="BT3">
+        <v>7.8</v>
+      </c>
+      <c r="BU3">
+        <v>5.5</v>
+      </c>
+      <c r="BV3">
+        <v>50</v>
+      </c>
+      <c r="BW3">
+        <v>13.5</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>15</v>
+      </c>
+      <c r="BZ3">
+        <v>60</v>
+      </c>
+      <c r="CA3">
         <v>14</v>
       </c>
-      <c r="AA3">
-        <v>30</v>
-      </c>
-      <c r="AB3">
-        <v>13</v>
-      </c>
-      <c r="AC3">
-        <v>8</v>
-      </c>
-      <c r="AD3">
-        <v>11.5</v>
-      </c>
-      <c r="AE3">
-        <v>27</v>
-      </c>
-      <c r="AF3">
-        <v>28</v>
-      </c>
-      <c r="AG3">
-        <v>16.5</v>
-      </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
-        <v>46</v>
-      </c>
-      <c r="AJ3">
-        <v>90</v>
-      </c>
-      <c r="AK3">
-        <v>55</v>
-      </c>
-      <c r="AL3">
-        <v>90</v>
-      </c>
-      <c r="AM3">
-        <v>150</v>
-      </c>
-      <c r="AN3">
-        <v>65</v>
-      </c>
-      <c r="AO3">
-        <v>23</v>
-      </c>
-      <c r="AP3">
-        <v>10</v>
-      </c>
-      <c r="AQ3">
-        <v>7.4</v>
-      </c>
-      <c r="AR3">
-        <v>10.5</v>
-      </c>
-      <c r="AS3">
-        <v>21</v>
-      </c>
-      <c r="AT3">
-        <v>9.6</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>9.6</v>
-      </c>
-      <c r="AW3">
-        <v>20</v>
-      </c>
-      <c r="AX3">
-        <v>21</v>
-      </c>
-      <c r="AY3">
-        <v>12</v>
-      </c>
-      <c r="AZ3">
-        <v>16.5</v>
-      </c>
-      <c r="BA3">
-        <v>32</v>
-      </c>
-      <c r="BB3">
-        <v>50</v>
-      </c>
-      <c r="BC3">
-        <v>34</v>
-      </c>
-      <c r="BD3">
-        <v>44</v>
-      </c>
-      <c r="BE3">
-        <v>9.6</v>
-      </c>
-      <c r="BF3">
-        <v>42</v>
-      </c>
-      <c r="BG3">
-        <v>16.5</v>
-      </c>
-      <c r="BH3">
-        <v>3.2</v>
-      </c>
-      <c r="BI3">
-        <v>2.58</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
-      </c>
-      <c r="BK3">
-        <v>5.3</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>9.6</v>
-      </c>
-      <c r="BN3">
-        <v>7.4</v>
-      </c>
-      <c r="BO3">
-        <v>5.5</v>
-      </c>
-      <c r="BP3">
-        <v>36</v>
-      </c>
-      <c r="BQ3">
-        <v>8</v>
-      </c>
-      <c r="BR3">
-        <v>50</v>
-      </c>
-      <c r="BS3">
-        <v>8.4</v>
-      </c>
-      <c r="BT3">
-        <v>5.1</v>
-      </c>
-      <c r="BU3">
-        <v>3.9</v>
-      </c>
-      <c r="BV3">
-        <v>17.5</v>
-      </c>
-      <c r="BW3">
-        <v>6.4</v>
-      </c>
-      <c r="BX3">
-        <v>36</v>
-      </c>
-      <c r="BY3">
-        <v>8</v>
-      </c>
-      <c r="BZ3">
-        <v>34</v>
-      </c>
-      <c r="CA3">
-        <v>7.8</v>
-      </c>
       <c r="CB3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1802,19 +1805,19 @@
         <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F4">
         <v>2.26</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H4">
         <v>3.75</v>
@@ -1826,10 +1829,10 @@
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1838,10 +1841,10 @@
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1853,16 +1856,16 @@
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
         <v>1.34</v>
       </c>
       <c r="W4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1898,7 +1901,7 @@
         <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>28</v>
@@ -1919,7 +1922,7 @@
         <v>60</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
@@ -1955,7 +1958,7 @@
         <v>44</v>
       </c>
       <c r="BB4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC4">
         <v>23</v>
@@ -1973,67 +1976,67 @@
         <v>46</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL4">
         <v>150</v>
       </c>
       <c r="BM4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>34</v>
       </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2044,79 +2047,79 @@
         <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M5">
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
         <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S5">
         <v>2.34</v>
       </c>
       <c r="T5">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U5">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y5">
         <v>32</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -2125,10 +2128,10 @@
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
@@ -2137,40 +2140,40 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AR5">
         <v>50</v>
       </c>
       <c r="AS5">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2185,31 +2188,31 @@
         <v>60</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY5">
         <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
         <v>50</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5">
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BG5">
         <v>50</v>
@@ -2218,64 +2221,64 @@
         <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>19.5</v>
       </c>
       <c r="BS5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT5">
+        <v>10.5</v>
+      </c>
+      <c r="BU5">
         <v>9.4</v>
       </c>
-      <c r="BT5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU5">
-        <v>7.4</v>
-      </c>
       <c r="BV5">
+        <v>48</v>
+      </c>
+      <c r="BW5">
+        <v>12</v>
+      </c>
+      <c r="BX5">
         <v>44</v>
       </c>
-      <c r="BW5">
-        <v>12.5</v>
-      </c>
-      <c r="BX5">
-        <v>42</v>
-      </c>
       <c r="BY5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2286,25 +2289,25 @@
         <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F6">
         <v>1.27</v>
       </c>
       <c r="G6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J6">
         <v>5.6</v>
@@ -2316,28 +2319,28 @@
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
+        <v>1.59</v>
+      </c>
+      <c r="R6">
         <v>1.56</v>
       </c>
-      <c r="R6">
-        <v>1.53</v>
-      </c>
       <c r="S6">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
         <v>1.73</v>
@@ -2346,7 +2349,7 @@
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X6">
         <v>30</v>
@@ -2370,10 +2373,10 @@
         <v>55</v>
       </c>
       <c r="AE6">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AF6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2397,22 +2400,22 @@
         <v>210</v>
       </c>
       <c r="AN6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO6">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="AP6">
         <v>20</v>
       </c>
       <c r="AQ6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2421,103 +2424,103 @@
         <v>11.5</v>
       </c>
       <c r="AV6">
+        <v>5.5</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>6.8</v>
+      </c>
+      <c r="AY6">
+        <v>8.4</v>
+      </c>
+      <c r="AZ6">
         <v>5.3</v>
       </c>
-      <c r="AW6">
-        <v>5.8</v>
-      </c>
-      <c r="AX6">
-        <v>6.2</v>
-      </c>
-      <c r="AY6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>5.1</v>
-      </c>
       <c r="BA6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC6">
         <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE6">
+        <v>5.9</v>
+      </c>
+      <c r="BF6">
+        <v>3.85</v>
+      </c>
+      <c r="BG6">
+        <v>6</v>
+      </c>
+      <c r="BH6">
+        <v>4.8</v>
+      </c>
+      <c r="BI6">
+        <v>3.4</v>
+      </c>
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
+        <v>9.4</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>7</v>
+      </c>
+      <c r="BN6">
+        <v>4</v>
+      </c>
+      <c r="BO6">
+        <v>3.15</v>
+      </c>
+      <c r="BP6">
+        <v>7.6</v>
+      </c>
+      <c r="BQ6">
         <v>5.7</v>
       </c>
-      <c r="BF6">
-        <v>3.75</v>
-      </c>
-      <c r="BG6">
+      <c r="BR6">
+        <v>26</v>
+      </c>
+      <c r="BS6">
         <v>5.8</v>
       </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2528,13 +2531,13 @@
         <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F7">
         <v>3.35</v>
@@ -2555,7 +2558,7 @@
         <v>3.65</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2567,16 +2570,16 @@
         <v>1.46</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
         <v>1.23</v>
       </c>
       <c r="S7">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -2594,28 +2597,28 @@
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
         <v>15</v>
       </c>
       <c r="AA7">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AB7">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>12.5</v>
       </c>
       <c r="AE7">
+        <v>36</v>
+      </c>
+      <c r="AF7">
         <v>32</v>
-      </c>
-      <c r="AF7">
-        <v>28</v>
       </c>
       <c r="AG7">
         <v>17</v>
@@ -2624,10 +2627,10 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK7">
         <v>65</v>
@@ -2642,124 +2645,124 @@
         <v>85</v>
       </c>
       <c r="AO7">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP7">
+        <v>3.65</v>
+      </c>
+      <c r="AQ7">
+        <v>3.35</v>
+      </c>
+      <c r="AR7">
+        <v>3.8</v>
+      </c>
+      <c r="AS7">
         <v>4.4</v>
       </c>
-      <c r="AQ7">
-        <v>5.4</v>
-      </c>
-      <c r="AR7">
-        <v>4.6</v>
-      </c>
-      <c r="AS7">
-        <v>5.6</v>
-      </c>
       <c r="AT7">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AU7">
+        <v>3.25</v>
+      </c>
+      <c r="AV7">
         <v>3.6</v>
       </c>
-      <c r="AV7">
-        <v>4.3</v>
-      </c>
       <c r="AW7">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX7">
+        <v>4.4</v>
+      </c>
+      <c r="AY7">
+        <v>3.9</v>
+      </c>
+      <c r="AZ7">
+        <v>4.1</v>
+      </c>
+      <c r="BA7">
+        <v>4.7</v>
+      </c>
+      <c r="BB7">
+        <v>4.8</v>
+      </c>
+      <c r="BC7">
+        <v>4.7</v>
+      </c>
+      <c r="BD7">
+        <v>4.8</v>
+      </c>
+      <c r="BE7">
+        <v>4.9</v>
+      </c>
+      <c r="BF7">
+        <v>4.8</v>
+      </c>
+      <c r="BG7">
+        <v>4.4</v>
+      </c>
+      <c r="BH7">
+        <v>3.1</v>
+      </c>
+      <c r="BI7">
+        <v>2.42</v>
+      </c>
+      <c r="BJ7">
+        <v>11</v>
+      </c>
+      <c r="BK7">
+        <v>5</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>2.3</v>
+      </c>
+      <c r="BN7">
+        <v>7.2</v>
+      </c>
+      <c r="BO7">
+        <v>4</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>7.4</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>8</v>
+      </c>
+      <c r="BT7">
         <v>5.3</v>
       </c>
-      <c r="AY7">
-        <v>4.7</v>
-      </c>
-      <c r="AZ7">
-        <v>5.1</v>
-      </c>
-      <c r="BA7">
-        <v>5.9</v>
-      </c>
-      <c r="BB7">
+      <c r="BU7">
+        <v>3.35</v>
+      </c>
+      <c r="BV7">
+        <v>19.5</v>
+      </c>
+      <c r="BW7">
         <v>6.2</v>
       </c>
-      <c r="BC7">
-        <v>6</v>
-      </c>
-      <c r="BD7">
-        <v>6</v>
-      </c>
-      <c r="BE7">
-        <v>6.4</v>
-      </c>
-      <c r="BF7">
-        <v>6</v>
-      </c>
-      <c r="BG7">
-        <v>5.3</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.72</v>
-      </c>
-      <c r="BJ7">
-        <v>15</v>
-      </c>
-      <c r="BK7">
-        <v>1.54</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.72</v>
-      </c>
-      <c r="BN7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO7">
-        <v>1.46</v>
-      </c>
-      <c r="BP7">
-        <v>50</v>
-      </c>
-      <c r="BQ7">
-        <v>1.66</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.68</v>
-      </c>
-      <c r="BT7">
-        <v>7</v>
-      </c>
-      <c r="BU7">
-        <v>1.38</v>
-      </c>
-      <c r="BV7">
-        <v>28</v>
-      </c>
-      <c r="BW7">
-        <v>1.62</v>
-      </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.67</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.67</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2770,31 +2773,31 @@
         <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="G8">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="I8">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="J8">
         <v>4.5</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
         <v>1.17</v>
@@ -2809,7 +2812,7 @@
         <v>1.1</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q8">
         <v>1.32</v>
@@ -2818,31 +2821,31 @@
         <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="T8">
         <v>1.37</v>
       </c>
       <c r="U8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="X8">
         <v>55</v>
       </c>
       <c r="Y8">
+        <v>27</v>
+      </c>
+      <c r="Z8">
         <v>30</v>
       </c>
-      <c r="Z8">
-        <v>36</v>
-      </c>
       <c r="AA8">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB8">
         <v>27</v>
@@ -2851,13 +2854,13 @@
         <v>14</v>
       </c>
       <c r="AD8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AE8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AF8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>15</v>
@@ -2866,10 +2869,10 @@
         <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AJ8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -2881,22 +2884,22 @@
         <v>42</v>
       </c>
       <c r="AN8">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
+        <v>20</v>
+      </c>
+      <c r="AR8">
         <v>21</v>
       </c>
-      <c r="AR8">
-        <v>5.2</v>
-      </c>
       <c r="AS8">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT8">
         <v>17.5</v>
@@ -2905,25 +2908,25 @@
         <v>10.5</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX8">
         <v>17</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB8">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2932,76 +2935,76 @@
         <v>16</v>
       </c>
       <c r="BE8">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BH8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI8">
         <v>5.3</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW8">
         <v>7.8</v>
       </c>
       <c r="BX8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY8">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8">
         <v>9.800000000000001</v>
       </c>
       <c r="CA8">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3012,31 +3015,31 @@
         <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F9">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="K9">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>1.2</v>
@@ -3051,7 +3054,7 @@
         <v>1.14</v>
       </c>
       <c r="P9">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q9">
         <v>1.43</v>
@@ -3060,58 +3063,58 @@
         <v>1.87</v>
       </c>
       <c r="S9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U9">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="X9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y9">
         <v>950</v>
       </c>
       <c r="Z9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA9">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="AB9">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AC9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD9">
         <v>950</v>
       </c>
       <c r="AE9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK9">
         <v>14.5</v>
@@ -3120,67 +3123,67 @@
         <v>46</v>
       </c>
       <c r="AM9">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AO9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP9">
+        <v>6.8</v>
+      </c>
+      <c r="AQ9">
+        <v>6.8</v>
+      </c>
+      <c r="AR9">
+        <v>7.6</v>
+      </c>
+      <c r="AS9">
+        <v>8</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>10.5</v>
+      </c>
+      <c r="AV9">
+        <v>26</v>
+      </c>
+      <c r="AW9">
         <v>7.8</v>
       </c>
-      <c r="AQ9">
-        <v>8</v>
-      </c>
-      <c r="AR9">
-        <v>9</v>
-      </c>
-      <c r="AS9">
-        <v>9.4</v>
-      </c>
-      <c r="AT9">
-        <v>9.4</v>
-      </c>
-      <c r="AU9">
-        <v>11.5</v>
-      </c>
-      <c r="AV9">
-        <v>7.8</v>
-      </c>
-      <c r="AW9">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AX9">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY9">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
         <v>19.5</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BB9">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BF9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
@@ -3219,10 +3222,10 @@
         <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3237,13 +3240,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3254,13 +3257,13 @@
         <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10">
         <v>1.71</v>
@@ -3302,7 +3305,7 @@
         <v>1.47</v>
       </c>
       <c r="S10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T10">
         <v>1.71</v>
@@ -3485,7 +3488,7 @@
         <v>6.4</v>
       </c>
       <c r="CB10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3496,13 +3499,13 @@
         <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F11">
         <v>1.16</v>
@@ -3511,7 +3514,7 @@
         <v>1.19</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11">
         <v>26</v>
@@ -3727,7 +3730,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3738,19 +3741,19 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F12">
         <v>3.15</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H12">
         <v>2.12</v>
@@ -3774,10 +3777,10 @@
         <v>5.7</v>
       </c>
       <c r="O12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
         <v>1.56</v>
@@ -3786,7 +3789,7 @@
         <v>1.64</v>
       </c>
       <c r="S12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T12">
         <v>1.53</v>
@@ -3837,7 +3840,7 @@
         <v>36</v>
       </c>
       <c r="AJ12">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK12">
         <v>42</v>
@@ -3861,7 +3864,7 @@
         <v>10</v>
       </c>
       <c r="AR12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS12">
         <v>20</v>
@@ -3870,10 +3873,10 @@
         <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12">
         <v>17.5</v>
@@ -3882,7 +3885,7 @@
         <v>18</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12">
         <v>13</v>
@@ -3897,7 +3900,7 @@
         <v>6</v>
       </c>
       <c r="BD12">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
         <v>6.4</v>
@@ -3906,7 +3909,7 @@
         <v>16</v>
       </c>
       <c r="BG12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH12">
         <v>4.5</v>
@@ -3969,7 +3972,7 @@
         <v>7.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3980,16 +3983,16 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F13">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G13">
         <v>2.02</v>
@@ -3998,10 +4001,10 @@
         <v>4.5</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
         <v>3.75</v>
@@ -4025,7 +4028,7 @@
         <v>2.08</v>
       </c>
       <c r="R13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
         <v>3.75</v>
@@ -4037,7 +4040,7 @@
         <v>1.94</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
         <v>1.98</v>
@@ -4067,10 +4070,10 @@
         <v>80</v>
       </c>
       <c r="AF13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH13">
         <v>24</v>
@@ -4094,7 +4097,7 @@
         <v>16.5</v>
       </c>
       <c r="AO13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP13">
         <v>9.800000000000001</v>
@@ -4103,10 +4106,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS13">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT13">
         <v>7</v>
@@ -4118,7 +4121,7 @@
         <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX13">
         <v>9.800000000000001</v>
@@ -4130,25 +4133,25 @@
         <v>17.5</v>
       </c>
       <c r="BA13">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC13">
         <v>16.5</v>
       </c>
       <c r="BD13">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE13">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF13">
         <v>12</v>
       </c>
       <c r="BG13">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH13">
         <v>3.25</v>
@@ -4160,13 +4163,13 @@
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN13">
         <v>4.6</v>
@@ -4175,7 +4178,7 @@
         <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
         <v>6.8</v>
@@ -4184,13 +4187,13 @@
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT13">
         <v>8.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -4208,10 +4211,10 @@
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4222,25 +4225,25 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F14">
         <v>4.1</v>
       </c>
       <c r="G14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H14">
         <v>1.92</v>
       </c>
       <c r="I14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J14">
         <v>3.55</v>
@@ -4249,7 +4252,7 @@
         <v>4</v>
       </c>
       <c r="L14">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M14">
         <v>1.07</v>
@@ -4258,13 +4261,13 @@
         <v>3.45</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P14">
         <v>1.86</v>
       </c>
       <c r="Q14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
         <v>1.33</v>
@@ -4360,7 +4363,7 @@
         <v>8</v>
       </c>
       <c r="AW14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX14">
         <v>4.4</v>
@@ -4402,22 +4405,22 @@
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN14">
         <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ14">
         <v>8.199999999999999</v>
@@ -4432,19 +4435,19 @@
         <v>4.8</v>
       </c>
       <c r="BU14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BX14">
         <v>30</v>
       </c>
       <c r="BY14">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4453,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4464,28 +4467,28 @@
         <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15">
         <v>1.37</v>
       </c>
       <c r="G15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I15">
         <v>11.5</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
         <v>5.6</v>
@@ -4500,19 +4503,19 @@
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
         <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
         <v>1.4</v>
       </c>
       <c r="S15">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="T15">
         <v>2.06</v>
@@ -4524,7 +4527,7 @@
         <v>1.09</v>
       </c>
       <c r="W15">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
         <v>21</v>
@@ -4695,7 +4698,7 @@
         <v>1.29</v>
       </c>
       <c r="CB15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4706,64 +4709,64 @@
         <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F16">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H16">
         <v>2.04</v>
       </c>
       <c r="I16">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J16">
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>1.25</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O16">
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q16">
         <v>1.58</v>
       </c>
       <c r="R16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T16">
         <v>1.56</v>
       </c>
       <c r="U16">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V16">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W16">
         <v>1.37</v>
@@ -4778,7 +4781,7 @@
         <v>18</v>
       </c>
       <c r="AA16">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB16">
         <v>21</v>
@@ -4787,10 +4790,10 @@
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE16">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AF16">
         <v>34</v>
@@ -4799,31 +4802,31 @@
         <v>17.5</v>
       </c>
       <c r="AH16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AJ16">
         <v>1000</v>
       </c>
       <c r="AK16">
+        <v>36</v>
+      </c>
+      <c r="AL16">
         <v>38</v>
       </c>
-      <c r="AL16">
-        <v>80</v>
-      </c>
       <c r="AM16">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="AN16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO16">
         <v>9.4</v>
       </c>
       <c r="AP16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ16">
         <v>13</v>
@@ -4832,10 +4835,10 @@
         <v>14.5</v>
       </c>
       <c r="AS16">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT16">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4853,16 +4856,16 @@
         <v>13.5</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BB16">
         <v>32</v>
       </c>
       <c r="BC16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD16">
         <v>22</v>
@@ -4871,10 +4874,10 @@
         <v>29</v>
       </c>
       <c r="BF16">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH16">
         <v>4.4</v>
@@ -4886,7 +4889,7 @@
         <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4904,13 +4907,13 @@
         <v>25</v>
       </c>
       <c r="BQ16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
         <v>5.3</v>
@@ -4922,10 +4925,10 @@
         <v>13.5</v>
       </c>
       <c r="BW16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
         <v>7.6</v>
@@ -4934,10 +4937,10 @@
         <v>14.5</v>
       </c>
       <c r="CA16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4948,31 +4951,31 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F17">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H17">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K17">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4987,13 +4990,13 @@
         <v>1.26</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
       </c>
       <c r="R17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
         <v>2.92</v>
@@ -5005,22 +5008,22 @@
         <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W17">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X17">
         <v>22</v>
       </c>
       <c r="Y17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z17">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA17">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB17">
         <v>17</v>
@@ -5029,10 +5032,10 @@
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF17">
         <v>26</v>
@@ -5044,13 +5047,13 @@
         <v>19.5</v>
       </c>
       <c r="AI17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ17">
         <v>55</v>
       </c>
       <c r="AK17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL17">
         <v>46</v>
@@ -5062,31 +5065,31 @@
         <v>29</v>
       </c>
       <c r="AO17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AP17">
         <v>13</v>
       </c>
       <c r="AQ17">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17">
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT17">
         <v>11.5</v>
       </c>
       <c r="AU17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV17">
         <v>8.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AX17">
         <v>18</v>
@@ -5095,22 +5098,22 @@
         <v>11</v>
       </c>
       <c r="AZ17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA17">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB17">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC17">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD17">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE17">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF17">
         <v>19.5</v>
@@ -5140,25 +5143,25 @@
         <v>6.6</v>
       </c>
       <c r="BO17">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV17">
         <v>18</v>
@@ -5167,7 +5170,7 @@
         <v>6.6</v>
       </c>
       <c r="BX17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY17">
         <v>7.6</v>
@@ -5179,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5190,31 +5193,31 @@
         <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F18">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G18">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H18">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J18">
         <v>3.4</v>
       </c>
       <c r="K18">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L18">
         <v>1.33</v>
@@ -5232,7 +5235,7 @@
         <v>1.93</v>
       </c>
       <c r="Q18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R18">
         <v>1.36</v>
@@ -5268,7 +5271,7 @@
         <v>13.5</v>
       </c>
       <c r="AC18">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18">
         <v>16</v>
@@ -5316,7 +5319,7 @@
         <v>15</v>
       </c>
       <c r="AS18">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT18">
         <v>8.199999999999999</v>
@@ -5328,7 +5331,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX18">
         <v>12.5</v>
@@ -5340,25 +5343,25 @@
         <v>12.5</v>
       </c>
       <c r="BA18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC18">
         <v>20</v>
       </c>
       <c r="BD18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE18">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF18">
         <v>16.5</v>
       </c>
       <c r="BG18">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH18">
         <v>3.45</v>
@@ -5421,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5432,25 +5435,25 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F19">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H19">
         <v>7.8</v>
       </c>
       <c r="I19">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J19">
         <v>4.7</v>
@@ -5468,7 +5471,7 @@
         <v>4.5</v>
       </c>
       <c r="O19">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P19">
         <v>2.22</v>
@@ -5480,7 +5483,7 @@
         <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T19">
         <v>1.91</v>
@@ -5537,7 +5540,7 @@
         <v>17.5</v>
       </c>
       <c r="AL19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM19">
         <v>150</v>
@@ -5555,10 +5558,10 @@
         <v>4.6</v>
       </c>
       <c r="AR19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS19">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT19">
         <v>7.2</v>
@@ -5567,10 +5570,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX19">
         <v>7</v>
@@ -5594,13 +5597,13 @@
         <v>4.7</v>
       </c>
       <c r="BE19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF19">
         <v>5</v>
       </c>
       <c r="BG19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5663,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5674,13 +5677,13 @@
         <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F20">
         <v>1.65</v>
@@ -5689,10 +5692,10 @@
         <v>1.74</v>
       </c>
       <c r="H20">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I20">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
         <v>3.85</v>
@@ -5713,7 +5716,7 @@
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q20">
         <v>1.98</v>
@@ -5728,7 +5731,7 @@
         <v>1.96</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
         <v>1.18</v>
@@ -5755,10 +5758,10 @@
         <v>11</v>
       </c>
       <c r="AD20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE20">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF20">
         <v>12</v>
@@ -5782,7 +5785,7 @@
         <v>48</v>
       </c>
       <c r="AM20">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN20">
         <v>13.5</v>
@@ -5803,7 +5806,7 @@
         <v>4.3</v>
       </c>
       <c r="AT20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU20">
         <v>6.8</v>
@@ -5842,7 +5845,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH20">
         <v>4.1</v>
@@ -5905,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5916,13 +5919,13 @@
         <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F21">
         <v>1.66</v>
@@ -5934,7 +5937,7 @@
         <v>4.9</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -6000,7 +6003,7 @@
         <v>25</v>
       </c>
       <c r="AE21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF21">
         <v>14</v>
@@ -6039,7 +6042,7 @@
         <v>15.5</v>
       </c>
       <c r="AR21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS21">
         <v>4.1</v>
@@ -6078,7 +6081,7 @@
         <v>3.8</v>
       </c>
       <c r="BE21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF21">
         <v>6.4</v>
@@ -6096,7 +6099,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -6108,13 +6111,13 @@
         <v>4.6</v>
       </c>
       <c r="BO21">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP21">
         <v>11.5</v>
       </c>
       <c r="BQ21">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BR21">
         <v>24</v>
@@ -6126,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="BU21">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -6147,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6158,13 +6161,13 @@
         <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F22">
         <v>3.2</v>
@@ -6185,7 +6188,7 @@
         <v>3.45</v>
       </c>
       <c r="L22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -6275,10 +6278,10 @@
         <v>25</v>
       </c>
       <c r="AP22">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ22">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR22">
         <v>13</v>
@@ -6296,13 +6299,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW22">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="AX22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY22">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
         <v>15</v>
@@ -6326,7 +6329,7 @@
         <v>4</v>
       </c>
       <c r="BG22">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BH22">
         <v>3.35</v>
@@ -6389,7 +6392,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6400,31 +6403,31 @@
         <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F23">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I23">
+        <v>4.3</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
         <v>4.5</v>
-      </c>
-      <c r="J23">
-        <v>4.1</v>
-      </c>
-      <c r="K23">
-        <v>4.7</v>
       </c>
       <c r="L23">
         <v>1.25</v>
@@ -6451,22 +6454,22 @@
         <v>2.34</v>
       </c>
       <c r="T23">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U23">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="X23">
         <v>29</v>
       </c>
       <c r="Y23">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z23">
         <v>40</v>
@@ -6484,7 +6487,7 @@
         <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF23">
         <v>15.5</v>
@@ -6511,16 +6514,16 @@
         <v>70</v>
       </c>
       <c r="AN23">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO23">
         <v>40</v>
       </c>
       <c r="AP23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR23">
         <v>21</v>
@@ -6529,31 +6532,31 @@
         <v>7.8</v>
       </c>
       <c r="AT23">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AU23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW23">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
       </c>
       <c r="AY23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ23">
         <v>5.7</v>
       </c>
       <c r="BA23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC23">
         <v>14.5</v>
@@ -6586,25 +6589,25 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN23">
         <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ23">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR23">
         <v>22</v>
       </c>
       <c r="BS23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT23">
         <v>8</v>
@@ -6616,7 +6619,7 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX23">
         <v>34</v>
@@ -6628,10 +6631,10 @@
         <v>15</v>
       </c>
       <c r="CA23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6642,31 +6645,31 @@
         <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F24">
         <v>8.199999999999999</v>
       </c>
       <c r="G24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H24">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I24">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="J24">
         <v>5.7</v>
       </c>
       <c r="K24">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L24">
         <v>1.22</v>
@@ -6681,7 +6684,7 @@
         <v>1.16</v>
       </c>
       <c r="P24">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q24">
         <v>1.5</v>
@@ -6696,7 +6699,7 @@
         <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
         <v>3.35</v>
@@ -6714,7 +6717,7 @@
         <v>11</v>
       </c>
       <c r="AA24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB24">
         <v>38</v>
@@ -6729,7 +6732,7 @@
         <v>13.5</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG24">
         <v>30</v>
@@ -6738,28 +6741,28 @@
         <v>23</v>
       </c>
       <c r="AI24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ24">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AK24">
         <v>100</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO24">
         <v>4.6</v>
       </c>
       <c r="AP24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
@@ -6771,10 +6774,10 @@
         <v>11.5</v>
       </c>
       <c r="AT24">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AU24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV24">
         <v>9.4</v>
@@ -6783,7 +6786,7 @@
         <v>12</v>
       </c>
       <c r="AX24">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AY24">
         <v>27</v>
@@ -6795,7 +6798,7 @@
         <v>23</v>
       </c>
       <c r="BB24">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BC24">
         <v>38</v>
@@ -6822,31 +6825,31 @@
         <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN24">
         <v>12</v>
       </c>
       <c r="BO24">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BP24">
         <v>60</v>
       </c>
       <c r="BQ24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR24">
         <v>55</v>
       </c>
       <c r="BS24">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BT24">
         <v>4.3</v>
@@ -6855,7 +6858,7 @@
         <v>3.35</v>
       </c>
       <c r="BV24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW24">
         <v>6</v>
@@ -6864,16 +6867,16 @@
         <v>19</v>
       </c>
       <c r="BY24">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA24">
         <v>6</v>
       </c>
       <c r="CB24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6884,19 +6887,19 @@
         <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F25">
         <v>1.5</v>
       </c>
       <c r="G25">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H25">
         <v>6.6</v>
@@ -6905,7 +6908,7 @@
         <v>7.2</v>
       </c>
       <c r="J25">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K25">
         <v>5.3</v>
@@ -6917,13 +6920,13 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O25">
         <v>1.16</v>
       </c>
       <c r="P25">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
         <v>1.5</v>
@@ -6935,10 +6938,10 @@
         <v>2.24</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V25">
         <v>1.16</v>
@@ -6962,7 +6965,7 @@
         <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD25">
         <v>27</v>
@@ -6977,7 +6980,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI25">
         <v>1000</v>
@@ -6992,7 +6995,7 @@
         <v>25</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN25">
         <v>5.2</v>
@@ -7001,7 +7004,7 @@
         <v>65</v>
       </c>
       <c r="AP25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ25">
         <v>29</v>
@@ -7013,7 +7016,7 @@
         <v>46</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU25">
         <v>11</v>
@@ -7043,10 +7046,10 @@
         <v>12.5</v>
       </c>
       <c r="BD25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE25">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BF25">
         <v>4.9</v>
@@ -7115,7 +7118,7 @@
         <v>6.2</v>
       </c>
       <c r="CB25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7126,16 +7129,16 @@
         <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G26">
         <v>1.16</v>
@@ -7255,7 +7258,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT26">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AU26">
         <v>21</v>
@@ -7267,25 +7270,25 @@
         <v>8.6</v>
       </c>
       <c r="AX26">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AY26">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AZ26">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BA26">
         <v>8.4</v>
       </c>
       <c r="BB26">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC26">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BD26">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BE26">
         <v>8.4</v>
@@ -7357,7 +7360,7 @@
         <v>4.5</v>
       </c>
       <c r="CB26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7368,28 +7371,28 @@
         <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F27">
         <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H27">
         <v>3.4</v>
       </c>
       <c r="I27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7398,37 +7401,37 @@
         <v>1.46</v>
       </c>
       <c r="M27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P27">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S27">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V27">
         <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X27">
         <v>13.5</v>
@@ -7443,22 +7446,22 @@
         <v>85</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG27">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
         <v>20</v>
@@ -7467,37 +7470,37 @@
         <v>70</v>
       </c>
       <c r="AJ27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL27">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM27">
         <v>140</v>
       </c>
       <c r="AN27">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO27">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP27">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ27">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AT27">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU27">
         <v>5.9</v>
@@ -7506,37 +7509,37 @@
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27">
         <v>16</v>
       </c>
       <c r="BA27">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB27">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE27">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG27">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BH27">
         <v>3.2</v>
@@ -7578,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="BU27">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV27">
         <v>34</v>
@@ -7599,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7610,49 +7613,49 @@
         <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F28">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G28">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H28">
         <v>3.8</v>
       </c>
       <c r="I28">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J28">
+        <v>3.15</v>
+      </c>
+      <c r="K28">
         <v>3.2</v>
       </c>
-      <c r="K28">
-        <v>3.3</v>
-      </c>
       <c r="L28">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M28">
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q28">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R28">
         <v>1.27</v>
@@ -7670,7 +7673,7 @@
         <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X28">
         <v>13</v>
@@ -7727,7 +7730,7 @@
         <v>65</v>
       </c>
       <c r="AP28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ28">
         <v>9.6</v>
@@ -7739,22 +7742,22 @@
         <v>7.8</v>
       </c>
       <c r="AT28">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU28">
         <v>6.2</v>
       </c>
       <c r="AV28">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW28">
         <v>38</v>
       </c>
       <c r="AX28">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY28">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28">
         <v>16</v>
@@ -7841,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7852,31 +7855,31 @@
         <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F29">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G29">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H29">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I29">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K29">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7885,142 +7888,142 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="O29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P29">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="R29">
         <v>2.48</v>
       </c>
       <c r="S29">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T29">
         <v>1.28</v>
       </c>
       <c r="U29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V29">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX29">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC29">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8083,7 +8086,7 @@
         <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8094,13 +8097,13 @@
         <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F30">
         <v>2.2</v>
@@ -8115,7 +8118,7 @@
         <v>3.5</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
         <v>3.9</v>
@@ -8142,7 +8145,7 @@
         <v>1.54</v>
       </c>
       <c r="S30">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T30">
         <v>1.59</v>
@@ -8160,7 +8163,7 @@
         <v>22</v>
       </c>
       <c r="Y30">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z30">
         <v>27</v>
@@ -8202,10 +8205,10 @@
         <v>29</v>
       </c>
       <c r="AM30">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO30">
         <v>26</v>
@@ -8268,7 +8271,7 @@
         <v>4.3</v>
       </c>
       <c r="BI30">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BJ30">
         <v>9.199999999999999</v>
@@ -8325,7 +8328,7 @@
         <v>6.4</v>
       </c>
       <c r="CB30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8336,16 +8339,16 @@
         <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F31">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G31">
         <v>2.38</v>
@@ -8354,13 +8357,13 @@
         <v>3.15</v>
       </c>
       <c r="I31">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J31">
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L31">
         <v>1.32</v>
@@ -8378,7 +8381,7 @@
         <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R31">
         <v>1.42</v>
@@ -8390,10 +8393,10 @@
         <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
         <v>1.72</v>
@@ -8402,7 +8405,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z31">
         <v>25</v>
@@ -8414,7 +8417,7 @@
         <v>12</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD31">
         <v>15</v>
@@ -8447,7 +8450,7 @@
         <v>100</v>
       </c>
       <c r="AN31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO31">
         <v>34</v>
@@ -8474,7 +8477,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX31">
         <v>13</v>
@@ -8486,19 +8489,19 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC31">
         <v>19.5</v>
       </c>
       <c r="BD31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE31">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF31">
         <v>12</v>
@@ -8567,7 +8570,7 @@
         <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8578,31 +8581,31 @@
         <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F32">
         <v>1.58</v>
       </c>
       <c r="G32">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H32">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L32">
         <v>1.25</v>
@@ -8611,22 +8614,22 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P32">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q32">
         <v>1.59</v>
       </c>
       <c r="R32">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S32">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T32">
         <v>1.65</v>
@@ -8644,40 +8647,40 @@
         <v>27</v>
       </c>
       <c r="Y32">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z32">
         <v>60</v>
       </c>
       <c r="AA32">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB32">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD32">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE32">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH32">
         <v>18.5</v>
       </c>
       <c r="AI32">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ32">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK32">
         <v>16.5</v>
@@ -8686,37 +8689,37 @@
         <v>29</v>
       </c>
       <c r="AM32">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO32">
         <v>70</v>
       </c>
       <c r="AP32">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ32">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="AR32">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS32">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT32">
         <v>9.800000000000001</v>
       </c>
       <c r="AU32">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV32">
         <v>19.5</v>
       </c>
       <c r="AW32">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX32">
         <v>10</v>
@@ -8725,28 +8728,28 @@
         <v>8</v>
       </c>
       <c r="AZ32">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA32">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD32">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BE32">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF32">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG32">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH32">
         <v>4.6</v>
@@ -8809,7 +8812,7 @@
         <v>5.7</v>
       </c>
       <c r="CB32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8820,16 +8823,16 @@
         <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F33">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -8847,10 +8850,10 @@
         <v>3.2</v>
       </c>
       <c r="L33">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M33">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N33">
         <v>2.16</v>
@@ -8862,7 +8865,7 @@
         <v>1.38</v>
       </c>
       <c r="Q33">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="R33">
         <v>1.13</v>
@@ -8877,13 +8880,13 @@
         <v>1.59</v>
       </c>
       <c r="V33">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
         <v>1.25</v>
       </c>
       <c r="X33">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y33">
         <v>6.8</v>
@@ -8940,55 +8943,55 @@
         <v>3.4</v>
       </c>
       <c r="AQ33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR33">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS33">
+        <v>5.7</v>
+      </c>
+      <c r="AT33">
+        <v>4.1</v>
+      </c>
+      <c r="AU33">
+        <v>3.5</v>
+      </c>
+      <c r="AV33">
+        <v>4.6</v>
+      </c>
+      <c r="AW33">
+        <v>5.7</v>
+      </c>
+      <c r="AX33">
         <v>5.4</v>
       </c>
-      <c r="AT33">
-        <v>4</v>
-      </c>
-      <c r="AU33">
-        <v>3.4</v>
-      </c>
-      <c r="AV33">
-        <v>4.4</v>
-      </c>
-      <c r="AW33">
+      <c r="AY33">
+        <v>5.1</v>
+      </c>
+      <c r="AZ33">
         <v>5.4</v>
       </c>
-      <c r="AX33">
-        <v>5.1</v>
-      </c>
-      <c r="AY33">
-        <v>4.8</v>
-      </c>
-      <c r="AZ33">
-        <v>5.1</v>
-      </c>
       <c r="BA33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB33">
+        <v>6.2</v>
+      </c>
+      <c r="BC33">
+        <v>6</v>
+      </c>
+      <c r="BD33">
+        <v>6.2</v>
+      </c>
+      <c r="BE33">
+        <v>6.4</v>
+      </c>
+      <c r="BF33">
+        <v>6.2</v>
+      </c>
+      <c r="BG33">
         <v>5.8</v>
-      </c>
-      <c r="BC33">
-        <v>5.7</v>
-      </c>
-      <c r="BD33">
-        <v>5.9</v>
-      </c>
-      <c r="BE33">
-        <v>6</v>
-      </c>
-      <c r="BF33">
-        <v>5.9</v>
-      </c>
-      <c r="BG33">
-        <v>5.5</v>
       </c>
       <c r="BH33">
         <v>2.52</v>
@@ -9051,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9062,28 +9065,28 @@
         <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F34">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G34">
         <v>990</v>
       </c>
       <c r="H34">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I34">
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9293,7 +9296,7 @@
         <v>1.04</v>
       </c>
       <c r="CB34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9304,16 +9307,16 @@
         <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G35">
         <v>3.4</v>
@@ -9322,7 +9325,7 @@
         <v>2.38</v>
       </c>
       <c r="I35">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J35">
         <v>3.3</v>
@@ -9361,7 +9364,7 @@
         <v>2.12</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
         <v>1.42</v>
@@ -9451,7 +9454,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA35">
         <v>6.6</v>
@@ -9535,7 +9538,7 @@
         <v>7.6</v>
       </c>
       <c r="CB35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9546,28 +9549,28 @@
         <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F36">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G36">
         <v>990</v>
       </c>
       <c r="H36">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="I36">
         <v>990</v>
       </c>
       <c r="J36">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="K36">
         <v>950</v>
@@ -9579,22 +9582,22 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="O36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P36">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q36">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R36">
         <v>1.12</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
         <v>1.11</v>
@@ -9603,10 +9606,10 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W36">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9777,7 +9780,7 @@
         <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9788,40 +9791,40 @@
         <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F37">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G37">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H37">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I37">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J37">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L37">
         <v>1.3</v>
       </c>
       <c r="M37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O37">
         <v>1.27</v>
@@ -9848,13 +9851,13 @@
         <v>1.24</v>
       </c>
       <c r="W37">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X37">
         <v>21</v>
       </c>
       <c r="Y37">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z37">
         <v>46</v>
@@ -9884,7 +9887,7 @@
         <v>19</v>
       </c>
       <c r="AI37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ37">
         <v>20</v>
@@ -9893,7 +9896,7 @@
         <v>970</v>
       </c>
       <c r="AL37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM37">
         <v>110</v>
@@ -9911,10 +9914,10 @@
         <v>16</v>
       </c>
       <c r="AR37">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT37">
         <v>7.2</v>
@@ -9926,7 +9929,7 @@
         <v>16.5</v>
       </c>
       <c r="AW37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9938,43 +9941,43 @@
         <v>16</v>
       </c>
       <c r="BA37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB37">
         <v>17</v>
       </c>
       <c r="BC37">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD37">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF37">
         <v>9.199999999999999</v>
       </c>
       <c r="BG37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH37">
         <v>3.7</v>
       </c>
       <c r="BI37">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ37">
         <v>9.6</v>
       </c>
       <c r="BK37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN37">
         <v>4.6</v>
@@ -10004,13 +10007,13 @@
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
@@ -10019,7 +10022,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB37" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10030,13 +10033,13 @@
         <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F38">
         <v>1.22</v>
@@ -10051,13 +10054,13 @@
         <v>15.5</v>
       </c>
       <c r="J38">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M38">
         <v>1.02</v>
@@ -10069,31 +10072,31 @@
         <v>1.11</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S38">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T38">
         <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V38">
         <v>1.06</v>
       </c>
       <c r="W38">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="X38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y38">
         <v>80</v>
@@ -10105,7 +10108,7 @@
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC38">
         <v>20</v>
@@ -10123,16 +10126,16 @@
         <v>12</v>
       </c>
       <c r="AH38">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AI38">
         <v>160</v>
       </c>
       <c r="AJ38">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL38">
         <v>32</v>
@@ -10141,34 +10144,34 @@
         <v>150</v>
       </c>
       <c r="AN38">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AO38">
         <v>230</v>
       </c>
       <c r="AP38">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AQ38">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT38">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU38">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AV38">
         <v>42</v>
       </c>
       <c r="AW38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX38">
         <v>9.4</v>
@@ -10177,25 +10180,25 @@
         <v>11</v>
       </c>
       <c r="AZ38">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA38">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BB38">
         <v>9.4</v>
       </c>
       <c r="BC38">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF38">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BG38">
         <v>11.5</v>
@@ -10261,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10272,13 +10275,13 @@
         <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F39">
         <v>3.1</v>
@@ -10299,7 +10302,7 @@
         <v>3.3</v>
       </c>
       <c r="L39">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M39">
         <v>1.12</v>
@@ -10440,7 +10443,7 @@
         <v>5.8</v>
       </c>
       <c r="BG39">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="BH39">
         <v>2.82</v>
@@ -10503,7 +10506,7 @@
         <v>9</v>
       </c>
       <c r="CB39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10514,16 +10517,16 @@
         <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F40">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G40">
         <v>1.65</v>
@@ -10532,7 +10535,7 @@
         <v>7.2</v>
       </c>
       <c r="I40">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J40">
         <v>3.85</v>
@@ -10544,13 +10547,13 @@
         <v>1.39</v>
       </c>
       <c r="M40">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P40">
         <v>1.76</v>
@@ -10559,37 +10562,37 @@
         <v>2.08</v>
       </c>
       <c r="R40">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S40">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U40">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W40">
         <v>2.52</v>
       </c>
       <c r="X40">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y40">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z40">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA40">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB40">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC40">
         <v>11</v>
@@ -10601,7 +10604,7 @@
         <v>160</v>
       </c>
       <c r="AF40">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG40">
         <v>12</v>
@@ -10613,34 +10616,34 @@
         <v>160</v>
       </c>
       <c r="AJ40">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL40">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM40">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AN40">
         <v>13.5</v>
       </c>
       <c r="AO40">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AP40">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ40">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AR40">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS40">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AT40">
         <v>6</v>
@@ -10649,40 +10652,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV40">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="AW40">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX40">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY40">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ40">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="BA40">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB40">
         <v>13</v>
       </c>
       <c r="BC40">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD40">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE40">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BF40">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG40">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BH40">
         <v>3.2</v>
@@ -10745,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10756,19 +10759,19 @@
         <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F41">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G41">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H41">
         <v>4.8</v>
@@ -10780,7 +10783,7 @@
         <v>3.5</v>
       </c>
       <c r="K41">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L41">
         <v>1.42</v>
@@ -10789,34 +10792,34 @@
         <v>1.08</v>
       </c>
       <c r="N41">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O41">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P41">
         <v>1.77</v>
       </c>
       <c r="Q41">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R41">
         <v>1.29</v>
       </c>
       <c r="S41">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T41">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U41">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V41">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W41">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X41">
         <v>15.5</v>
@@ -10840,7 +10843,7 @@
         <v>22</v>
       </c>
       <c r="AE41">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF41">
         <v>13</v>
@@ -10855,7 +10858,7 @@
         <v>100</v>
       </c>
       <c r="AJ41">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK41">
         <v>22</v>
@@ -10894,13 +10897,13 @@
         <v>15</v>
       </c>
       <c r="AW41">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX41">
         <v>7.8</v>
       </c>
       <c r="AY41">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ41">
         <v>15.5</v>
@@ -10924,7 +10927,7 @@
         <v>10.5</v>
       </c>
       <c r="BG41">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH41">
         <v>3.35</v>
@@ -10987,7 +10990,7 @@
         <v>7.4</v>
       </c>
       <c r="CB41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -10998,13 +11001,13 @@
         <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F42">
         <v>2.28</v>
@@ -11229,30 +11232,30 @@
         <v>1.04</v>
       </c>
       <c r="CB42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
         <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F43">
         <v>3.65</v>
       </c>
       <c r="G43">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H43">
         <v>2.36</v>
@@ -11264,7 +11267,7 @@
         <v>3.1</v>
       </c>
       <c r="K43">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L43">
         <v>1.56</v>
@@ -11273,16 +11276,16 @@
         <v>1.13</v>
       </c>
       <c r="N43">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O43">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P43">
         <v>1.54</v>
       </c>
       <c r="Q43">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R43">
         <v>1.19</v>
@@ -11297,13 +11300,13 @@
         <v>1.78</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W43">
         <v>1.35</v>
       </c>
       <c r="X43">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y43">
         <v>7.4</v>
@@ -11315,10 +11318,10 @@
         <v>34</v>
       </c>
       <c r="AB43">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC43">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD43">
         <v>12.5</v>
@@ -11339,16 +11342,16 @@
         <v>65</v>
       </c>
       <c r="AJ43">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK43">
         <v>65</v>
       </c>
       <c r="AL43">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN43">
         <v>90</v>
@@ -11360,13 +11363,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ43">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR43">
         <v>11.5</v>
       </c>
       <c r="AS43">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AT43">
         <v>9.4</v>
@@ -11378,7 +11381,7 @@
         <v>11</v>
       </c>
       <c r="AW43">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX43">
         <v>21</v>
@@ -11387,19 +11390,19 @@
         <v>15</v>
       </c>
       <c r="AZ43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB43">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC43">
         <v>50</v>
       </c>
       <c r="BD43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE43">
         <v>48</v>
@@ -11408,13 +11411,13 @@
         <v>34</v>
       </c>
       <c r="BG43">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH43">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI43">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ43">
         <v>11</v>
@@ -11438,16 +11441,16 @@
         <v>36</v>
       </c>
       <c r="BQ43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT43">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU43">
         <v>4</v>
@@ -11456,7 +11459,7 @@
         <v>21</v>
       </c>
       <c r="BW43">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX43">
         <v>1000</v>
@@ -11465,13 +11468,13 @@
         <v>12</v>
       </c>
       <c r="BZ43">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA43">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11482,175 +11485,175 @@
         <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F44">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="G44">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H44">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="J44">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="K44">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="L44">
         <v>1.01</v>
       </c>
       <c r="M44">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N44">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="O44">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="P44">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q44">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S44">
-        <v>2.98</v>
+        <v>5.7</v>
       </c>
       <c r="T44">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U44">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X44">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB44">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC44">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD44">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE44">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF44">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG44">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH44">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI44">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK44">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL44">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM44">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN44">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO44">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP44">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ44">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR44">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS44">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT44">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU44">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV44">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW44">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX44">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY44">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ44">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA44">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB44">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC44">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD44">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE44">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF44">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG44">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11713,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11724,34 +11727,34 @@
         <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G45">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H45">
         <v>2.2</v>
       </c>
       <c r="I45">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="J45">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K45">
         <v>3.95</v>
       </c>
       <c r="L45">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M45">
         <v>1.06</v>
@@ -11772,19 +11775,19 @@
         <v>1.34</v>
       </c>
       <c r="S45">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T45">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U45">
         <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W45">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X45">
         <v>18</v>
@@ -11955,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11966,31 +11969,31 @@
         <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -11999,7 +12002,7 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O46">
         <v>1.41</v>
@@ -12008,13 +12011,13 @@
         <v>1.25</v>
       </c>
       <c r="Q46">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="R46">
         <v>1.18</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="T46">
         <v>1.11</v>
@@ -12023,10 +12026,10 @@
         <v>1.11</v>
       </c>
       <c r="V46">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12197,7 +12200,7 @@
         <v>1.04</v>
       </c>
       <c r="CB46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12208,28 +12211,28 @@
         <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F47">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G47">
         <v>990</v>
       </c>
       <c r="H47">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I47">
         <v>990</v>
       </c>
       <c r="J47">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12241,13 +12244,13 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O47">
         <v>1.01</v>
       </c>
       <c r="P47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q47">
         <v>1.42</v>
@@ -12265,10 +12268,10 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12439,24 +12442,24 @@
         <v>1.04</v>
       </c>
       <c r="CB47" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
         <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F48">
         <v>2.66</v>
@@ -12471,7 +12474,7 @@
         <v>3.5</v>
       </c>
       <c r="J48">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K48">
         <v>2.96</v>
@@ -12498,19 +12501,19 @@
         <v>1.14</v>
       </c>
       <c r="S48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T48">
         <v>2.36</v>
       </c>
       <c r="U48">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V48">
         <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X48">
         <v>7</v>
@@ -12558,7 +12561,7 @@
         <v>1000</v>
       </c>
       <c r="AM48">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="AN48">
         <v>65</v>
@@ -12567,16 +12570,16 @@
         <v>1000</v>
       </c>
       <c r="AP48">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ48">
         <v>7.6</v>
       </c>
       <c r="AR48">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS48">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT48">
         <v>6.4</v>
@@ -12591,10 +12594,10 @@
         <v>30</v>
       </c>
       <c r="AX48">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY48">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ48">
         <v>21</v>
@@ -12606,7 +12609,7 @@
         <v>40</v>
       </c>
       <c r="BC48">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BD48">
         <v>36</v>
@@ -12681,24 +12684,24 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CB48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
         <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F49">
         <v>2.68</v>
@@ -12725,7 +12728,7 @@
         <v>1.13</v>
       </c>
       <c r="N49">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O49">
         <v>1.55</v>
@@ -12779,7 +12782,7 @@
         <v>170</v>
       </c>
       <c r="AF49">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG49">
         <v>13.5</v>
@@ -12923,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="CB49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:80">
@@ -12934,19 +12937,19 @@
         <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F50">
         <v>1.72</v>
       </c>
       <c r="G50">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H50">
         <v>6.2</v>
@@ -12991,7 +12994,7 @@
         <v>1.66</v>
       </c>
       <c r="V50">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W50">
         <v>2.24</v>
@@ -13000,7 +13003,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y50">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z50">
         <v>60</v>
@@ -13015,7 +13018,7 @@
         <v>8.6</v>
       </c>
       <c r="AD50">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE50">
         <v>1000</v>
@@ -13069,7 +13072,7 @@
         <v>7.4</v>
       </c>
       <c r="AV50">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW50">
         <v>40</v>
@@ -13108,13 +13111,13 @@
         <v>2.9</v>
       </c>
       <c r="BI50">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="BJ50">
         <v>13</v>
       </c>
       <c r="BK50">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BL50">
         <v>1000</v>
@@ -13126,7 +13129,7 @@
         <v>4.2</v>
       </c>
       <c r="BO50">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BP50">
         <v>14</v>
@@ -13144,7 +13147,7 @@
         <v>10.5</v>
       </c>
       <c r="BU50">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BV50">
         <v>1000</v>
@@ -13165,7 +13168,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13176,13 +13179,13 @@
         <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F51">
         <v>1.89</v>
@@ -13407,7 +13410,7 @@
         <v>1.35</v>
       </c>
       <c r="CB51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="240">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
     <t>Costa Rican Primera Division</t>
   </si>
   <si>
-    <t>Argentinian Primera Division</t>
-  </si>
-  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -361,9 +361,6 @@
     <t>2026-08-03</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>00:30:00</t>
   </si>
   <si>
@@ -436,12 +433,12 @@
     <t>22:30:00</t>
   </si>
   <si>
+    <t>Lanus</t>
+  </si>
+  <si>
     <t>Inter San Carlos</t>
   </si>
   <si>
-    <t>Lanus</t>
-  </si>
-  <si>
     <t>Santa Fe</t>
   </si>
   <si>
@@ -586,12 +583,12 @@
     <t>Caracas</t>
   </si>
   <si>
+    <t>Instituto</t>
+  </si>
+  <si>
     <t>Cs Herediano</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
     <t>Once Caldas</t>
   </si>
   <si>
@@ -736,7 +733,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-02 18:42:52</t>
+    <t>2026-08-02 20:52:13</t>
   </si>
 </sst>
 </file>
@@ -1324,235 +1321,235 @@
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F2">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
+        <v>1.67</v>
+      </c>
+      <c r="M2">
+        <v>1.15</v>
+      </c>
+      <c r="N2">
+        <v>2.5</v>
+      </c>
+      <c r="O2">
+        <v>1.65</v>
+      </c>
+      <c r="P2">
         <v>1.47</v>
       </c>
-      <c r="M2">
-        <v>1.09</v>
-      </c>
-      <c r="N2">
-        <v>3.25</v>
-      </c>
-      <c r="O2">
-        <v>1.43</v>
-      </c>
-      <c r="P2">
-        <v>1.74</v>
-      </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AA2">
+        <v>120</v>
+      </c>
+      <c r="AB2">
+        <v>6.6</v>
+      </c>
+      <c r="AC2">
+        <v>7.4</v>
+      </c>
+      <c r="AD2">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>95</v>
+      </c>
+      <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
         <v>29</v>
       </c>
-      <c r="AB2">
-        <v>13</v>
-      </c>
-      <c r="AC2">
+      <c r="AI2">
+        <v>170</v>
+      </c>
+      <c r="AJ2">
+        <v>30</v>
+      </c>
+      <c r="AK2">
+        <v>34</v>
+      </c>
+      <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>250</v>
+      </c>
+      <c r="AN2">
+        <v>36</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
+        <v>9.6</v>
+      </c>
+      <c r="AR2">
+        <v>25</v>
+      </c>
+      <c r="AS2">
+        <v>40</v>
+      </c>
+      <c r="AT2">
+        <v>6</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>18</v>
+      </c>
+      <c r="AW2">
+        <v>38</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2">
+        <v>26</v>
+      </c>
+      <c r="BA2">
+        <v>42</v>
+      </c>
+      <c r="BB2">
+        <v>25</v>
+      </c>
+      <c r="BC2">
+        <v>30</v>
+      </c>
+      <c r="BD2">
+        <v>46</v>
+      </c>
+      <c r="BE2">
+        <v>160</v>
+      </c>
+      <c r="BF2">
+        <v>30</v>
+      </c>
+      <c r="BG2">
+        <v>46</v>
+      </c>
+      <c r="BH2">
+        <v>2.52</v>
+      </c>
+      <c r="BI2">
+        <v>2.4</v>
+      </c>
+      <c r="BJ2">
+        <v>12.5</v>
+      </c>
+      <c r="BK2">
         <v>8</v>
       </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
-      <c r="AE2">
-        <v>27</v>
-      </c>
-      <c r="AF2">
-        <v>28</v>
-      </c>
-      <c r="AG2">
-        <v>16.5</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>46</v>
-      </c>
-      <c r="AJ2">
-        <v>85</v>
-      </c>
-      <c r="AK2">
-        <v>55</v>
-      </c>
-      <c r="AL2">
-        <v>85</v>
-      </c>
-      <c r="AM2">
-        <v>160</v>
-      </c>
-      <c r="AN2">
-        <v>80</v>
-      </c>
-      <c r="AO2">
-        <v>23</v>
-      </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>220</v>
+      </c>
+      <c r="BN2">
+        <v>4.6</v>
+      </c>
+      <c r="BO2">
+        <v>4.3</v>
+      </c>
+      <c r="BP2">
+        <v>19.5</v>
+      </c>
+      <c r="BQ2">
+        <v>10.5</v>
+      </c>
+      <c r="BR2">
+        <v>48</v>
+      </c>
+      <c r="BS2">
+        <v>14.5</v>
+      </c>
+      <c r="BT2">
         <v>7.4</v>
       </c>
-      <c r="AR2">
-        <v>11.5</v>
-      </c>
-      <c r="AS2">
-        <v>23</v>
-      </c>
-      <c r="AT2">
-        <v>10.5</v>
-      </c>
-      <c r="AU2">
+      <c r="BU2">
         <v>6.6</v>
       </c>
-      <c r="AV2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>21</v>
-      </c>
-      <c r="AX2">
-        <v>22</v>
-      </c>
-      <c r="AY2">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2">
-        <v>17</v>
-      </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
+      <c r="BV2">
         <v>50</v>
       </c>
-      <c r="BC2">
-        <v>32</v>
-      </c>
-      <c r="BD2">
-        <v>42</v>
-      </c>
-      <c r="BE2">
-        <v>11</v>
-      </c>
-      <c r="BF2">
-        <v>40</v>
-      </c>
-      <c r="BG2">
-        <v>18.5</v>
-      </c>
-      <c r="BH2">
-        <v>3.2</v>
-      </c>
-      <c r="BI2">
-        <v>2.58</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
-      <c r="BK2">
-        <v>5.3</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>9.6</v>
-      </c>
-      <c r="BN2">
-        <v>7.2</v>
-      </c>
-      <c r="BO2">
-        <v>6</v>
-      </c>
-      <c r="BP2">
-        <v>36</v>
-      </c>
-      <c r="BQ2">
-        <v>8</v>
-      </c>
-      <c r="BR2">
-        <v>50</v>
-      </c>
-      <c r="BS2">
-        <v>8.4</v>
-      </c>
-      <c r="BT2">
-        <v>5.1</v>
-      </c>
-      <c r="BU2">
-        <v>4.2</v>
-      </c>
-      <c r="BV2">
-        <v>18</v>
-      </c>
       <c r="BW2">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BX2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1563,238 +1560,238 @@
         <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3">
+        <v>3.65</v>
+      </c>
+      <c r="G3">
+        <v>3.95</v>
+      </c>
+      <c r="H3">
         <v>2.24</v>
       </c>
-      <c r="G3">
+      <c r="I3">
+        <v>2.32</v>
+      </c>
+      <c r="J3">
+        <v>3.3</v>
+      </c>
+      <c r="K3">
+        <v>3.45</v>
+      </c>
+      <c r="L3">
+        <v>1.47</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
+        <v>3.2</v>
+      </c>
+      <c r="O3">
+        <v>1.43</v>
+      </c>
+      <c r="P3">
+        <v>1.74</v>
+      </c>
+      <c r="Q3">
         <v>2.26</v>
       </c>
-      <c r="H3">
+      <c r="R3">
+        <v>1.27</v>
+      </c>
+      <c r="S3">
         <v>4.3</v>
       </c>
-      <c r="I3">
-        <v>4.4</v>
-      </c>
-      <c r="J3">
-        <v>3.05</v>
-      </c>
-      <c r="K3">
-        <v>3.1</v>
-      </c>
-      <c r="L3">
-        <v>1.67</v>
-      </c>
-      <c r="M3">
-        <v>1.16</v>
-      </c>
-      <c r="N3">
-        <v>2.5</v>
-      </c>
-      <c r="O3">
-        <v>1.65</v>
-      </c>
-      <c r="P3">
-        <v>1.48</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3">
-        <v>1.16</v>
-      </c>
-      <c r="S3">
+      <c r="T3">
+        <v>1.94</v>
+      </c>
+      <c r="U3">
+        <v>1.96</v>
+      </c>
+      <c r="V3">
+        <v>1.76</v>
+      </c>
+      <c r="W3">
+        <v>1.34</v>
+      </c>
+      <c r="X3">
+        <v>12</v>
+      </c>
+      <c r="Y3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z3">
+        <v>14</v>
+      </c>
+      <c r="AA3">
+        <v>32</v>
+      </c>
+      <c r="AB3">
+        <v>13</v>
+      </c>
+      <c r="AC3">
+        <v>8</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
+        <v>27</v>
+      </c>
+      <c r="AF3">
+        <v>27</v>
+      </c>
+      <c r="AG3">
+        <v>16.5</v>
+      </c>
+      <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>46</v>
+      </c>
+      <c r="AJ3">
+        <v>90</v>
+      </c>
+      <c r="AK3">
+        <v>55</v>
+      </c>
+      <c r="AL3">
+        <v>85</v>
+      </c>
+      <c r="AM3">
+        <v>160</v>
+      </c>
+      <c r="AN3">
+        <v>80</v>
+      </c>
+      <c r="AO3">
+        <v>23</v>
+      </c>
+      <c r="AP3">
+        <v>10</v>
+      </c>
+      <c r="AQ3">
+        <v>7.4</v>
+      </c>
+      <c r="AR3">
+        <v>12.5</v>
+      </c>
+      <c r="AS3">
+        <v>23</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>9.6</v>
+      </c>
+      <c r="AW3">
+        <v>21</v>
+      </c>
+      <c r="AX3">
+        <v>22</v>
+      </c>
+      <c r="AY3">
+        <v>13.5</v>
+      </c>
+      <c r="AZ3">
+        <v>17</v>
+      </c>
+      <c r="BA3">
+        <v>32</v>
+      </c>
+      <c r="BB3">
+        <v>50</v>
+      </c>
+      <c r="BC3">
+        <v>34</v>
+      </c>
+      <c r="BD3">
+        <v>44</v>
+      </c>
+      <c r="BE3">
+        <v>95</v>
+      </c>
+      <c r="BF3">
+        <v>42</v>
+      </c>
+      <c r="BG3">
+        <v>18.5</v>
+      </c>
+      <c r="BH3">
+        <v>3.2</v>
+      </c>
+      <c r="BI3">
+        <v>2.58</v>
+      </c>
+      <c r="BJ3">
+        <v>10.5</v>
+      </c>
+      <c r="BK3">
+        <v>5.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>120</v>
+      </c>
+      <c r="BN3">
+        <v>7.2</v>
+      </c>
+      <c r="BO3">
+        <v>6</v>
+      </c>
+      <c r="BP3">
+        <v>34</v>
+      </c>
+      <c r="BQ3">
+        <v>8.4</v>
+      </c>
+      <c r="BR3">
+        <v>50</v>
+      </c>
+      <c r="BS3">
+        <v>9</v>
+      </c>
+      <c r="BT3">
+        <v>5.1</v>
+      </c>
+      <c r="BU3">
+        <v>4.2</v>
+      </c>
+      <c r="BV3">
+        <v>18</v>
+      </c>
+      <c r="BW3">
         <v>6.8</v>
       </c>
-      <c r="T3">
-        <v>2.4</v>
-      </c>
-      <c r="U3">
-        <v>1.68</v>
-      </c>
-      <c r="V3">
-        <v>1.29</v>
-      </c>
-      <c r="W3">
-        <v>1.79</v>
-      </c>
-      <c r="X3">
-        <v>7.6</v>
-      </c>
-      <c r="Y3">
-        <v>11</v>
-      </c>
-      <c r="Z3">
-        <v>29</v>
-      </c>
-      <c r="AA3">
-        <v>120</v>
-      </c>
-      <c r="AB3">
-        <v>6.6</v>
-      </c>
-      <c r="AC3">
-        <v>7.2</v>
-      </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>95</v>
-      </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>29</v>
-      </c>
-      <c r="AI3">
-        <v>130</v>
-      </c>
-      <c r="AJ3">
-        <v>30</v>
-      </c>
-      <c r="AK3">
-        <v>38</v>
-      </c>
-      <c r="AL3">
-        <v>75</v>
-      </c>
-      <c r="AM3">
-        <v>250</v>
-      </c>
-      <c r="AN3">
+      <c r="BX3">
         <v>36</v>
       </c>
-      <c r="AO3">
-        <v>160</v>
-      </c>
-      <c r="AP3">
-        <v>6.8</v>
-      </c>
-      <c r="AQ3">
-        <v>9.6</v>
-      </c>
-      <c r="AR3">
-        <v>25</v>
-      </c>
-      <c r="AS3">
-        <v>65</v>
-      </c>
-      <c r="AT3">
-        <v>6</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>18</v>
-      </c>
-      <c r="AW3">
-        <v>65</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>26</v>
-      </c>
-      <c r="BA3">
-        <v>95</v>
-      </c>
-      <c r="BB3">
-        <v>27</v>
-      </c>
-      <c r="BC3">
-        <v>30</v>
-      </c>
-      <c r="BD3">
-        <v>55</v>
-      </c>
-      <c r="BE3">
-        <v>55</v>
-      </c>
-      <c r="BF3">
-        <v>30</v>
-      </c>
-      <c r="BG3">
-        <v>42</v>
-      </c>
-      <c r="BH3">
-        <v>2.54</v>
-      </c>
-      <c r="BI3">
-        <v>2.4</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>7.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>17.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.6</v>
-      </c>
-      <c r="BO3">
-        <v>4.3</v>
-      </c>
-      <c r="BP3">
-        <v>19.5</v>
-      </c>
-      <c r="BQ3">
-        <v>9.4</v>
-      </c>
-      <c r="BR3">
-        <v>48</v>
-      </c>
-      <c r="BS3">
-        <v>13.5</v>
-      </c>
-      <c r="BT3">
-        <v>7.8</v>
-      </c>
-      <c r="BU3">
-        <v>5.5</v>
-      </c>
-      <c r="BV3">
-        <v>50</v>
-      </c>
-      <c r="BW3">
-        <v>13.5</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
       <c r="BY3">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1805,34 +1802,34 @@
         <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F4">
+        <v>2.2</v>
+      </c>
+      <c r="G4">
         <v>2.26</v>
       </c>
-      <c r="G4">
-        <v>2.3</v>
-      </c>
       <c r="H4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1841,76 +1838,76 @@
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>1.87</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X4">
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE4">
         <v>55</v>
       </c>
       <c r="AF4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>28</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4">
         <v>120</v>
@@ -1919,19 +1916,19 @@
         <v>21</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP4">
         <v>11</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
         <v>23</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1940,103 +1937,103 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
+        <v>14.5</v>
+      </c>
+      <c r="AW4">
         <v>14</v>
-      </c>
-      <c r="AW4">
-        <v>34</v>
       </c>
       <c r="AX4">
         <v>12</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>14.5</v>
       </c>
       <c r="BB4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4">
         <v>38</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>150</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4">
         <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV4">
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2047,28 +2044,28 @@
         <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H5">
+        <v>6.6</v>
+      </c>
+      <c r="I5">
         <v>6.8</v>
       </c>
-      <c r="I5">
-        <v>7.2</v>
-      </c>
       <c r="J5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K5">
         <v>5.3</v>
@@ -2083,31 +2080,31 @@
         <v>6.4</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R5">
         <v>1.73</v>
       </c>
       <c r="S5">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T5">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -2116,10 +2113,10 @@
         <v>32</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -2128,16 +2125,16 @@
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH5">
         <v>19</v>
@@ -2152,19 +2149,19 @@
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO5">
         <v>70</v>
       </c>
       <c r="AP5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ5">
         <v>30</v>
@@ -2173,31 +2170,31 @@
         <v>50</v>
       </c>
       <c r="AS5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX5">
         <v>10</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -2209,37 +2206,37 @@
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF5">
         <v>5</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
         <v>8.4</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM5">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>8.800000000000001</v>
@@ -2248,10 +2245,10 @@
         <v>8</v>
       </c>
       <c r="BR5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BT5">
         <v>10.5</v>
@@ -2263,22 +2260,22 @@
         <v>48</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA5">
         <v>10</v>
       </c>
       <c r="CB5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2289,25 +2286,25 @@
         <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6">
         <v>1.27</v>
       </c>
       <c r="G6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>5.6</v>
@@ -2319,7 +2316,7 @@
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
         <v>5.1</v>
@@ -2334,16 +2331,16 @@
         <v>1.59</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
         <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V6">
         <v>1.07</v>
@@ -2352,7 +2349,7 @@
         <v>3.9</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6">
         <v>50</v>
@@ -2364,10 +2361,10 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD6">
         <v>55</v>
@@ -2376,7 +2373,7 @@
         <v>280</v>
       </c>
       <c r="AF6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2400,46 +2397,46 @@
         <v>210</v>
       </c>
       <c r="AN6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AO6">
         <v>380</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
         <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6">
         <v>6.8</v>
       </c>
       <c r="AY6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB6">
         <v>8</v>
@@ -2451,16 +2448,16 @@
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI6">
         <v>3.4</v>
@@ -2475,52 +2472,52 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN6">
         <v>4</v>
       </c>
       <c r="BO6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
         <v>7.6</v>
       </c>
       <c r="BQ6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
         <v>11.5</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2531,25 +2528,25 @@
         <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F7">
         <v>3.35</v>
       </c>
       <c r="G7">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
         <v>2.16</v>
       </c>
       <c r="I7">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -2579,7 +2576,7 @@
         <v>1.23</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -2588,10 +2585,10 @@
         <v>1.86</v>
       </c>
       <c r="V7">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2609,16 +2606,16 @@
         <v>14</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG7">
         <v>17</v>
@@ -2627,79 +2624,79 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK7">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL7">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM7">
         <v>170</v>
       </c>
       <c r="AN7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP7">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AR7">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS7">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU7">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AV7">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AW7">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX7">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AY7">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA7">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC7">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD7">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE7">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF7">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG7">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH7">
         <v>3.1</v>
@@ -2762,7 +2759,7 @@
         <v>7.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2773,25 +2770,25 @@
         <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="I8">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -2806,22 +2803,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>1.1</v>
       </c>
       <c r="P8">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q8">
         <v>1.32</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="T8">
         <v>1.37</v>
@@ -2830,10 +2827,10 @@
         <v>3.3</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X8">
         <v>55</v>
@@ -2842,7 +2839,7 @@
         <v>27</v>
       </c>
       <c r="Z8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA8">
         <v>48</v>
@@ -2854,7 +2851,7 @@
         <v>14</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE8">
         <v>26</v>
@@ -2872,7 +2869,7 @@
         <v>24</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -2881,16 +2878,16 @@
         <v>25</v>
       </c>
       <c r="AM8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AN8">
         <v>9.199999999999999</v>
       </c>
       <c r="AO8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP8">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8">
         <v>20</v>
@@ -2899,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT8">
         <v>17.5</v>
@@ -2926,7 +2923,7 @@
         <v>18</v>
       </c>
       <c r="BB8">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2935,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="BE8">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BF8">
         <v>6.6</v>
@@ -2944,10 +2941,10 @@
         <v>7.6</v>
       </c>
       <c r="BH8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ8">
         <v>8</v>
@@ -2956,7 +2953,7 @@
         <v>5</v>
       </c>
       <c r="BL8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
         <v>10.5</v>
@@ -2965,13 +2962,13 @@
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
         <v>18</v>
@@ -2983,28 +2980,28 @@
         <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA8">
         <v>7.6</v>
       </c>
       <c r="CB8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3015,13 +3012,13 @@
         <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F9">
         <v>1.3</v>
@@ -3078,10 +3075,10 @@
         <v>3.75</v>
       </c>
       <c r="X9">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Y9">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z9">
         <v>120</v>
@@ -3096,7 +3093,7 @@
         <v>15.5</v>
       </c>
       <c r="AD9">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AE9">
         <v>160</v>
@@ -3111,7 +3108,7 @@
         <v>26</v>
       </c>
       <c r="AI9">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="AJ9">
         <v>12</v>
@@ -3123,7 +3120,7 @@
         <v>46</v>
       </c>
       <c r="AM9">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AN9">
         <v>4.1</v>
@@ -3132,16 +3129,16 @@
         <v>160</v>
       </c>
       <c r="AP9">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
@@ -3153,7 +3150,7 @@
         <v>26</v>
       </c>
       <c r="AW9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9">
         <v>8.6</v>
@@ -3165,7 +3162,7 @@
         <v>19.5</v>
       </c>
       <c r="BA9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB9">
         <v>9.4</v>
@@ -3177,13 +3174,13 @@
         <v>23</v>
       </c>
       <c r="BE9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF9">
         <v>3.45</v>
       </c>
       <c r="BG9">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
@@ -3246,7 +3243,7 @@
         <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3257,13 +3254,13 @@
         <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F10">
         <v>1.71</v>
@@ -3281,7 +3278,7 @@
         <v>3.85</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>1.33</v>
@@ -3320,58 +3317,58 @@
         <v>2.14</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y10">
         <v>21</v>
       </c>
       <c r="Z10">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA10">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC10">
+        <v>10</v>
+      </c>
+      <c r="AD10">
+        <v>21</v>
+      </c>
+      <c r="AE10">
+        <v>150</v>
+      </c>
+      <c r="AF10">
+        <v>12.5</v>
+      </c>
+      <c r="AG10">
         <v>11</v>
-      </c>
-      <c r="AD10">
-        <v>23</v>
-      </c>
-      <c r="AE10">
-        <v>75</v>
-      </c>
-      <c r="AF10">
-        <v>13.5</v>
-      </c>
-      <c r="AG10">
-        <v>12</v>
       </c>
       <c r="AH10">
         <v>22</v>
       </c>
       <c r="AI10">
+        <v>150</v>
+      </c>
+      <c r="AJ10">
+        <v>20</v>
+      </c>
+      <c r="AK10">
+        <v>19</v>
+      </c>
+      <c r="AL10">
         <v>80</v>
       </c>
-      <c r="AJ10">
-        <v>22</v>
-      </c>
-      <c r="AK10">
-        <v>21</v>
-      </c>
-      <c r="AL10">
-        <v>36</v>
-      </c>
       <c r="AM10">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO10">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="AP10">
         <v>14</v>
@@ -3380,10 +3377,10 @@
         <v>15</v>
       </c>
       <c r="AR10">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS10">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -3395,7 +3392,7 @@
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AX10">
         <v>9</v>
@@ -3407,7 +3404,7 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BB10">
         <v>14</v>
@@ -3416,16 +3413,16 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BE10">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF10">
         <v>7.4</v>
       </c>
       <c r="BG10">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH10">
         <v>4</v>
@@ -3488,7 +3485,7 @@
         <v>6.4</v>
       </c>
       <c r="CB10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3499,13 +3496,13 @@
         <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F11">
         <v>1.16</v>
@@ -3514,7 +3511,7 @@
         <v>1.19</v>
       </c>
       <c r="H11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11">
         <v>26</v>
@@ -3610,22 +3607,22 @@
         <v>310</v>
       </c>
       <c r="AN11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR11">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS11">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT11">
         <v>9.6</v>
@@ -3634,10 +3631,10 @@
         <v>17.5</v>
       </c>
       <c r="AV11">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AW11">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX11">
         <v>6.2</v>
@@ -3646,10 +3643,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA11">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
         <v>6.2</v>
@@ -3658,16 +3655,16 @@
         <v>10.5</v>
       </c>
       <c r="BD11">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF11">
         <v>2.78</v>
       </c>
       <c r="BG11">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3730,7 +3727,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3741,13 +3738,13 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F12">
         <v>3.15</v>
@@ -3765,7 +3762,7 @@
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3783,7 +3780,7 @@
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R12">
         <v>1.64</v>
@@ -3795,7 +3792,7 @@
         <v>1.53</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V12">
         <v>1.79</v>
@@ -3840,7 +3837,7 @@
         <v>36</v>
       </c>
       <c r="AJ12">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK12">
         <v>42</v>
@@ -3900,7 +3897,7 @@
         <v>6</v>
       </c>
       <c r="BD12">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BE12">
         <v>6.4</v>
@@ -3951,7 +3948,7 @@
         <v>5.5</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV12">
         <v>14.5</v>
@@ -3960,7 +3957,7 @@
         <v>7.2</v>
       </c>
       <c r="BX12">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BY12">
         <v>9</v>
@@ -3972,7 +3969,7 @@
         <v>7.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3983,13 +3980,13 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F13">
         <v>1.87</v>
@@ -4007,7 +4004,7 @@
         <v>3.5</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.44</v>
@@ -4022,7 +4019,7 @@
         <v>1.37</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
         <v>2.08</v>
@@ -4031,31 +4028,31 @@
         <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T13">
         <v>1.9</v>
       </c>
       <c r="U13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X13">
         <v>14.5</v>
       </c>
       <c r="Y13">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z13">
         <v>42</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>9.199999999999999</v>
@@ -4067,37 +4064,37 @@
         <v>22</v>
       </c>
       <c r="AE13">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AF13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH13">
         <v>24</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AJ13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL13">
         <v>48</v>
       </c>
       <c r="AM13">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN13">
         <v>16.5</v>
       </c>
       <c r="AO13">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="AP13">
         <v>9.800000000000001</v>
@@ -4106,10 +4103,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
         <v>7</v>
@@ -4121,7 +4118,7 @@
         <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX13">
         <v>9.800000000000001</v>
@@ -4133,25 +4130,25 @@
         <v>17.5</v>
       </c>
       <c r="BA13">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC13">
         <v>16.5</v>
       </c>
       <c r="BD13">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE13">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF13">
         <v>12</v>
       </c>
       <c r="BG13">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13">
         <v>3.25</v>
@@ -4214,7 +4211,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4225,13 +4222,13 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F14">
         <v>4.1</v>
@@ -4240,25 +4237,25 @@
         <v>4.8</v>
       </c>
       <c r="H14">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I14">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M14">
         <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
         <v>1.32</v>
@@ -4288,43 +4285,43 @@
         <v>1.26</v>
       </c>
       <c r="X14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y14">
         <v>11</v>
       </c>
       <c r="Z14">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB14">
         <v>16.5</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
         <v>12.5</v>
       </c>
       <c r="AE14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF14">
         <v>34</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI14">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK14">
         <v>60</v>
@@ -4336,7 +4333,7 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AO14">
         <v>18</v>
@@ -4366,7 +4363,7 @@
         <v>18</v>
       </c>
       <c r="AX14">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY14">
         <v>13</v>
@@ -4375,22 +4372,22 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB14">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC14">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD14">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE14">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF14">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BG14">
         <v>11.5</v>
@@ -4405,22 +4402,22 @@
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14">
         <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ14">
         <v>8.199999999999999</v>
@@ -4435,19 +4432,19 @@
         <v>4.8</v>
       </c>
       <c r="BU14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BX14">
         <v>30</v>
       </c>
       <c r="BY14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4456,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4467,13 +4464,13 @@
         <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F15">
         <v>1.37</v>
@@ -4533,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="Y15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z15">
         <v>110</v>
@@ -4545,10 +4542,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD15">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE15">
         <v>210</v>
@@ -4557,85 +4554,85 @@
         <v>9.4</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI15">
         <v>170</v>
       </c>
       <c r="AJ15">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK15">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM15">
         <v>210</v>
       </c>
       <c r="AN15">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO15">
         <v>310</v>
       </c>
       <c r="AP15">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ15">
+        <v>5.9</v>
+      </c>
+      <c r="AR15">
+        <v>6.8</v>
+      </c>
+      <c r="AS15">
+        <v>7</v>
+      </c>
+      <c r="AT15">
+        <v>4</v>
+      </c>
+      <c r="AU15">
         <v>4.6</v>
       </c>
-      <c r="AR15">
+      <c r="AV15">
+        <v>6</v>
+      </c>
+      <c r="AW15">
+        <v>7</v>
+      </c>
+      <c r="AX15">
+        <v>4.1</v>
+      </c>
+      <c r="AY15">
+        <v>4.3</v>
+      </c>
+      <c r="AZ15">
+        <v>5.8</v>
+      </c>
+      <c r="BA15">
+        <v>6.8</v>
+      </c>
+      <c r="BB15">
+        <v>4.5</v>
+      </c>
+      <c r="BC15">
         <v>5</v>
       </c>
-      <c r="AS15">
-        <v>5.2</v>
-      </c>
-      <c r="AT15">
-        <v>3.35</v>
-      </c>
-      <c r="AU15">
-        <v>3.75</v>
-      </c>
-      <c r="AV15">
-        <v>4.7</v>
-      </c>
-      <c r="AW15">
-        <v>5.1</v>
-      </c>
-      <c r="AX15">
-        <v>3.35</v>
-      </c>
-      <c r="AY15">
-        <v>3.65</v>
-      </c>
-      <c r="AZ15">
-        <v>4.5</v>
-      </c>
-      <c r="BA15">
-        <v>5.1</v>
-      </c>
-      <c r="BB15">
-        <v>3.75</v>
-      </c>
-      <c r="BC15">
-        <v>4.1</v>
-      </c>
       <c r="BD15">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE15">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF15">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BG15">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BH15">
         <v>4.5</v>
@@ -4698,7 +4695,7 @@
         <v>1.29</v>
       </c>
       <c r="CB15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4709,37 +4706,37 @@
         <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F16">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G16">
         <v>3.7</v>
       </c>
       <c r="H16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J16">
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.25</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>5.9</v>
@@ -4748,40 +4745,40 @@
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
         <v>1.58</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S16">
         <v>2.4</v>
       </c>
       <c r="T16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W16">
         <v>1.37</v>
       </c>
       <c r="X16">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y16">
         <v>15</v>
       </c>
       <c r="Z16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA16">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AB16">
         <v>21</v>
@@ -4790,7 +4787,7 @@
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE16">
         <v>18.5</v>
@@ -4799,34 +4796,34 @@
         <v>34</v>
       </c>
       <c r="AG16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL16">
         <v>38</v>
       </c>
       <c r="AM16">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="AN16">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AO16">
         <v>9.4</v>
       </c>
       <c r="AP16">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ16">
         <v>13</v>
@@ -4835,10 +4832,10 @@
         <v>14.5</v>
       </c>
       <c r="AS16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT16">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4847,37 +4844,37 @@
         <v>10</v>
       </c>
       <c r="AW16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AY16">
+        <v>14</v>
+      </c>
+      <c r="AZ16">
         <v>13.5</v>
       </c>
-      <c r="AZ16">
-        <v>13</v>
-      </c>
       <c r="BA16">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BB16">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC16">
         <v>21</v>
       </c>
       <c r="BD16">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BE16">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF16">
         <v>21</v>
       </c>
       <c r="BG16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH16">
         <v>4.4</v>
@@ -4940,7 +4937,7 @@
         <v>8.4</v>
       </c>
       <c r="CB16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4951,31 +4948,31 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G17">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H17">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I17">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4990,10 +4987,10 @@
         <v>1.26</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R17">
         <v>1.44</v>
@@ -5008,55 +5005,55 @@
         <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AA17">
         <v>32</v>
       </c>
       <c r="AB17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH17">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ17">
         <v>55</v>
       </c>
       <c r="AK17">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM17">
         <v>90</v>
@@ -5068,55 +5065,55 @@
         <v>17</v>
       </c>
       <c r="AP17">
+        <v>16</v>
+      </c>
+      <c r="AQ17">
+        <v>10</v>
+      </c>
+      <c r="AR17">
+        <v>14</v>
+      </c>
+      <c r="AS17">
+        <v>26</v>
+      </c>
+      <c r="AT17">
         <v>13</v>
-      </c>
-      <c r="AQ17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR17">
-        <v>13</v>
-      </c>
-      <c r="AS17">
-        <v>4.6</v>
-      </c>
-      <c r="AT17">
-        <v>11.5</v>
       </c>
       <c r="AU17">
         <v>8</v>
       </c>
       <c r="AV17">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA17">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BB17">
-        <v>4.9</v>
+        <v>44</v>
       </c>
       <c r="BC17">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BD17">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BE17">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="BF17">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BG17">
         <v>13</v>
@@ -5131,16 +5128,16 @@
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO17">
         <v>5.5</v>
@@ -5149,13 +5146,13 @@
         <v>24</v>
       </c>
       <c r="BQ17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR17">
         <v>34</v>
       </c>
       <c r="BS17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT17">
         <v>5.7</v>
@@ -5164,16 +5161,16 @@
         <v>4.7</v>
       </c>
       <c r="BV17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX17">
         <v>28</v>
       </c>
       <c r="BY17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5182,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5193,31 +5190,31 @@
         <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F18">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G18">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H18">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J18">
         <v>3.4</v>
       </c>
       <c r="K18">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L18">
         <v>1.33</v>
@@ -5232,7 +5229,7 @@
         <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
         <v>1.93</v>
@@ -5250,10 +5247,10 @@
         <v>2.18</v>
       </c>
       <c r="V18">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X18">
         <v>17.5</v>
@@ -5268,7 +5265,7 @@
         <v>60</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC18">
         <v>8.199999999999999</v>
@@ -5280,10 +5277,10 @@
         <v>42</v>
       </c>
       <c r="AF18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH18">
         <v>21</v>
@@ -5292,7 +5289,7 @@
         <v>55</v>
       </c>
       <c r="AJ18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK18">
         <v>34</v>
@@ -5304,7 +5301,7 @@
         <v>110</v>
       </c>
       <c r="AN18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO18">
         <v>36</v>
@@ -5319,7 +5316,7 @@
         <v>15</v>
       </c>
       <c r="AS18">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT18">
         <v>8.199999999999999</v>
@@ -5331,7 +5328,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AX18">
         <v>12.5</v>
@@ -5343,25 +5340,25 @@
         <v>12.5</v>
       </c>
       <c r="BA18">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB18">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="BC18">
         <v>20</v>
       </c>
       <c r="BD18">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BE18">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF18">
         <v>16.5</v>
       </c>
       <c r="BG18">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH18">
         <v>3.45</v>
@@ -5379,19 +5376,19 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18">
         <v>32</v>
@@ -5400,13 +5397,13 @@
         <v>10</v>
       </c>
       <c r="BT18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU18">
         <v>4.7</v>
       </c>
       <c r="BV18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW18">
         <v>9.4</v>
@@ -5424,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5435,13 +5432,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F19">
         <v>1.42</v>
@@ -5498,55 +5495,55 @@
         <v>3</v>
       </c>
       <c r="X19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z19">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AA19">
         <v>320</v>
       </c>
       <c r="AB19">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC19">
         <v>13.5</v>
       </c>
       <c r="AD19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE19">
         <v>150</v>
       </c>
       <c r="AF19">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI19">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="AJ19">
         <v>14.5</v>
       </c>
       <c r="AK19">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL19">
         <v>36</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="AN19">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO19">
         <v>180</v>
@@ -5555,13 +5552,13 @@
         <v>16</v>
       </c>
       <c r="AQ19">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR19">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AS19">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT19">
         <v>7.2</v>
@@ -5570,10 +5567,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV19">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19">
         <v>7</v>
@@ -5585,7 +5582,7 @@
         <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB19">
         <v>9.6</v>
@@ -5594,16 +5591,16 @@
         <v>11.5</v>
       </c>
       <c r="BD19">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BE19">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF19">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG19">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5666,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5677,19 +5674,19 @@
         <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F20">
         <v>1.65</v>
       </c>
       <c r="G20">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H20">
         <v>5.7</v>
@@ -5749,7 +5746,7 @@
         <v>60</v>
       </c>
       <c r="AA20">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AB20">
         <v>9.4</v>
@@ -5785,13 +5782,13 @@
         <v>48</v>
       </c>
       <c r="AM20">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN20">
         <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP20">
         <v>10.5</v>
@@ -5803,7 +5800,7 @@
         <v>4.1</v>
       </c>
       <c r="AS20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT20">
         <v>6</v>
@@ -5815,7 +5812,7 @@
         <v>17</v>
       </c>
       <c r="AW20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX20">
         <v>8.6</v>
@@ -5827,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="BA20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB20">
         <v>12</v>
@@ -5836,7 +5833,7 @@
         <v>13.5</v>
       </c>
       <c r="BD20">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BE20">
         <v>4.3</v>
@@ -5908,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5919,31 +5916,31 @@
         <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F21">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G21">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
         <v>1.27</v>
@@ -5958,7 +5955,7 @@
         <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q21">
         <v>1.67</v>
@@ -5970,16 +5967,16 @@
         <v>2.72</v>
       </c>
       <c r="T21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
         <v>2.16</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X21">
         <v>25</v>
@@ -5991,10 +5988,10 @@
         <v>55</v>
       </c>
       <c r="AA21">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC21">
         <v>12</v>
@@ -6003,7 +6000,7 @@
         <v>25</v>
       </c>
       <c r="AE21">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AF21">
         <v>14</v>
@@ -6015,10 +6012,10 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK21">
         <v>21</v>
@@ -6027,13 +6024,13 @@
         <v>38</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO21">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AP21">
         <v>14.5</v>
@@ -6042,10 +6039,10 @@
         <v>15.5</v>
       </c>
       <c r="AR21">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AS21">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT21">
         <v>9</v>
@@ -6057,7 +6054,7 @@
         <v>17.5</v>
       </c>
       <c r="AW21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX21">
         <v>8.6</v>
@@ -6069,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB21">
         <v>12.5</v>
@@ -6078,16 +6075,16 @@
         <v>12</v>
       </c>
       <c r="BD21">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="BE21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF21">
         <v>6.4</v>
       </c>
       <c r="BG21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH21">
         <v>4.1</v>
@@ -6096,7 +6093,7 @@
         <v>3.55</v>
       </c>
       <c r="BJ21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK21">
         <v>7</v>
@@ -6114,19 +6111,19 @@
         <v>3.95</v>
       </c>
       <c r="BP21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ21">
         <v>8</v>
       </c>
       <c r="BR21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
         <v>7.8</v>
       </c>
       <c r="BT21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU21">
         <v>6.8</v>
@@ -6135,7 +6132,7 @@
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX21">
         <v>1000</v>
@@ -6150,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6161,13 +6158,13 @@
         <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F22">
         <v>3.2</v>
@@ -6179,16 +6176,16 @@
         <v>2.3</v>
       </c>
       <c r="I22">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
         <v>3.45</v>
       </c>
       <c r="L22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -6200,7 +6197,7 @@
         <v>1.34</v>
       </c>
       <c r="P22">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q22">
         <v>2.02</v>
@@ -6218,10 +6215,10 @@
         <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X22">
         <v>16</v>
@@ -6269,7 +6266,7 @@
         <v>65</v>
       </c>
       <c r="AM22">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>50</v>
@@ -6287,7 +6284,7 @@
         <v>13</v>
       </c>
       <c r="AS22">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="AT22">
         <v>10.5</v>
@@ -6311,22 +6308,22 @@
         <v>15</v>
       </c>
       <c r="BA22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB22">
+        <v>4.2</v>
+      </c>
+      <c r="BC22">
         <v>4.1</v>
       </c>
-      <c r="BC22">
-        <v>4</v>
-      </c>
       <c r="BD22">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BE22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF22">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BG22">
         <v>16</v>
@@ -6392,7 +6389,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6403,31 +6400,31 @@
         <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F23">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G23">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>1.25</v>
@@ -6442,7 +6439,7 @@
         <v>1.18</v>
       </c>
       <c r="P23">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
         <v>1.54</v>
@@ -6454,28 +6451,28 @@
         <v>2.34</v>
       </c>
       <c r="T23">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U23">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="X23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z23">
         <v>40</v>
       </c>
       <c r="AA23">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="AB23">
         <v>14.5</v>
@@ -6484,13 +6481,13 @@
         <v>11</v>
       </c>
       <c r="AD23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AF23">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
         <v>11.5</v>
@@ -6499,64 +6496,64 @@
         <v>16.5</v>
       </c>
       <c r="AI23">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AJ23">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL23">
         <v>32</v>
       </c>
       <c r="AM23">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AN23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO23">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AP23">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="AR23">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AS23">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AT23">
         <v>11</v>
       </c>
       <c r="AU23">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
       </c>
       <c r="AY23">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC23">
         <v>14.5</v>
@@ -6571,7 +6568,7 @@
         <v>7.2</v>
       </c>
       <c r="BG23">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH23">
         <v>4.6</v>
@@ -6595,13 +6592,13 @@
         <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR23">
         <v>22</v>
@@ -6610,10 +6607,10 @@
         <v>7</v>
       </c>
       <c r="BT23">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6622,19 +6619,19 @@
         <v>7.6</v>
       </c>
       <c r="BX23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6645,13 +6642,13 @@
         <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F24">
         <v>8.199999999999999</v>
@@ -6672,7 +6669,7 @@
         <v>5.8</v>
       </c>
       <c r="L24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M24">
         <v>1.02</v>
@@ -6699,7 +6696,7 @@
         <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
         <v>3.35</v>
@@ -6735,7 +6732,7 @@
         <v>80</v>
       </c>
       <c r="AG24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH24">
         <v>23</v>
@@ -6747,7 +6744,7 @@
         <v>260</v>
       </c>
       <c r="AK24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL24">
         <v>80</v>
@@ -6777,7 +6774,7 @@
         <v>22</v>
       </c>
       <c r="AU24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV24">
         <v>9.4</v>
@@ -6825,31 +6822,31 @@
         <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN24">
         <v>12</v>
       </c>
       <c r="BO24">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BP24">
         <v>60</v>
       </c>
       <c r="BQ24">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR24">
         <v>55</v>
       </c>
       <c r="BS24">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT24">
         <v>4.3</v>
@@ -6858,7 +6855,7 @@
         <v>3.35</v>
       </c>
       <c r="BV24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW24">
         <v>6</v>
@@ -6867,16 +6864,16 @@
         <v>19</v>
       </c>
       <c r="BY24">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA24">
         <v>6</v>
       </c>
       <c r="CB24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6887,19 +6884,19 @@
         <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F25">
         <v>1.5</v>
       </c>
       <c r="G25">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H25">
         <v>6.6</v>
@@ -6914,7 +6911,7 @@
         <v>5.3</v>
       </c>
       <c r="L25">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M25">
         <v>1.03</v>
@@ -6938,7 +6935,7 @@
         <v>2.24</v>
       </c>
       <c r="T25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U25">
         <v>2.42</v>
@@ -6956,7 +6953,7 @@
         <v>36</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA25">
         <v>190</v>
@@ -6983,7 +6980,7 @@
         <v>20</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ25">
         <v>15</v>
@@ -6995,7 +6992,7 @@
         <v>25</v>
       </c>
       <c r="AM25">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN25">
         <v>5.2</v>
@@ -7049,7 +7046,7 @@
         <v>22</v>
       </c>
       <c r="BE25">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF25">
         <v>4.9</v>
@@ -7067,16 +7064,16 @@
         <v>9.6</v>
       </c>
       <c r="BK25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN25">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO25">
         <v>4</v>
@@ -7085,13 +7082,13 @@
         <v>9</v>
       </c>
       <c r="BQ25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR25">
         <v>19</v>
       </c>
       <c r="BS25">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT25">
         <v>10.5</v>
@@ -7103,22 +7100,22 @@
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25">
         <v>11</v>
       </c>
       <c r="CA25">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7129,13 +7126,13 @@
         <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F26">
         <v>1.14</v>
@@ -7150,7 +7147,7 @@
         <v>28</v>
       </c>
       <c r="J26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="K26">
         <v>13</v>
@@ -7168,22 +7165,22 @@
         <v>1.09</v>
       </c>
       <c r="P26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
         <v>1.33</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
         <v>1.75</v>
       </c>
       <c r="T26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
         <v>1.03</v>
@@ -7192,7 +7189,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y26">
         <v>950</v>
@@ -7207,16 +7204,16 @@
         <v>17</v>
       </c>
       <c r="AC26">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AD26">
-        <v>950</v>
+        <v>510</v>
       </c>
       <c r="AE26">
         <v>410</v>
       </c>
       <c r="AF26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG26">
         <v>16</v>
@@ -7228,7 +7225,7 @@
         <v>250</v>
       </c>
       <c r="AJ26">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK26">
         <v>15.5</v>
@@ -7240,22 +7237,22 @@
         <v>220</v>
       </c>
       <c r="AN26">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AO26">
         <v>430</v>
       </c>
       <c r="AP26">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="AQ26">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR26">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS26">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26">
         <v>13</v>
@@ -7264,10 +7261,10 @@
         <v>21</v>
       </c>
       <c r="AV26">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW26">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX26">
         <v>8.6</v>
@@ -7276,10 +7273,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ26">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB26">
         <v>7.8</v>
@@ -7288,16 +7285,16 @@
         <v>12</v>
       </c>
       <c r="BD26">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="BE26">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BF26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BG26">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH26">
         <v>6.8</v>
@@ -7360,7 +7357,7 @@
         <v>4.5</v>
       </c>
       <c r="CB26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7371,13 +7368,13 @@
         <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F27">
         <v>2.22</v>
@@ -7386,16 +7383,16 @@
         <v>2.44</v>
       </c>
       <c r="H27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I27">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J27">
         <v>3.2</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
         <v>1.46</v>
@@ -7428,25 +7425,25 @@
         <v>1.98</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X27">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y27">
         <v>14</v>
       </c>
       <c r="Z27">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA27">
         <v>85</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC27">
         <v>7.8</v>
@@ -7464,7 +7461,7 @@
         <v>12</v>
       </c>
       <c r="AH27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI27">
         <v>70</v>
@@ -7476,10 +7473,10 @@
         <v>29</v>
       </c>
       <c r="AL27">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM27">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN27">
         <v>25</v>
@@ -7497,7 +7494,7 @@
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT27">
         <v>7.6</v>
@@ -7509,7 +7506,7 @@
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX27">
         <v>12</v>
@@ -7521,25 +7518,25 @@
         <v>16</v>
       </c>
       <c r="BA27">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BB27">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE27">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27">
         <v>18</v>
       </c>
       <c r="BG27">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH27">
         <v>3.2</v>
@@ -7563,7 +7560,7 @@
         <v>5.2</v>
       </c>
       <c r="BO27">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP27">
         <v>19</v>
@@ -7602,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7613,34 +7610,34 @@
         <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F28">
         <v>2.3</v>
       </c>
       <c r="G28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
         <v>3.2</v>
       </c>
       <c r="L28">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M28">
         <v>1.09</v>
@@ -7673,19 +7670,19 @@
         <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y28">
         <v>13.5</v>
       </c>
       <c r="Z28">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA28">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB28">
         <v>8.800000000000001</v>
@@ -7694,10 +7691,10 @@
         <v>7.6</v>
       </c>
       <c r="AD28">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE28">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF28">
         <v>14.5</v>
@@ -7706,28 +7703,28 @@
         <v>11.5</v>
       </c>
       <c r="AH28">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI28">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AJ28">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK28">
         <v>29</v>
       </c>
       <c r="AL28">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AM28">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN28">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AO28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AP28">
         <v>8.4</v>
@@ -7736,10 +7733,10 @@
         <v>9.6</v>
       </c>
       <c r="AR28">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS28">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="AT28">
         <v>7.4</v>
@@ -7763,28 +7760,28 @@
         <v>16</v>
       </c>
       <c r="BA28">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BB28">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC28">
         <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE28">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF28">
         <v>17.5</v>
       </c>
       <c r="BG28">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI28">
         <v>2.48</v>
@@ -7793,31 +7790,31 @@
         <v>10.5</v>
       </c>
       <c r="BK28">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN28">
         <v>5.2</v>
       </c>
       <c r="BO28">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP28">
         <v>19</v>
       </c>
       <c r="BQ28">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28">
         <v>7</v>
@@ -7826,16 +7823,16 @@
         <v>5</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW28">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7844,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7855,16 +7852,16 @@
         <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F29">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G29">
         <v>3.55</v>
@@ -7873,10 +7870,10 @@
         <v>1.93</v>
       </c>
       <c r="I29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J29">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K29">
         <v>5.1</v>
@@ -7912,31 +7909,31 @@
         <v>3.9</v>
       </c>
       <c r="V29">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W29">
         <v>1.39</v>
       </c>
       <c r="X29">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="Y29">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="Z29">
         <v>30</v>
       </c>
       <c r="AA29">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AB29">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC29">
         <v>16.5</v>
       </c>
       <c r="AD29">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AE29">
         <v>18.5</v>
@@ -7945,7 +7942,7 @@
         <v>60</v>
       </c>
       <c r="AG29">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH29">
         <v>13.5</v>
@@ -7957,13 +7954,13 @@
         <v>90</v>
       </c>
       <c r="AK29">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AL29">
         <v>28</v>
       </c>
       <c r="AM29">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AN29">
         <v>12</v>
@@ -7972,19 +7969,19 @@
         <v>5.4</v>
       </c>
       <c r="AP29">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR29">
         <v>20</v>
       </c>
       <c r="AS29">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT29">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU29">
         <v>11.5</v>
@@ -7993,10 +7990,10 @@
         <v>10.5</v>
       </c>
       <c r="AW29">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX29">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AY29">
         <v>17</v>
@@ -8008,10 +8005,10 @@
         <v>13</v>
       </c>
       <c r="BB29">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC29">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD29">
         <v>18.5</v>
@@ -8086,7 +8083,7 @@
         <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8097,13 +8094,13 @@
         <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F30">
         <v>2.2</v>
@@ -8118,7 +8115,7 @@
         <v>3.5</v>
       </c>
       <c r="J30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
         <v>3.9</v>
@@ -8139,7 +8136,7 @@
         <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R30">
         <v>1.54</v>
@@ -8157,13 +8154,13 @@
         <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X30">
         <v>22</v>
       </c>
       <c r="Y30">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z30">
         <v>27</v>
@@ -8187,7 +8184,7 @@
         <v>16.5</v>
       </c>
       <c r="AG30">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH30">
         <v>15.5</v>
@@ -8217,7 +8214,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR30">
         <v>23</v>
@@ -8271,10 +8268,10 @@
         <v>4.3</v>
       </c>
       <c r="BI30">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK30">
         <v>4.7</v>
@@ -8283,7 +8280,7 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN30">
         <v>5.6</v>
@@ -8301,7 +8298,7 @@
         <v>25</v>
       </c>
       <c r="BS30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT30">
         <v>7.2</v>
@@ -8313,7 +8310,7 @@
         <v>25</v>
       </c>
       <c r="BW30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX30">
         <v>32</v>
@@ -8325,10 +8322,10 @@
         <v>18.5</v>
       </c>
       <c r="CA30">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8339,22 +8336,22 @@
         <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F31">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G31">
         <v>2.38</v>
       </c>
       <c r="H31">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I31">
         <v>3.5</v>
@@ -8447,7 +8444,7 @@
         <v>36</v>
       </c>
       <c r="AM31">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN31">
         <v>17</v>
@@ -8465,7 +8462,7 @@
         <v>20</v>
       </c>
       <c r="AS31">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AT31">
         <v>9.6</v>
@@ -8477,7 +8474,7 @@
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AX31">
         <v>13</v>
@@ -8489,19 +8486,19 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC31">
         <v>19.5</v>
       </c>
       <c r="BD31">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BE31">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF31">
         <v>12</v>
@@ -8570,7 +8567,7 @@
         <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8581,31 +8578,31 @@
         <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F32">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G32">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H32">
         <v>5.9</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L32">
         <v>1.25</v>
@@ -8617,58 +8614,58 @@
         <v>5.2</v>
       </c>
       <c r="O32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P32">
         <v>2.42</v>
       </c>
       <c r="Q32">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R32">
         <v>1.59</v>
       </c>
       <c r="S32">
+        <v>2.36</v>
+      </c>
+      <c r="T32">
+        <v>1.68</v>
+      </c>
+      <c r="U32">
         <v>2.38</v>
       </c>
-      <c r="T32">
-        <v>1.65</v>
-      </c>
-      <c r="U32">
-        <v>2.24</v>
-      </c>
       <c r="V32">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W32">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z32">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AA32">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB32">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC32">
         <v>11</v>
       </c>
       <c r="AD32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE32">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8680,7 +8677,7 @@
         <v>70</v>
       </c>
       <c r="AJ32">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK32">
         <v>16.5</v>
@@ -8689,67 +8686,67 @@
         <v>29</v>
       </c>
       <c r="AM32">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN32">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO32">
         <v>70</v>
       </c>
       <c r="AP32">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ32">
+        <v>11.5</v>
+      </c>
+      <c r="AR32">
+        <v>6.8</v>
+      </c>
+      <c r="AS32">
+        <v>7.4</v>
+      </c>
+      <c r="AT32">
+        <v>9</v>
+      </c>
+      <c r="AU32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV32">
         <v>20</v>
       </c>
-      <c r="AR32">
-        <v>6.6</v>
-      </c>
-      <c r="AS32">
-        <v>7.2</v>
-      </c>
-      <c r="AT32">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU32">
-        <v>8</v>
-      </c>
-      <c r="AV32">
-        <v>19.5</v>
-      </c>
       <c r="AW32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX32">
         <v>10</v>
       </c>
       <c r="AY32">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ32">
+        <v>14.5</v>
+      </c>
+      <c r="BA32">
+        <v>7</v>
+      </c>
+      <c r="BB32">
+        <v>13.5</v>
+      </c>
+      <c r="BC32">
         <v>13</v>
       </c>
-      <c r="BA32">
-        <v>6.8</v>
-      </c>
-      <c r="BB32">
-        <v>13</v>
-      </c>
-      <c r="BC32">
-        <v>12</v>
-      </c>
       <c r="BD32">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BE32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF32">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH32">
         <v>4.6</v>
@@ -8812,7 +8809,7 @@
         <v>5.7</v>
       </c>
       <c r="CB32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8823,31 +8820,31 @@
         <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F33">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H33">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="I33">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="J33">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="K33">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L33">
         <v>1.66</v>
@@ -8862,10 +8859,10 @@
         <v>1.67</v>
       </c>
       <c r="P33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q33">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="R33">
         <v>1.13</v>
@@ -8880,10 +8877,10 @@
         <v>1.59</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W33">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X33">
         <v>7.2</v>
@@ -8892,43 +8889,43 @@
         <v>6.8</v>
       </c>
       <c r="Z33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA33">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AB33">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC33">
         <v>7.6</v>
       </c>
       <c r="AD33">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE33">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AF33">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AG33">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH33">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI33">
-        <v>100</v>
+        <v>460</v>
       </c>
       <c r="AJ33">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK33">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AL33">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AM33">
         <v>350</v>
@@ -8937,61 +8934,61 @@
         <v>180</v>
       </c>
       <c r="AO33">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AP33">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AQ33">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AR33">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS33">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT33">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AU33">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AV33">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW33">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AX33">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY33">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AZ33">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA33">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB33">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC33">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD33">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE33">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF33">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BG33">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BH33">
         <v>2.52</v>
@@ -9039,7 +9036,7 @@
         <v>24</v>
       </c>
       <c r="BW33">
-        <v>7.2</v>
+        <v>1.88</v>
       </c>
       <c r="BX33">
         <v>1000</v>
@@ -9054,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9065,31 +9062,31 @@
         <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F34">
-        <v>1.13</v>
+        <v>1.81</v>
       </c>
       <c r="G34">
-        <v>990</v>
+        <v>2.62</v>
       </c>
       <c r="H34">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="I34">
-        <v>990</v>
+        <v>21</v>
       </c>
       <c r="J34">
-        <v>1.22</v>
+        <v>2.74</v>
       </c>
       <c r="K34">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9098,13 +9095,13 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O34">
         <v>1.58</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q34">
         <v>1.58</v>
@@ -9122,10 +9119,10 @@
         <v>1.11</v>
       </c>
       <c r="V34">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9143,7 +9140,7 @@
         <v>1000</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD34">
         <v>1000</v>
@@ -9164,7 +9161,7 @@
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34">
         <v>1000</v>
@@ -9182,58 +9179,58 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AU34">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AW34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9296,7 +9293,7 @@
         <v>1.04</v>
       </c>
       <c r="CB34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9307,22 +9304,22 @@
         <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F35">
         <v>3.15</v>
       </c>
       <c r="G35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H35">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I35">
         <v>2.56</v>
@@ -9331,31 +9328,31 @@
         <v>3.3</v>
       </c>
       <c r="K35">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L35">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M35">
         <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O35">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P35">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q35">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R35">
         <v>1.33</v>
       </c>
       <c r="S35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T35">
         <v>1.75</v>
@@ -9367,10 +9364,10 @@
         <v>1.64</v>
       </c>
       <c r="W35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X35">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y35">
         <v>11</v>
@@ -9382,10 +9379,10 @@
         <v>38</v>
       </c>
       <c r="AB35">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC35">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD35">
         <v>12.5</v>
@@ -9409,7 +9406,7 @@
         <v>75</v>
       </c>
       <c r="AK35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL35">
         <v>50</v>
@@ -9418,7 +9415,7 @@
         <v>120</v>
       </c>
       <c r="AN35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO35">
         <v>27</v>
@@ -9433,7 +9430,7 @@
         <v>13.5</v>
       </c>
       <c r="AS35">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -9445,7 +9442,7 @@
         <v>10</v>
       </c>
       <c r="AW35">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AX35">
         <v>18.5</v>
@@ -9457,34 +9454,34 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BB35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC35">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BD35">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BE35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF35">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BG35">
         <v>16</v>
       </c>
       <c r="BH35">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI35">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK35">
         <v>5.9</v>
@@ -9502,13 +9499,13 @@
         <v>5.4</v>
       </c>
       <c r="BP35">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ35">
         <v>7.4</v>
       </c>
       <c r="BR35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS35">
         <v>8.199999999999999</v>
@@ -9523,22 +9520,22 @@
         <v>19.5</v>
       </c>
       <c r="BW35">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX35">
         <v>34</v>
       </c>
       <c r="BY35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA35">
         <v>7.6</v>
       </c>
       <c r="CB35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9549,31 +9546,31 @@
         <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F36">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="G36">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="H36">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="I36">
-        <v>990</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>1.56</v>
+        <v>2.68</v>
       </c>
       <c r="K36">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9582,7 +9579,7 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O36">
         <v>1.36</v>
@@ -9606,10 +9603,10 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W36">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9621,13 +9618,13 @@
         <v>1000</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB36">
         <v>1000</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD36">
         <v>1000</v>
@@ -9648,7 +9645,7 @@
         <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK36">
         <v>1000</v>
@@ -9666,58 +9663,58 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36">
         <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9780,7 +9777,7 @@
         <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9791,22 +9788,22 @@
         <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F37">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G37">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H37">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I37">
         <v>5.3</v>
@@ -9851,22 +9848,22 @@
         <v>1.24</v>
       </c>
       <c r="W37">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X37">
         <v>21</v>
       </c>
       <c r="Y37">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z37">
         <v>46</v>
       </c>
       <c r="AA37">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC37">
         <v>9.199999999999999</v>
@@ -9878,7 +9875,7 @@
         <v>75</v>
       </c>
       <c r="AF37">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG37">
         <v>10.5</v>
@@ -9887,19 +9884,19 @@
         <v>19</v>
       </c>
       <c r="AI37">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AJ37">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AK37">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AL37">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM37">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN37">
         <v>13</v>
@@ -9914,10 +9911,10 @@
         <v>16</v>
       </c>
       <c r="AR37">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AS37">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT37">
         <v>7.2</v>
@@ -9929,7 +9926,7 @@
         <v>16.5</v>
       </c>
       <c r="AW37">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9941,88 +9938,88 @@
         <v>16</v>
       </c>
       <c r="BA37">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BB37">
         <v>17</v>
       </c>
       <c r="BC37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD37">
         <v>7</v>
       </c>
       <c r="BE37">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF37">
         <v>9.199999999999999</v>
       </c>
       <c r="BG37">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH37">
         <v>3.7</v>
       </c>
       <c r="BI37">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ37">
         <v>9.6</v>
       </c>
       <c r="BK37">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN37">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO37">
         <v>4.1</v>
       </c>
       <c r="BP37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ37">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT37">
         <v>8.199999999999999</v>
       </c>
       <c r="BU37">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV37">
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10033,13 +10030,13 @@
         <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F38">
         <v>1.22</v>
@@ -10051,7 +10048,7 @@
         <v>15</v>
       </c>
       <c r="I38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="J38">
         <v>8.4</v>
@@ -10066,7 +10063,7 @@
         <v>1.02</v>
       </c>
       <c r="N38">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38">
         <v>1.11</v>
@@ -10087,7 +10084,7 @@
         <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
         <v>1.06</v>
@@ -10096,7 +10093,7 @@
         <v>5.4</v>
       </c>
       <c r="X38">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y38">
         <v>80</v>
@@ -10135,16 +10132,16 @@
         <v>11.5</v>
       </c>
       <c r="AK38">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AL38">
         <v>32</v>
       </c>
       <c r="AM38">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN38">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AO38">
         <v>230</v>
@@ -10156,13 +10153,13 @@
         <v>48</v>
       </c>
       <c r="AR38">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS38">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU38">
         <v>18</v>
@@ -10171,22 +10168,22 @@
         <v>42</v>
       </c>
       <c r="AW38">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX38">
         <v>9.4</v>
       </c>
       <c r="AY38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ38">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB38">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC38">
         <v>13</v>
@@ -10195,13 +10192,13 @@
         <v>26</v>
       </c>
       <c r="BE38">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF38">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BG38">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH38">
         <v>5.6</v>
@@ -10213,19 +10210,19 @@
         <v>12</v>
       </c>
       <c r="BK38">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN38">
         <v>4.2</v>
       </c>
       <c r="BO38">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP38">
         <v>6.6</v>
@@ -10237,25 +10234,25 @@
         <v>18.5</v>
       </c>
       <c r="BS38">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT38">
         <v>16.5</v>
       </c>
       <c r="BU38">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX38">
         <v>100</v>
       </c>
       <c r="BY38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ38">
         <v>0</v>
@@ -10264,7 +10261,7 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10275,22 +10272,22 @@
         <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F39">
         <v>3.1</v>
       </c>
       <c r="G39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H39">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I39">
         <v>2.8</v>
@@ -10350,7 +10347,7 @@
         <v>55</v>
       </c>
       <c r="AB39">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC39">
         <v>7.4</v>
@@ -10359,7 +10356,7 @@
         <v>13.5</v>
       </c>
       <c r="AE39">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF39">
         <v>23</v>
@@ -10371,10 +10368,10 @@
         <v>24</v>
       </c>
       <c r="AI39">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ39">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AK39">
         <v>65</v>
@@ -10386,64 +10383,64 @@
         <v>210</v>
       </c>
       <c r="AN39">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AO39">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP39">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ39">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR39">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS39">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="AT39">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU39">
         <v>6</v>
       </c>
       <c r="AV39">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW39">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="AX39">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY39">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ39">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA39">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB39">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC39">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD39">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF39">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG39">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BH39">
         <v>2.82</v>
@@ -10506,7 +10503,7 @@
         <v>9</v>
       </c>
       <c r="CB39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10517,13 +10514,13 @@
         <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F40">
         <v>1.57</v>
@@ -10553,13 +10550,13 @@
         <v>3.25</v>
       </c>
       <c r="O40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P40">
         <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R40">
         <v>1.27</v>
@@ -10586,7 +10583,7 @@
         <v>23</v>
       </c>
       <c r="Z40">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AA40">
         <v>300</v>
@@ -10622,10 +10619,10 @@
         <v>22</v>
       </c>
       <c r="AL40">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM40">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN40">
         <v>13.5</v>
@@ -10676,13 +10673,13 @@
         <v>14.5</v>
       </c>
       <c r="BD40">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE40">
         <v>5.9</v>
       </c>
       <c r="BF40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG40">
         <v>5.9</v>
@@ -10703,7 +10700,7 @@
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>2.62</v>
+        <v>9.6</v>
       </c>
       <c r="BN40">
         <v>3.9</v>
@@ -10748,7 +10745,7 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10759,13 +10756,13 @@
         <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F41">
         <v>1.79</v>
@@ -10822,16 +10819,16 @@
         <v>2.08</v>
       </c>
       <c r="X41">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y41">
         <v>17</v>
       </c>
       <c r="Z41">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AA41">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB41">
         <v>8.199999999999999</v>
@@ -10843,37 +10840,37 @@
         <v>22</v>
       </c>
       <c r="AE41">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="AF41">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG41">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH41">
         <v>23</v>
       </c>
       <c r="AI41">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AJ41">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK41">
         <v>22</v>
       </c>
       <c r="AL41">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AM41">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN41">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO41">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AP41">
         <v>9.4</v>
@@ -10882,10 +10879,10 @@
         <v>11.5</v>
       </c>
       <c r="AR41">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS41">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT41">
         <v>6.6</v>
@@ -10897,7 +10894,7 @@
         <v>15</v>
       </c>
       <c r="AW41">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX41">
         <v>7.8</v>
@@ -10909,7 +10906,7 @@
         <v>15.5</v>
       </c>
       <c r="BA41">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BB41">
         <v>14.5</v>
@@ -10918,16 +10915,16 @@
         <v>15</v>
       </c>
       <c r="BD41">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE41">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF41">
         <v>10.5</v>
       </c>
       <c r="BG41">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BH41">
         <v>3.35</v>
@@ -10978,7 +10975,7 @@
         <v>8.4</v>
       </c>
       <c r="BX41">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY41">
         <v>8.6</v>
@@ -10990,7 +10987,7 @@
         <v>7.4</v>
       </c>
       <c r="CB41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -11001,13 +10998,13 @@
         <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F42">
         <v>2.28</v>
@@ -11073,22 +11070,22 @@
         <v>38</v>
       </c>
       <c r="AA42">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB42">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AC42">
         <v>16.5</v>
       </c>
       <c r="AD42">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE42">
         <v>28</v>
       </c>
       <c r="AF42">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AG42">
         <v>16.5</v>
@@ -11100,34 +11097,34 @@
         <v>27</v>
       </c>
       <c r="AJ42">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AK42">
         <v>25</v>
       </c>
       <c r="AL42">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM42">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AN42">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO42">
         <v>9.4</v>
       </c>
       <c r="AP42">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ42">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR42">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS42">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT42">
         <v>21</v>
@@ -11154,7 +11151,7 @@
         <v>18</v>
       </c>
       <c r="BB42">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC42">
         <v>16</v>
@@ -11163,7 +11160,7 @@
         <v>16.5</v>
       </c>
       <c r="BE42">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF42">
         <v>5.9</v>
@@ -11232,24 +11229,24 @@
         <v>1.04</v>
       </c>
       <c r="CB42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
         <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F43">
         <v>3.65</v>
@@ -11276,7 +11273,7 @@
         <v>1.13</v>
       </c>
       <c r="N43">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O43">
         <v>1.55</v>
@@ -11294,7 +11291,7 @@
         <v>5.6</v>
       </c>
       <c r="T43">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U43">
         <v>1.78</v>
@@ -11342,13 +11339,13 @@
         <v>65</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK43">
         <v>65</v>
       </c>
       <c r="AL43">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM43">
         <v>180</v>
@@ -11402,13 +11399,13 @@
         <v>50</v>
       </c>
       <c r="BD43">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BE43">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF43">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BG43">
         <v>30</v>
@@ -11417,40 +11414,40 @@
         <v>2.76</v>
       </c>
       <c r="BI43">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ43">
         <v>11</v>
       </c>
       <c r="BK43">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN43">
         <v>6.8</v>
       </c>
       <c r="BO43">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP43">
         <v>36</v>
       </c>
       <c r="BQ43">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT43">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU43">
         <v>4</v>
@@ -11459,22 +11456,22 @@
         <v>21</v>
       </c>
       <c r="BW43">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ43">
         <v>1000</v>
       </c>
       <c r="CA43">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB43" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11485,31 +11482,31 @@
         <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F44">
+        <v>2.78</v>
+      </c>
+      <c r="G44">
+        <v>3.2</v>
+      </c>
+      <c r="H44">
+        <v>2.94</v>
+      </c>
+      <c r="I44">
+        <v>3.35</v>
+      </c>
+      <c r="J44">
         <v>2.72</v>
       </c>
-      <c r="G44">
-        <v>3.3</v>
-      </c>
-      <c r="H44">
-        <v>3</v>
-      </c>
-      <c r="I44">
-        <v>3.45</v>
-      </c>
-      <c r="J44">
-        <v>2.54</v>
-      </c>
       <c r="K44">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11518,49 +11515,49 @@
         <v>1.15</v>
       </c>
       <c r="N44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P44">
         <v>1.43</v>
       </c>
       <c r="Q44">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R44">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S44">
         <v>5.7</v>
       </c>
       <c r="T44">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U44">
         <v>1.69</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W44">
         <v>1.47</v>
       </c>
       <c r="X44">
+        <v>7.6</v>
+      </c>
+      <c r="Y44">
         <v>8.4</v>
       </c>
-      <c r="Y44">
-        <v>9.6</v>
-      </c>
       <c r="Z44">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA44">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AB44">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC44">
         <v>7.2</v>
@@ -11569,91 +11566,91 @@
         <v>16</v>
       </c>
       <c r="AE44">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AF44">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG44">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH44">
         <v>27</v>
       </c>
       <c r="AI44">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AJ44">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK44">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL44">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="AM44">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN44">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AO44">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AP44">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AQ44">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AR44">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AS44">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT44">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AV44">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AW44">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AX44">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY44">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ44">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BA44">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BB44">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BC44">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BD44">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BF44">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG44">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11716,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11727,40 +11724,40 @@
         <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F45">
         <v>3.1</v>
       </c>
       <c r="G45">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H45">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I45">
         <v>2.52</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K45">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L45">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M45">
         <v>1.06</v>
       </c>
       <c r="N45">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O45">
         <v>1.3</v>
@@ -11772,22 +11769,22 @@
         <v>1.89</v>
       </c>
       <c r="R45">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S45">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T45">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V45">
         <v>1.65</v>
       </c>
       <c r="W45">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X45">
         <v>18</v>
@@ -11796,160 +11793,160 @@
         <v>12.5</v>
       </c>
       <c r="Z45">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA45">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB45">
         <v>16</v>
       </c>
       <c r="AC45">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD45">
         <v>14</v>
       </c>
       <c r="AE45">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF45">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG45">
         <v>17.5</v>
       </c>
       <c r="AH45">
+        <v>18</v>
+      </c>
+      <c r="AI45">
+        <v>40</v>
+      </c>
+      <c r="AJ45">
+        <v>130</v>
+      </c>
+      <c r="AK45">
+        <v>40</v>
+      </c>
+      <c r="AL45">
+        <v>50</v>
+      </c>
+      <c r="AM45">
+        <v>320</v>
+      </c>
+      <c r="AN45">
+        <v>44</v>
+      </c>
+      <c r="AO45">
+        <v>20</v>
+      </c>
+      <c r="AP45">
+        <v>12</v>
+      </c>
+      <c r="AQ45">
+        <v>7.6</v>
+      </c>
+      <c r="AR45">
+        <v>12.5</v>
+      </c>
+      <c r="AS45">
+        <v>11.5</v>
+      </c>
+      <c r="AT45">
+        <v>11</v>
+      </c>
+      <c r="AU45">
+        <v>6.8</v>
+      </c>
+      <c r="AV45">
+        <v>8.4</v>
+      </c>
+      <c r="AW45">
         <v>21</v>
       </c>
-      <c r="AI45">
-        <v>46</v>
-      </c>
-      <c r="AJ45">
-        <v>75</v>
-      </c>
-      <c r="AK45">
-        <v>48</v>
-      </c>
-      <c r="AL45">
-        <v>60</v>
-      </c>
-      <c r="AM45">
-        <v>110</v>
-      </c>
-      <c r="AN45">
-        <v>46</v>
-      </c>
-      <c r="AO45">
-        <v>23</v>
-      </c>
-      <c r="AP45">
-        <v>3.45</v>
-      </c>
-      <c r="AQ45">
-        <v>3.2</v>
-      </c>
-      <c r="AR45">
-        <v>3.5</v>
-      </c>
-      <c r="AS45">
-        <v>3.85</v>
-      </c>
-      <c r="AT45">
-        <v>3.4</v>
-      </c>
-      <c r="AU45">
-        <v>3</v>
-      </c>
-      <c r="AV45">
-        <v>3.3</v>
-      </c>
-      <c r="AW45">
-        <v>3.8</v>
-      </c>
       <c r="AX45">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="AY45">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="AZ45">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="BA45">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BB45">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BC45">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BD45">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BE45">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF45">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BG45">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH45">
         <v>3.6</v>
       </c>
       <c r="BI45">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ45">
         <v>9.800000000000001</v>
       </c>
       <c r="BK45">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BN45">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO45">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BP45">
         <v>28</v>
       </c>
       <c r="BQ45">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR45">
         <v>40</v>
       </c>
       <c r="BS45">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BT45">
         <v>5.5</v>
       </c>
       <c r="BU45">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BV45">
         <v>18</v>
       </c>
       <c r="BW45">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX45">
         <v>32</v>
       </c>
       <c r="BY45">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -11958,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11969,31 +11966,31 @@
         <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F46">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="G46">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="H46">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I46">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="J46">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K46">
-        <v>110</v>
+        <v>3.6</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12002,142 +11999,142 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="O46">
         <v>1.41</v>
       </c>
       <c r="P46">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q46">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S46">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="T46">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U46">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V46">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="W46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X46">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y46">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z46">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA46">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB46">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC46">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD46">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE46">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF46">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG46">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH46">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI46">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ46">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK46">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AL46">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AM46">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AO46">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE46">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BF46">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12200,7 +12197,7 @@
         <v>1.04</v>
       </c>
       <c r="CB46" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12211,28 +12208,28 @@
         <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F47">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G47">
         <v>990</v>
       </c>
       <c r="H47">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I47">
         <v>990</v>
       </c>
       <c r="J47">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12247,7 +12244,7 @@
         <v>1.36</v>
       </c>
       <c r="O47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P47">
         <v>1.36</v>
@@ -12259,7 +12256,7 @@
         <v>1.15</v>
       </c>
       <c r="S47">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T47">
         <v>1.11</v>
@@ -12268,10 +12265,10 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W47">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12442,57 +12439,57 @@
         <v>1.04</v>
       </c>
       <c r="CB47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
         <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F48">
         <v>2.66</v>
       </c>
       <c r="G48">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H48">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I48">
         <v>3.5</v>
       </c>
       <c r="J48">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K48">
         <v>2.96</v>
       </c>
       <c r="L48">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="M48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N48">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O48">
         <v>1.7</v>
       </c>
       <c r="P48">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -12513,7 +12510,7 @@
         <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X48">
         <v>7</v>
@@ -12525,7 +12522,7 @@
         <v>21</v>
       </c>
       <c r="AA48">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB48">
         <v>7.2</v>
@@ -12549,7 +12546,7 @@
         <v>28</v>
       </c>
       <c r="AI48">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ48">
         <v>50</v>
@@ -12558,16 +12555,16 @@
         <v>48</v>
       </c>
       <c r="AL48">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM48">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AN48">
         <v>65</v>
       </c>
       <c r="AO48">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP48">
         <v>6.4</v>
@@ -12615,7 +12612,7 @@
         <v>36</v>
       </c>
       <c r="BE48">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BF48">
         <v>42</v>
@@ -12639,7 +12636,7 @@
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN48">
         <v>5.6</v>
@@ -12657,7 +12654,7 @@
         <v>60</v>
       </c>
       <c r="BS48">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT48">
         <v>6.6</v>
@@ -12666,7 +12663,7 @@
         <v>4.7</v>
       </c>
       <c r="BV48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW48">
         <v>8.6</v>
@@ -12675,51 +12672,51 @@
         <v>70</v>
       </c>
       <c r="BY48">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ48">
         <v>70</v>
       </c>
       <c r="CA48">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
         <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F49">
         <v>2.68</v>
       </c>
       <c r="G49">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H49">
         <v>3.2</v>
       </c>
       <c r="I49">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49">
         <v>3.05</v>
-      </c>
-      <c r="K49">
-        <v>3.1</v>
       </c>
       <c r="L49">
         <v>1.48</v>
@@ -12731,13 +12728,13 @@
         <v>2.66</v>
       </c>
       <c r="O49">
+        <v>1.56</v>
+      </c>
+      <c r="P49">
         <v>1.55</v>
       </c>
-      <c r="P49">
-        <v>1.57</v>
-      </c>
       <c r="Q49">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R49">
         <v>1.2</v>
@@ -12749,7 +12746,7 @@
         <v>2.12</v>
       </c>
       <c r="U49">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V49">
         <v>1.43</v>
@@ -12758,7 +12755,7 @@
         <v>1.56</v>
       </c>
       <c r="X49">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y49">
         <v>9.4</v>
@@ -12767,10 +12764,10 @@
         <v>21</v>
       </c>
       <c r="AA49">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="AB49">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC49">
         <v>7.2</v>
@@ -12779,7 +12776,7 @@
         <v>15.5</v>
       </c>
       <c r="AE49">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AF49">
         <v>17</v>
@@ -12788,34 +12785,34 @@
         <v>13.5</v>
       </c>
       <c r="AH49">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI49">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ49">
         <v>100</v>
       </c>
       <c r="AK49">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL49">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM49">
         <v>1000</v>
       </c>
       <c r="AN49">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO49">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AP49">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ49">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR49">
         <v>17.5</v>
@@ -12830,10 +12827,10 @@
         <v>6.4</v>
       </c>
       <c r="AV49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW49">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX49">
         <v>14</v>
@@ -12842,7 +12839,7 @@
         <v>12</v>
       </c>
       <c r="AZ49">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA49">
         <v>36</v>
@@ -12851,13 +12848,13 @@
         <v>24</v>
       </c>
       <c r="BC49">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD49">
         <v>32</v>
       </c>
       <c r="BE49">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF49">
         <v>28</v>
@@ -12926,7 +12923,7 @@
         <v>9</v>
       </c>
       <c r="CB49" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:80">
@@ -12937,13 +12934,13 @@
         <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F50">
         <v>1.72</v>
@@ -12955,16 +12952,16 @@
         <v>6.2</v>
       </c>
       <c r="I50">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J50">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K50">
         <v>3.7</v>
       </c>
       <c r="L50">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M50">
         <v>1.11</v>
@@ -12985,7 +12982,7 @@
         <v>1.21</v>
       </c>
       <c r="S50">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T50">
         <v>2.32</v>
@@ -13003,13 +13000,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y50">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z50">
         <v>60</v>
       </c>
       <c r="AA50">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB50">
         <v>6.2</v>
@@ -13021,7 +13018,7 @@
         <v>30</v>
       </c>
       <c r="AE50">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AF50">
         <v>9</v>
@@ -13033,7 +13030,7 @@
         <v>32</v>
       </c>
       <c r="AI50">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AJ50">
         <v>18.5</v>
@@ -13042,13 +13039,13 @@
         <v>26</v>
       </c>
       <c r="AL50">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM50">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AN50">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO50">
         <v>1000</v>
@@ -13060,7 +13057,7 @@
         <v>13.5</v>
       </c>
       <c r="AR50">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AS50">
         <v>46</v>
@@ -13084,7 +13081,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA50">
         <v>44</v>
@@ -13099,7 +13096,7 @@
         <v>46</v>
       </c>
       <c r="BE50">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF50">
         <v>15</v>
@@ -13111,7 +13108,7 @@
         <v>2.9</v>
       </c>
       <c r="BI50">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ50">
         <v>13</v>
@@ -13123,25 +13120,25 @@
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN50">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO50">
         <v>3.5</v>
       </c>
       <c r="BP50">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ50">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT50">
         <v>10.5</v>
@@ -13153,22 +13150,22 @@
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ50">
         <v>1000</v>
       </c>
       <c r="CA50">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13179,25 +13176,25 @@
         <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F51">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="G51">
         <v>2.12</v>
       </c>
       <c r="H51">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I51">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J51">
         <v>3.3</v>
@@ -13212,7 +13209,7 @@
         <v>1.08</v>
       </c>
       <c r="N51">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O51">
         <v>1.37</v>
@@ -13236,118 +13233,118 @@
         <v>1.9</v>
       </c>
       <c r="V51">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W51">
         <v>1.89</v>
       </c>
       <c r="X51">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y51">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z51">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AA51">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB51">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC51">
         <v>8.4</v>
       </c>
       <c r="AD51">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE51">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF51">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG51">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH51">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI51">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ51">
         <v>29</v>
       </c>
       <c r="AK51">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL51">
         <v>55</v>
       </c>
       <c r="AM51">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN51">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO51">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP51">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="AQ51">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR51">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS51">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT51">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AU51">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AV51">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AW51">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AX51">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY51">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AZ51">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="BA51">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BB51">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BC51">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BD51">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE51">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF51">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="BG51">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH51">
         <v>3.9</v>
@@ -13410,7 +13407,7 @@
         <v>1.35</v>
       </c>
       <c r="CB51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -733,7 +733,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-02 20:52:13</t>
+    <t>2026-08-02 23:00:04</t>
   </si>
 </sst>
 </file>
@@ -1327,226 +1327,226 @@
         <v>189</v>
       </c>
       <c r="F2">
+        <v>3.95</v>
+      </c>
+      <c r="G2">
+        <v>4.1</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1.65</v>
+      </c>
+      <c r="K2">
+        <v>1.67</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>2.22</v>
       </c>
-      <c r="G2">
-        <v>2.26</v>
-      </c>
-      <c r="H2">
-        <v>4.3</v>
-      </c>
-      <c r="I2">
+      <c r="N2">
+        <v>1.15</v>
+      </c>
+      <c r="O2">
+        <v>7.2</v>
+      </c>
+      <c r="P2">
+        <v>1.02</v>
+      </c>
+      <c r="Q2">
+        <v>48</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>200</v>
+      </c>
+      <c r="T2">
+        <v>13.5</v>
+      </c>
+      <c r="U2">
+        <v>1.06</v>
+      </c>
+      <c r="V2">
+        <v>1.16</v>
+      </c>
+      <c r="W2">
+        <v>1.32</v>
+      </c>
+      <c r="X2">
+        <v>1.98</v>
+      </c>
+      <c r="Y2">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>5.1</v>
+      </c>
+      <c r="AC2">
+        <v>85</v>
+      </c>
+      <c r="AD2">
+        <v>990</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>44</v>
+      </c>
+      <c r="AG2">
+        <v>990</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.8</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>36</v>
+      </c>
+      <c r="AS2">
+        <v>190</v>
+      </c>
+      <c r="AT2">
         <v>4.4</v>
       </c>
-      <c r="J2">
-        <v>3.05</v>
-      </c>
-      <c r="K2">
-        <v>3.15</v>
-      </c>
-      <c r="L2">
-        <v>1.67</v>
-      </c>
-      <c r="M2">
-        <v>1.15</v>
-      </c>
-      <c r="N2">
-        <v>2.5</v>
-      </c>
-      <c r="O2">
-        <v>1.65</v>
-      </c>
-      <c r="P2">
-        <v>1.47</v>
-      </c>
-      <c r="Q2">
-        <v>3.05</v>
-      </c>
-      <c r="R2">
-        <v>1.16</v>
-      </c>
-      <c r="S2">
-        <v>6.8</v>
-      </c>
-      <c r="T2">
-        <v>2.4</v>
-      </c>
-      <c r="U2">
-        <v>1.67</v>
-      </c>
-      <c r="V2">
-        <v>1.29</v>
-      </c>
-      <c r="W2">
-        <v>1.79</v>
-      </c>
-      <c r="X2">
-        <v>7.6</v>
-      </c>
-      <c r="Y2">
-        <v>10.5</v>
-      </c>
-      <c r="Z2">
-        <v>29</v>
-      </c>
-      <c r="AA2">
-        <v>120</v>
-      </c>
-      <c r="AB2">
-        <v>6.6</v>
-      </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
-      <c r="AD2">
-        <v>22</v>
-      </c>
-      <c r="AE2">
-        <v>95</v>
-      </c>
-      <c r="AF2">
-        <v>11.5</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>170</v>
-      </c>
-      <c r="AJ2">
-        <v>30</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>250</v>
-      </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>7</v>
-      </c>
-      <c r="AQ2">
-        <v>9.6</v>
-      </c>
-      <c r="AR2">
-        <v>25</v>
-      </c>
-      <c r="AS2">
-        <v>40</v>
-      </c>
-      <c r="AT2">
-        <v>6</v>
-      </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>310</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="AZ2">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="BD2">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="BE2">
+        <v>280</v>
+      </c>
+      <c r="BF2">
         <v>160</v>
       </c>
-      <c r="BF2">
-        <v>30</v>
-      </c>
       <c r="BG2">
-        <v>46</v>
+        <v>300</v>
       </c>
       <c r="BH2">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>239</v>
@@ -1569,226 +1569,226 @@
         <v>190</v>
       </c>
       <c r="F3">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="G3">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="H3">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>2.64</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>2.78</v>
+      </c>
+      <c r="AD3">
+        <v>4.8</v>
+      </c>
+      <c r="AE3">
+        <v>18.5</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>7.2</v>
+      </c>
+      <c r="AH3">
+        <v>11</v>
+      </c>
+      <c r="AI3">
+        <v>55</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>70</v>
+      </c>
+      <c r="AM3">
+        <v>270</v>
+      </c>
+      <c r="AN3">
+        <v>230</v>
+      </c>
+      <c r="AO3">
+        <v>85</v>
+      </c>
+      <c r="AP3">
         <v>13</v>
       </c>
-      <c r="AC3">
-        <v>8</v>
-      </c>
-      <c r="AD3">
-        <v>11.5</v>
-      </c>
-      <c r="AE3">
-        <v>27</v>
-      </c>
-      <c r="AF3">
-        <v>27</v>
-      </c>
-      <c r="AG3">
+      <c r="AQ3">
+        <v>13</v>
+      </c>
+      <c r="AR3">
+        <v>13</v>
+      </c>
+      <c r="AS3">
+        <v>13</v>
+      </c>
+      <c r="AT3">
+        <v>13</v>
+      </c>
+      <c r="AU3">
+        <v>2.66</v>
+      </c>
+      <c r="AV3">
+        <v>4.1</v>
+      </c>
+      <c r="AW3">
         <v>16.5</v>
       </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
-        <v>46</v>
-      </c>
-      <c r="AJ3">
-        <v>90</v>
-      </c>
-      <c r="AK3">
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>6.4</v>
+      </c>
+      <c r="AZ3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA3">
+        <v>36</v>
+      </c>
+      <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
+        <v>36</v>
+      </c>
+      <c r="BD3">
         <v>55</v>
       </c>
-      <c r="AL3">
-        <v>85</v>
-      </c>
-      <c r="AM3">
-        <v>160</v>
-      </c>
-      <c r="AN3">
+      <c r="BE3">
+        <v>120</v>
+      </c>
+      <c r="BF3">
         <v>80</v>
       </c>
-      <c r="AO3">
-        <v>23</v>
-      </c>
-      <c r="AP3">
-        <v>10</v>
-      </c>
-      <c r="AQ3">
-        <v>7.4</v>
-      </c>
-      <c r="AR3">
-        <v>12.5</v>
-      </c>
-      <c r="AS3">
-        <v>23</v>
-      </c>
-      <c r="AT3">
-        <v>10.5</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>9.6</v>
-      </c>
-      <c r="AW3">
-        <v>21</v>
-      </c>
-      <c r="AX3">
-        <v>22</v>
-      </c>
-      <c r="AY3">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3">
-        <v>17</v>
-      </c>
-      <c r="BA3">
-        <v>32</v>
-      </c>
-      <c r="BB3">
-        <v>50</v>
-      </c>
-      <c r="BC3">
-        <v>34</v>
-      </c>
-      <c r="BD3">
-        <v>44</v>
-      </c>
-      <c r="BE3">
-        <v>95</v>
-      </c>
-      <c r="BF3">
-        <v>42</v>
-      </c>
       <c r="BG3">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>239</v>
@@ -1811,226 +1811,226 @@
         <v>191</v>
       </c>
       <c r="F4">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="G4">
-        <v>2.26</v>
+        <v>1.54</v>
       </c>
       <c r="H4">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
+        <v>10.5</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="J4">
-        <v>3.35</v>
-      </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="W4">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>4.6</v>
+      </c>
+      <c r="AC4">
+        <v>5.5</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
         <v>85</v>
       </c>
-      <c r="AB4">
-        <v>8.6</v>
-      </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
-        <v>17</v>
-      </c>
-      <c r="AE4">
-        <v>55</v>
-      </c>
       <c r="AF4">
+        <v>6.4</v>
+      </c>
+      <c r="AG4">
+        <v>8</v>
+      </c>
+      <c r="AH4">
+        <v>21</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>19.5</v>
+      </c>
+      <c r="AK4">
+        <v>26</v>
+      </c>
+      <c r="AL4">
+        <v>80</v>
+      </c>
+      <c r="AM4">
+        <v>340</v>
+      </c>
+      <c r="AN4">
+        <v>40</v>
+      </c>
+      <c r="AO4">
+        <v>240</v>
+      </c>
+      <c r="AP4">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4">
+        <v>19.5</v>
+      </c>
+      <c r="AR4">
+        <v>19.5</v>
+      </c>
+      <c r="AS4">
+        <v>19.5</v>
+      </c>
+      <c r="AT4">
+        <v>4.3</v>
+      </c>
+      <c r="AU4">
+        <v>5.1</v>
+      </c>
+      <c r="AV4">
         <v>13.5</v>
       </c>
-      <c r="AG4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH4">
+      <c r="AW4">
+        <v>60</v>
+      </c>
+      <c r="AX4">
+        <v>5.9</v>
+      </c>
+      <c r="AY4">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4">
         <v>19</v>
       </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>28</v>
-      </c>
-      <c r="AK4">
-        <v>25</v>
-      </c>
-      <c r="AL4">
-        <v>42</v>
-      </c>
-      <c r="AM4">
+      <c r="BA4">
+        <v>75</v>
+      </c>
+      <c r="BB4">
+        <v>17.5</v>
+      </c>
+      <c r="BC4">
+        <v>23</v>
+      </c>
+      <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
+        <v>240</v>
+      </c>
+      <c r="BF4">
+        <v>32</v>
+      </c>
+      <c r="BG4">
         <v>120</v>
       </c>
-      <c r="AN4">
-        <v>21</v>
-      </c>
-      <c r="AO4">
-        <v>65</v>
-      </c>
-      <c r="AP4">
-        <v>11</v>
-      </c>
-      <c r="AQ4">
-        <v>12</v>
-      </c>
-      <c r="AR4">
-        <v>23</v>
-      </c>
-      <c r="AS4">
-        <v>46</v>
-      </c>
-      <c r="AT4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4">
-        <v>6.8</v>
-      </c>
-      <c r="AV4">
-        <v>14.5</v>
-      </c>
-      <c r="AW4">
-        <v>14</v>
-      </c>
-      <c r="AX4">
-        <v>12</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>17.5</v>
-      </c>
-      <c r="BA4">
-        <v>14.5</v>
-      </c>
-      <c r="BB4">
-        <v>25</v>
-      </c>
-      <c r="BC4">
-        <v>22</v>
-      </c>
-      <c r="BD4">
-        <v>38</v>
-      </c>
-      <c r="BE4">
-        <v>16</v>
-      </c>
-      <c r="BF4">
-        <v>18</v>
-      </c>
-      <c r="BG4">
-        <v>48</v>
-      </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>239</v>
@@ -2053,226 +2053,226 @@
         <v>192</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
+        <v>3.75</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>6.4</v>
+      </c>
+      <c r="Q5">
+        <v>1.17</v>
+      </c>
+      <c r="R5">
+        <v>2.26</v>
+      </c>
+      <c r="S5">
+        <v>1.72</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1.12</v>
+      </c>
+      <c r="W5">
+        <v>2.6</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>7</v>
+      </c>
+      <c r="AD5">
+        <v>40</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>5.2</v>
+      </c>
+      <c r="AH5">
+        <v>14.5</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>8.6</v>
+      </c>
+      <c r="AL5">
+        <v>21</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>8.4</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>3.5</v>
+      </c>
+      <c r="AQ5">
+        <v>3.5</v>
+      </c>
+      <c r="AR5">
+        <v>3.5</v>
+      </c>
+      <c r="AS5">
+        <v>3.5</v>
+      </c>
+      <c r="AT5">
+        <v>3.5</v>
+      </c>
+      <c r="AU5">
+        <v>5.9</v>
+      </c>
+      <c r="AV5">
+        <v>9.6</v>
+      </c>
+      <c r="AW5">
+        <v>4.4</v>
+      </c>
+      <c r="AX5">
+        <v>3.5</v>
+      </c>
+      <c r="AY5">
+        <v>3.95</v>
+      </c>
+      <c r="AZ5">
+        <v>8</v>
+      </c>
+      <c r="BA5">
+        <v>5.5</v>
+      </c>
+      <c r="BB5">
+        <v>3.5</v>
+      </c>
+      <c r="BC5">
+        <v>5.6</v>
+      </c>
+      <c r="BD5">
+        <v>12.5</v>
+      </c>
+      <c r="BE5">
+        <v>4.4</v>
+      </c>
+      <c r="BF5">
         <v>5.3</v>
       </c>
-      <c r="L5">
-        <v>1.27</v>
-      </c>
-      <c r="M5">
-        <v>1.03</v>
-      </c>
-      <c r="N5">
-        <v>6.4</v>
-      </c>
-      <c r="O5">
-        <v>1.17</v>
-      </c>
-      <c r="P5">
-        <v>2.82</v>
-      </c>
-      <c r="Q5">
-        <v>1.52</v>
-      </c>
-      <c r="R5">
-        <v>1.73</v>
-      </c>
-      <c r="S5">
-        <v>2.3</v>
-      </c>
-      <c r="T5">
-        <v>1.69</v>
-      </c>
-      <c r="U5">
-        <v>2.38</v>
-      </c>
-      <c r="V5">
-        <v>1.17</v>
-      </c>
-      <c r="W5">
-        <v>2.88</v>
-      </c>
-      <c r="X5">
-        <v>29</v>
-      </c>
-      <c r="Y5">
-        <v>32</v>
-      </c>
-      <c r="Z5">
-        <v>60</v>
-      </c>
-      <c r="AA5">
-        <v>170</v>
-      </c>
-      <c r="AB5">
-        <v>13</v>
-      </c>
-      <c r="AC5">
-        <v>12</v>
-      </c>
-      <c r="AD5">
-        <v>25</v>
-      </c>
-      <c r="AE5">
-        <v>75</v>
-      </c>
-      <c r="AF5">
-        <v>11.5</v>
-      </c>
-      <c r="AG5">
-        <v>9.4</v>
-      </c>
-      <c r="AH5">
-        <v>19</v>
-      </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>14.5</v>
-      </c>
-      <c r="AK5">
-        <v>14.5</v>
-      </c>
-      <c r="AL5">
-        <v>26</v>
-      </c>
-      <c r="AM5">
-        <v>80</v>
-      </c>
-      <c r="AN5">
-        <v>5.3</v>
-      </c>
-      <c r="AO5">
-        <v>70</v>
-      </c>
-      <c r="AP5">
-        <v>27</v>
-      </c>
-      <c r="AQ5">
-        <v>30</v>
-      </c>
-      <c r="AR5">
-        <v>50</v>
-      </c>
-      <c r="AS5">
-        <v>20</v>
-      </c>
-      <c r="AT5">
-        <v>11.5</v>
-      </c>
-      <c r="AU5">
-        <v>11</v>
-      </c>
-      <c r="AV5">
-        <v>23</v>
-      </c>
-      <c r="AW5">
-        <v>65</v>
-      </c>
-      <c r="AX5">
-        <v>10</v>
-      </c>
-      <c r="AY5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5">
-        <v>17.5</v>
-      </c>
-      <c r="BA5">
-        <v>55</v>
-      </c>
-      <c r="BB5">
-        <v>13</v>
-      </c>
-      <c r="BC5">
-        <v>13</v>
-      </c>
-      <c r="BD5">
-        <v>24</v>
-      </c>
-      <c r="BE5">
-        <v>65</v>
-      </c>
-      <c r="BF5">
-        <v>5</v>
-      </c>
       <c r="BG5">
-        <v>55</v>
+        <v>4.6</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>1.16</v>
       </c>
       <c r="BK5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BN5">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>239</v>
@@ -2295,226 +2295,226 @@
         <v>193</v>
       </c>
       <c r="F6">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="H6">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>190</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>36</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q6">
+        <v>1.1</v>
+      </c>
+      <c r="R6">
+        <v>2.88</v>
+      </c>
+      <c r="S6">
+        <v>1.46</v>
+      </c>
+      <c r="T6">
+        <v>1.89</v>
+      </c>
+      <c r="U6">
+        <v>1.85</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>17.5</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>11</v>
+      </c>
+      <c r="AG6">
+        <v>14</v>
+      </c>
+      <c r="AH6">
+        <v>60</v>
+      </c>
+      <c r="AI6">
+        <v>280</v>
+      </c>
+      <c r="AJ6">
+        <v>6.8</v>
+      </c>
+      <c r="AK6">
+        <v>9.4</v>
+      </c>
+      <c r="AL6">
+        <v>28</v>
+      </c>
+      <c r="AM6">
+        <v>160</v>
+      </c>
+      <c r="AN6">
+        <v>2.52</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>8</v>
+      </c>
+      <c r="AQ6">
+        <v>8</v>
+      </c>
+      <c r="AR6">
+        <v>8</v>
+      </c>
+      <c r="AS6">
+        <v>8</v>
+      </c>
+      <c r="AT6">
+        <v>8</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>8</v>
+      </c>
+      <c r="AW6">
+        <v>8</v>
+      </c>
+      <c r="AX6">
+        <v>7.8</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>30</v>
+      </c>
+      <c r="BA6">
+        <v>130</v>
+      </c>
+      <c r="BB6">
+        <v>5.1</v>
+      </c>
+      <c r="BC6">
+        <v>7.6</v>
+      </c>
+      <c r="BD6">
+        <v>22</v>
+      </c>
+      <c r="BE6">
+        <v>85</v>
+      </c>
+      <c r="BF6">
+        <v>2.16</v>
+      </c>
+      <c r="BG6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>4.9</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>4.9</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>5</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>4.9</v>
+      </c>
+      <c r="BP6">
+        <v>2.62</v>
+      </c>
+      <c r="BQ6">
+        <v>1.82</v>
+      </c>
+      <c r="BR6">
         <v>11.5</v>
       </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>5.6</v>
-      </c>
-      <c r="K6">
-        <v>7.4</v>
-      </c>
-      <c r="L6">
-        <v>1.29</v>
-      </c>
-      <c r="M6">
-        <v>1.04</v>
-      </c>
-      <c r="N6">
-        <v>5.1</v>
-      </c>
-      <c r="O6">
-        <v>1.2</v>
-      </c>
-      <c r="P6">
-        <v>2.44</v>
-      </c>
-      <c r="Q6">
-        <v>1.59</v>
-      </c>
-      <c r="R6">
-        <v>1.57</v>
-      </c>
-      <c r="S6">
+      <c r="BS6">
+        <v>5.9</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>4.9</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>4.9</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>4.9</v>
+      </c>
+      <c r="BZ6">
+        <v>3.05</v>
+      </c>
+      <c r="CA6">
         <v>2.46</v>
-      </c>
-      <c r="T6">
-        <v>2.06</v>
-      </c>
-      <c r="U6">
-        <v>1.74</v>
-      </c>
-      <c r="V6">
-        <v>1.07</v>
-      </c>
-      <c r="W6">
-        <v>3.9</v>
-      </c>
-      <c r="X6">
-        <v>29</v>
-      </c>
-      <c r="Y6">
-        <v>50</v>
-      </c>
-      <c r="Z6">
-        <v>150</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>10</v>
-      </c>
-      <c r="AC6">
-        <v>15.5</v>
-      </c>
-      <c r="AD6">
-        <v>55</v>
-      </c>
-      <c r="AE6">
-        <v>280</v>
-      </c>
-      <c r="AF6">
-        <v>9</v>
-      </c>
-      <c r="AG6">
-        <v>12</v>
-      </c>
-      <c r="AH6">
-        <v>38</v>
-      </c>
-      <c r="AI6">
-        <v>190</v>
-      </c>
-      <c r="AJ6">
-        <v>12</v>
-      </c>
-      <c r="AK6">
-        <v>16</v>
-      </c>
-      <c r="AL6">
-        <v>48</v>
-      </c>
-      <c r="AM6">
-        <v>210</v>
-      </c>
-      <c r="AN6">
-        <v>5.1</v>
-      </c>
-      <c r="AO6">
-        <v>380</v>
-      </c>
-      <c r="AP6">
-        <v>19.5</v>
-      </c>
-      <c r="AQ6">
-        <v>6</v>
-      </c>
-      <c r="AR6">
-        <v>6</v>
-      </c>
-      <c r="AS6">
-        <v>6.2</v>
-      </c>
-      <c r="AT6">
-        <v>7.6</v>
-      </c>
-      <c r="AU6">
-        <v>11.5</v>
-      </c>
-      <c r="AV6">
-        <v>6.2</v>
-      </c>
-      <c r="AW6">
-        <v>6.2</v>
-      </c>
-      <c r="AX6">
-        <v>6.8</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
-      </c>
-      <c r="AZ6">
-        <v>5.9</v>
-      </c>
-      <c r="BA6">
-        <v>6</v>
-      </c>
-      <c r="BB6">
-        <v>8</v>
-      </c>
-      <c r="BC6">
-        <v>11.5</v>
-      </c>
-      <c r="BD6">
-        <v>28</v>
-      </c>
-      <c r="BE6">
-        <v>6.2</v>
-      </c>
-      <c r="BF6">
-        <v>4</v>
-      </c>
-      <c r="BG6">
-        <v>6.2</v>
-      </c>
-      <c r="BH6">
-        <v>4.7</v>
-      </c>
-      <c r="BI6">
-        <v>3.4</v>
-      </c>
-      <c r="BJ6">
-        <v>14</v>
-      </c>
-      <c r="BK6">
-        <v>9.4</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>7.4</v>
-      </c>
-      <c r="BN6">
-        <v>4</v>
-      </c>
-      <c r="BO6">
-        <v>3.2</v>
-      </c>
-      <c r="BP6">
-        <v>7.6</v>
-      </c>
-      <c r="BQ6">
-        <v>5.8</v>
-      </c>
-      <c r="BR6">
-        <v>25</v>
-      </c>
-      <c r="BS6">
-        <v>6</v>
-      </c>
-      <c r="BT6">
-        <v>17</v>
-      </c>
-      <c r="BU6">
-        <v>5.4</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>7.4</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>7.2</v>
-      </c>
-      <c r="BZ6">
-        <v>11.5</v>
-      </c>
-      <c r="CA6">
-        <v>4.6</v>
       </c>
       <c r="CB6" t="s">
         <v>239</v>
@@ -2537,16 +2537,16 @@
         <v>194</v>
       </c>
       <c r="F7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -2567,10 +2567,10 @@
         <v>1.46</v>
       </c>
       <c r="P7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>1.23</v>
@@ -2582,28 +2582,28 @@
         <v>2</v>
       </c>
       <c r="U7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7">
         <v>15</v>
       </c>
       <c r="AA7">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -2639,64 +2639,64 @@
         <v>170</v>
       </c>
       <c r="AN7">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO7">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AR7">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU7">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AV7">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX7">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AY7">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC7">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD7">
+        <v>6.4</v>
+      </c>
+      <c r="BE7">
+        <v>6.6</v>
+      </c>
+      <c r="BF7">
+        <v>6.4</v>
+      </c>
+      <c r="BG7">
         <v>5.6</v>
-      </c>
-      <c r="BE7">
-        <v>5.9</v>
-      </c>
-      <c r="BF7">
-        <v>5.6</v>
-      </c>
-      <c r="BG7">
-        <v>5</v>
       </c>
       <c r="BH7">
         <v>3.1</v>
@@ -2779,28 +2779,28 @@
         <v>195</v>
       </c>
       <c r="F8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G8">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I8">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J8">
         <v>4.5</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
         <v>9</v>
@@ -2815,7 +2815,7 @@
         <v>1.32</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S8">
         <v>1.79</v>
@@ -2824,7 +2824,7 @@
         <v>1.37</v>
       </c>
       <c r="U8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V8">
         <v>1.56</v>
@@ -2836,10 +2836,10 @@
         <v>55</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8">
         <v>48</v>
@@ -2866,10 +2866,10 @@
         <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -2878,7 +2878,7 @@
         <v>25</v>
       </c>
       <c r="AM8">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AN8">
         <v>9.199999999999999</v>
@@ -2887,7 +2887,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
         <v>20</v>
@@ -2962,7 +2962,7 @@
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP8">
         <v>15</v>
@@ -2980,7 +2980,7 @@
         <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV8">
         <v>17.5</v>
@@ -3021,19 +3021,19 @@
         <v>196</v>
       </c>
       <c r="F9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G9">
         <v>1.36</v>
       </c>
       <c r="H9">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K9">
         <v>6.8</v>
@@ -3132,7 +3132,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AR9">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="BF9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG9">
         <v>15</v>
@@ -3347,7 +3347,7 @@
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>150</v>
@@ -3416,7 +3416,7 @@
         <v>18</v>
       </c>
       <c r="BE10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF10">
         <v>7.4</v>
@@ -3505,10 +3505,10 @@
         <v>198</v>
       </c>
       <c r="F11">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H11">
         <v>22</v>
@@ -3517,10 +3517,10 @@
         <v>26</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L11">
         <v>1.16</v>
@@ -3529,7 +3529,7 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O11">
         <v>1.14</v>
@@ -3547,7 +3547,7 @@
         <v>2.06</v>
       </c>
       <c r="T11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U11">
         <v>1.62</v>
@@ -3556,7 +3556,7 @@
         <v>1.04</v>
       </c>
       <c r="W11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X11">
         <v>42</v>
@@ -3607,22 +3607,22 @@
         <v>310</v>
       </c>
       <c r="AN11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT11">
         <v>9.6</v>
@@ -3631,10 +3631,10 @@
         <v>17.5</v>
       </c>
       <c r="AV11">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX11">
         <v>6.2</v>
@@ -3643,10 +3643,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
         <v>6.2</v>
@@ -3655,16 +3655,16 @@
         <v>10.5</v>
       </c>
       <c r="BD11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
         <v>2.78</v>
       </c>
       <c r="BG11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3750,7 +3750,7 @@
         <v>3.15</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
         <v>2.12</v>
@@ -3777,7 +3777,7 @@
         <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q12">
         <v>1.54</v>
@@ -3992,19 +3992,19 @@
         <v>1.87</v>
       </c>
       <c r="G13">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
         <v>1.44</v>
@@ -4013,7 +4013,7 @@
         <v>1.08</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13">
         <v>1.37</v>
@@ -4037,19 +4037,19 @@
         <v>1.95</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X13">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z13">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -4061,7 +4061,7 @@
         <v>9.4</v>
       </c>
       <c r="AD13">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE13">
         <v>320</v>
@@ -4073,16 +4073,16 @@
         <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AI13">
         <v>320</v>
       </c>
       <c r="AJ13">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AK13">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AL13">
         <v>48</v>
@@ -4091,7 +4091,7 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO13">
         <v>290</v>
@@ -4106,7 +4106,7 @@
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
         <v>7</v>
@@ -4118,7 +4118,7 @@
         <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13">
         <v>9.800000000000001</v>
@@ -4130,7 +4130,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
         <v>10.5</v>
@@ -4139,22 +4139,22 @@
         <v>16.5</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
         <v>12</v>
       </c>
       <c r="BG13">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH13">
         <v>3.25</v>
       </c>
       <c r="BI13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13">
         <v>10.5</v>
@@ -4279,10 +4279,10 @@
         <v>2</v>
       </c>
       <c r="V14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
         <v>15</v>
@@ -4414,7 +4414,7 @@
         <v>8</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP14">
         <v>40</v>
@@ -4715,13 +4715,13 @@
         <v>203</v>
       </c>
       <c r="F16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G16">
         <v>3.7</v>
       </c>
       <c r="H16">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I16">
         <v>2.08</v>
@@ -4730,7 +4730,7 @@
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>1.25</v>
@@ -4745,7 +4745,7 @@
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q16">
         <v>1.58</v>
@@ -4778,13 +4778,13 @@
         <v>18.5</v>
       </c>
       <c r="AA16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB16">
         <v>21</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
         <v>11</v>
@@ -4793,7 +4793,7 @@
         <v>18.5</v>
       </c>
       <c r="AF16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG16">
         <v>16</v>
@@ -4808,7 +4808,7 @@
         <v>70</v>
       </c>
       <c r="AK16">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL16">
         <v>38</v>
@@ -4826,7 +4826,7 @@
         <v>22</v>
       </c>
       <c r="AQ16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR16">
         <v>14.5</v>
@@ -4844,7 +4844,7 @@
         <v>10</v>
       </c>
       <c r="AW16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX16">
         <v>27</v>
@@ -4859,7 +4859,7 @@
         <v>23</v>
       </c>
       <c r="BB16">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC16">
         <v>21</v>
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="BG16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH16">
         <v>4.4</v>
@@ -4898,7 +4898,7 @@
         <v>7.2</v>
       </c>
       <c r="BO16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP16">
         <v>25</v>
@@ -4963,16 +4963,16 @@
         <v>3.25</v>
       </c>
       <c r="H17">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I17">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4981,28 +4981,28 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R17">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S17">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="T17">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V17">
         <v>1.73</v>
@@ -5014,16 +5014,16 @@
         <v>20</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA17">
         <v>32</v>
       </c>
       <c r="AB17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -5038,10 +5038,10 @@
         <v>25</v>
       </c>
       <c r="AG17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI17">
         <v>32</v>
@@ -5050,19 +5050,19 @@
         <v>55</v>
       </c>
       <c r="AK17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL17">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM17">
         <v>90</v>
       </c>
       <c r="AN17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO17">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AP17">
         <v>16</v>
@@ -5080,7 +5080,7 @@
         <v>13</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17">
         <v>9.800000000000001</v>
@@ -5095,25 +5095,25 @@
         <v>12.5</v>
       </c>
       <c r="AZ17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB17">
         <v>44</v>
       </c>
       <c r="BC17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE17">
         <v>60</v>
       </c>
       <c r="BF17">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BG17">
         <v>13</v>
@@ -5125,7 +5125,7 @@
         <v>3</v>
       </c>
       <c r="BJ17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17">
         <v>6.8</v>
@@ -5146,19 +5146,19 @@
         <v>24</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS17">
         <v>7.8</v>
       </c>
       <c r="BT17">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV17">
         <v>17.5</v>
@@ -5199,10 +5199,10 @@
         <v>205</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G18">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -5400,7 +5400,7 @@
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV18">
         <v>25</v>
@@ -5447,16 +5447,16 @@
         <v>1.49</v>
       </c>
       <c r="H19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J19">
         <v>4.7</v>
       </c>
       <c r="K19">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5483,10 +5483,10 @@
         <v>2.72</v>
       </c>
       <c r="T19">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V19">
         <v>1.11</v>
@@ -5507,7 +5507,7 @@
         <v>320</v>
       </c>
       <c r="AB19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19">
         <v>13.5</v>
@@ -5519,7 +5519,7 @@
         <v>150</v>
       </c>
       <c r="AF19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG19">
         <v>11</v>
@@ -5531,7 +5531,7 @@
         <v>460</v>
       </c>
       <c r="AJ19">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK19">
         <v>16</v>
@@ -5555,10 +5555,10 @@
         <v>14.5</v>
       </c>
       <c r="AR19">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS19">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT19">
         <v>7.2</v>
@@ -5570,7 +5570,7 @@
         <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19">
         <v>7</v>
@@ -5582,7 +5582,7 @@
         <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB19">
         <v>9.6</v>
@@ -5594,7 +5594,7 @@
         <v>18</v>
       </c>
       <c r="BE19">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF19">
         <v>5.4</v>
@@ -5683,10 +5683,10 @@
         <v>207</v>
       </c>
       <c r="F20">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G20">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H20">
         <v>5.7</v>
@@ -5695,46 +5695,46 @@
         <v>6.4</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P20">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S20">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T20">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V20">
         <v>1.18</v>
       </c>
       <c r="W20">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X20">
         <v>17.5</v>
@@ -5743,7 +5743,7 @@
         <v>23</v>
       </c>
       <c r="Z20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA20">
         <v>900</v>
@@ -5755,7 +5755,7 @@
         <v>11</v>
       </c>
       <c r="AD20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20">
         <v>110</v>
@@ -5770,7 +5770,7 @@
         <v>27</v>
       </c>
       <c r="AI20">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ20">
         <v>21</v>
@@ -5785,7 +5785,7 @@
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO20">
         <v>130</v>
@@ -5797,34 +5797,34 @@
         <v>14</v>
       </c>
       <c r="AR20">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS20">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT20">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV20">
         <v>17</v>
       </c>
       <c r="AW20">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX20">
         <v>8.6</v>
       </c>
       <c r="AY20">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20">
         <v>16</v>
       </c>
       <c r="BA20">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB20">
         <v>12</v>
@@ -5836,13 +5836,13 @@
         <v>16</v>
       </c>
       <c r="BE20">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH20">
         <v>4.1</v>
@@ -5925,64 +5925,64 @@
         <v>208</v>
       </c>
       <c r="F21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R21">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U21">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X21">
         <v>25</v>
       </c>
       <c r="Y21">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="Z21">
         <v>55</v>
@@ -5991,22 +5991,22 @@
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE21">
         <v>400</v>
       </c>
       <c r="AF21">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
         <v>23</v>
@@ -6039,13 +6039,13 @@
         <v>15.5</v>
       </c>
       <c r="AR21">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS21">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU21">
         <v>8.6</v>
@@ -6054,10 +6054,10 @@
         <v>17.5</v>
       </c>
       <c r="AW21">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX21">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
@@ -6066,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BB21">
         <v>12.5</v>
@@ -6078,19 +6078,19 @@
         <v>16</v>
       </c>
       <c r="BE21">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF21">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG21">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BH21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ21">
         <v>10</v>
@@ -6108,16 +6108,16 @@
         <v>4.6</v>
       </c>
       <c r="BO21">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ21">
         <v>8</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS21">
         <v>7.8</v>
@@ -6132,7 +6132,7 @@
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX21">
         <v>1000</v>
@@ -6179,7 +6179,7 @@
         <v>2.54</v>
       </c>
       <c r="J22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22">
         <v>3.45</v>
@@ -6191,7 +6191,7 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O22">
         <v>1.34</v>
@@ -6203,7 +6203,7 @@
         <v>2.02</v>
       </c>
       <c r="R22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S22">
         <v>3.6</v>
@@ -6218,13 +6218,13 @@
         <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X22">
         <v>16</v>
       </c>
       <c r="Y22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>18.5</v>
@@ -6245,7 +6245,7 @@
         <v>32</v>
       </c>
       <c r="AF22">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG22">
         <v>17.5</v>
@@ -6308,19 +6308,19 @@
         <v>15</v>
       </c>
       <c r="BA22">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB22">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC22">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD22">
         <v>36</v>
       </c>
       <c r="BE22">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF22">
         <v>7.2</v>
@@ -6409,7 +6409,7 @@
         <v>210</v>
       </c>
       <c r="F23">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G23">
         <v>2.1</v>
@@ -6418,13 +6418,13 @@
         <v>3.5</v>
       </c>
       <c r="I23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J23">
         <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>1.25</v>
@@ -6496,7 +6496,7 @@
         <v>16.5</v>
       </c>
       <c r="AI23">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AJ23">
         <v>25</v>
@@ -6514,7 +6514,7 @@
         <v>9.6</v>
       </c>
       <c r="AO23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP23">
         <v>21</v>
@@ -6592,7 +6592,7 @@
         <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP23">
         <v>13.5</v>
@@ -6654,19 +6654,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24">
+        <v>1.4</v>
+      </c>
+      <c r="I24">
         <v>1.42</v>
-      </c>
-      <c r="I24">
-        <v>1.43</v>
       </c>
       <c r="J24">
         <v>5.7</v>
       </c>
       <c r="K24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L24">
         <v>1.25</v>
@@ -6690,13 +6690,13 @@
         <v>1.76</v>
       </c>
       <c r="S24">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U24">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
         <v>3.35</v>
@@ -6729,28 +6729,28 @@
         <v>13.5</v>
       </c>
       <c r="AF24">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AG24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AH24">
         <v>23</v>
       </c>
       <c r="AI24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ24">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="AK24">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AL24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN24">
         <v>85</v>
@@ -6771,7 +6771,7 @@
         <v>11.5</v>
       </c>
       <c r="AT24">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AU24">
         <v>12</v>
@@ -6783,7 +6783,7 @@
         <v>12</v>
       </c>
       <c r="AX24">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AY24">
         <v>27</v>
@@ -6923,13 +6923,13 @@
         <v>1.16</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q25">
         <v>1.5</v>
       </c>
       <c r="R25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S25">
         <v>2.24</v>
@@ -6950,10 +6950,10 @@
         <v>29</v>
       </c>
       <c r="Y25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z25">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AA25">
         <v>190</v>
@@ -6995,16 +6995,16 @@
         <v>75</v>
       </c>
       <c r="AN25">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AO25">
         <v>65</v>
       </c>
       <c r="AP25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR25">
         <v>55</v>
@@ -7052,7 +7052,7 @@
         <v>4.9</v>
       </c>
       <c r="BG25">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BH25">
         <v>4.9</v>
@@ -7135,7 +7135,7 @@
         <v>213</v>
       </c>
       <c r="F26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G26">
         <v>1.16</v>
@@ -7180,13 +7180,13 @@
         <v>2.06</v>
       </c>
       <c r="U26">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V26">
         <v>1.03</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="X26">
         <v>65</v>
@@ -7243,7 +7243,7 @@
         <v>430</v>
       </c>
       <c r="AP26">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AQ26">
         <v>8.4</v>
@@ -7258,7 +7258,7 @@
         <v>13</v>
       </c>
       <c r="AU26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV26">
         <v>8.4</v>
@@ -7273,22 +7273,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ26">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BA26">
         <v>8.800000000000001</v>
       </c>
       <c r="BB26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD26">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="BE26">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF26">
         <v>2.2</v>
@@ -7380,7 +7380,7 @@
         <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H27">
         <v>3.45</v>
@@ -7389,7 +7389,7 @@
         <v>3.95</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K27">
         <v>3.55</v>
@@ -7407,7 +7407,7 @@
         <v>1.38</v>
       </c>
       <c r="P27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
         <v>2.14</v>
@@ -7434,7 +7434,7 @@
         <v>12.5</v>
       </c>
       <c r="Y27">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z27">
         <v>27</v>
@@ -7494,7 +7494,7 @@
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27">
         <v>7.6</v>
@@ -7506,7 +7506,7 @@
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX27">
         <v>12</v>
@@ -7527,10 +7527,10 @@
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF27">
         <v>18</v>
@@ -7625,7 +7625,7 @@
         <v>2.38</v>
       </c>
       <c r="H28">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I28">
         <v>4</v>
@@ -7637,22 +7637,22 @@
         <v>3.2</v>
       </c>
       <c r="L28">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M28">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N28">
         <v>3.15</v>
       </c>
       <c r="O28">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P28">
         <v>1.73</v>
       </c>
       <c r="Q28">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R28">
         <v>1.27</v>
@@ -7664,7 +7664,7 @@
         <v>1.88</v>
       </c>
       <c r="U28">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V28">
         <v>1.33</v>
@@ -7712,7 +7712,7 @@
         <v>75</v>
       </c>
       <c r="AK28">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AL28">
         <v>290</v>
@@ -7769,10 +7769,10 @@
         <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE28">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF28">
         <v>17.5</v>
@@ -7861,22 +7861,22 @@
         <v>216</v>
       </c>
       <c r="F29">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G29">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H29">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="I29">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="J29">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K29">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7888,40 +7888,40 @@
         <v>11</v>
       </c>
       <c r="O29">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q29">
         <v>1.25</v>
       </c>
       <c r="R29">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="T29">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="U29">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V29">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="W29">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X29">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="Y29">
         <v>75</v>
       </c>
       <c r="Z29">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AA29">
         <v>80</v>
@@ -7930,46 +7930,46 @@
         <v>100</v>
       </c>
       <c r="AC29">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD29">
         <v>18.5</v>
       </c>
       <c r="AE29">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AF29">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AG29">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH29">
         <v>13.5</v>
       </c>
       <c r="AI29">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AJ29">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AK29">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AM29">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AN29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO29">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AP29">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ29">
         <v>14.5</v>
@@ -7981,7 +7981,7 @@
         <v>14.5</v>
       </c>
       <c r="AT29">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AU29">
         <v>11.5</v>
@@ -7993,10 +7993,10 @@
         <v>14.5</v>
       </c>
       <c r="AX29">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY29">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ29">
         <v>11</v>
@@ -8005,7 +8005,7 @@
         <v>13</v>
       </c>
       <c r="BB29">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC29">
         <v>14.5</v>
@@ -8020,7 +8020,7 @@
         <v>8.6</v>
       </c>
       <c r="BG29">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8118,7 +8118,7 @@
         <v>3.8</v>
       </c>
       <c r="K30">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L30">
         <v>1.28</v>
@@ -8130,19 +8130,19 @@
         <v>5</v>
       </c>
       <c r="O30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P30">
         <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R30">
         <v>1.54</v>
       </c>
       <c r="S30">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T30">
         <v>1.59</v>
@@ -8274,25 +8274,25 @@
         <v>9</v>
       </c>
       <c r="BK30">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN30">
         <v>5.6</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP30">
         <v>15.5</v>
       </c>
       <c r="BQ30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR30">
         <v>25</v>
@@ -8304,7 +8304,7 @@
         <v>7.2</v>
       </c>
       <c r="BU30">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV30">
         <v>25</v>
@@ -8316,10 +8316,10 @@
         <v>32</v>
       </c>
       <c r="BY30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ30">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA30">
         <v>6.6</v>
@@ -8345,16 +8345,16 @@
         <v>218</v>
       </c>
       <c r="F31">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G31">
         <v>2.38</v>
       </c>
       <c r="H31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8372,7 +8372,7 @@
         <v>4.1</v>
       </c>
       <c r="O31">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P31">
         <v>2.08</v>
@@ -8384,7 +8384,7 @@
         <v>1.42</v>
       </c>
       <c r="S31">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T31">
         <v>1.68</v>
@@ -8587,13 +8587,13 @@
         <v>219</v>
       </c>
       <c r="F32">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G32">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H32">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I32">
         <v>6.6</v>
@@ -8602,7 +8602,7 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L32">
         <v>1.25</v>
@@ -8623,7 +8623,7 @@
         <v>1.58</v>
       </c>
       <c r="R32">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S32">
         <v>2.36</v>
@@ -8653,7 +8653,7 @@
         <v>160</v>
       </c>
       <c r="AB32">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC32">
         <v>11</v>
@@ -8701,13 +8701,13 @@
         <v>11.5</v>
       </c>
       <c r="AR32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS32">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT32">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU32">
         <v>8.800000000000001</v>
@@ -8716,7 +8716,7 @@
         <v>20</v>
       </c>
       <c r="AW32">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX32">
         <v>10</v>
@@ -8728,7 +8728,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB32">
         <v>13.5</v>
@@ -8740,13 +8740,13 @@
         <v>14.5</v>
       </c>
       <c r="BE32">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH32">
         <v>4.6</v>
@@ -8841,10 +8841,10 @@
         <v>2.58</v>
       </c>
       <c r="J33">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="K33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L33">
         <v>1.66</v>
@@ -8853,16 +8853,16 @@
         <v>1.16</v>
       </c>
       <c r="N33">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="O33">
         <v>1.67</v>
       </c>
       <c r="P33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R33">
         <v>1.13</v>
@@ -8913,7 +8913,7 @@
         <v>21</v>
       </c>
       <c r="AH33">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AI33">
         <v>460</v>
@@ -9071,10 +9071,10 @@
         <v>221</v>
       </c>
       <c r="F34">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="G34">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H34">
         <v>3.7</v>
@@ -9086,7 +9086,7 @@
         <v>2.74</v>
       </c>
       <c r="K34">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9095,13 +9095,13 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O34">
         <v>1.58</v>
       </c>
       <c r="P34">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q34">
         <v>1.58</v>
@@ -9122,10 +9122,10 @@
         <v>1.17</v>
       </c>
       <c r="W34">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y34">
         <v>1000</v>
@@ -9140,7 +9140,7 @@
         <v>1000</v>
       </c>
       <c r="AC34">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AD34">
         <v>1000</v>
@@ -9152,7 +9152,7 @@
         <v>1000</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH34">
         <v>1000</v>
@@ -9164,7 +9164,7 @@
         <v>900</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL34">
         <v>1000</v>
@@ -9179,55 +9179,55 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AQ34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AR34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AS34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AT34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AU34">
         <v>4.4</v>
       </c>
       <c r="AV34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AW34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AX34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AY34">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AZ34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BA34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BB34">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BC34">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BD34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BE34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BF34">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BG34">
         <v>1.55</v>
@@ -9331,7 +9331,7 @@
         <v>3.6</v>
       </c>
       <c r="L35">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M35">
         <v>1.07</v>
@@ -9418,7 +9418,7 @@
         <v>40</v>
       </c>
       <c r="AO35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP35">
         <v>10</v>
@@ -9457,7 +9457,7 @@
         <v>18</v>
       </c>
       <c r="BB35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC35">
         <v>16</v>
@@ -9475,10 +9475,10 @@
         <v>16</v>
       </c>
       <c r="BH35">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI35">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ35">
         <v>10</v>
@@ -9490,7 +9490,7 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN35">
         <v>6.6</v>
@@ -9502,37 +9502,37 @@
         <v>27</v>
       </c>
       <c r="BQ35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR35">
         <v>40</v>
       </c>
       <c r="BS35">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT35">
         <v>5.6</v>
       </c>
       <c r="BU35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX35">
         <v>34</v>
       </c>
       <c r="BY35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ35">
         <v>30</v>
       </c>
       <c r="CA35">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB35" t="s">
         <v>239</v>
@@ -9555,13 +9555,13 @@
         <v>223</v>
       </c>
       <c r="F36">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G36">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="H36">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -9582,19 +9582,19 @@
         <v>1.72</v>
       </c>
       <c r="O36">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P36">
         <v>1.71</v>
       </c>
       <c r="Q36">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R36">
         <v>1.12</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
         <v>1.11</v>
@@ -9606,7 +9606,7 @@
         <v>1.25</v>
       </c>
       <c r="W36">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9636,7 +9636,7 @@
         <v>1000</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH36">
         <v>1000</v>
@@ -9648,7 +9648,7 @@
         <v>900</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL36">
         <v>1000</v>
@@ -9663,52 +9663,52 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF36">
         <v>1.55</v>
@@ -9863,7 +9863,7 @@
         <v>900</v>
       </c>
       <c r="AB37">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC37">
         <v>9.199999999999999</v>
@@ -9878,7 +9878,7 @@
         <v>11.5</v>
       </c>
       <c r="AG37">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH37">
         <v>19</v>
@@ -9914,7 +9914,7 @@
         <v>18</v>
       </c>
       <c r="AS37">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT37">
         <v>7.2</v>
@@ -9926,7 +9926,7 @@
         <v>16.5</v>
       </c>
       <c r="AW37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9947,10 +9947,10 @@
         <v>9</v>
       </c>
       <c r="BD37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE37">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF37">
         <v>9.199999999999999</v>
@@ -10039,22 +10039,22 @@
         <v>225</v>
       </c>
       <c r="F38">
+        <v>1.21</v>
+      </c>
+      <c r="G38">
         <v>1.22</v>
       </c>
-      <c r="G38">
-        <v>1.23</v>
-      </c>
       <c r="H38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I38">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J38">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K38">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L38">
         <v>1.21</v>
@@ -10066,10 +10066,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P38">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
         <v>1.37</v>
@@ -10078,22 +10078,22 @@
         <v>2.02</v>
       </c>
       <c r="S38">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="T38">
         <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V38">
         <v>1.06</v>
       </c>
       <c r="W38">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="X38">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y38">
         <v>80</v>
@@ -10111,7 +10111,7 @@
         <v>20</v>
       </c>
       <c r="AD38">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE38">
         <v>250</v>
@@ -10120,7 +10120,7 @@
         <v>11</v>
       </c>
       <c r="AG38">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH38">
         <v>34</v>
@@ -10141,7 +10141,7 @@
         <v>500</v>
       </c>
       <c r="AN38">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AO38">
         <v>230</v>
@@ -10150,37 +10150,37 @@
         <v>40</v>
       </c>
       <c r="AQ38">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AR38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS38">
+        <v>13.5</v>
+      </c>
+      <c r="AT38">
+        <v>14</v>
+      </c>
+      <c r="AU38">
+        <v>18.5</v>
+      </c>
+      <c r="AV38">
+        <v>44</v>
+      </c>
+      <c r="AW38">
         <v>13</v>
-      </c>
-      <c r="AT38">
-        <v>13.5</v>
-      </c>
-      <c r="AU38">
-        <v>18</v>
-      </c>
-      <c r="AV38">
-        <v>42</v>
-      </c>
-      <c r="AW38">
-        <v>12.5</v>
       </c>
       <c r="AX38">
         <v>9.4</v>
       </c>
       <c r="AY38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA38">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB38">
         <v>9.199999999999999</v>
@@ -10192,13 +10192,13 @@
         <v>26</v>
       </c>
       <c r="BE38">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF38">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BG38">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH38">
         <v>5.6</v>
@@ -10210,49 +10210,49 @@
         <v>12</v>
       </c>
       <c r="BK38">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN38">
         <v>4.2</v>
       </c>
       <c r="BO38">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP38">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BQ38">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR38">
         <v>18.5</v>
       </c>
       <c r="BS38">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT38">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU38">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BX38">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ38">
         <v>0</v>
@@ -10284,7 +10284,7 @@
         <v>3.1</v>
       </c>
       <c r="G39">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H39">
         <v>2.48</v>
@@ -10380,7 +10380,7 @@
         <v>95</v>
       </c>
       <c r="AM39">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN39">
         <v>150</v>
@@ -10413,7 +10413,7 @@
         <v>6.2</v>
       </c>
       <c r="AX39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY39">
         <v>12.5</v>
@@ -10565,7 +10565,7 @@
         <v>4.2</v>
       </c>
       <c r="T40">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U40">
         <v>1.75</v>
@@ -10768,22 +10768,22 @@
         <v>1.79</v>
       </c>
       <c r="G41">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H41">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I41">
         <v>6.2</v>
       </c>
       <c r="J41">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K41">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L41">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M41">
         <v>1.08</v>
@@ -10795,7 +10795,7 @@
         <v>1.37</v>
       </c>
       <c r="P41">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q41">
         <v>2.06</v>
@@ -10807,16 +10807,16 @@
         <v>3.75</v>
       </c>
       <c r="T41">
+        <v>1.91</v>
+      </c>
+      <c r="U41">
         <v>1.9</v>
-      </c>
-      <c r="U41">
-        <v>1.88</v>
       </c>
       <c r="V41">
         <v>1.19</v>
       </c>
       <c r="W41">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X41">
         <v>13.5</v>
@@ -10843,7 +10843,7 @@
         <v>470</v>
       </c>
       <c r="AF41">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG41">
         <v>11</v>
@@ -10882,7 +10882,7 @@
         <v>14.5</v>
       </c>
       <c r="AS41">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT41">
         <v>6.6</v>
@@ -10894,7 +10894,7 @@
         <v>15</v>
       </c>
       <c r="AW41">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX41">
         <v>7.8</v>
@@ -10906,7 +10906,7 @@
         <v>15.5</v>
       </c>
       <c r="BA41">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB41">
         <v>14.5</v>
@@ -10915,16 +10915,16 @@
         <v>15</v>
       </c>
       <c r="BD41">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE41">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF41">
         <v>10.5</v>
       </c>
       <c r="BG41">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH41">
         <v>3.35</v>
@@ -11007,7 +11007,7 @@
         <v>229</v>
       </c>
       <c r="F42">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G42">
         <v>2.5</v>
@@ -11031,7 +11031,7 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O42">
         <v>1.09</v>
@@ -11064,7 +11064,7 @@
         <v>950</v>
       </c>
       <c r="Y42">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z42">
         <v>38</v>
@@ -11112,16 +11112,16 @@
         <v>7.8</v>
       </c>
       <c r="AO42">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ42">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR42">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS42">
         <v>6</v>
@@ -11151,7 +11151,7 @@
         <v>18</v>
       </c>
       <c r="BB42">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC42">
         <v>16</v>
@@ -11160,7 +11160,7 @@
         <v>16.5</v>
       </c>
       <c r="BE42">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF42">
         <v>5.9</v>
@@ -11255,7 +11255,7 @@
         <v>3.85</v>
       </c>
       <c r="H43">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I43">
         <v>2.44</v>
@@ -11291,10 +11291,10 @@
         <v>5.6</v>
       </c>
       <c r="T43">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U43">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V43">
         <v>1.69</v>
@@ -11312,7 +11312,7 @@
         <v>13.5</v>
       </c>
       <c r="AA43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB43">
         <v>10</v>
@@ -11324,7 +11324,7 @@
         <v>12.5</v>
       </c>
       <c r="AE43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF43">
         <v>25</v>
@@ -11339,7 +11339,7 @@
         <v>65</v>
       </c>
       <c r="AJ43">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK43">
         <v>65</v>
@@ -11348,10 +11348,10 @@
         <v>90</v>
       </c>
       <c r="AM43">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN43">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO43">
         <v>36</v>
@@ -11396,7 +11396,7 @@
         <v>32</v>
       </c>
       <c r="BC43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD43">
         <v>75</v>
@@ -11405,10 +11405,10 @@
         <v>70</v>
       </c>
       <c r="BF43">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BG43">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH43">
         <v>2.76</v>
@@ -11420,13 +11420,13 @@
         <v>11</v>
       </c>
       <c r="BK43">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN43">
         <v>6.8</v>
@@ -11441,7 +11441,7 @@
         <v>11.5</v>
       </c>
       <c r="BR43">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS43">
         <v>13.5</v>
@@ -11456,13 +11456,13 @@
         <v>21</v>
       </c>
       <c r="BW43">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ43">
         <v>1000</v>
@@ -11536,7 +11536,7 @@
         <v>2.22</v>
       </c>
       <c r="U44">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V44">
         <v>1.42</v>
@@ -11787,7 +11787,7 @@
         <v>1.39</v>
       </c>
       <c r="X45">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y45">
         <v>12.5</v>
@@ -11874,25 +11874,25 @@
         <v>14.5</v>
       </c>
       <c r="BA45">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB45">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC45">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD45">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE45">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF45">
         <v>8</v>
       </c>
       <c r="BG45">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH45">
         <v>3.6</v>
@@ -11999,22 +11999,22 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="O46">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P46">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q46">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R46">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S46">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="T46">
         <v>1.98</v>
@@ -12029,7 +12029,7 @@
         <v>1.28</v>
       </c>
       <c r="X46">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y46">
         <v>9.199999999999999</v>
@@ -12086,10 +12086,10 @@
         <v>3.05</v>
       </c>
       <c r="AQ46">
-        <v>2.68</v>
+        <v>6.2</v>
       </c>
       <c r="AR46">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AS46">
         <v>17.5</v>
@@ -12098,40 +12098,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU46">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="AV46">
-        <v>2.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW46">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="AX46">
         <v>20</v>
       </c>
       <c r="AY46">
-        <v>3.2</v>
+        <v>14.5</v>
       </c>
       <c r="AZ46">
-        <v>3.3</v>
+        <v>17.5</v>
       </c>
       <c r="BA46">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="BB46">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="BC46">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="BD46">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="BE46">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="BF46">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="BG46">
         <v>13</v>
@@ -12217,13 +12217,13 @@
         <v>234</v>
       </c>
       <c r="F47">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="G47">
         <v>990</v>
       </c>
       <c r="H47">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="I47">
         <v>990</v>
@@ -12265,10 +12265,10 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W47">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12286,7 +12286,7 @@
         <v>1000</v>
       </c>
       <c r="AC47">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD47">
         <v>1000</v>
@@ -12307,7 +12307,7 @@
         <v>1000</v>
       </c>
       <c r="AJ47">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47">
         <v>1000</v>
@@ -12325,58 +12325,58 @@
         <v>1000</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU47">
         <v>1.01</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG47">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12459,16 +12459,16 @@
         <v>235</v>
       </c>
       <c r="F48">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G48">
         <v>2.76</v>
       </c>
       <c r="H48">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J48">
         <v>2.94</v>
@@ -12477,19 +12477,19 @@
         <v>2.96</v>
       </c>
       <c r="L48">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M48">
         <v>1.17</v>
       </c>
       <c r="N48">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O48">
         <v>1.7</v>
       </c>
       <c r="P48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -12585,7 +12585,7 @@
         <v>6.4</v>
       </c>
       <c r="AV48">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW48">
         <v>30</v>
@@ -12594,7 +12594,7 @@
         <v>13</v>
       </c>
       <c r="AY48">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ48">
         <v>21</v>
@@ -12701,16 +12701,16 @@
         <v>236</v>
       </c>
       <c r="F49">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G49">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H49">
         <v>3.2</v>
       </c>
       <c r="I49">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J49">
         <v>3</v>
@@ -12719,19 +12719,19 @@
         <v>3.05</v>
       </c>
       <c r="L49">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M49">
         <v>1.13</v>
       </c>
       <c r="N49">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O49">
         <v>1.56</v>
       </c>
       <c r="P49">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -12740,7 +12740,7 @@
         <v>1.2</v>
       </c>
       <c r="S49">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T49">
         <v>2.12</v>
@@ -12749,7 +12749,7 @@
         <v>1.81</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>1.56</v>
@@ -12779,10 +12779,10 @@
         <v>110</v>
       </c>
       <c r="AF49">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH49">
         <v>23</v>
@@ -12791,10 +12791,10 @@
         <v>160</v>
       </c>
       <c r="AJ49">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AK49">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL49">
         <v>150</v>
@@ -12812,19 +12812,19 @@
         <v>7.6</v>
       </c>
       <c r="AQ49">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR49">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS49">
         <v>29</v>
       </c>
       <c r="AT49">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU49">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV49">
         <v>14</v>
@@ -12833,13 +12833,13 @@
         <v>27</v>
       </c>
       <c r="AX49">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY49">
         <v>12</v>
       </c>
       <c r="AZ49">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA49">
         <v>36</v>
@@ -12872,7 +12872,7 @@
         <v>11.5</v>
       </c>
       <c r="BK49">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL49">
         <v>1000</v>
@@ -12943,7 +12943,7 @@
         <v>237</v>
       </c>
       <c r="F50">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G50">
         <v>1.8</v>
@@ -12976,7 +12976,7 @@
         <v>1.59</v>
       </c>
       <c r="Q50">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
         <v>1.21</v>
@@ -13012,10 +13012,10 @@
         <v>6.2</v>
       </c>
       <c r="AC50">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD50">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE50">
         <v>690</v>
@@ -13033,7 +13033,7 @@
         <v>440</v>
       </c>
       <c r="AJ50">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK50">
         <v>26</v>
@@ -13063,7 +13063,7 @@
         <v>46</v>
       </c>
       <c r="AT50">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU50">
         <v>7.4</v>
@@ -13075,13 +13075,13 @@
         <v>40</v>
       </c>
       <c r="AX50">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY50">
         <v>9.4</v>
       </c>
       <c r="AZ50">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA50">
         <v>44</v>
@@ -13126,7 +13126,7 @@
         <v>4.1</v>
       </c>
       <c r="BO50">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BP50">
         <v>13.5</v>
@@ -13144,7 +13144,7 @@
         <v>10.5</v>
       </c>
       <c r="BU50">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV50">
         <v>1000</v>
@@ -13185,13 +13185,13 @@
         <v>238</v>
       </c>
       <c r="F51">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G51">
         <v>2.12</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I51">
         <v>5</v>
@@ -13209,7 +13209,7 @@
         <v>1.08</v>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O51">
         <v>1.37</v>
@@ -13224,16 +13224,16 @@
         <v>1.27</v>
       </c>
       <c r="S51">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T51">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U51">
         <v>1.9</v>
       </c>
       <c r="V51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W51">
         <v>1.89</v>
@@ -13305,10 +13305,10 @@
         <v>7.4</v>
       </c>
       <c r="AT51">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU51">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV51">
         <v>5.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -679,7 +679,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-03 03:16:47</t>
+    <t>2026-08-03 05:24:55</t>
   </si>
 </sst>
 </file>
@@ -1273,211 +1273,211 @@
         <v>176</v>
       </c>
       <c r="F2">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="G2">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="H2">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="I2">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.51</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="W2">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AG2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>900</v>
       </c>
       <c r="AK2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AL2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR2">
         <v>9.6</v>
       </c>
       <c r="AS2">
+        <v>18</v>
+      </c>
+      <c r="AT2">
+        <v>12.5</v>
+      </c>
+      <c r="AU2">
+        <v>7.6</v>
+      </c>
+      <c r="AV2">
+        <v>9</v>
+      </c>
+      <c r="AW2">
+        <v>20</v>
+      </c>
+      <c r="AX2">
+        <v>30</v>
+      </c>
+      <c r="AY2">
+        <v>18</v>
+      </c>
+      <c r="AZ2">
         <v>21</v>
       </c>
-      <c r="AT2">
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>19</v>
-      </c>
-      <c r="AX2">
-        <v>25</v>
-      </c>
-      <c r="AY2">
-        <v>15</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
       <c r="BA2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BC2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BD2">
         <v>55</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BG2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BH2">
         <v>3</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
+        <v>15</v>
+      </c>
+      <c r="BN2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO2">
+        <v>5.5</v>
+      </c>
+      <c r="BP2">
+        <v>70</v>
+      </c>
+      <c r="BQ2">
         <v>12.5</v>
       </c>
-      <c r="BN2">
-        <v>7.6</v>
-      </c>
-      <c r="BO2">
-        <v>5.8</v>
-      </c>
-      <c r="BP2">
-        <v>65</v>
-      </c>
-      <c r="BQ2">
-        <v>10</v>
-      </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BT2">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BV2">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW2">
         <v>7.6</v>
@@ -1486,13 +1486,13 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="CB2" t="s">
         <v>221</v>
@@ -1515,16 +1515,16 @@
         <v>177</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
         <v>2.54</v>
       </c>
       <c r="H3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I3">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J3">
         <v>4.6</v>
@@ -1548,22 +1548,22 @@
         <v>3.85</v>
       </c>
       <c r="Q3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="T3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="V3">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W3">
         <v>1.65</v>
@@ -1572,10 +1572,10 @@
         <v>55</v>
       </c>
       <c r="Y3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA3">
         <v>48</v>
@@ -1611,16 +1611,16 @@
         <v>22</v>
       </c>
       <c r="AL3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AN3">
         <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AP3">
         <v>30</v>
@@ -1629,10 +1629,10 @@
         <v>22</v>
       </c>
       <c r="AR3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT3">
         <v>21</v>
@@ -1641,7 +1641,7 @@
         <v>12</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>19</v>
@@ -1701,28 +1701,28 @@
         <v>5.8</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS3">
         <v>8.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
         <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX3">
         <v>19</v>
@@ -1731,7 +1731,7 @@
         <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA3">
         <v>7.6</v>
@@ -1757,22 +1757,22 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G4">
         <v>1.34</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>1.24</v>
@@ -1781,49 +1781,49 @@
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P4">
         <v>3</v>
       </c>
       <c r="Q4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R4">
         <v>1.87</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="X4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>240</v>
       </c>
       <c r="Z4">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AA4">
         <v>380</v>
       </c>
       <c r="AB4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC4">
         <v>15.5</v>
@@ -1850,7 +1850,7 @@
         <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL4">
         <v>46</v>
@@ -1871,10 +1871,10 @@
         <v>20</v>
       </c>
       <c r="AR4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
@@ -1883,10 +1883,10 @@
         <v>12.5</v>
       </c>
       <c r="AV4">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1898,10 +1898,10 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC4">
         <v>11.5</v>
@@ -1910,10 +1910,10 @@
         <v>16.5</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG4">
         <v>15</v>
@@ -1928,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1940,13 +1940,13 @@
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="BP4">
         <v>7.4</v>
       </c>
       <c r="BQ4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR4">
         <v>20</v>
@@ -1976,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="CA4">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB4" t="s">
         <v>221</v>
@@ -1999,10 +1999,10 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G5">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H5">
         <v>4.5</v>
@@ -2023,25 +2023,25 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
         <v>2.12</v>
@@ -2050,7 +2050,7 @@
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -2086,7 +2086,7 @@
         <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AJ5">
         <v>20</v>
@@ -2247,13 +2247,13 @@
         <v>1.17</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -2271,31 +2271,31 @@
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R6">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S6">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
         <v>1.04</v>
       </c>
       <c r="W6">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y6">
         <v>75</v>
@@ -2307,13 +2307,13 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
         <v>28</v>
       </c>
       <c r="AD6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2349,16 +2349,16 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -2367,10 +2367,10 @@
         <v>20</v>
       </c>
       <c r="AV6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX6">
         <v>7.2</v>
@@ -2382,7 +2382,7 @@
         <v>32</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
         <v>7.2</v>
@@ -2391,19 +2391,19 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
         <v>4</v>
@@ -2412,22 +2412,22 @@
         <v>16</v>
       </c>
       <c r="BK6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BQ6">
         <v>4.4</v>
@@ -2436,31 +2436,31 @@
         <v>24</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT6">
         <v>23</v>
       </c>
       <c r="BU6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BZ6">
         <v>7</v>
       </c>
       <c r="CA6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB6" t="s">
         <v>221</v>
@@ -2489,13 +2489,13 @@
         <v>3.4</v>
       </c>
       <c r="H7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.3</v>
@@ -2507,31 +2507,31 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R7">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W7">
         <v>1.41</v>
@@ -2540,19 +2540,19 @@
         <v>29</v>
       </c>
       <c r="Y7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB7">
         <v>22</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
         <v>12</v>
@@ -2564,22 +2564,22 @@
         <v>36</v>
       </c>
       <c r="AG7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH7">
         <v>18</v>
       </c>
       <c r="AI7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK7">
         <v>42</v>
       </c>
       <c r="AL7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>75</v>
@@ -2594,25 +2594,25 @@
         <v>18</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AT7">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AU7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX7">
         <v>23</v>
@@ -2630,16 +2630,16 @@
         <v>36</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE7">
         <v>46</v>
       </c>
       <c r="BF7">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
         <v>9.4</v>
@@ -2651,7 +2651,7 @@
         <v>3.5</v>
       </c>
       <c r="BJ7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK7">
         <v>6.4</v>
@@ -2660,10 +2660,10 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
         <v>5.3</v>
@@ -2672,7 +2672,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2696,13 +2696,13 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="CA7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
         <v>221</v>
@@ -2725,13 +2725,13 @@
         <v>182</v>
       </c>
       <c r="F8">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
         <v>4.9</v>
@@ -2740,10 +2740,10 @@
         <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2752,55 +2752,55 @@
         <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
         <v>2.12</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
         <v>3.9</v>
       </c>
       <c r="T8">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y8">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8">
         <v>900</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE8">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AF8">
         <v>11.5</v>
@@ -2812,16 +2812,16 @@
         <v>25</v>
       </c>
       <c r="AI8">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="AJ8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8">
         <v>580</v>
@@ -2830,7 +2830,7 @@
         <v>17.5</v>
       </c>
       <c r="AO8">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP8">
         <v>11</v>
@@ -2839,22 +2839,22 @@
         <v>14</v>
       </c>
       <c r="AR8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS8">
         <v>75</v>
       </c>
       <c r="AT8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV8">
         <v>16</v>
       </c>
       <c r="AW8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX8">
         <v>9.800000000000001</v>
@@ -2863,25 +2863,25 @@
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8">
         <v>46</v>
       </c>
       <c r="BB8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC8">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE8">
         <v>30</v>
       </c>
       <c r="BF8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG8">
         <v>50</v>
@@ -2890,7 +2890,7 @@
         <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2902,7 +2902,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
@@ -2914,7 +2914,7 @@
         <v>14</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
@@ -2926,13 +2926,13 @@
         <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
@@ -2973,7 +2973,7 @@
         <v>4.8</v>
       </c>
       <c r="H9">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2982,7 +2982,7 @@
         <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.42</v>
@@ -2991,16 +2991,16 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
         <v>1.89</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R9">
         <v>1.33</v>
@@ -3012,7 +3012,7 @@
         <v>1.84</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V9">
         <v>2</v>
@@ -3021,10 +3021,10 @@
         <v>1.27</v>
       </c>
       <c r="X9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
         <v>12.5</v>
@@ -3036,7 +3036,7 @@
         <v>16.5</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD9">
         <v>11</v>
@@ -3051,28 +3051,28 @@
         <v>18.5</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>40</v>
       </c>
       <c r="AJ9">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK9">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AL9">
         <v>70</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AP9">
         <v>12</v>
@@ -3087,7 +3087,7 @@
         <v>18.5</v>
       </c>
       <c r="AT9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU9">
         <v>7.2</v>
@@ -3099,70 +3099,70 @@
         <v>17.5</v>
       </c>
       <c r="AX9">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="AY9">
         <v>13</v>
       </c>
       <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
         <v>6.2</v>
       </c>
-      <c r="BA9">
-        <v>7.2</v>
-      </c>
       <c r="BB9">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BC9">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD9">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BE9">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG9">
         <v>12</v>
       </c>
       <c r="BH9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO9">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BP9">
         <v>42</v>
       </c>
       <c r="BQ9">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR9">
         <v>55</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9">
         <v>4.7</v>
@@ -3174,13 +3174,13 @@
         <v>14</v>
       </c>
       <c r="BW9">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>30</v>
       </c>
       <c r="BY9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3209,16 +3209,16 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3227,46 +3227,46 @@
         <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S10">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T10">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
         <v>1.21</v>
       </c>
       <c r="W10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X10">
         <v>25</v>
       </c>
       <c r="Y10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z10">
         <v>55</v>
@@ -3275,10 +3275,10 @@
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
         <v>26</v>
@@ -3287,7 +3287,7 @@
         <v>160</v>
       </c>
       <c r="AF10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -3296,7 +3296,7 @@
         <v>23</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AJ10">
         <v>20</v>
@@ -3311,22 +3311,22 @@
         <v>320</v>
       </c>
       <c r="AN10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO10">
         <v>600</v>
       </c>
       <c r="AP10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS10">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
@@ -3335,10 +3335,10 @@
         <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX10">
         <v>9.6</v>
@@ -3350,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB10">
         <v>15</v>
@@ -3368,7 +3368,7 @@
         <v>8</v>
       </c>
       <c r="BG10">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH10">
         <v>3.9</v>
@@ -3380,13 +3380,13 @@
         <v>10</v>
       </c>
       <c r="BK10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
@@ -3398,19 +3398,19 @@
         <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3422,7 +3422,7 @@
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3475,25 +3475,25 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
         <v>1.31</v>
       </c>
       <c r="P11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q11">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T11">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U11">
         <v>2</v>
@@ -3511,7 +3511,7 @@
         <v>23</v>
       </c>
       <c r="Z11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3520,7 +3520,7 @@
         <v>8.6</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD11">
         <v>24</v>
@@ -3538,40 +3538,40 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="AJ11">
         <v>17</v>
       </c>
       <c r="AK11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO11">
         <v>700</v>
       </c>
       <c r="AP11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ11">
         <v>17.5</v>
       </c>
       <c r="AR11">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
         <v>8.4</v>
@@ -3580,7 +3580,7 @@
         <v>19</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3592,22 +3592,22 @@
         <v>18</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB11">
         <v>14</v>
       </c>
       <c r="BC11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE11">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11">
         <v>10</v>
@@ -3616,34 +3616,34 @@
         <v>3.5</v>
       </c>
       <c r="BI11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP11">
         <v>11</v>
       </c>
       <c r="BQ11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR11">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
         <v>10.5</v>
@@ -3652,19 +3652,19 @@
         <v>9.4</v>
       </c>
       <c r="BU11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
         <v>55</v>
       </c>
       <c r="BW11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3693,22 +3693,22 @@
         <v>186</v>
       </c>
       <c r="F12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G12">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12">
         <v>4.8</v>
       </c>
       <c r="K12">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L12">
         <v>1.33</v>
@@ -3717,49 +3717,49 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S12">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T12">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
         <v>1.12</v>
       </c>
       <c r="W12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12">
         <v>32</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA12">
         <v>320</v>
       </c>
       <c r="AB12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12">
         <v>12</v>
@@ -3768,7 +3768,7 @@
         <v>34</v>
       </c>
       <c r="AE12">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF12">
         <v>9.199999999999999</v>
@@ -3795,10 +3795,10 @@
         <v>380</v>
       </c>
       <c r="AN12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO12">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3810,31 +3810,31 @@
         <v>55</v>
       </c>
       <c r="AS12">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="AT12">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AX12">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB12">
         <v>10.5</v>
@@ -3846,13 +3846,13 @@
         <v>24</v>
       </c>
       <c r="BE12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG12">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="BH12">
         <v>4.2</v>
@@ -3861,7 +3861,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
         <v>8.4</v>
@@ -3870,16 +3870,16 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN12">
         <v>4.1</v>
       </c>
       <c r="BO12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ12">
         <v>6.8</v>
@@ -3888,7 +3888,7 @@
         <v>24</v>
       </c>
       <c r="BS12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT12">
         <v>12.5</v>
@@ -3903,7 +3903,7 @@
         <v>9</v>
       </c>
       <c r="BX12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
         <v>8.800000000000001</v>
@@ -3938,7 +3938,7 @@
         <v>3.6</v>
       </c>
       <c r="G13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
         <v>2.02</v>
@@ -3956,31 +3956,31 @@
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T13">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V13">
         <v>1.94</v>
@@ -3989,16 +3989,16 @@
         <v>1.37</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB13">
         <v>21</v>
@@ -4016,13 +4016,13 @@
         <v>32</v>
       </c>
       <c r="AG13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH13">
         <v>15</v>
       </c>
       <c r="AI13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ13">
         <v>70</v>
@@ -4031,16 +4031,16 @@
         <v>36</v>
       </c>
       <c r="AL13">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AN13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP13">
         <v>22</v>
@@ -4052,13 +4052,13 @@
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13">
         <v>10</v>
@@ -4067,7 +4067,7 @@
         <v>16.5</v>
       </c>
       <c r="AX13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY13">
         <v>14</v>
@@ -4079,7 +4079,7 @@
         <v>23</v>
       </c>
       <c r="BB13">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC13">
         <v>32</v>
@@ -4088,10 +4088,10 @@
         <v>32</v>
       </c>
       <c r="BE13">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BF13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BG13">
         <v>8.6</v>
@@ -4106,16 +4106,16 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BN13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO13">
         <v>5.3</v>
@@ -4124,13 +4124,13 @@
         <v>25</v>
       </c>
       <c r="BQ13">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
@@ -4142,19 +4142,19 @@
         <v>13</v>
       </c>
       <c r="BW13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>14.5</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>221</v>
@@ -4177,22 +4177,22 @@
         <v>188</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="G14">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H14">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
         <v>3.8</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
         <v>1.34</v>
@@ -4225,76 +4225,76 @@
         <v>2.38</v>
       </c>
       <c r="V14">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y14">
         <v>13.5</v>
       </c>
       <c r="Z14">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC14">
         <v>9</v>
       </c>
       <c r="AD14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE14">
+        <v>25</v>
+      </c>
+      <c r="AF14">
         <v>23</v>
       </c>
-      <c r="AF14">
-        <v>24</v>
-      </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI14">
         <v>32</v>
       </c>
       <c r="AJ14">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO14">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AP14">
         <v>17</v>
       </c>
       <c r="AQ14">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT14">
         <v>14</v>
@@ -4306,13 +4306,13 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14">
         <v>14</v>
@@ -4321,22 +4321,22 @@
         <v>27</v>
       </c>
       <c r="BB14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BC14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE14">
         <v>55</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
@@ -4354,16 +4354,16 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BP14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ14">
         <v>6.8</v>
@@ -4372,25 +4372,25 @@
         <v>32</v>
       </c>
       <c r="BS14">
+        <v>7.6</v>
+      </c>
+      <c r="BT14">
+        <v>6</v>
+      </c>
+      <c r="BU14">
+        <v>4.9</v>
+      </c>
+      <c r="BV14">
+        <v>18.5</v>
+      </c>
+      <c r="BW14">
+        <v>6.4</v>
+      </c>
+      <c r="BX14">
+        <v>28</v>
+      </c>
+      <c r="BY14">
         <v>7.4</v>
-      </c>
-      <c r="BT14">
-        <v>5.8</v>
-      </c>
-      <c r="BU14">
-        <v>4.8</v>
-      </c>
-      <c r="BV14">
-        <v>17.5</v>
-      </c>
-      <c r="BW14">
-        <v>6.2</v>
-      </c>
-      <c r="BX14">
-        <v>27</v>
-      </c>
-      <c r="BY14">
-        <v>7.2</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4419,22 +4419,22 @@
         <v>189</v>
       </c>
       <c r="F15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H15">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15">
-        <v>60</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K15">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
         <v>1.36</v>
@@ -4446,22 +4446,22 @@
         <v>4.2</v>
       </c>
       <c r="O15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
         <v>1.42</v>
       </c>
       <c r="S15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U15">
         <v>1.76</v>
@@ -4470,115 +4470,115 @@
         <v>1.1</v>
       </c>
       <c r="W15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y15">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC15">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD15">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF15">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AG15">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ15">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AK15">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP15">
-        <v>1.45</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AR15">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS15">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU15">
-        <v>1.36</v>
+        <v>5.2</v>
       </c>
       <c r="AV15">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW15">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX15">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AY15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15">
-        <v>1.43</v>
+        <v>6.8</v>
       </c>
       <c r="BA15">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB15">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC15">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BD15">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE15">
-        <v>1.45</v>
+        <v>8.6</v>
       </c>
       <c r="BF15">
-        <v>1.32</v>
+        <v>3.95</v>
       </c>
       <c r="BG15">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15">
         <v>3.85</v>
@@ -4661,16 +4661,16 @@
         <v>190</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G16">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
         <v>3.45</v>
@@ -4679,22 +4679,22 @@
         <v>3.7</v>
       </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O16">
         <v>1.32</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q16">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R16">
         <v>1.37</v>
@@ -4706,49 +4706,49 @@
         <v>1.74</v>
       </c>
       <c r="U16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X16">
         <v>15</v>
       </c>
       <c r="Y16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
         <v>17</v>
       </c>
       <c r="AI16">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AJ16">
         <v>34</v>
@@ -4766,22 +4766,22 @@
         <v>20</v>
       </c>
       <c r="AO16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16">
         <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AS16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT16">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
@@ -4808,19 +4808,19 @@
         <v>14.5</v>
       </c>
       <c r="BC16">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BD16">
         <v>17.5</v>
       </c>
       <c r="BE16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF16">
         <v>17.5</v>
       </c>
       <c r="BG16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16">
         <v>3.45</v>
@@ -4838,7 +4838,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN16">
         <v>5.4</v>
@@ -4847,16 +4847,16 @@
         <v>4.8</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16">
         <v>6.4</v>
@@ -4868,13 +4868,13 @@
         <v>25</v>
       </c>
       <c r="BW16">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX16">
         <v>36</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>2.44</v>
       </c>
       <c r="I17">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
         <v>3.45</v>
@@ -4927,16 +4927,16 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P17">
         <v>1.86</v>
       </c>
       <c r="Q17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R17">
         <v>1.32</v>
@@ -4954,7 +4954,7 @@
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X17">
         <v>16</v>
@@ -4963,7 +4963,7 @@
         <v>10.5</v>
       </c>
       <c r="Z17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA17">
         <v>90</v>
@@ -4972,7 +4972,7 @@
         <v>12.5</v>
       </c>
       <c r="AC17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17">
         <v>14</v>
@@ -4987,7 +4987,7 @@
         <v>14.5</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17">
         <v>50</v>
@@ -5005,7 +5005,7 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO17">
         <v>25</v>
@@ -5050,13 +5050,13 @@
         <v>42</v>
       </c>
       <c r="BC17">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BD17">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE17">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF17">
         <v>30</v>
@@ -5068,37 +5068,37 @@
         <v>3.3</v>
       </c>
       <c r="BI17">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN17">
         <v>6.6</v>
       </c>
       <c r="BO17">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT17">
         <v>5.5</v>
@@ -5110,13 +5110,13 @@
         <v>19.5</v>
       </c>
       <c r="BW17">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
@@ -5145,16 +5145,16 @@
         <v>192</v>
       </c>
       <c r="F18">
+        <v>1.49</v>
+      </c>
+      <c r="G18">
         <v>1.51</v>
       </c>
-      <c r="G18">
-        <v>1.52</v>
-      </c>
       <c r="H18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
         <v>5.1</v>
@@ -5169,61 +5169,61 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O18">
         <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S18">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T18">
         <v>1.67</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W18">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X18">
         <v>32</v>
       </c>
       <c r="Y18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z18">
         <v>65</v>
       </c>
       <c r="AA18">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC18">
         <v>12.5</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE18">
         <v>75</v>
       </c>
       <c r="AF18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5235,7 +5235,7 @@
         <v>70</v>
       </c>
       <c r="AJ18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK18">
         <v>14</v>
@@ -5247,13 +5247,13 @@
         <v>75</v>
       </c>
       <c r="AN18">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ18">
         <v>32</v>
@@ -5262,28 +5262,28 @@
         <v>55</v>
       </c>
       <c r="AS18">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT18">
         <v>12</v>
       </c>
       <c r="AU18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV18">
         <v>23</v>
       </c>
       <c r="AW18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX18">
         <v>10.5</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA18">
         <v>55</v>
@@ -5292,19 +5292,19 @@
         <v>13.5</v>
       </c>
       <c r="BC18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD18">
         <v>22</v>
       </c>
       <c r="BE18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH18">
         <v>4.8</v>
@@ -5316,7 +5316,7 @@
         <v>9.6</v>
       </c>
       <c r="BK18">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5334,22 +5334,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR18">
         <v>28</v>
       </c>
       <c r="BS18">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT18">
         <v>10.5</v>
       </c>
       <c r="BU18">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW18">
         <v>13</v>
@@ -5364,7 +5364,7 @@
         <v>11</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB18" t="s">
         <v>221</v>
@@ -5396,7 +5396,7 @@
         <v>2.48</v>
       </c>
       <c r="I19">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J19">
         <v>3.05</v>
@@ -5411,7 +5411,7 @@
         <v>1.12</v>
       </c>
       <c r="N19">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O19">
         <v>1.52</v>
@@ -5423,7 +5423,7 @@
         <v>2.58</v>
       </c>
       <c r="R19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19">
         <v>5.1</v>
@@ -5462,7 +5462,7 @@
         <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19">
         <v>23</v>
@@ -5471,19 +5471,19 @@
         <v>16</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AJ19">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AK19">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AL19">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AM19">
         <v>580</v>
@@ -5492,7 +5492,7 @@
         <v>150</v>
       </c>
       <c r="AO19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP19">
         <v>7.4</v>
@@ -5501,10 +5501,10 @@
         <v>6.8</v>
       </c>
       <c r="AR19">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AT19">
         <v>8.199999999999999</v>
@@ -5513,7 +5513,7 @@
         <v>6</v>
       </c>
       <c r="AV19">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW19">
         <v>29</v>
@@ -5522,31 +5522,31 @@
         <v>18</v>
       </c>
       <c r="AY19">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
         <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BB19">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BC19">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BD19">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BE19">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BF19">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BG19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BH19">
         <v>2.82</v>
@@ -5635,13 +5635,13 @@
         <v>2.1</v>
       </c>
       <c r="H20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>4.5</v>
@@ -5650,13 +5650,13 @@
         <v>1.28</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N20">
         <v>5.3</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
         <v>2.52</v>
@@ -5668,16 +5668,16 @@
         <v>1.6</v>
       </c>
       <c r="S20">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T20">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U20">
         <v>2.48</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
         <v>1.9</v>
@@ -5704,7 +5704,7 @@
         <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AF20">
         <v>16.5</v>
@@ -5731,13 +5731,13 @@
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO20">
         <v>29</v>
       </c>
       <c r="AP20">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
         <v>17</v>
@@ -5746,13 +5746,13 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT20">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
         <v>13</v>
@@ -5761,7 +5761,7 @@
         <v>26</v>
       </c>
       <c r="AX20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY20">
         <v>9.4</v>
@@ -5782,10 +5782,10 @@
         <v>21</v>
       </c>
       <c r="BE20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF20">
         <v>7.8</v>
-      </c>
-      <c r="BF20">
-        <v>8</v>
       </c>
       <c r="BG20">
         <v>9</v>
@@ -5800,7 +5800,7 @@
         <v>9</v>
       </c>
       <c r="BK20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL20">
         <v>1000</v>
@@ -5818,7 +5818,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR20">
         <v>22</v>
@@ -5833,7 +5833,7 @@
         <v>4.4</v>
       </c>
       <c r="BV20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW20">
         <v>7.6</v>
@@ -5871,76 +5871,76 @@
         <v>195</v>
       </c>
       <c r="F21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G21">
         <v>1.16</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J21">
         <v>10</v>
       </c>
       <c r="K21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="L21">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M21">
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="O21">
         <v>1.11</v>
       </c>
       <c r="P21">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="T21">
         <v>2.14</v>
       </c>
       <c r="U21">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21">
         <v>7.2</v>
       </c>
       <c r="X21">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y21">
         <v>950</v>
       </c>
       <c r="Z21">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AA21">
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC21">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AD21">
         <v>510</v>
@@ -5949,10 +5949,10 @@
         <v>430</v>
       </c>
       <c r="AF21">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH21">
         <v>50</v>
@@ -5961,49 +5961,49 @@
         <v>270</v>
       </c>
       <c r="AJ21">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AK21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM21">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN21">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AO21">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AP21">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AQ21">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AR21">
         <v>9.4</v>
       </c>
       <c r="AS21">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU21">
         <v>18</v>
       </c>
       <c r="AV21">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX21">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY21">
         <v>12</v>
@@ -6012,10 +6012,10 @@
         <v>34</v>
       </c>
       <c r="BA21">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC21">
         <v>12</v>
@@ -6024,70 +6024,70 @@
         <v>34</v>
       </c>
       <c r="BE21">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF21">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BG21">
         <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI21">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO21">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BP21">
         <v>5.9</v>
       </c>
       <c r="BQ21">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BR21">
         <v>22</v>
       </c>
       <c r="BS21">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BU21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CA21">
         <v>5.1</v>
@@ -6113,73 +6113,73 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I22">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K22">
         <v>5.7</v>
       </c>
       <c r="L22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="Q22">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="R22">
+        <v>1.74</v>
+      </c>
+      <c r="S22">
+        <v>2.32</v>
+      </c>
+      <c r="T22">
         <v>1.78</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>2.22</v>
       </c>
-      <c r="T22">
-        <v>1.73</v>
-      </c>
-      <c r="U22">
-        <v>2.3</v>
-      </c>
       <c r="V22">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC22">
         <v>13</v>
@@ -6188,58 +6188,58 @@
         <v>10.5</v>
       </c>
       <c r="AE22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF22">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AG22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH22">
         <v>22</v>
       </c>
       <c r="AI22">
+        <v>28</v>
+      </c>
+      <c r="AJ22">
+        <v>250</v>
+      </c>
+      <c r="AK22">
+        <v>110</v>
+      </c>
+      <c r="AL22">
+        <v>85</v>
+      </c>
+      <c r="AM22">
+        <v>95</v>
+      </c>
+      <c r="AN22">
+        <v>110</v>
+      </c>
+      <c r="AO22">
+        <v>4.7</v>
+      </c>
+      <c r="AP22">
         <v>26</v>
       </c>
-      <c r="AJ22">
-        <v>260</v>
-      </c>
-      <c r="AK22">
-        <v>95</v>
-      </c>
-      <c r="AL22">
-        <v>80</v>
-      </c>
-      <c r="AM22">
-        <v>100</v>
-      </c>
-      <c r="AN22">
-        <v>80</v>
-      </c>
-      <c r="AO22">
-        <v>4.5</v>
-      </c>
-      <c r="AP22">
-        <v>28</v>
-      </c>
       <c r="AQ22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR22">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS22">
         <v>11.5</v>
       </c>
       <c r="AT22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AU22">
         <v>11.5</v>
       </c>
       <c r="AV22">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW22">
         <v>12</v>
@@ -6248,19 +6248,19 @@
         <v>65</v>
       </c>
       <c r="AY22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ22">
         <v>20</v>
       </c>
       <c r="BA22">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB22">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BC22">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BD22">
         <v>65</v>
@@ -6269,67 +6269,67 @@
         <v>75</v>
       </c>
       <c r="BF22">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BG22">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH22">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI22">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BJ22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK22">
         <v>6.4</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM22">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BP22">
+        <v>65</v>
+      </c>
+      <c r="BQ22">
+        <v>13</v>
+      </c>
+      <c r="BR22">
         <v>55</v>
       </c>
-      <c r="BQ22">
-        <v>14</v>
-      </c>
-      <c r="BR22">
-        <v>50</v>
-      </c>
       <c r="BS22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BV22">
         <v>8</v>
       </c>
       <c r="BW22">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX22">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BY22">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA22">
         <v>6.4</v>
@@ -6355,16 +6355,16 @@
         <v>197</v>
       </c>
       <c r="F23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G23">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H23">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I23">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J23">
         <v>3.2</v>
@@ -6382,7 +6382,7 @@
         <v>3.3</v>
       </c>
       <c r="O23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
         <v>1.76</v>
@@ -6397,16 +6397,16 @@
         <v>4.3</v>
       </c>
       <c r="T23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X23">
         <v>11</v>
@@ -6427,10 +6427,10 @@
         <v>7.2</v>
       </c>
       <c r="AD23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF23">
         <v>14</v>
@@ -6448,7 +6448,7 @@
         <v>34</v>
       </c>
       <c r="AK23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL23">
         <v>110</v>
@@ -6457,10 +6457,10 @@
         <v>130</v>
       </c>
       <c r="AN23">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP23">
         <v>10</v>
@@ -6490,16 +6490,16 @@
         <v>12.5</v>
       </c>
       <c r="AY23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23">
         <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB23">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC23">
         <v>24</v>
@@ -6508,7 +6508,7 @@
         <v>40</v>
       </c>
       <c r="BE23">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF23">
         <v>21</v>
@@ -6526,7 +6526,7 @@
         <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6550,7 +6550,7 @@
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT23">
         <v>6.8</v>
@@ -6562,13 +6562,13 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>2.38</v>
       </c>
       <c r="H24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I24">
         <v>3.65</v>
@@ -6633,7 +6633,7 @@
         <v>2.24</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
         <v>4.3</v>
@@ -6642,7 +6642,7 @@
         <v>1.86</v>
       </c>
       <c r="U24">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V24">
         <v>1.38</v>
@@ -6651,16 +6651,16 @@
         <v>1.72</v>
       </c>
       <c r="X24">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y24">
         <v>13</v>
       </c>
       <c r="Z24">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA24">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB24">
         <v>9.199999999999999</v>
@@ -6687,7 +6687,7 @@
         <v>70</v>
       </c>
       <c r="AJ24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK24">
         <v>29</v>
@@ -6747,7 +6747,7 @@
         <v>21</v>
       </c>
       <c r="BD24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE24">
         <v>80</v>
@@ -6774,7 +6774,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN24">
         <v>5.2</v>
@@ -6786,16 +6786,16 @@
         <v>19.5</v>
       </c>
       <c r="BQ24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR24">
         <v>38</v>
       </c>
       <c r="BS24">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU24">
         <v>5.7</v>
@@ -6804,13 +6804,13 @@
         <v>32</v>
       </c>
       <c r="BW24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX24">
         <v>46</v>
       </c>
       <c r="BY24">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6845,28 +6845,28 @@
         <v>3.45</v>
       </c>
       <c r="H25">
+        <v>2.02</v>
+      </c>
+      <c r="I25">
         <v>2.06</v>
       </c>
-      <c r="I25">
-        <v>2.1</v>
-      </c>
       <c r="J25">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K25">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L25">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O25">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P25">
         <v>4.7</v>
@@ -6878,127 +6878,127 @@
         <v>2.52</v>
       </c>
       <c r="S25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="U25">
         <v>3.9</v>
       </c>
       <c r="V25">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W25">
         <v>1.4</v>
       </c>
       <c r="X25">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="Y25">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z25">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB25">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AC25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD25">
         <v>14</v>
       </c>
       <c r="AE25">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF25">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AG25">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH25">
         <v>13.5</v>
       </c>
       <c r="AI25">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AJ25">
         <v>80</v>
       </c>
       <c r="AK25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL25">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AM25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN25">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO25">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AP25">
         <v>46</v>
       </c>
       <c r="AQ25">
+        <v>28</v>
+      </c>
+      <c r="AR25">
         <v>23</v>
       </c>
-      <c r="AR25">
+      <c r="AS25">
+        <v>29</v>
+      </c>
+      <c r="AT25">
+        <v>36</v>
+      </c>
+      <c r="AU25">
+        <v>13.5</v>
+      </c>
+      <c r="AV25">
+        <v>12</v>
+      </c>
+      <c r="AW25">
+        <v>16</v>
+      </c>
+      <c r="AX25">
+        <v>40</v>
+      </c>
+      <c r="AY25">
+        <v>16.5</v>
+      </c>
+      <c r="AZ25">
+        <v>11.5</v>
+      </c>
+      <c r="BA25">
+        <v>17.5</v>
+      </c>
+      <c r="BB25">
+        <v>46</v>
+      </c>
+      <c r="BC25">
+        <v>25</v>
+      </c>
+      <c r="BD25">
         <v>22</v>
       </c>
-      <c r="AS25">
-        <v>23</v>
-      </c>
-      <c r="AT25">
-        <v>30</v>
-      </c>
-      <c r="AU25">
-        <v>11.5</v>
-      </c>
-      <c r="AV25">
-        <v>10.5</v>
-      </c>
-      <c r="AW25">
-        <v>15.5</v>
-      </c>
-      <c r="AX25">
-        <v>36</v>
-      </c>
-      <c r="AY25">
-        <v>15</v>
-      </c>
-      <c r="AZ25">
-        <v>11</v>
-      </c>
-      <c r="BA25">
-        <v>17</v>
-      </c>
-      <c r="BB25">
-        <v>42</v>
-      </c>
-      <c r="BC25">
-        <v>23</v>
-      </c>
-      <c r="BD25">
-        <v>21</v>
-      </c>
       <c r="BE25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BF25">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG25">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH25">
         <v>7.2</v>
@@ -7010,7 +7010,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -7096,13 +7096,13 @@
         <v>3.75</v>
       </c>
       <c r="K26">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
         <v>5.1</v>
@@ -7114,13 +7114,13 @@
         <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R26">
         <v>1.55</v>
       </c>
       <c r="S26">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T26">
         <v>1.59</v>
@@ -7129,34 +7129,34 @@
         <v>2.56</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.78</v>
       </c>
       <c r="X26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y26">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA26">
         <v>60</v>
       </c>
       <c r="AB26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF26">
         <v>16.5</v>
@@ -7168,7 +7168,7 @@
         <v>15</v>
       </c>
       <c r="AI26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ26">
         <v>32</v>
@@ -7177,34 +7177,34 @@
         <v>21</v>
       </c>
       <c r="AL26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM26">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO26">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP26">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ26">
         <v>15.5</v>
       </c>
       <c r="AR26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS26">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT26">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26">
         <v>13</v>
@@ -7213,13 +7213,13 @@
         <v>30</v>
       </c>
       <c r="AX26">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY26">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA26">
         <v>34</v>
@@ -7228,10 +7228,10 @@
         <v>27</v>
       </c>
       <c r="BC26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE26">
         <v>55</v>
@@ -7240,10 +7240,10 @@
         <v>11.5</v>
       </c>
       <c r="BG26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI26">
         <v>3.6</v>
@@ -7252,13 +7252,13 @@
         <v>9</v>
       </c>
       <c r="BK26">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM26">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN26">
         <v>5.6</v>
@@ -7270,37 +7270,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR26">
         <v>25</v>
       </c>
       <c r="BS26">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT26">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU26">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV26">
         <v>24</v>
       </c>
       <c r="BW26">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX26">
         <v>32</v>
       </c>
       <c r="BY26">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ26">
         <v>18</v>
       </c>
       <c r="CA26">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="s">
         <v>221</v>
@@ -7323,19 +7323,19 @@
         <v>201</v>
       </c>
       <c r="F27">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G27">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="H27">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I27">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27">
         <v>3.75</v>
@@ -7347,76 +7347,76 @@
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q27">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S27">
         <v>3.15</v>
       </c>
       <c r="T27">
+        <v>1.69</v>
+      </c>
+      <c r="U27">
+        <v>2.34</v>
+      </c>
+      <c r="V27">
+        <v>1.45</v>
+      </c>
+      <c r="W27">
         <v>1.68</v>
       </c>
-      <c r="U27">
-        <v>2.28</v>
-      </c>
-      <c r="V27">
-        <v>1.4</v>
-      </c>
-      <c r="W27">
-        <v>1.73</v>
-      </c>
       <c r="X27">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB27">
         <v>12</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ27">
         <v>32</v>
       </c>
       <c r="AK27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27">
         <v>36</v>
@@ -7425,25 +7425,25 @@
         <v>80</v>
       </c>
       <c r="AN27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO27">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR27">
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU27">
         <v>7.6</v>
@@ -7452,37 +7452,37 @@
         <v>12</v>
       </c>
       <c r="AW27">
+        <v>30</v>
+      </c>
+      <c r="AX27">
+        <v>15</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>14.5</v>
+      </c>
+      <c r="BA27">
+        <v>36</v>
+      </c>
+      <c r="BB27">
         <v>28</v>
       </c>
-      <c r="AX27">
-        <v>13</v>
-      </c>
-      <c r="AY27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ27">
-        <v>14</v>
-      </c>
-      <c r="BA27">
+      <c r="BC27">
         <v>21</v>
       </c>
-      <c r="BB27">
-        <v>27</v>
-      </c>
-      <c r="BC27">
-        <v>19.5</v>
-      </c>
       <c r="BD27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE27">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH27">
         <v>3.85</v>
@@ -7494,13 +7494,13 @@
         <v>9.4</v>
       </c>
       <c r="BK27">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN27">
         <v>5.5</v>
@@ -7512,13 +7512,13 @@
         <v>17</v>
       </c>
       <c r="BQ27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR27">
         <v>28</v>
       </c>
       <c r="BS27">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT27">
         <v>6.8</v>
@@ -7527,13 +7527,13 @@
         <v>5.6</v>
       </c>
       <c r="BV27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY27">
         <v>8.4</v>
@@ -7542,7 +7542,7 @@
         <v>23</v>
       </c>
       <c r="CA27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB27" t="s">
         <v>221</v>
@@ -7565,226 +7565,226 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="G28">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="H28">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I28">
+        <v>8.6</v>
+      </c>
+      <c r="J28">
+        <v>4.7</v>
+      </c>
+      <c r="K28">
+        <v>5.9</v>
+      </c>
+      <c r="L28">
+        <v>1.27</v>
+      </c>
+      <c r="M28">
+        <v>1.03</v>
+      </c>
+      <c r="N28">
+        <v>5.6</v>
+      </c>
+      <c r="O28">
+        <v>1.18</v>
+      </c>
+      <c r="P28">
+        <v>2.58</v>
+      </c>
+      <c r="Q28">
+        <v>1.54</v>
+      </c>
+      <c r="R28">
+        <v>1.63</v>
+      </c>
+      <c r="S28">
+        <v>2.36</v>
+      </c>
+      <c r="T28">
+        <v>1.72</v>
+      </c>
+      <c r="U28">
+        <v>2.04</v>
+      </c>
+      <c r="V28">
+        <v>1.13</v>
+      </c>
+      <c r="W28">
+        <v>3.05</v>
+      </c>
+      <c r="X28">
+        <v>32</v>
+      </c>
+      <c r="Y28">
+        <v>34</v>
+      </c>
+      <c r="Z28">
+        <v>170</v>
+      </c>
+      <c r="AA28">
+        <v>230</v>
+      </c>
+      <c r="AB28">
+        <v>12.5</v>
+      </c>
+      <c r="AC28">
+        <v>13</v>
+      </c>
+      <c r="AD28">
+        <v>32</v>
+      </c>
+      <c r="AE28">
+        <v>260</v>
+      </c>
+      <c r="AF28">
+        <v>11.5</v>
+      </c>
+      <c r="AG28">
+        <v>11.5</v>
+      </c>
+      <c r="AH28">
+        <v>25</v>
+      </c>
+      <c r="AI28">
+        <v>85</v>
+      </c>
+      <c r="AJ28">
+        <v>14</v>
+      </c>
+      <c r="AK28">
+        <v>15.5</v>
+      </c>
+      <c r="AL28">
+        <v>32</v>
+      </c>
+      <c r="AM28">
+        <v>580</v>
+      </c>
+      <c r="AN28">
+        <v>5.5</v>
+      </c>
+      <c r="AO28">
+        <v>110</v>
+      </c>
+      <c r="AP28">
+        <v>21</v>
+      </c>
+      <c r="AQ28">
+        <v>6.2</v>
+      </c>
+      <c r="AR28">
+        <v>6.8</v>
+      </c>
+      <c r="AS28">
+        <v>7.4</v>
+      </c>
+      <c r="AT28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU28">
+        <v>10</v>
+      </c>
+      <c r="AV28">
+        <v>6.2</v>
+      </c>
+      <c r="AW28">
         <v>7</v>
       </c>
-      <c r="J28">
-        <v>4.1</v>
-      </c>
-      <c r="K28">
-        <v>4.7</v>
-      </c>
-      <c r="L28">
-        <v>1.29</v>
-      </c>
-      <c r="M28">
-        <v>1.04</v>
-      </c>
-      <c r="N28">
-        <v>5.1</v>
-      </c>
-      <c r="O28">
-        <v>1.2</v>
-      </c>
-      <c r="P28">
-        <v>2.42</v>
-      </c>
-      <c r="Q28">
-        <v>1.61</v>
-      </c>
-      <c r="R28">
-        <v>1.59</v>
-      </c>
-      <c r="S28">
-        <v>2.48</v>
-      </c>
-      <c r="T28">
-        <v>1.68</v>
-      </c>
-      <c r="U28">
-        <v>2.38</v>
-      </c>
-      <c r="V28">
-        <v>1.17</v>
-      </c>
-      <c r="W28">
-        <v>2.48</v>
-      </c>
-      <c r="X28">
-        <v>950</v>
-      </c>
-      <c r="Y28">
-        <v>28</v>
-      </c>
-      <c r="Z28">
-        <v>120</v>
-      </c>
-      <c r="AA28">
-        <v>170</v>
-      </c>
-      <c r="AB28">
-        <v>11.5</v>
-      </c>
-      <c r="AC28">
-        <v>11</v>
-      </c>
-      <c r="AD28">
-        <v>26</v>
-      </c>
-      <c r="AE28">
-        <v>160</v>
-      </c>
-      <c r="AF28">
-        <v>12</v>
-      </c>
-      <c r="AG28">
-        <v>11</v>
-      </c>
-      <c r="AH28">
-        <v>19</v>
-      </c>
-      <c r="AI28">
-        <v>160</v>
-      </c>
-      <c r="AJ28">
-        <v>17</v>
-      </c>
-      <c r="AK28">
-        <v>16.5</v>
-      </c>
-      <c r="AL28">
-        <v>30</v>
-      </c>
-      <c r="AM28">
-        <v>260</v>
-      </c>
-      <c r="AN28">
-        <v>7.2</v>
-      </c>
-      <c r="AO28">
-        <v>80</v>
-      </c>
-      <c r="AP28">
-        <v>18.5</v>
-      </c>
-      <c r="AQ28">
-        <v>5.9</v>
-      </c>
-      <c r="AR28">
-        <v>6.6</v>
-      </c>
-      <c r="AS28">
-        <v>7.2</v>
-      </c>
-      <c r="AT28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU28">
-        <v>8.6</v>
-      </c>
-      <c r="AV28">
-        <v>21</v>
-      </c>
-      <c r="AW28">
-        <v>6.8</v>
-      </c>
       <c r="AX28">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY28">
         <v>8.6</v>
       </c>
       <c r="AZ28">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB28">
+        <v>9.4</v>
+      </c>
+      <c r="BC28">
+        <v>11.5</v>
+      </c>
+      <c r="BD28">
         <v>13</v>
       </c>
-      <c r="BC28">
-        <v>13</v>
-      </c>
-      <c r="BD28">
-        <v>14.5</v>
-      </c>
       <c r="BE28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF28">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BG28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH28">
+        <v>4.9</v>
+      </c>
+      <c r="BI28">
+        <v>3.7</v>
+      </c>
+      <c r="BJ28">
+        <v>11.5</v>
+      </c>
+      <c r="BK28">
+        <v>4.6</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>7.2</v>
+      </c>
+      <c r="BN28">
         <v>4.5</v>
       </c>
-      <c r="BI28">
-        <v>3.5</v>
-      </c>
-      <c r="BJ28">
-        <v>10.5</v>
-      </c>
-      <c r="BK28">
-        <v>4.9</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>8.4</v>
-      </c>
-      <c r="BN28">
-        <v>4.6</v>
-      </c>
       <c r="BO28">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP28">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BQ28">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BR28">
         <v>22</v>
       </c>
       <c r="BS28">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BT28">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU28">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV28">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BW28">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX28">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BY28">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ28">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA28">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB28" t="s">
         <v>221</v>
@@ -7810,19 +7810,19 @@
         <v>3.65</v>
       </c>
       <c r="G29">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H29">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I29">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J29">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L29">
         <v>1.69</v>
@@ -7831,34 +7831,34 @@
         <v>1.17</v>
       </c>
       <c r="N29">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="O29">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="P29">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R29">
         <v>1.12</v>
       </c>
       <c r="S29">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="T29">
         <v>2.4</v>
       </c>
       <c r="U29">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V29">
         <v>1.61</v>
       </c>
       <c r="W29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X29">
         <v>6.8</v>
@@ -7879,13 +7879,13 @@
         <v>7.6</v>
       </c>
       <c r="AD29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE29">
         <v>140</v>
       </c>
       <c r="AF29">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AG29">
         <v>21</v>
@@ -7894,10 +7894,10 @@
         <v>38</v>
       </c>
       <c r="AI29">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="AJ29">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK29">
         <v>240</v>
@@ -7906,7 +7906,7 @@
         <v>540</v>
       </c>
       <c r="AM29">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AN29">
         <v>600</v>
@@ -7915,58 +7915,58 @@
         <v>600</v>
       </c>
       <c r="AP29">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ29">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR29">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS29">
+        <v>7.4</v>
+      </c>
+      <c r="AT29">
+        <v>7.6</v>
+      </c>
+      <c r="AU29">
+        <v>6</v>
+      </c>
+      <c r="AV29">
+        <v>5.5</v>
+      </c>
+      <c r="AW29">
+        <v>7.4</v>
+      </c>
+      <c r="AX29">
         <v>6.8</v>
       </c>
-      <c r="AT29">
-        <v>4.4</v>
-      </c>
-      <c r="AU29">
-        <v>3.95</v>
-      </c>
-      <c r="AV29">
-        <v>5.3</v>
-      </c>
-      <c r="AW29">
+      <c r="AY29">
+        <v>16</v>
+      </c>
+      <c r="AZ29">
         <v>7</v>
       </c>
-      <c r="AX29">
-        <v>6.2</v>
-      </c>
-      <c r="AY29">
-        <v>5.9</v>
-      </c>
-      <c r="AZ29">
-        <v>6.6</v>
-      </c>
       <c r="BA29">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB29">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC29">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD29">
+        <v>8.4</v>
+      </c>
+      <c r="BE29">
+        <v>8.6</v>
+      </c>
+      <c r="BF29">
+        <v>8.4</v>
+      </c>
+      <c r="BG29">
         <v>7.8</v>
-      </c>
-      <c r="BE29">
-        <v>8</v>
-      </c>
-      <c r="BF29">
-        <v>7.8</v>
-      </c>
-      <c r="BG29">
-        <v>7.2</v>
       </c>
       <c r="BH29">
         <v>2.46</v>
@@ -7990,7 +7990,7 @@
         <v>7.4</v>
       </c>
       <c r="BO29">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BP29">
         <v>1000</v>
@@ -8008,7 +8008,7 @@
         <v>5.3</v>
       </c>
       <c r="BU29">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV29">
         <v>26</v>
@@ -8049,226 +8049,226 @@
         <v>204</v>
       </c>
       <c r="F30">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="G30">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="H30">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="I30">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J30">
         <v>2.74</v>
       </c>
       <c r="K30">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N30">
-        <v>1.35</v>
+        <v>2.24</v>
       </c>
       <c r="O30">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P30">
+        <v>1.45</v>
+      </c>
+      <c r="Q30">
+        <v>2.84</v>
+      </c>
+      <c r="R30">
+        <v>1.14</v>
+      </c>
+      <c r="S30">
+        <v>3.45</v>
+      </c>
+      <c r="T30">
+        <v>2.32</v>
+      </c>
+      <c r="U30">
+        <v>1.56</v>
+      </c>
+      <c r="V30">
         <v>1.29</v>
       </c>
-      <c r="Q30">
-        <v>2.78</v>
-      </c>
-      <c r="R30">
-        <v>1.12</v>
-      </c>
-      <c r="S30">
-        <v>1.61</v>
-      </c>
-      <c r="T30">
-        <v>1.11</v>
-      </c>
-      <c r="U30">
-        <v>1.11</v>
-      </c>
-      <c r="V30">
-        <v>1.19</v>
-      </c>
       <c r="W30">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="X30">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="Y30">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="Z30">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="AA30">
         <v>900</v>
       </c>
       <c r="AB30">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AC30">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF30">
+        <v>15.5</v>
+      </c>
+      <c r="AG30">
+        <v>15</v>
+      </c>
+      <c r="AH30">
+        <v>32</v>
+      </c>
+      <c r="AI30">
+        <v>150</v>
+      </c>
+      <c r="AJ30">
+        <v>75</v>
+      </c>
+      <c r="AK30">
         <v>65</v>
-      </c>
-      <c r="AG30">
-        <v>950</v>
-      </c>
-      <c r="AH30">
-        <v>950</v>
-      </c>
-      <c r="AI30">
-        <v>1000</v>
-      </c>
-      <c r="AJ30">
-        <v>900</v>
-      </c>
-      <c r="AK30">
-        <v>150</v>
       </c>
       <c r="AL30">
         <v>210</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN30">
         <v>600</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP30">
-        <v>1.18</v>
+        <v>3.35</v>
       </c>
       <c r="AQ30">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AR30">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="AS30">
-        <v>1.27</v>
+        <v>5.6</v>
       </c>
       <c r="AT30">
-        <v>1.23</v>
+        <v>3.3</v>
       </c>
       <c r="AU30">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AV30">
-        <v>1.26</v>
+        <v>4.6</v>
       </c>
       <c r="AW30">
-        <v>1.27</v>
+        <v>5.5</v>
       </c>
       <c r="AX30">
-        <v>1.24</v>
+        <v>4.3</v>
       </c>
       <c r="AY30">
-        <v>1.22</v>
+        <v>4.2</v>
       </c>
       <c r="AZ30">
-        <v>1.24</v>
+        <v>5</v>
       </c>
       <c r="BA30">
-        <v>1.27</v>
+        <v>5.7</v>
       </c>
       <c r="BB30">
-        <v>1.26</v>
+        <v>5.2</v>
       </c>
       <c r="BC30">
-        <v>1.24</v>
+        <v>5.3</v>
       </c>
       <c r="BD30">
-        <v>1.26</v>
+        <v>5.6</v>
       </c>
       <c r="BE30">
-        <v>1.27</v>
+        <v>5.8</v>
       </c>
       <c r="BF30">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG30">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI30">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK30">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO30">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ30">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU30">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB30" t="s">
         <v>221</v>
@@ -8291,61 +8291,61 @@
         <v>205</v>
       </c>
       <c r="F31">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G31">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H31">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I31">
         <v>2.56</v>
       </c>
       <c r="J31">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O31">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P31">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q31">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T31">
         <v>1.78</v>
       </c>
       <c r="U31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
         <v>1.64</v>
       </c>
       <c r="W31">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X31">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y31">
         <v>10.5</v>
@@ -8354,10 +8354,10 @@
         <v>16.5</v>
       </c>
       <c r="AA31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -8366,10 +8366,10 @@
         <v>12</v>
       </c>
       <c r="AE31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG31">
         <v>14.5</v>
@@ -8381,10 +8381,10 @@
         <v>42</v>
       </c>
       <c r="AJ31">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK31">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL31">
         <v>55</v>
@@ -8393,10 +8393,10 @@
         <v>580</v>
       </c>
       <c r="AN31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP31">
         <v>10</v>
@@ -8408,7 +8408,7 @@
         <v>13.5</v>
       </c>
       <c r="AS31">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
@@ -8420,7 +8420,7 @@
         <v>10</v>
       </c>
       <c r="AW31">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AX31">
         <v>18.5</v>
@@ -8432,10 +8432,10 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BB31">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BC31">
         <v>27</v>
@@ -8444,10 +8444,10 @@
         <v>34</v>
       </c>
       <c r="BE31">
-        <v>8.6</v>
+        <v>70</v>
       </c>
       <c r="BF31">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BG31">
         <v>16</v>
@@ -8477,7 +8477,7 @@
         <v>5.4</v>
       </c>
       <c r="BP31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ31">
         <v>8.4</v>
@@ -8498,7 +8498,7 @@
         <v>19.5</v>
       </c>
       <c r="BW31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX31">
         <v>34</v>
@@ -8510,7 +8510,7 @@
         <v>30</v>
       </c>
       <c r="CA31">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB31" t="s">
         <v>221</v>
@@ -8533,10 +8533,10 @@
         <v>206</v>
       </c>
       <c r="F32">
+        <v>1.76</v>
+      </c>
+      <c r="G32">
         <v>1.79</v>
-      </c>
-      <c r="G32">
-        <v>1.82</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -8545,10 +8545,10 @@
         <v>5.2</v>
       </c>
       <c r="J32">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L32">
         <v>1.37</v>
@@ -8557,7 +8557,7 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O32">
         <v>1.27</v>
@@ -8566,28 +8566,28 @@
         <v>2.16</v>
       </c>
       <c r="Q32">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R32">
         <v>1.45</v>
       </c>
       <c r="S32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T32">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U32">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
         <v>1.23</v>
       </c>
       <c r="W32">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y32">
         <v>23</v>
@@ -8599,13 +8599,13 @@
         <v>900</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC32">
         <v>9.199999999999999</v>
       </c>
       <c r="AD32">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE32">
         <v>75</v>
@@ -8614,28 +8614,28 @@
         <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH32">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AI32">
         <v>320</v>
       </c>
       <c r="AJ32">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="AK32">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="AL32">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM32">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN32">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO32">
         <v>75</v>
@@ -8647,10 +8647,10 @@
         <v>17</v>
       </c>
       <c r="AR32">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AS32">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT32">
         <v>8.800000000000001</v>
@@ -8659,13 +8659,13 @@
         <v>8</v>
       </c>
       <c r="AV32">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW32">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY32">
         <v>8.800000000000001</v>
@@ -8674,25 +8674,25 @@
         <v>16</v>
       </c>
       <c r="BA32">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BB32">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BC32">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD32">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BE32">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG32">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BH32">
         <v>3.7</v>
@@ -8781,13 +8781,13 @@
         <v>1.22</v>
       </c>
       <c r="H33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I33">
         <v>16.5</v>
       </c>
       <c r="J33">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -8805,19 +8805,19 @@
         <v>1.11</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q33">
         <v>1.37</v>
       </c>
       <c r="R33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S33">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="T33">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U33">
         <v>2</v>
@@ -8829,19 +8829,19 @@
         <v>5.6</v>
       </c>
       <c r="X33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y33">
         <v>80</v>
       </c>
       <c r="Z33">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AA33">
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC33">
         <v>20</v>
@@ -8853,13 +8853,13 @@
         <v>220</v>
       </c>
       <c r="AF33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH33">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI33">
         <v>180</v>
@@ -8868,7 +8868,7 @@
         <v>9.6</v>
       </c>
       <c r="AK33">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL33">
         <v>32</v>
@@ -8877,67 +8877,67 @@
         <v>500</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP33">
         <v>40</v>
       </c>
       <c r="AQ33">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AR33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS33">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AT33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU33">
         <v>18</v>
       </c>
       <c r="AV33">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AW33">
         <v>19.5</v>
       </c>
       <c r="AX33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC33">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD33">
         <v>29</v>
       </c>
       <c r="BE33">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF33">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="BG33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH33">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI33">
         <v>5</v>
@@ -8952,13 +8952,13 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="BN33">
         <v>4.1</v>
       </c>
       <c r="BO33">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BP33">
         <v>6.4</v>
@@ -8970,25 +8970,25 @@
         <v>18.5</v>
       </c>
       <c r="BS33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT33">
         <v>17.5</v>
       </c>
       <c r="BU33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
+        <v>15.5</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
         <v>14.5</v>
-      </c>
-      <c r="BX33">
-        <v>1000</v>
-      </c>
-      <c r="BY33">
-        <v>14</v>
       </c>
       <c r="BZ33">
         <v>0</v>
@@ -9017,19 +9017,19 @@
         <v>208</v>
       </c>
       <c r="F34">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="H34">
         <v>3.25</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J34">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K34">
         <v>3.75</v>
@@ -9038,10 +9038,10 @@
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O34">
         <v>1.37</v>
@@ -9050,61 +9050,61 @@
         <v>1.71</v>
       </c>
       <c r="Q34">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R34">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="S34">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="T34">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U34">
         <v>1.11</v>
       </c>
       <c r="V34">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W34">
         <v>1.76</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA34">
         <v>900</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC34">
         <v>950</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG34">
         <v>950</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AJ34">
         <v>900</v>
@@ -9113,7 +9113,7 @@
         <v>150</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM34">
         <v>1000</v>
@@ -9125,52 +9125,52 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AQ34">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AR34">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AS34">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AT34">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AU34">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AV34">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AW34">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AX34">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AY34">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AZ34">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="BA34">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="BB34">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="BC34">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="BD34">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="BE34">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BF34">
         <v>1.55</v>
@@ -9179,7 +9179,7 @@
         <v>1.55</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI34">
         <v>1.04</v>
@@ -9259,10 +9259,10 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G35">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H35">
         <v>7.2</v>
@@ -9271,10 +9271,10 @@
         <v>8.4</v>
       </c>
       <c r="J35">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L35">
         <v>1.46</v>
@@ -9283,22 +9283,22 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O35">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P35">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q35">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R35">
         <v>1.28</v>
       </c>
       <c r="S35">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T35">
         <v>2.18</v>
@@ -9307,16 +9307,16 @@
         <v>1.75</v>
       </c>
       <c r="V35">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W35">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y35">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z35">
         <v>150</v>
@@ -9349,7 +9349,7 @@
         <v>160</v>
       </c>
       <c r="AJ35">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK35">
         <v>22</v>
@@ -9370,25 +9370,25 @@
         <v>11</v>
       </c>
       <c r="AQ35">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR35">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS35">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT35">
         <v>6</v>
       </c>
       <c r="AU35">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV35">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW35">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX35">
         <v>7.4</v>
@@ -9397,82 +9397,82 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ35">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA35">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB35">
         <v>12.5</v>
       </c>
       <c r="BC35">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BD35">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE35">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF35">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG35">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH35">
         <v>3.25</v>
       </c>
       <c r="BI35">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ35">
         <v>12</v>
       </c>
       <c r="BK35">
+        <v>7</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>16</v>
+      </c>
+      <c r="BN35">
+        <v>3.85</v>
+      </c>
+      <c r="BO35">
+        <v>3.15</v>
+      </c>
+      <c r="BP35">
+        <v>10.5</v>
+      </c>
+      <c r="BQ35">
         <v>6.4</v>
       </c>
-      <c r="BL35">
-        <v>1000</v>
-      </c>
-      <c r="BM35">
-        <v>13.5</v>
-      </c>
-      <c r="BN35">
-        <v>3.9</v>
-      </c>
-      <c r="BO35">
-        <v>3.5</v>
-      </c>
-      <c r="BP35">
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
         <v>11</v>
-      </c>
-      <c r="BQ35">
-        <v>6.2</v>
-      </c>
-      <c r="BR35">
-        <v>1000</v>
-      </c>
-      <c r="BS35">
-        <v>10</v>
       </c>
       <c r="BT35">
         <v>11</v>
       </c>
       <c r="BU35">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>5.8</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K36">
         <v>3.7</v>
@@ -9531,10 +9531,10 @@
         <v>1.37</v>
       </c>
       <c r="P36">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q36">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R36">
         <v>1.3</v>
@@ -9543,25 +9543,25 @@
         <v>3.9</v>
       </c>
       <c r="T36">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U36">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W36">
         <v>2.1</v>
       </c>
       <c r="X36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y36">
         <v>16.5</v>
       </c>
       <c r="Z36">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA36">
         <v>900</v>
@@ -9570,7 +9570,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC36">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD36">
         <v>21</v>
@@ -9579,13 +9579,13 @@
         <v>470</v>
       </c>
       <c r="AF36">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG36">
         <v>11</v>
       </c>
       <c r="AH36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI36">
         <v>370</v>
@@ -9597,7 +9597,7 @@
         <v>22</v>
       </c>
       <c r="AL36">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AM36">
         <v>580</v>
@@ -9606,61 +9606,61 @@
         <v>15</v>
       </c>
       <c r="AO36">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="AP36">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ36">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR36">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AS36">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT36">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU36">
         <v>7.2</v>
       </c>
       <c r="AV36">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW36">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="AX36">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY36">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ36">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA36">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BB36">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC36">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD36">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BE36">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF36">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG36">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH36">
         <v>3.35</v>
@@ -9705,7 +9705,7 @@
         <v>5.4</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW36">
         <v>8.4</v>
@@ -9717,7 +9717,7 @@
         <v>8.6</v>
       </c>
       <c r="BZ36">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
         <v>7.2</v>
@@ -9743,7 +9743,7 @@
         <v>211</v>
       </c>
       <c r="F37">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G37">
         <v>2.44</v>
@@ -9752,19 +9752,19 @@
         <v>2.68</v>
       </c>
       <c r="I37">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K37">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L37">
         <v>1.18</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N37">
         <v>10.5</v>
@@ -9791,10 +9791,10 @@
         <v>3.75</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X37">
         <v>140</v>
@@ -9803,25 +9803,25 @@
         <v>55</v>
       </c>
       <c r="Z37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA37">
         <v>110</v>
       </c>
       <c r="AB37">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC37">
         <v>15</v>
       </c>
       <c r="AD37">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE37">
         <v>25</v>
       </c>
       <c r="AF37">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG37">
         <v>15</v>
@@ -9845,25 +9845,25 @@
         <v>55</v>
       </c>
       <c r="AN37">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO37">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AQ37">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AR37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS37">
         <v>26</v>
       </c>
       <c r="AT37">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU37">
         <v>12.5</v>
@@ -9875,7 +9875,7 @@
         <v>20</v>
       </c>
       <c r="AX37">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY37">
         <v>12</v>
@@ -9887,7 +9887,7 @@
         <v>19</v>
       </c>
       <c r="BB37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC37">
         <v>17.5</v>
@@ -9896,13 +9896,13 @@
         <v>17.5</v>
       </c>
       <c r="BE37">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BF37">
         <v>6.8</v>
       </c>
       <c r="BG37">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH37">
         <v>6.8</v>
@@ -9944,7 +9944,7 @@
         <v>7.6</v>
       </c>
       <c r="BU37">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BV37">
         <v>17.5</v>
@@ -9985,7 +9985,7 @@
         <v>212</v>
       </c>
       <c r="F38">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G38">
         <v>3.8</v>
@@ -9997,16 +9997,16 @@
         <v>2.42</v>
       </c>
       <c r="J38">
+        <v>3.1</v>
+      </c>
+      <c r="K38">
         <v>3.15</v>
-      </c>
-      <c r="K38">
-        <v>3.2</v>
       </c>
       <c r="L38">
         <v>1.58</v>
       </c>
       <c r="M38">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N38">
         <v>2.8</v>
@@ -10015,7 +10015,7 @@
         <v>1.53</v>
       </c>
       <c r="P38">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q38">
         <v>2.66</v>
@@ -10027,7 +10027,7 @@
         <v>5.5</v>
       </c>
       <c r="T38">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U38">
         <v>1.81</v>
@@ -10039,13 +10039,13 @@
         <v>1.35</v>
       </c>
       <c r="X38">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y38">
         <v>7.6</v>
       </c>
       <c r="Z38">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA38">
         <v>34</v>
@@ -10054,7 +10054,7 @@
         <v>10.5</v>
       </c>
       <c r="AC38">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD38">
         <v>12</v>
@@ -10081,13 +10081,13 @@
         <v>60</v>
       </c>
       <c r="AL38">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM38">
         <v>180</v>
       </c>
       <c r="AN38">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO38">
         <v>34</v>
@@ -10096,13 +10096,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR38">
         <v>11.5</v>
       </c>
       <c r="AS38">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AT38">
         <v>9.4</v>
@@ -10129,7 +10129,7 @@
         <v>32</v>
       </c>
       <c r="BB38">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BC38">
         <v>50</v>
@@ -10227,43 +10227,43 @@
         <v>213</v>
       </c>
       <c r="F39">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G39">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I39">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J39">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="K39">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="L39">
         <v>1.69</v>
       </c>
       <c r="M39">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N39">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O39">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P39">
         <v>1.42</v>
       </c>
       <c r="Q39">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S39">
         <v>6.4</v>
@@ -10275,10 +10275,10 @@
         <v>1.71</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X39">
         <v>7.2</v>
@@ -10287,7 +10287,7 @@
         <v>8.4</v>
       </c>
       <c r="Z39">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA39">
         <v>220</v>
@@ -10296,16 +10296,16 @@
         <v>8</v>
       </c>
       <c r="AC39">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD39">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE39">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AF39">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG39">
         <v>15.5</v>
@@ -10344,13 +10344,13 @@
         <v>7</v>
       </c>
       <c r="AS39">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT39">
         <v>6.8</v>
       </c>
       <c r="AU39">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV39">
         <v>6.4</v>
@@ -10365,31 +10365,31 @@
         <v>6.4</v>
       </c>
       <c r="AZ39">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="BA39">
+        <v>10</v>
+      </c>
+      <c r="BB39">
+        <v>9.4</v>
+      </c>
+      <c r="BC39">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD39">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BB39">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC39">
-        <v>9</v>
-      </c>
-      <c r="BD39">
-        <v>9.6</v>
       </c>
       <c r="BE39">
         <v>10.5</v>
       </c>
       <c r="BF39">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG39">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH39">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BI39">
         <v>2.12</v>
@@ -10404,7 +10404,7 @@
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN39">
         <v>5.9</v>
@@ -10413,16 +10413,16 @@
         <v>4.5</v>
       </c>
       <c r="BP39">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ39">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT39">
         <v>6</v>
@@ -10434,13 +10434,13 @@
         <v>32</v>
       </c>
       <c r="BW39">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX39">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ39">
         <v>0</v>
@@ -10469,55 +10469,55 @@
         <v>214</v>
       </c>
       <c r="F40">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G40">
         <v>3.55</v>
       </c>
       <c r="H40">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="I40">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J40">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K40">
         <v>3.85</v>
       </c>
       <c r="L40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M40">
         <v>1.06</v>
       </c>
       <c r="N40">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O40">
         <v>1.3</v>
       </c>
       <c r="P40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q40">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S40">
         <v>3.25</v>
       </c>
       <c r="T40">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U40">
         <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
         <v>1.39</v>
@@ -10577,7 +10577,7 @@
         <v>21</v>
       </c>
       <c r="AP40">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AQ40">
         <v>5.6</v>
@@ -10717,19 +10717,19 @@
         <v>4.6</v>
       </c>
       <c r="H41">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I41">
         <v>2.14</v>
       </c>
       <c r="J41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K41">
         <v>3.55</v>
       </c>
       <c r="L41">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M41">
         <v>1.1</v>
@@ -10768,7 +10768,7 @@
         <v>13.5</v>
       </c>
       <c r="Y41">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z41">
         <v>12</v>
@@ -10804,10 +10804,10 @@
         <v>900</v>
       </c>
       <c r="AK41">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="AL41">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="AM41">
         <v>580</v>
@@ -10828,7 +10828,7 @@
         <v>10.5</v>
       </c>
       <c r="AS41">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AT41">
         <v>11.5</v>
@@ -10840,10 +10840,10 @@
         <v>9.6</v>
       </c>
       <c r="AW41">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AX41">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AY41">
         <v>15.5</v>
@@ -10852,31 +10852,31 @@
         <v>18.5</v>
       </c>
       <c r="BA41">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB41">
         <v>10.5</v>
       </c>
       <c r="BC41">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD41">
         <v>10</v>
       </c>
       <c r="BE41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG41">
         <v>18</v>
       </c>
       <c r="BH41">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI41">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ41">
         <v>11</v>
@@ -10888,49 +10888,49 @@
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN41">
         <v>7.6</v>
       </c>
       <c r="BO41">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BP41">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
+        <v>10.5</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
         <v>11.5</v>
       </c>
-      <c r="BR41">
-        <v>60</v>
-      </c>
-      <c r="BS41">
-        <v>13</v>
-      </c>
       <c r="BT41">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU41">
         <v>3.6</v>
       </c>
       <c r="BV41">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW41">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX41">
         <v>36</v>
       </c>
       <c r="BY41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ41">
         <v>36</v>
       </c>
       <c r="CA41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB41" t="s">
         <v>221</v>
@@ -10953,61 +10953,61 @@
         <v>216</v>
       </c>
       <c r="F42">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G42">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H42">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I42">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="J42">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K42">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L42">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M42">
         <v>1.09</v>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O42">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P42">
         <v>1.68</v>
       </c>
       <c r="Q42">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R42">
         <v>1.25</v>
       </c>
       <c r="S42">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T42">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U42">
         <v>1.9</v>
       </c>
       <c r="V42">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X42">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -11016,10 +11016,10 @@
         <v>14.5</v>
       </c>
       <c r="AA42">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB42">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -11028,13 +11028,13 @@
         <v>12</v>
       </c>
       <c r="AE42">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF42">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH42">
         <v>21</v>
@@ -11043,10 +11043,10 @@
         <v>50</v>
       </c>
       <c r="AJ42">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK42">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL42">
         <v>85</v>
@@ -11055,40 +11055,40 @@
         <v>580</v>
       </c>
       <c r="AN42">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AO42">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AP42">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ42">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR42">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS42">
         <v>6.6</v>
       </c>
       <c r="AT42">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU42">
         <v>4</v>
       </c>
       <c r="AV42">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AW42">
         <v>6.4</v>
       </c>
       <c r="AX42">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY42">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AZ42">
         <v>5.9</v>
@@ -11097,34 +11097,34 @@
         <v>7</v>
       </c>
       <c r="BB42">
+        <v>7.4</v>
+      </c>
+      <c r="BC42">
+        <v>7</v>
+      </c>
+      <c r="BD42">
+        <v>7.2</v>
+      </c>
+      <c r="BE42">
         <v>7.6</v>
       </c>
-      <c r="BC42">
+      <c r="BF42">
         <v>7.2</v>
       </c>
-      <c r="BD42">
-        <v>7.4</v>
-      </c>
-      <c r="BE42">
-        <v>7.8</v>
-      </c>
-      <c r="BF42">
-        <v>7.4</v>
-      </c>
       <c r="BG42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH42">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI42">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ42">
         <v>11</v>
       </c>
       <c r="BK42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11133,34 +11133,34 @@
         <v>2.36</v>
       </c>
       <c r="BN42">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP42">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ42">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BR42">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BT42">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU42">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BV42">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BW42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX42">
         <v>38</v>
@@ -11169,7 +11169,7 @@
         <v>2.24</v>
       </c>
       <c r="BZ42">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA42">
         <v>2.24</v>
@@ -11204,13 +11204,13 @@
         <v>3.25</v>
       </c>
       <c r="I43">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J43">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K43">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L43">
         <v>1.7</v>
@@ -11222,7 +11222,7 @@
         <v>2.36</v>
       </c>
       <c r="O43">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P43">
         <v>1.44</v>
@@ -11240,16 +11240,16 @@
         <v>2.4</v>
       </c>
       <c r="U43">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V43">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
         <v>1.54</v>
       </c>
       <c r="X43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y43">
         <v>8.199999999999999</v>
@@ -11309,10 +11309,10 @@
         <v>7.6</v>
       </c>
       <c r="AR43">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS43">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT43">
         <v>6.6</v>
@@ -11324,37 +11324,37 @@
         <v>14.5</v>
       </c>
       <c r="AW43">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX43">
+        <v>14</v>
+      </c>
+      <c r="AY43">
         <v>13</v>
       </c>
-      <c r="AY43">
-        <v>12.5</v>
-      </c>
       <c r="AZ43">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA43">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB43">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BC43">
         <v>38</v>
       </c>
       <c r="BD43">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE43">
         <v>110</v>
       </c>
       <c r="BF43">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BG43">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH43">
         <v>2.54</v>
@@ -11440,13 +11440,13 @@
         <v>2.74</v>
       </c>
       <c r="G44">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H44">
         <v>3.2</v>
       </c>
       <c r="I44">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J44">
         <v>3</v>
@@ -11458,7 +11458,7 @@
         <v>1.59</v>
       </c>
       <c r="M44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N44">
         <v>2.74</v>
@@ -11470,25 +11470,25 @@
         <v>1.56</v>
       </c>
       <c r="Q44">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R44">
         <v>1.2</v>
       </c>
       <c r="S44">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T44">
         <v>2.12</v>
       </c>
       <c r="U44">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V44">
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X44">
         <v>8.4</v>
@@ -11497,13 +11497,13 @@
         <v>9.4</v>
       </c>
       <c r="Z44">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA44">
         <v>140</v>
       </c>
       <c r="AB44">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC44">
         <v>7</v>
@@ -11515,7 +11515,7 @@
         <v>110</v>
       </c>
       <c r="AF44">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG44">
         <v>14</v>
@@ -11554,19 +11554,19 @@
         <v>17</v>
       </c>
       <c r="AS44">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT44">
         <v>7.4</v>
       </c>
       <c r="AU44">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV44">
         <v>13.5</v>
       </c>
       <c r="AW44">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX44">
         <v>13.5</v>
@@ -11578,25 +11578,25 @@
         <v>19.5</v>
       </c>
       <c r="BA44">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB44">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC44">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BD44">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE44">
         <v>70</v>
       </c>
       <c r="BF44">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG44">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH44">
         <v>2.78</v>
@@ -11679,22 +11679,22 @@
         <v>219</v>
       </c>
       <c r="F45">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G45">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H45">
         <v>6.2</v>
       </c>
       <c r="I45">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J45">
         <v>3.65</v>
       </c>
       <c r="K45">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L45">
         <v>1.55</v>
@@ -11703,40 +11703,40 @@
         <v>1.11</v>
       </c>
       <c r="N45">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O45">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q45">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S45">
         <v>5.3</v>
       </c>
       <c r="T45">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U45">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W45">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X45">
         <v>9.800000000000001</v>
       </c>
       <c r="Y45">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z45">
         <v>60</v>
@@ -11745,7 +11745,7 @@
         <v>690</v>
       </c>
       <c r="AB45">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC45">
         <v>8.800000000000001</v>
@@ -11769,7 +11769,7 @@
         <v>440</v>
       </c>
       <c r="AJ45">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK45">
         <v>26</v>
@@ -11781,7 +11781,7 @@
         <v>700</v>
       </c>
       <c r="AN45">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO45">
         <v>1000</v>
@@ -11799,25 +11799,25 @@
         <v>46</v>
       </c>
       <c r="AT45">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU45">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV45">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AW45">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AX45">
         <v>7.8</v>
       </c>
       <c r="AY45">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ45">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BA45">
         <v>44</v>
@@ -11832,7 +11832,7 @@
         <v>46</v>
       </c>
       <c r="BE45">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF45">
         <v>15</v>
@@ -11856,7 +11856,7 @@
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN45">
         <v>4.2</v>
@@ -11865,40 +11865,40 @@
         <v>3.25</v>
       </c>
       <c r="BP45">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ45">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR45">
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT45">
         <v>10.5</v>
       </c>
       <c r="BU45">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ45">
         <v>1000</v>
       </c>
       <c r="CA45">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB45" t="s">
         <v>221</v>
@@ -11924,16 +11924,16 @@
         <v>1.96</v>
       </c>
       <c r="G46">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H46">
         <v>4.1</v>
       </c>
       <c r="I46">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J46">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K46">
         <v>3.6</v>
@@ -11972,10 +11972,10 @@
         <v>1.26</v>
       </c>
       <c r="W46">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X46">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y46">
         <v>15</v>
@@ -11993,7 +11993,7 @@
         <v>8.4</v>
       </c>
       <c r="AD46">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE46">
         <v>370</v>
@@ -12005,7 +12005,7 @@
         <v>11.5</v>
       </c>
       <c r="AH46">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI46">
         <v>500</v>
@@ -12038,7 +12038,7 @@
         <v>13</v>
       </c>
       <c r="AS46">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT46">
         <v>6.8</v>
@@ -12050,7 +12050,7 @@
         <v>15</v>
       </c>
       <c r="AW46">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX46">
         <v>10</v>
@@ -12062,7 +12062,7 @@
         <v>17</v>
       </c>
       <c r="BA46">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB46">
         <v>20</v>
@@ -12071,13 +12071,13 @@
         <v>19.5</v>
       </c>
       <c r="BD46">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE46">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF46">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="BG46">
         <v>10</v>
@@ -12122,7 +12122,7 @@
         <v>8</v>
       </c>
       <c r="BU46">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV46">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -679,7 +679,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-03 05:24:55</t>
+    <t>2026-08-03 07:32:48</t>
   </si>
 </sst>
 </file>
@@ -1273,223 +1273,223 @@
         <v>176</v>
       </c>
       <c r="F2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G2">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="H2">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z2">
         <v>10.5</v>
       </c>
       <c r="AA2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AG2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK2">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AL2">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AO2">
         <v>18</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR2">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
         <v>20</v>
       </c>
       <c r="AX2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AY2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2">
         <v>42</v>
       </c>
       <c r="BB2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BC2">
         <v>55</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BG2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH2">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BP2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BS2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BV2">
         <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA2">
         <v>34</v>
@@ -1518,13 +1518,13 @@
         <v>2.36</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J3">
         <v>4.6</v>
@@ -1539,7 +1539,7 @@
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O3">
         <v>1.1</v>
@@ -1563,16 +1563,16 @@
         <v>3.5</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
         <v>55</v>
       </c>
       <c r="Y3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z3">
         <v>38</v>
@@ -1584,10 +1584,10 @@
         <v>28</v>
       </c>
       <c r="AC3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>23</v>
@@ -1608,7 +1608,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3">
         <v>24</v>
@@ -1620,19 +1620,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AP3">
         <v>30</v>
       </c>
       <c r="AQ3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR3">
         <v>24</v>
       </c>
       <c r="AS3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT3">
         <v>21</v>
@@ -1662,10 +1662,10 @@
         <v>28</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE3">
         <v>29</v>
@@ -1674,7 +1674,7 @@
         <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3">
         <v>6.2</v>
@@ -1686,13 +1686,13 @@
         <v>8</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>6.8</v>
@@ -1704,31 +1704,31 @@
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
         <v>18</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU3">
         <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
         <v>19</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>9.4</v>
@@ -1757,7 +1757,7 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G4">
         <v>1.34</v>
@@ -1766,217 +1766,217 @@
         <v>10.5</v>
       </c>
       <c r="I4">
-        <v>12.5</v>
+        <v>870</v>
       </c>
       <c r="J4">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L4">
         <v>1.24</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R4">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="S4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T4">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>240</v>
+        <v>950</v>
       </c>
       <c r="Z4">
         <v>150</v>
       </c>
       <c r="AA4">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AE4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AJ4">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AK4">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AL4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM4">
-        <v>380</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>15</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4">
-        <v>20</v>
+        <v>1.83</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>1.86</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="AT4">
-        <v>10.5</v>
+        <v>1.73</v>
       </c>
       <c r="AU4">
-        <v>12.5</v>
+        <v>1.74</v>
       </c>
       <c r="AV4">
-        <v>32</v>
+        <v>1.81</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>1.89</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>1.87</v>
       </c>
       <c r="BB4">
-        <v>9.4</v>
+        <v>1.68</v>
       </c>
       <c r="BC4">
-        <v>11.5</v>
+        <v>1.72</v>
       </c>
       <c r="BD4">
-        <v>16.5</v>
+        <v>1.81</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>1.87</v>
       </c>
       <c r="BF4">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>1.87</v>
       </c>
       <c r="BH4">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>221</v>
@@ -2002,10 +2002,10 @@
         <v>1.76</v>
       </c>
       <c r="G5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
         <v>5.5</v>
@@ -2029,19 +2029,19 @@
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
         <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
         <v>2.12</v>
@@ -2050,7 +2050,7 @@
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -2059,10 +2059,10 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB5">
         <v>11</v>
@@ -2074,7 +2074,7 @@
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -2086,7 +2086,7 @@
         <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>20</v>
@@ -2095,16 +2095,16 @@
         <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="AN5">
         <v>10</v>
       </c>
       <c r="AO5">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="AP5">
         <v>15.5</v>
@@ -2149,7 +2149,7 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
         <v>7.6</v>
@@ -2164,7 +2164,7 @@
         <v>4</v>
       </c>
       <c r="BI5">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
         <v>10</v>
@@ -2247,13 +2247,13 @@
         <v>1.17</v>
       </c>
       <c r="H6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I6">
         <v>27</v>
       </c>
       <c r="J6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -2274,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R6">
         <v>1.81</v>
@@ -2289,10 +2289,10 @@
         <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="X6">
         <v>46</v>
@@ -2301,13 +2301,13 @@
         <v>75</v>
       </c>
       <c r="Z6">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6">
         <v>28</v>
@@ -2328,13 +2328,13 @@
         <v>60</v>
       </c>
       <c r="AI6">
-        <v>330</v>
+        <v>440</v>
       </c>
       <c r="AJ6">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AK6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL6">
         <v>60</v>
@@ -2352,13 +2352,13 @@
         <v>30</v>
       </c>
       <c r="AQ6">
+        <v>6.6</v>
+      </c>
+      <c r="AR6">
         <v>6.8</v>
       </c>
-      <c r="AR6">
-        <v>7.4</v>
-      </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -2367,10 +2367,10 @@
         <v>20</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AW6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
         <v>7.2</v>
@@ -2382,31 +2382,31 @@
         <v>32</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
         <v>2.92</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ6">
         <v>16</v>
@@ -2418,19 +2418,19 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BN6">
         <v>3.65</v>
       </c>
       <c r="BO6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BP6">
         <v>5.7</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
         <v>24</v>
@@ -2460,7 +2460,7 @@
         <v>7</v>
       </c>
       <c r="CA6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
         <v>221</v>
@@ -2483,22 +2483,22 @@
         <v>181</v>
       </c>
       <c r="F7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H7">
         <v>2.16</v>
       </c>
       <c r="I7">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J7">
         <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.29</v>
@@ -2513,16 +2513,16 @@
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
         <v>1.65</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T7">
         <v>1.53</v>
@@ -2531,31 +2531,31 @@
         <v>2.68</v>
       </c>
       <c r="V7">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
         <v>29</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
         <v>21</v>
       </c>
       <c r="AA7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
         <v>24</v>
@@ -2564,7 +2564,7 @@
         <v>36</v>
       </c>
       <c r="AG7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH7">
         <v>18</v>
@@ -2573,13 +2573,13 @@
         <v>40</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AK7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM7">
         <v>75</v>
@@ -2591,7 +2591,7 @@
         <v>13</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ7">
         <v>13</v>
@@ -2603,16 +2603,16 @@
         <v>24</v>
       </c>
       <c r="AT7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX7">
         <v>23</v>
@@ -2627,28 +2627,28 @@
         <v>22</v>
       </c>
       <c r="BB7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD7">
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
@@ -2660,10 +2660,10 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO7">
         <v>5.3</v>
@@ -2672,13 +2672,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT7">
         <v>5.5</v>
@@ -2690,19 +2690,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>221</v>
@@ -2725,10 +2725,10 @@
         <v>182</v>
       </c>
       <c r="F8">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="G8">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H8">
         <v>4.6</v>
@@ -2740,7 +2740,7 @@
         <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
         <v>1.45</v>
@@ -2752,10 +2752,10 @@
         <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
         <v>2.12</v>
@@ -2776,7 +2776,7 @@
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X8">
         <v>13</v>
@@ -2788,19 +2788,19 @@
         <v>40</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF8">
         <v>11.5</v>
@@ -2809,10 +2809,10 @@
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI8">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AJ8">
         <v>24</v>
@@ -2821,16 +2821,16 @@
         <v>22</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO8">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AP8">
         <v>11</v>
@@ -2839,58 +2839,58 @@
         <v>14</v>
       </c>
       <c r="AR8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AS8">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AT8">
+        <v>7.6</v>
+      </c>
+      <c r="AU8">
         <v>7.4</v>
       </c>
-      <c r="AU8">
-        <v>7</v>
-      </c>
       <c r="AV8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AX8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BB8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD8">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE8">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="BF8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BH8">
         <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2902,7 +2902,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
@@ -2911,7 +2911,7 @@
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>7.4</v>
@@ -2926,25 +2926,25 @@
         <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>221</v>
@@ -2970,19 +2970,19 @@
         <v>4.3</v>
       </c>
       <c r="G9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H9">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.42</v>
@@ -2991,88 +2991,88 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
         <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
         <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
         <v>2.02</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
         <v>11</v>
       </c>
       <c r="AE9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF9">
         <v>36</v>
       </c>
       <c r="AG9">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>40</v>
       </c>
       <c r="AJ9">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="AK9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP9">
         <v>12</v>
@@ -3084,49 +3084,49 @@
         <v>10</v>
       </c>
       <c r="AS9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU9">
         <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW9">
         <v>17.5</v>
       </c>
       <c r="AX9">
+        <v>7.6</v>
+      </c>
+      <c r="AY9">
         <v>15</v>
       </c>
-      <c r="AY9">
-        <v>13</v>
-      </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA9">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC9">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD9">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH9">
         <v>3.5</v>
@@ -3138,49 +3138,49 @@
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
         <v>8.4</v>
       </c>
       <c r="BO9">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BP9">
         <v>42</v>
       </c>
       <c r="BQ9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
         <v>4.7</v>
       </c>
       <c r="BU9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BX9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I10">
         <v>5.9</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>1.35</v>
@@ -3236,7 +3236,7 @@
         <v>4.5</v>
       </c>
       <c r="O10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
         <v>2.2</v>
@@ -3245,13 +3245,13 @@
         <v>1.8</v>
       </c>
       <c r="R10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S10">
         <v>2.96</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
         <v>2.08</v>
@@ -3263,7 +3263,7 @@
         <v>2.36</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y10">
         <v>26</v>
@@ -3272,19 +3272,19 @@
         <v>55</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10">
         <v>26</v>
       </c>
       <c r="AE10">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3293,40 +3293,40 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL10">
         <v>38</v>
       </c>
       <c r="AM10">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP10">
         <v>16</v>
       </c>
       <c r="AQ10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
         <v>34</v>
       </c>
       <c r="AS10">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
@@ -3350,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB10">
         <v>15</v>
@@ -3362,13 +3362,13 @@
         <v>23</v>
       </c>
       <c r="BE10">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BF10">
         <v>8</v>
       </c>
       <c r="BG10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH10">
         <v>3.9</v>
@@ -3380,13 +3380,13 @@
         <v>10</v>
       </c>
       <c r="BK10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
@@ -3398,16 +3398,16 @@
         <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU10">
         <v>5.3</v>
@@ -3422,7 +3422,7 @@
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3451,22 +3451,22 @@
         <v>185</v>
       </c>
       <c r="F11">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G11">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I11">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.4</v>
@@ -3475,58 +3475,58 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
+        <v>1.99</v>
+      </c>
+      <c r="Q11">
+        <v>1.95</v>
+      </c>
+      <c r="R11">
+        <v>1.37</v>
+      </c>
+      <c r="S11">
+        <v>3.4</v>
+      </c>
+      <c r="T11">
+        <v>1.86</v>
+      </c>
+      <c r="U11">
         <v>2.02</v>
       </c>
-      <c r="Q11">
-        <v>1.93</v>
-      </c>
-      <c r="R11">
-        <v>1.38</v>
-      </c>
-      <c r="S11">
-        <v>3.35</v>
-      </c>
-      <c r="T11">
-        <v>1.9</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
       <c r="V11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="X11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y11">
         <v>23</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB11">
         <v>8.6</v>
       </c>
       <c r="AC11">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AF11">
         <v>12</v>
@@ -3535,88 +3535,88 @@
         <v>12</v>
       </c>
       <c r="AH11">
+        <v>20</v>
+      </c>
+      <c r="AI11">
+        <v>85</v>
+      </c>
+      <c r="AJ11">
+        <v>20</v>
+      </c>
+      <c r="AK11">
         <v>23</v>
       </c>
-      <c r="AI11">
-        <v>320</v>
-      </c>
-      <c r="AJ11">
-        <v>17</v>
-      </c>
-      <c r="AK11">
-        <v>22</v>
-      </c>
       <c r="AL11">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO11">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP11">
         <v>15</v>
       </c>
       <c r="AQ11">
+        <v>18</v>
+      </c>
+      <c r="AR11">
+        <v>38</v>
+      </c>
+      <c r="AS11">
+        <v>17</v>
+      </c>
+      <c r="AT11">
+        <v>7.8</v>
+      </c>
+      <c r="AU11">
+        <v>8</v>
+      </c>
+      <c r="AV11">
+        <v>18.5</v>
+      </c>
+      <c r="AW11">
+        <v>65</v>
+      </c>
+      <c r="AX11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11">
+        <v>9</v>
+      </c>
+      <c r="AZ11">
         <v>17.5</v>
       </c>
-      <c r="AR11">
-        <v>23</v>
-      </c>
-      <c r="AS11">
-        <v>7.6</v>
-      </c>
-      <c r="AT11">
-        <v>7.6</v>
-      </c>
-      <c r="AU11">
-        <v>8.4</v>
-      </c>
-      <c r="AV11">
-        <v>19</v>
-      </c>
-      <c r="AW11">
-        <v>23</v>
-      </c>
-      <c r="AX11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY11">
-        <v>8.6</v>
-      </c>
-      <c r="AZ11">
-        <v>18</v>
-      </c>
       <c r="BA11">
-        <v>7.4</v>
+        <v>60</v>
       </c>
       <c r="BB11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="BE11">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF11">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH11">
         <v>3.5</v>
       </c>
       <c r="BI11">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3628,7 +3628,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
@@ -3637,34 +3637,34 @@
         <v>3.4</v>
       </c>
       <c r="BP11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS11">
         <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3693,25 +3693,25 @@
         <v>186</v>
       </c>
       <c r="F12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G12">
         <v>1.48</v>
       </c>
       <c r="H12">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>4.8</v>
       </c>
       <c r="K12">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3720,25 +3720,25 @@
         <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U12">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
         <v>1.12</v>
@@ -3756,82 +3756,82 @@
         <v>85</v>
       </c>
       <c r="AA12">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
         <v>34</v>
       </c>
       <c r="AE12">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI12">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="AJ12">
         <v>13</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL12">
         <v>36</v>
       </c>
       <c r="AM12">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="AN12">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO12">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR12">
         <v>55</v>
       </c>
       <c r="AS12">
-        <v>90</v>
+        <v>11.5</v>
       </c>
       <c r="AT12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
         <v>25</v>
       </c>
       <c r="AW12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
         <v>60</v>
@@ -3846,19 +3846,19 @@
         <v>24</v>
       </c>
       <c r="BE12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF12">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG12">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
@@ -3870,7 +3870,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BN12">
         <v>4.1</v>
@@ -3888,25 +3888,25 @@
         <v>24</v>
       </c>
       <c r="BS12">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BT12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3935,22 +3935,22 @@
         <v>187</v>
       </c>
       <c r="F13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H13">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I13">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J13">
         <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3959,31 +3959,31 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3995,22 +3995,22 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AA13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB13">
         <v>21</v>
       </c>
       <c r="AC13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD13">
         <v>11</v>
       </c>
       <c r="AE13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF13">
         <v>32</v>
@@ -4022,10 +4022,10 @@
         <v>15</v>
       </c>
       <c r="AI13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK13">
         <v>36</v>
@@ -4034,19 +4034,19 @@
         <v>38</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AN13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP13">
         <v>22</v>
       </c>
       <c r="AQ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR13">
         <v>14.5</v>
@@ -4055,22 +4055,22 @@
         <v>23</v>
       </c>
       <c r="AT13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV13">
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX13">
         <v>28</v>
       </c>
       <c r="AY13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13">
         <v>13.5</v>
@@ -4082,19 +4082,19 @@
         <v>55</v>
       </c>
       <c r="BC13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD13">
         <v>32</v>
       </c>
       <c r="BE13">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BF13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -4115,13 +4115,13 @@
         <v>15</v>
       </c>
       <c r="BN13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ13">
         <v>10.5</v>
@@ -4130,7 +4130,7 @@
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
@@ -4139,19 +4139,19 @@
         <v>4.8</v>
       </c>
       <c r="BV13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA13">
         <v>8.199999999999999</v>
@@ -4177,7 +4177,7 @@
         <v>188</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G14">
         <v>2.9</v>
@@ -4189,10 +4189,10 @@
         <v>2.6</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>1.34</v>
@@ -4219,13 +4219,13 @@
         <v>2.84</v>
       </c>
       <c r="T14">
+        <v>1.6</v>
+      </c>
+      <c r="U14">
+        <v>2.44</v>
+      </c>
+      <c r="V14">
         <v>1.62</v>
-      </c>
-      <c r="U14">
-        <v>2.38</v>
-      </c>
-      <c r="V14">
-        <v>1.63</v>
       </c>
       <c r="W14">
         <v>1.52</v>
@@ -4234,7 +4234,7 @@
         <v>19</v>
       </c>
       <c r="Y14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
         <v>19</v>
@@ -4261,7 +4261,7 @@
         <v>13</v>
       </c>
       <c r="AH14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI14">
         <v>32</v>
@@ -4282,7 +4282,7 @@
         <v>21</v>
       </c>
       <c r="AO14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP14">
         <v>17</v>
@@ -4339,7 +4339,7 @@
         <v>14.5</v>
       </c>
       <c r="BH14">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI14">
         <v>3.05</v>
@@ -4348,13 +4348,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
         <v>6.4</v>
@@ -4366,31 +4366,31 @@
         <v>22</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT14">
         <v>6</v>
       </c>
       <c r="BU14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4419,16 +4419,16 @@
         <v>189</v>
       </c>
       <c r="F15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H15">
         <v>8.199999999999999</v>
       </c>
       <c r="I15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J15">
         <v>4.8</v>
@@ -4446,13 +4446,13 @@
         <v>4.2</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P15">
         <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R15">
         <v>1.42</v>
@@ -4470,7 +4470,7 @@
         <v>1.1</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X15">
         <v>19</v>
@@ -4479,10 +4479,10 @@
         <v>32</v>
       </c>
       <c r="Z15">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="AA15">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB15">
         <v>8.4</v>
@@ -4494,7 +4494,7 @@
         <v>40</v>
       </c>
       <c r="AE15">
-        <v>480</v>
+        <v>190</v>
       </c>
       <c r="AF15">
         <v>8.6</v>
@@ -4506,7 +4506,7 @@
         <v>30</v>
       </c>
       <c r="AI15">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
         <v>12</v>
@@ -4527,7 +4527,7 @@
         <v>300</v>
       </c>
       <c r="AP15">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
         <v>7</v>
@@ -4539,7 +4539,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AU15">
         <v>5.2</v>
@@ -4563,10 +4563,10 @@
         <v>8.6</v>
       </c>
       <c r="BB15">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC15">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BD15">
         <v>7.4</v>
@@ -4661,22 +4661,22 @@
         <v>190</v>
       </c>
       <c r="F16">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="G16">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I16">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
         <v>1.41</v>
@@ -4691,82 +4691,82 @@
         <v>1.32</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q16">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R16">
         <v>1.37</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T16">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W16">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="X16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AB16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>8</v>
       </c>
       <c r="AD16">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE16">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AF16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16">
         <v>17</v>
       </c>
       <c r="AI16">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AM16">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AN16">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP16">
         <v>12.5</v>
@@ -4778,22 +4778,22 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT16">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AX16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16">
         <v>10</v>
@@ -4802,25 +4802,25 @@
         <v>14.5</v>
       </c>
       <c r="BA16">
+        <v>10</v>
+      </c>
+      <c r="BB16">
+        <v>8.6</v>
+      </c>
+      <c r="BC16">
+        <v>21</v>
+      </c>
+      <c r="BD16">
+        <v>9</v>
+      </c>
+      <c r="BE16">
         <v>10.5</v>
       </c>
-      <c r="BB16">
-        <v>14.5</v>
-      </c>
-      <c r="BC16">
-        <v>13</v>
-      </c>
-      <c r="BD16">
-        <v>17.5</v>
-      </c>
-      <c r="BE16">
-        <v>12</v>
-      </c>
       <c r="BF16">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG16">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BH16">
         <v>3.45</v>
@@ -4832,7 +4832,7 @@
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4841,37 +4841,37 @@
         <v>15.5</v>
       </c>
       <c r="BN16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
         <v>11</v>
       </c>
       <c r="BT16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU16">
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW16">
         <v>10.5</v>
       </c>
       <c r="BX16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY16">
         <v>12</v>
@@ -4903,16 +4903,16 @@
         <v>191</v>
       </c>
       <c r="F17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G17">
         <v>3.35</v>
       </c>
       <c r="H17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I17">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J17">
         <v>3.25</v>
@@ -4921,19 +4921,19 @@
         <v>3.45</v>
       </c>
       <c r="L17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M17">
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O17">
         <v>1.35</v>
       </c>
       <c r="P17">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
         <v>2.08</v>
@@ -4957,7 +4957,7 @@
         <v>1.43</v>
       </c>
       <c r="X17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y17">
         <v>10.5</v>
@@ -4966,7 +4966,7 @@
         <v>18</v>
       </c>
       <c r="AA17">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AB17">
         <v>12.5</v>
@@ -4993,19 +4993,19 @@
         <v>50</v>
       </c>
       <c r="AJ17">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AK17">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AL17">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN17">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AO17">
         <v>25</v>
@@ -5020,7 +5020,7 @@
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="AT17">
         <v>10.5</v>
@@ -5053,10 +5053,10 @@
         <v>32</v>
       </c>
       <c r="BD17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF17">
         <v>30</v>
@@ -5068,22 +5068,22 @@
         <v>3.3</v>
       </c>
       <c r="BI17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO17">
         <v>4.8</v>
@@ -5092,13 +5092,13 @@
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT17">
         <v>5.5</v>
@@ -5107,22 +5107,22 @@
         <v>4.1</v>
       </c>
       <c r="BV17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB17" t="s">
         <v>221</v>
@@ -5157,7 +5157,7 @@
         <v>7.2</v>
       </c>
       <c r="J18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K18">
         <v>5.3</v>
@@ -5178,7 +5178,7 @@
         <v>2.98</v>
       </c>
       <c r="Q18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
         <v>1.79</v>
@@ -5205,7 +5205,7 @@
         <v>34</v>
       </c>
       <c r="Z18">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AA18">
         <v>170</v>
@@ -5226,10 +5226,10 @@
         <v>12</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI18">
         <v>70</v>
@@ -5238,7 +5238,7 @@
         <v>14.5</v>
       </c>
       <c r="AK18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL18">
         <v>25</v>
@@ -5250,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="AO18">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP18">
         <v>28</v>
@@ -5262,7 +5262,7 @@
         <v>55</v>
       </c>
       <c r="AS18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5277,13 +5277,13 @@
         <v>55</v>
       </c>
       <c r="AX18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA18">
         <v>55</v>
@@ -5304,13 +5304,13 @@
         <v>4.8</v>
       </c>
       <c r="BG18">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH18">
         <v>4.8</v>
       </c>
       <c r="BI18">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ18">
         <v>9.6</v>
@@ -5328,7 +5328,7 @@
         <v>4.5</v>
       </c>
       <c r="BO18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP18">
         <v>8.800000000000001</v>
@@ -5486,10 +5486,10 @@
         <v>110</v>
       </c>
       <c r="AM19">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="AN19">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AO19">
         <v>42</v>
@@ -5516,7 +5516,7 @@
         <v>10.5</v>
       </c>
       <c r="AW19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AX19">
         <v>18</v>
@@ -5540,13 +5540,13 @@
         <v>44</v>
       </c>
       <c r="BE19">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BF19">
         <v>42</v>
       </c>
       <c r="BG19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>2.82</v>
@@ -5629,7 +5629,7 @@
         <v>194</v>
       </c>
       <c r="F20">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G20">
         <v>2.1</v>
@@ -5683,16 +5683,16 @@
         <v>1.9</v>
       </c>
       <c r="X20">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y20">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AB20">
         <v>14.5</v>
@@ -5704,7 +5704,7 @@
         <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AF20">
         <v>16.5</v>
@@ -5716,7 +5716,7 @@
         <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AJ20">
         <v>32</v>
@@ -5725,10 +5725,10 @@
         <v>19.5</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM20">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="AN20">
         <v>9.6</v>
@@ -5746,7 +5746,7 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
         <v>11.5</v>
@@ -5773,7 +5773,7 @@
         <v>21</v>
       </c>
       <c r="BB20">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC20">
         <v>15.5</v>
@@ -5782,7 +5782,7 @@
         <v>21</v>
       </c>
       <c r="BE20">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20">
         <v>7.8</v>
@@ -5871,34 +5871,34 @@
         <v>195</v>
       </c>
       <c r="F21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G21">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I21">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J21">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K21">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="L21">
         <v>1.21</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P21">
         <v>3.4</v>
@@ -5907,22 +5907,22 @@
         <v>1.37</v>
       </c>
       <c r="R21">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S21">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="T21">
         <v>2.14</v>
       </c>
       <c r="U21">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V21">
         <v>1.04</v>
       </c>
       <c r="W21">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="X21">
         <v>48</v>
@@ -5931,7 +5931,7 @@
         <v>950</v>
       </c>
       <c r="Z21">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5940,79 +5940,79 @@
         <v>14</v>
       </c>
       <c r="AC21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD21">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="AE21">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="AF21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH21">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI21">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AJ21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AK21">
         <v>15</v>
       </c>
       <c r="AL21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN21">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AO21">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="AP21">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AQ21">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT21">
         <v>11</v>
       </c>
       <c r="AU21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV21">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW21">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21">
         <v>34</v>
       </c>
       <c r="BA21">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB21">
         <v>7.4</v>
@@ -6024,73 +6024,73 @@
         <v>34</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF21">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BG21">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21">
         <v>5.9</v>
       </c>
       <c r="BI21">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BJ21">
         <v>15</v>
       </c>
       <c r="BK21">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BN21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO21">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BP21">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BQ21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR21">
         <v>22</v>
       </c>
       <c r="BS21">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT21">
         <v>22</v>
       </c>
       <c r="BU21">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ21">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CA21">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB21" t="s">
         <v>221</v>
@@ -6113,22 +6113,22 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H22">
         <v>1.4</v>
       </c>
       <c r="I22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J22">
         <v>5.6</v>
       </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L22">
         <v>1.27</v>
@@ -6140,7 +6140,7 @@
         <v>6.6</v>
       </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
         <v>2.86</v>
@@ -6152,16 +6152,16 @@
         <v>1.74</v>
       </c>
       <c r="S22">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T22">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="W22">
         <v>1.12</v>
@@ -6173,10 +6173,10 @@
         <v>12</v>
       </c>
       <c r="Z22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB22">
         <v>38</v>
@@ -6185,52 +6185,52 @@
         <v>13</v>
       </c>
       <c r="AD22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE22">
         <v>13</v>
       </c>
       <c r="AF22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AG22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH22">
         <v>22</v>
       </c>
       <c r="AI22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ22">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AK22">
         <v>110</v>
       </c>
       <c r="AL22">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM22">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN22">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP22">
         <v>26</v>
       </c>
       <c r="AQ22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR22">
         <v>9.6</v>
       </c>
       <c r="AS22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT22">
         <v>32</v>
@@ -6239,7 +6239,7 @@
         <v>11.5</v>
       </c>
       <c r="AV22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW22">
         <v>12</v>
@@ -6263,40 +6263,40 @@
         <v>65</v>
       </c>
       <c r="BD22">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BE22">
         <v>75</v>
       </c>
       <c r="BF22">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG22">
         <v>4.5</v>
       </c>
       <c r="BH22">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI22">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22">
         <v>10.5</v>
       </c>
       <c r="BK22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL22">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BM22">
         <v>14</v>
       </c>
       <c r="BN22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP22">
         <v>65</v>
@@ -6305,7 +6305,7 @@
         <v>13</v>
       </c>
       <c r="BR22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS22">
         <v>12.5</v>
@@ -6314,13 +6314,13 @@
         <v>4.2</v>
       </c>
       <c r="BU22">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV22">
         <v>8</v>
       </c>
       <c r="BW22">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BX22">
         <v>19.5</v>
@@ -6332,7 +6332,7 @@
         <v>10.5</v>
       </c>
       <c r="CA22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="s">
         <v>221</v>
@@ -6355,55 +6355,55 @@
         <v>197</v>
       </c>
       <c r="F23">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G23">
         <v>2.42</v>
       </c>
       <c r="H23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J23">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K23">
         <v>3.3</v>
       </c>
       <c r="L23">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M23">
         <v>1.1</v>
       </c>
       <c r="N23">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q23">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T23">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U23">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
         <v>1.7</v>
@@ -6418,28 +6418,28 @@
         <v>24</v>
       </c>
       <c r="AA23">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>7.2</v>
       </c>
       <c r="AD23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF23">
         <v>14</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI23">
         <v>65</v>
@@ -6448,43 +6448,43 @@
         <v>34</v>
       </c>
       <c r="AK23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL23">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AM23">
         <v>130</v>
       </c>
       <c r="AN23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO23">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AP23">
         <v>10</v>
       </c>
       <c r="AQ23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR23">
         <v>21</v>
       </c>
       <c r="AS23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV23">
         <v>14</v>
       </c>
       <c r="AW23">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
@@ -6493,31 +6493,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ23">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB23">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD23">
         <v>40</v>
       </c>
       <c r="BE23">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BF23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI23">
         <v>2.52</v>
@@ -6526,7 +6526,7 @@
         <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6541,7 +6541,7 @@
         <v>4</v>
       </c>
       <c r="BP23">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BQ23">
         <v>13</v>
@@ -6550,7 +6550,7 @@
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23">
         <v>6.8</v>
@@ -6562,13 +6562,13 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6597,22 +6597,22 @@
         <v>198</v>
       </c>
       <c r="F24">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H24">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I24">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J24">
         <v>3.35</v>
       </c>
       <c r="K24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
         <v>1.48</v>
@@ -6621,34 +6621,34 @@
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U24">
         <v>1.98</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X24">
         <v>12</v>
@@ -6657,10 +6657,10 @@
         <v>13</v>
       </c>
       <c r="Z24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB24">
         <v>9.199999999999999</v>
@@ -6681,28 +6681,28 @@
         <v>11.5</v>
       </c>
       <c r="AH24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI24">
         <v>70</v>
       </c>
       <c r="AJ24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL24">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM24">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AN24">
         <v>25</v>
       </c>
       <c r="AO24">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP24">
         <v>10</v>
@@ -6735,22 +6735,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE24">
-        <v>80</v>
+        <v>9.6</v>
       </c>
       <c r="BF24">
         <v>19.5</v>
@@ -6762,7 +6762,7 @@
         <v>3.15</v>
       </c>
       <c r="BI24">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ24">
         <v>10.5</v>
@@ -6774,7 +6774,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN24">
         <v>5.2</v>
@@ -6783,16 +6783,16 @@
         <v>4.4</v>
       </c>
       <c r="BP24">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT24">
         <v>6.8</v>
@@ -6804,13 +6804,13 @@
         <v>32</v>
       </c>
       <c r="BW24">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24">
         <v>46</v>
       </c>
       <c r="BY24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6839,22 +6839,22 @@
         <v>199</v>
       </c>
       <c r="F25">
+        <v>3.3</v>
+      </c>
+      <c r="G25">
         <v>3.35</v>
-      </c>
-      <c r="G25">
-        <v>3.45</v>
       </c>
       <c r="H25">
         <v>2.02</v>
       </c>
       <c r="I25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J25">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>1.16</v>
@@ -6863,40 +6863,40 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="O25">
         <v>1.07</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R25">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="S25">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T25">
         <v>1.28</v>
       </c>
       <c r="U25">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="V25">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X25">
         <v>65</v>
       </c>
       <c r="Y25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Z25">
         <v>29</v>
@@ -6905,7 +6905,7 @@
         <v>34</v>
       </c>
       <c r="AB25">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AC25">
         <v>15.5</v>
@@ -6914,10 +6914,10 @@
         <v>14</v>
       </c>
       <c r="AE25">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF25">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AG25">
         <v>18.5</v>
@@ -6929,28 +6929,28 @@
         <v>19.5</v>
       </c>
       <c r="AJ25">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK25">
         <v>30</v>
       </c>
       <c r="AL25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM25">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AN25">
         <v>11</v>
       </c>
       <c r="AO25">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AP25">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AQ25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR25">
         <v>23</v>
@@ -6959,7 +6959,7 @@
         <v>29</v>
       </c>
       <c r="AT25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU25">
         <v>13.5</v>
@@ -6971,34 +6971,34 @@
         <v>16</v>
       </c>
       <c r="AX25">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY25">
         <v>16.5</v>
       </c>
       <c r="AZ25">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA25">
         <v>17.5</v>
       </c>
       <c r="BB25">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC25">
         <v>25</v>
       </c>
       <c r="BD25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE25">
         <v>28</v>
       </c>
       <c r="BF25">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG25">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH25">
         <v>7.2</v>
@@ -7016,7 +7016,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25">
         <v>8.4</v>
@@ -7028,13 +7028,13 @@
         <v>20</v>
       </c>
       <c r="BQ25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR25">
         <v>20</v>
       </c>
       <c r="BS25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT25">
         <v>6.8</v>
@@ -7043,7 +7043,7 @@
         <v>5.6</v>
       </c>
       <c r="BV25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW25">
         <v>9.6</v>
@@ -7052,7 +7052,7 @@
         <v>16</v>
       </c>
       <c r="BY25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ25">
         <v>8</v>
@@ -7081,58 +7081,58 @@
         <v>200</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G26">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H26">
         <v>3.35</v>
       </c>
       <c r="I26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J26">
         <v>3.75</v>
       </c>
       <c r="K26">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M26">
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O26">
         <v>1.22</v>
       </c>
       <c r="P26">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R26">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S26">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T26">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U26">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X26">
         <v>21</v>
@@ -7144,34 +7144,34 @@
         <v>26</v>
       </c>
       <c r="AA26">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC26">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF26">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG26">
         <v>11</v>
       </c>
       <c r="AH26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI26">
         <v>38</v>
       </c>
       <c r="AJ26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK26">
         <v>21</v>
@@ -7183,7 +7183,7 @@
         <v>60</v>
       </c>
       <c r="AN26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO26">
         <v>23</v>
@@ -7192,13 +7192,13 @@
         <v>19</v>
       </c>
       <c r="AQ26">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
         <v>24</v>
       </c>
       <c r="AS26">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT26">
         <v>12.5</v>
@@ -7210,16 +7210,16 @@
         <v>13</v>
       </c>
       <c r="AW26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX26">
         <v>15.5</v>
       </c>
       <c r="AY26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA26">
         <v>34</v>
@@ -7234,13 +7234,13 @@
         <v>26</v>
       </c>
       <c r="BE26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF26">
         <v>11.5</v>
       </c>
       <c r="BG26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BH26">
         <v>4.2</v>
@@ -7252,13 +7252,13 @@
         <v>9</v>
       </c>
       <c r="BK26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL26">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN26">
         <v>5.6</v>
@@ -7270,13 +7270,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR26">
         <v>25</v>
       </c>
       <c r="BS26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26">
         <v>7</v>
@@ -7291,7 +7291,7 @@
         <v>8</v>
       </c>
       <c r="BX26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY26">
         <v>8.6</v>
@@ -7326,7 +7326,7 @@
         <v>2.38</v>
       </c>
       <c r="G27">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H27">
         <v>3.1</v>
@@ -7365,22 +7365,22 @@
         <v>3.15</v>
       </c>
       <c r="T27">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U27">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V27">
         <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X27">
         <v>17</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z27">
         <v>23</v>
@@ -7392,7 +7392,7 @@
         <v>12</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD27">
         <v>13.5</v>
@@ -7404,7 +7404,7 @@
         <v>17</v>
       </c>
       <c r="AG27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
         <v>16</v>
@@ -7413,7 +7413,7 @@
         <v>42</v>
       </c>
       <c r="AJ27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK27">
         <v>25</v>
@@ -7425,7 +7425,7 @@
         <v>80</v>
       </c>
       <c r="AN27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO27">
         <v>30</v>
@@ -7452,7 +7452,7 @@
         <v>12</v>
       </c>
       <c r="AW27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX27">
         <v>15</v>
@@ -7464,10 +7464,10 @@
         <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC27">
         <v>21</v>
@@ -7482,67 +7482,67 @@
         <v>15</v>
       </c>
       <c r="BG27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH27">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI27">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ27">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK27">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN27">
         <v>5.5</v>
       </c>
       <c r="BO27">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ27">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BR27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS27">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT27">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU27">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV27">
         <v>25</v>
       </c>
       <c r="BW27">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX27">
         <v>34</v>
       </c>
       <c r="BY27">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ27">
         <v>23</v>
       </c>
       <c r="CA27">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="CB27" t="s">
         <v>221</v>
@@ -7565,82 +7565,82 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="G28">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="H28">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K28">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="L28">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M28">
         <v>1.03</v>
       </c>
       <c r="N28">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S28">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T28">
         <v>1.72</v>
       </c>
       <c r="U28">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W28">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="X28">
+        <v>29</v>
+      </c>
+      <c r="Y28">
         <v>32</v>
       </c>
-      <c r="Y28">
-        <v>34</v>
-      </c>
       <c r="Z28">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AA28">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AB28">
+        <v>12</v>
+      </c>
+      <c r="AC28">
         <v>12.5</v>
       </c>
-      <c r="AC28">
-        <v>13</v>
-      </c>
       <c r="AD28">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE28">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AF28">
         <v>11.5</v>
@@ -7649,13 +7649,13 @@
         <v>11.5</v>
       </c>
       <c r="AH28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI28">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK28">
         <v>15.5</v>
@@ -7664,19 +7664,19 @@
         <v>32</v>
       </c>
       <c r="AM28">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="AN28">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AO28">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP28">
         <v>21</v>
       </c>
       <c r="AQ28">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AR28">
         <v>6.8</v>
@@ -7688,103 +7688,103 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU28">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AW28">
         <v>7</v>
       </c>
       <c r="AX28">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY28">
         <v>8.6</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA28">
         <v>7</v>
       </c>
       <c r="BB28">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BC28">
         <v>11.5</v>
       </c>
       <c r="BD28">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BE28">
         <v>7</v>
       </c>
       <c r="BF28">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG28">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH28">
+        <v>4.7</v>
+      </c>
+      <c r="BI28">
+        <v>3.55</v>
+      </c>
+      <c r="BJ28">
+        <v>11</v>
+      </c>
+      <c r="BK28">
         <v>4.9</v>
       </c>
-      <c r="BI28">
-        <v>3.7</v>
-      </c>
-      <c r="BJ28">
-        <v>11.5</v>
-      </c>
-      <c r="BK28">
-        <v>4.6</v>
-      </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BN28">
         <v>4.5</v>
       </c>
       <c r="BO28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP28">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BQ28">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BR28">
         <v>22</v>
       </c>
       <c r="BS28">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BT28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU28">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX28">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA28">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CB28" t="s">
         <v>221</v>
@@ -7807,220 +7807,220 @@
         <v>203</v>
       </c>
       <c r="F29">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="G29">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="H29">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="I29">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="J29">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="K29">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L29">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="M29">
+        <v>1.13</v>
+      </c>
+      <c r="N29">
+        <v>2.46</v>
+      </c>
+      <c r="O29">
+        <v>1.57</v>
+      </c>
+      <c r="P29">
+        <v>1.51</v>
+      </c>
+      <c r="Q29">
+        <v>2.66</v>
+      </c>
+      <c r="R29">
         <v>1.17</v>
       </c>
-      <c r="N29">
-        <v>2.14</v>
-      </c>
-      <c r="O29">
-        <v>1.71</v>
-      </c>
-      <c r="P29">
-        <v>1.37</v>
-      </c>
-      <c r="Q29">
-        <v>3.2</v>
-      </c>
-      <c r="R29">
-        <v>1.12</v>
-      </c>
       <c r="S29">
+        <v>5.5</v>
+      </c>
+      <c r="T29">
+        <v>2.12</v>
+      </c>
+      <c r="U29">
+        <v>1.74</v>
+      </c>
+      <c r="V29">
+        <v>1.43</v>
+      </c>
+      <c r="W29">
+        <v>1.51</v>
+      </c>
+      <c r="X29">
+        <v>8.6</v>
+      </c>
+      <c r="Y29">
+        <v>9.4</v>
+      </c>
+      <c r="Z29">
+        <v>23</v>
+      </c>
+      <c r="AA29">
+        <v>85</v>
+      </c>
+      <c r="AB29">
+        <v>8.6</v>
+      </c>
+      <c r="AC29">
         <v>7.4</v>
       </c>
-      <c r="T29">
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
+        <v>55</v>
+      </c>
+      <c r="AF29">
+        <v>18.5</v>
+      </c>
+      <c r="AG29">
+        <v>15</v>
+      </c>
+      <c r="AH29">
+        <v>27</v>
+      </c>
+      <c r="AI29">
+        <v>90</v>
+      </c>
+      <c r="AJ29">
+        <v>55</v>
+      </c>
+      <c r="AK29">
+        <v>48</v>
+      </c>
+      <c r="AL29">
+        <v>80</v>
+      </c>
+      <c r="AM29">
+        <v>210</v>
+      </c>
+      <c r="AN29">
+        <v>60</v>
+      </c>
+      <c r="AO29">
+        <v>75</v>
+      </c>
+      <c r="AP29">
+        <v>6.8</v>
+      </c>
+      <c r="AQ29">
+        <v>7.4</v>
+      </c>
+      <c r="AR29">
+        <v>16</v>
+      </c>
+      <c r="AS29">
+        <v>6.8</v>
+      </c>
+      <c r="AT29">
+        <v>7</v>
+      </c>
+      <c r="AU29">
+        <v>5.8</v>
+      </c>
+      <c r="AV29">
+        <v>12.5</v>
+      </c>
+      <c r="AW29">
+        <v>6.6</v>
+      </c>
+      <c r="AX29">
+        <v>14</v>
+      </c>
+      <c r="AY29">
+        <v>11.5</v>
+      </c>
+      <c r="AZ29">
+        <v>19</v>
+      </c>
+      <c r="BA29">
+        <v>7</v>
+      </c>
+      <c r="BB29">
+        <v>34</v>
+      </c>
+      <c r="BC29">
+        <v>7.6</v>
+      </c>
+      <c r="BD29">
+        <v>7</v>
+      </c>
+      <c r="BE29">
+        <v>7.4</v>
+      </c>
+      <c r="BF29">
+        <v>36</v>
+      </c>
+      <c r="BG29">
+        <v>7</v>
+      </c>
+      <c r="BH29">
+        <v>2.8</v>
+      </c>
+      <c r="BI29">
         <v>2.4</v>
       </c>
-      <c r="U29">
-        <v>1.57</v>
-      </c>
-      <c r="V29">
-        <v>1.61</v>
-      </c>
-      <c r="W29">
-        <v>1.31</v>
-      </c>
-      <c r="X29">
-        <v>6.8</v>
-      </c>
-      <c r="Y29">
-        <v>6.8</v>
-      </c>
-      <c r="Z29">
-        <v>14.5</v>
-      </c>
-      <c r="AA29">
-        <v>150</v>
-      </c>
-      <c r="AB29">
-        <v>9.6</v>
-      </c>
-      <c r="AC29">
-        <v>7.6</v>
-      </c>
-      <c r="AD29">
-        <v>14.5</v>
-      </c>
-      <c r="AE29">
-        <v>140</v>
-      </c>
-      <c r="AF29">
-        <v>28</v>
-      </c>
-      <c r="AG29">
-        <v>21</v>
-      </c>
-      <c r="AH29">
-        <v>38</v>
-      </c>
-      <c r="AI29">
-        <v>460</v>
-      </c>
-      <c r="AJ29">
-        <v>230</v>
-      </c>
-      <c r="AK29">
-        <v>240</v>
-      </c>
-      <c r="AL29">
-        <v>540</v>
-      </c>
-      <c r="AM29">
-        <v>370</v>
-      </c>
-      <c r="AN29">
-        <v>600</v>
-      </c>
-      <c r="AO29">
-        <v>600</v>
-      </c>
-      <c r="AP29">
-        <v>3.85</v>
-      </c>
-      <c r="AQ29">
-        <v>5.1</v>
-      </c>
-      <c r="AR29">
+      <c r="BJ29">
+        <v>12</v>
+      </c>
+      <c r="BK29">
         <v>5.5</v>
       </c>
-      <c r="AS29">
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN29">
+        <v>5.5</v>
+      </c>
+      <c r="BO29">
+        <v>4.5</v>
+      </c>
+      <c r="BP29">
+        <v>26</v>
+      </c>
+      <c r="BQ29">
         <v>7.4</v>
       </c>
-      <c r="AT29">
-        <v>7.6</v>
-      </c>
-      <c r="AU29">
-        <v>6</v>
-      </c>
-      <c r="AV29">
-        <v>5.5</v>
-      </c>
-      <c r="AW29">
-        <v>7.4</v>
-      </c>
-      <c r="AX29">
-        <v>6.8</v>
-      </c>
-      <c r="AY29">
-        <v>16</v>
-      </c>
-      <c r="AZ29">
-        <v>7</v>
-      </c>
-      <c r="BA29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC29">
-        <v>8</v>
-      </c>
-      <c r="BD29">
-        <v>8.4</v>
-      </c>
-      <c r="BE29">
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
         <v>8.6</v>
       </c>
-      <c r="BF29">
-        <v>8.4</v>
-      </c>
-      <c r="BG29">
+      <c r="BT29">
+        <v>6.6</v>
+      </c>
+      <c r="BU29">
+        <v>5.2</v>
+      </c>
+      <c r="BV29">
+        <v>32</v>
+      </c>
+      <c r="BW29">
         <v>7.8</v>
       </c>
-      <c r="BH29">
-        <v>2.46</v>
-      </c>
-      <c r="BI29">
-        <v>2.04</v>
-      </c>
-      <c r="BJ29">
-        <v>13.5</v>
-      </c>
-      <c r="BK29">
-        <v>6</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>10.5</v>
-      </c>
-      <c r="BN29">
-        <v>7.4</v>
-      </c>
-      <c r="BO29">
-        <v>5.4</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>9.6</v>
-      </c>
-      <c r="BT29">
-        <v>5.3</v>
-      </c>
-      <c r="BU29">
-        <v>4</v>
-      </c>
-      <c r="BV29">
-        <v>26</v>
-      </c>
-      <c r="BW29">
-        <v>7.6</v>
-      </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8049,40 +8049,40 @@
         <v>204</v>
       </c>
       <c r="F30">
+        <v>2.16</v>
+      </c>
+      <c r="G30">
+        <v>2.68</v>
+      </c>
+      <c r="H30">
+        <v>3.55</v>
+      </c>
+      <c r="I30">
+        <v>4.8</v>
+      </c>
+      <c r="J30">
+        <v>2.62</v>
+      </c>
+      <c r="K30">
+        <v>3.4</v>
+      </c>
+      <c r="L30">
+        <v>1.61</v>
+      </c>
+      <c r="M30">
+        <v>1.14</v>
+      </c>
+      <c r="N30">
         <v>2.22</v>
-      </c>
-      <c r="G30">
-        <v>2.72</v>
-      </c>
-      <c r="H30">
-        <v>3.4</v>
-      </c>
-      <c r="I30">
-        <v>4.5</v>
-      </c>
-      <c r="J30">
-        <v>2.74</v>
-      </c>
-      <c r="K30">
-        <v>3.35</v>
-      </c>
-      <c r="L30">
-        <v>1.56</v>
-      </c>
-      <c r="M30">
-        <v>1.15</v>
-      </c>
-      <c r="N30">
-        <v>2.24</v>
       </c>
       <c r="O30">
         <v>1.62</v>
       </c>
       <c r="P30">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Q30">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R30">
         <v>1.14</v>
@@ -8091,133 +8091,133 @@
         <v>3.45</v>
       </c>
       <c r="T30">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U30">
         <v>1.56</v>
       </c>
       <c r="V30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W30">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X30">
         <v>7.8</v>
       </c>
       <c r="Y30">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA30">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB30">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC30">
         <v>8</v>
       </c>
       <c r="AD30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE30">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AF30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG30">
         <v>15</v>
       </c>
       <c r="AH30">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI30">
         <v>150</v>
       </c>
       <c r="AJ30">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AK30">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL30">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="AM30">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AN30">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AO30">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="AP30">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AQ30">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AR30">
+        <v>4.6</v>
+      </c>
+      <c r="AS30">
+        <v>5.1</v>
+      </c>
+      <c r="AT30">
+        <v>3.05</v>
+      </c>
+      <c r="AU30">
+        <v>3.2</v>
+      </c>
+      <c r="AV30">
+        <v>4.3</v>
+      </c>
+      <c r="AW30">
+        <v>5</v>
+      </c>
+      <c r="AX30">
+        <v>3.9</v>
+      </c>
+      <c r="AY30">
+        <v>3.9</v>
+      </c>
+      <c r="AZ30">
+        <v>4.6</v>
+      </c>
+      <c r="BA30">
+        <v>5.1</v>
+      </c>
+      <c r="BB30">
+        <v>4.7</v>
+      </c>
+      <c r="BC30">
+        <v>4.8</v>
+      </c>
+      <c r="BD30">
+        <v>5</v>
+      </c>
+      <c r="BE30">
+        <v>5.2</v>
+      </c>
+      <c r="BF30">
         <v>4.9</v>
       </c>
-      <c r="AS30">
-        <v>5.6</v>
-      </c>
-      <c r="AT30">
-        <v>3.3</v>
-      </c>
-      <c r="AU30">
-        <v>3.4</v>
-      </c>
-      <c r="AV30">
-        <v>4.6</v>
-      </c>
-      <c r="AW30">
-        <v>5.5</v>
-      </c>
-      <c r="AX30">
-        <v>4.3</v>
-      </c>
-      <c r="AY30">
-        <v>4.2</v>
-      </c>
-      <c r="AZ30">
-        <v>5</v>
-      </c>
-      <c r="BA30">
-        <v>5.7</v>
-      </c>
-      <c r="BB30">
-        <v>5.2</v>
-      </c>
-      <c r="BC30">
-        <v>5.3</v>
-      </c>
-      <c r="BD30">
-        <v>5.6</v>
-      </c>
-      <c r="BE30">
-        <v>5.8</v>
-      </c>
-      <c r="BF30">
-        <v>5.4</v>
-      </c>
       <c r="BG30">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH30">
         <v>2.64</v>
       </c>
       <c r="BI30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK30">
         <v>4.6</v>
@@ -8226,34 +8226,34 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BN30">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO30">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ30">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU30">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW30">
         <v>6</v>
@@ -8262,13 +8262,13 @@
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.88</v>
+        <v>6.2</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.87</v>
+        <v>6.2</v>
       </c>
       <c r="CB30" t="s">
         <v>221</v>
@@ -8291,13 +8291,13 @@
         <v>205</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H31">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I31">
         <v>2.56</v>
@@ -8306,34 +8306,34 @@
         <v>3.35</v>
       </c>
       <c r="K31">
+        <v>3.65</v>
+      </c>
+      <c r="L31">
+        <v>1.45</v>
+      </c>
+      <c r="M31">
+        <v>1.08</v>
+      </c>
+      <c r="N31">
         <v>3.6</v>
       </c>
-      <c r="L31">
-        <v>1.44</v>
-      </c>
-      <c r="M31">
-        <v>1.07</v>
-      </c>
-      <c r="N31">
-        <v>3.7</v>
-      </c>
       <c r="O31">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P31">
         <v>1.87</v>
       </c>
       <c r="Q31">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R31">
         <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T31">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U31">
         <v>2.1</v>
@@ -8348,19 +8348,19 @@
         <v>14</v>
       </c>
       <c r="Y31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z31">
         <v>16.5</v>
       </c>
       <c r="AA31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31">
         <v>12</v>
@@ -8375,7 +8375,7 @@
         <v>14.5</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI31">
         <v>42</v>
@@ -8384,31 +8384,31 @@
         <v>60</v>
       </c>
       <c r="AK31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL31">
         <v>55</v>
       </c>
       <c r="AM31">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO31">
         <v>24</v>
       </c>
       <c r="AP31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ31">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
@@ -8417,13 +8417,13 @@
         <v>6.8</v>
       </c>
       <c r="AV31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX31">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY31">
         <v>11.5</v>
@@ -8435,22 +8435,22 @@
         <v>32</v>
       </c>
       <c r="BB31">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BC31">
         <v>27</v>
       </c>
       <c r="BD31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE31">
         <v>70</v>
       </c>
       <c r="BF31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BG31">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH31">
         <v>3.35</v>
@@ -8533,109 +8533,109 @@
         <v>206</v>
       </c>
       <c r="F32">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G32">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I32">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K32">
         <v>4.3</v>
       </c>
       <c r="L32">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M32">
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O32">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q32">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R32">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S32">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T32">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U32">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X32">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z32">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA32">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB32">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC32">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD32">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE32">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF32">
         <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH32">
         <v>19</v>
       </c>
       <c r="AI32">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AJ32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK32">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL32">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AM32">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO32">
         <v>75</v>
@@ -8644,61 +8644,61 @@
         <v>16.5</v>
       </c>
       <c r="AQ32">
+        <v>20</v>
+      </c>
+      <c r="AR32">
+        <v>36</v>
+      </c>
+      <c r="AS32">
+        <v>13.5</v>
+      </c>
+      <c r="AT32">
+        <v>9</v>
+      </c>
+      <c r="AU32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>17.5</v>
+      </c>
+      <c r="AW32">
+        <v>50</v>
+      </c>
+      <c r="AX32">
+        <v>10</v>
+      </c>
+      <c r="AY32">
+        <v>9</v>
+      </c>
+      <c r="AZ32">
         <v>17</v>
-      </c>
-      <c r="AR32">
-        <v>34</v>
-      </c>
-      <c r="AS32">
-        <v>10.5</v>
-      </c>
-      <c r="AT32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU32">
-        <v>8</v>
-      </c>
-      <c r="AV32">
-        <v>17</v>
-      </c>
-      <c r="AW32">
-        <v>46</v>
-      </c>
-      <c r="AX32">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ32">
-        <v>16</v>
       </c>
       <c r="BA32">
         <v>44</v>
       </c>
       <c r="BB32">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE32">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF32">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG32">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI32">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ32">
         <v>9.6</v>
@@ -8710,7 +8710,7 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN32">
         <v>4.5</v>
@@ -8719,40 +8719,40 @@
         <v>4.1</v>
       </c>
       <c r="BP32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT32">
         <v>8.4</v>
       </c>
       <c r="BU32">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="CB32" t="s">
         <v>221</v>
@@ -8775,19 +8775,19 @@
         <v>207</v>
       </c>
       <c r="F33">
+        <v>1.2</v>
+      </c>
+      <c r="G33">
         <v>1.21</v>
       </c>
-      <c r="G33">
-        <v>1.22</v>
-      </c>
       <c r="H33">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="I33">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="J33">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -8808,7 +8808,7 @@
         <v>3.55</v>
       </c>
       <c r="Q33">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R33">
         <v>2.02</v>
@@ -8817,16 +8817,16 @@
         <v>1.95</v>
       </c>
       <c r="T33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W33">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="X33">
         <v>48</v>
@@ -8835,52 +8835,52 @@
         <v>80</v>
       </c>
       <c r="Z33">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD33">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE33">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AF33">
         <v>9.6</v>
       </c>
       <c r="AG33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI33">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ33">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL33">
         <v>32</v>
       </c>
       <c r="AM33">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AO33">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
         <v>40</v>
@@ -8889,22 +8889,22 @@
         <v>70</v>
       </c>
       <c r="AR33">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS33">
-        <v>22</v>
+        <v>400</v>
       </c>
       <c r="AT33">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU33">
         <v>18</v>
       </c>
       <c r="AV33">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW33">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AX33">
         <v>9.199999999999999</v>
@@ -8916,37 +8916,37 @@
         <v>32</v>
       </c>
       <c r="BA33">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BB33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD33">
         <v>29</v>
       </c>
       <c r="BE33">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="BF33">
         <v>2.96</v>
       </c>
       <c r="BG33">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BH33">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BJ33">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -8955,40 +8955,40 @@
         <v>70</v>
       </c>
       <c r="BN33">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BP33">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>0</v>
@@ -9017,22 +9017,22 @@
         <v>208</v>
       </c>
       <c r="F34">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G34">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H34">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I34">
-        <v>9.199999999999999</v>
+        <v>990</v>
       </c>
       <c r="J34">
-        <v>2.96</v>
+        <v>1.1</v>
       </c>
       <c r="K34">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9044,13 +9044,13 @@
         <v>1.71</v>
       </c>
       <c r="O34">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P34">
         <v>1.71</v>
       </c>
       <c r="Q34">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="R34">
         <v>1.26</v>
@@ -9068,52 +9068,52 @@
         <v>1.31</v>
       </c>
       <c r="W34">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X34">
         <v>19</v>
       </c>
       <c r="Y34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z34">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA34">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE34">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF34">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AG34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH34">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK34">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL34">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM34">
         <v>1000</v>
@@ -9125,58 +9125,58 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AR34">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AS34">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AT34">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AU34">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AV34">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AW34">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AX34">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="AY34">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AZ34">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="BA34">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="BB34">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="BC34">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="BD34">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="BE34">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="BF34">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="BG34">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="BH34">
         <v>3.9</v>
@@ -9188,55 +9188,55 @@
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="CB34" t="s">
         <v>221</v>
@@ -9259,19 +9259,19 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G35">
         <v>1.62</v>
       </c>
       <c r="H35">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>8.4</v>
       </c>
       <c r="J35">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K35">
         <v>4.3</v>
@@ -9280,13 +9280,13 @@
         <v>1.46</v>
       </c>
       <c r="M35">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O35">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P35">
         <v>1.78</v>
@@ -9307,19 +9307,19 @@
         <v>1.75</v>
       </c>
       <c r="V35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W35">
         <v>2.6</v>
       </c>
       <c r="X35">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y35">
         <v>24</v>
       </c>
       <c r="Z35">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AA35">
         <v>300</v>
@@ -9355,10 +9355,10 @@
         <v>22</v>
       </c>
       <c r="AL35">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM35">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AN35">
         <v>13.5</v>
@@ -9373,19 +9373,19 @@
         <v>5.4</v>
       </c>
       <c r="AR35">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS35">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT35">
         <v>6</v>
       </c>
       <c r="AU35">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV35">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW35">
         <v>6</v>
@@ -9397,7 +9397,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ35">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA35">
         <v>6</v>
@@ -9406,73 +9406,73 @@
         <v>12.5</v>
       </c>
       <c r="BC35">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BD35">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE35">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG35">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH35">
         <v>3.25</v>
       </c>
       <c r="BI35">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BJ35">
         <v>12</v>
       </c>
       <c r="BK35">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BN35">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO35">
         <v>3.15</v>
       </c>
       <c r="BP35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ35">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT35">
         <v>11</v>
       </c>
       <c r="BU35">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         <v>4.9</v>
       </c>
       <c r="I36">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J36">
         <v>3.55</v>
@@ -9546,7 +9546,7 @@
         <v>1.94</v>
       </c>
       <c r="U36">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V36">
         <v>1.21</v>
@@ -9564,7 +9564,7 @@
         <v>46</v>
       </c>
       <c r="AA36">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB36">
         <v>8.199999999999999</v>
@@ -9576,10 +9576,10 @@
         <v>21</v>
       </c>
       <c r="AE36">
-        <v>470</v>
+        <v>95</v>
       </c>
       <c r="AF36">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG36">
         <v>11</v>
@@ -9588,7 +9588,7 @@
         <v>26</v>
       </c>
       <c r="AI36">
-        <v>370</v>
+        <v>110</v>
       </c>
       <c r="AJ36">
         <v>21</v>
@@ -9600,13 +9600,13 @@
         <v>55</v>
       </c>
       <c r="AM36">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN36">
         <v>15</v>
       </c>
       <c r="AO36">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP36">
         <v>10.5</v>
@@ -9618,7 +9618,7 @@
         <v>32</v>
       </c>
       <c r="AS36">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT36">
         <v>6.8</v>
@@ -9654,31 +9654,31 @@
         <v>29</v>
       </c>
       <c r="BE36">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF36">
         <v>12</v>
       </c>
       <c r="BG36">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH36">
         <v>3.35</v>
       </c>
       <c r="BI36">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ36">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK36">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN36">
         <v>4.5</v>
@@ -9690,13 +9690,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ36">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT36">
         <v>9</v>
@@ -9708,19 +9708,19 @@
         <v>55</v>
       </c>
       <c r="BW36">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB36" t="s">
         <v>221</v>
@@ -9749,13 +9749,13 @@
         <v>2.44</v>
       </c>
       <c r="H37">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I37">
         <v>2.8</v>
       </c>
       <c r="J37">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K37">
         <v>4.9</v>
@@ -9767,22 +9767,22 @@
         <v>1.02</v>
       </c>
       <c r="N37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O37">
         <v>1.09</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R37">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T37">
         <v>1.32</v>
@@ -9791,13 +9791,13 @@
         <v>3.75</v>
       </c>
       <c r="V37">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X37">
-        <v>140</v>
+        <v>940</v>
       </c>
       <c r="Y37">
         <v>55</v>
@@ -9806,16 +9806,16 @@
         <v>60</v>
       </c>
       <c r="AA37">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AB37">
         <v>50</v>
       </c>
       <c r="AC37">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD37">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE37">
         <v>25</v>
@@ -9845,28 +9845,28 @@
         <v>55</v>
       </c>
       <c r="AN37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO37">
         <v>9.199999999999999</v>
       </c>
       <c r="AP37">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AQ37">
         <v>27</v>
       </c>
       <c r="AR37">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS37">
         <v>26</v>
       </c>
       <c r="AT37">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AU37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV37">
         <v>13</v>
@@ -9899,13 +9899,13 @@
         <v>22</v>
       </c>
       <c r="BF37">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG37">
         <v>8.199999999999999</v>
       </c>
       <c r="BH37">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI37">
         <v>5.2</v>
@@ -9914,16 +9914,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK37">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL37">
         <v>44</v>
       </c>
       <c r="BM37">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN37">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO37">
         <v>5.4</v>
@@ -9932,37 +9932,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR37">
         <v>18</v>
       </c>
       <c r="BS37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT37">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU37">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV37">
         <v>17.5</v>
       </c>
       <c r="BW37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX37">
         <v>19</v>
       </c>
       <c r="BY37">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ37">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CA37">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="CB37" t="s">
         <v>221</v>
@@ -9988,10 +9988,10 @@
         <v>3.7</v>
       </c>
       <c r="G38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H38">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I38">
         <v>2.42</v>
@@ -10006,16 +10006,16 @@
         <v>1.58</v>
       </c>
       <c r="M38">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N38">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P38">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q38">
         <v>2.66</v>
@@ -10027,7 +10027,7 @@
         <v>5.5</v>
       </c>
       <c r="T38">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U38">
         <v>1.81</v>
@@ -10093,7 +10093,7 @@
         <v>34</v>
       </c>
       <c r="AP38">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ38">
         <v>7</v>
@@ -10126,10 +10126,10 @@
         <v>22</v>
       </c>
       <c r="BA38">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB38">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC38">
         <v>50</v>
@@ -10138,7 +10138,7 @@
         <v>36</v>
       </c>
       <c r="BE38">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="BF38">
         <v>65</v>
@@ -10147,10 +10147,10 @@
         <v>29</v>
       </c>
       <c r="BH38">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ38">
         <v>11</v>
@@ -10177,7 +10177,7 @@
         <v>12</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS38">
         <v>14</v>
@@ -10189,10 +10189,10 @@
         <v>4.5</v>
       </c>
       <c r="BV38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW38">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX38">
         <v>1000</v>
@@ -10201,10 +10201,10 @@
         <v>13</v>
       </c>
       <c r="BZ38">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="CA38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB38" t="s">
         <v>221</v>
@@ -10227,40 +10227,40 @@
         <v>213</v>
       </c>
       <c r="F39">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G39">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H39">
         <v>3.05</v>
       </c>
       <c r="I39">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J39">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K39">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="L39">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N39">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O39">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="P39">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q39">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R39">
         <v>1.15</v>
@@ -10269,7 +10269,7 @@
         <v>6.4</v>
       </c>
       <c r="T39">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U39">
         <v>1.71</v>
@@ -10278,19 +10278,19 @@
         <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X39">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y39">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z39">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA39">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="AB39">
         <v>8</v>
@@ -10302,19 +10302,19 @@
         <v>16</v>
       </c>
       <c r="AE39">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AF39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG39">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH39">
         <v>27</v>
       </c>
       <c r="AI39">
-        <v>450</v>
+        <v>95</v>
       </c>
       <c r="AJ39">
         <v>60</v>
@@ -10323,28 +10323,28 @@
         <v>55</v>
       </c>
       <c r="AL39">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AM39">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN39">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AO39">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ39">
         <v>7</v>
       </c>
       <c r="AR39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS39">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT39">
         <v>6.8</v>
@@ -10353,49 +10353,49 @@
         <v>5.9</v>
       </c>
       <c r="AV39">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW39">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX39">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY39">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ39">
         <v>19</v>
       </c>
       <c r="BA39">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BB39">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC39">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BD39">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BE39">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF39">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG39">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH39">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BI39">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="BJ39">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK39">
         <v>9.4</v>
@@ -10404,28 +10404,28 @@
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN39">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO39">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP39">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ39">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BT39">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU39">
         <v>5.1</v>
@@ -10434,13 +10434,13 @@
         <v>32</v>
       </c>
       <c r="BW39">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ39">
         <v>0</v>
@@ -10469,22 +10469,22 @@
         <v>214</v>
       </c>
       <c r="F40">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G40">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="H40">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="I40">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="J40">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K40">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L40">
         <v>1.39</v>
@@ -10493,34 +10493,34 @@
         <v>1.06</v>
       </c>
       <c r="N40">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O40">
         <v>1.3</v>
       </c>
       <c r="P40">
+        <v>1.92</v>
+      </c>
+      <c r="Q40">
         <v>1.9</v>
       </c>
-      <c r="Q40">
-        <v>1.92</v>
-      </c>
       <c r="R40">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T40">
         <v>1.75</v>
       </c>
       <c r="U40">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X40">
         <v>15.5</v>
@@ -10529,160 +10529,160 @@
         <v>11</v>
       </c>
       <c r="Z40">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA40">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB40">
+        <v>15</v>
+      </c>
+      <c r="AC40">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD40">
+        <v>12.5</v>
+      </c>
+      <c r="AE40">
+        <v>25</v>
+      </c>
+      <c r="AF40">
+        <v>30</v>
+      </c>
+      <c r="AG40">
         <v>16</v>
-      </c>
-      <c r="AC40">
-        <v>8.6</v>
-      </c>
-      <c r="AD40">
-        <v>14</v>
-      </c>
-      <c r="AE40">
-        <v>27</v>
-      </c>
-      <c r="AF40">
-        <v>24</v>
-      </c>
-      <c r="AG40">
-        <v>14.5</v>
       </c>
       <c r="AH40">
         <v>18</v>
       </c>
       <c r="AI40">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ40">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AK40">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL40">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM40">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AN40">
         <v>40</v>
       </c>
       <c r="AO40">
+        <v>19</v>
+      </c>
+      <c r="AP40">
+        <v>12.5</v>
+      </c>
+      <c r="AQ40">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR40">
+        <v>12.5</v>
+      </c>
+      <c r="AS40">
+        <v>23</v>
+      </c>
+      <c r="AT40">
+        <v>11.5</v>
+      </c>
+      <c r="AU40">
+        <v>7.2</v>
+      </c>
+      <c r="AV40">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW40">
+        <v>20</v>
+      </c>
+      <c r="AX40">
         <v>21</v>
       </c>
-      <c r="AP40">
-        <v>12</v>
-      </c>
-      <c r="AQ40">
-        <v>5.6</v>
-      </c>
-      <c r="AR40">
-        <v>5.2</v>
-      </c>
-      <c r="AS40">
-        <v>11.5</v>
-      </c>
-      <c r="AT40">
-        <v>11</v>
-      </c>
-      <c r="AU40">
-        <v>6.8</v>
-      </c>
-      <c r="AV40">
-        <v>6.2</v>
-      </c>
-      <c r="AW40">
-        <v>21</v>
-      </c>
-      <c r="AX40">
-        <v>19.5</v>
-      </c>
       <c r="AY40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ40">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BA40">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BB40">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="BC40">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BD40">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BE40">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="BF40">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BG40">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH40">
         <v>3.6</v>
       </c>
       <c r="BI40">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ40">
         <v>9.800000000000001</v>
       </c>
       <c r="BK40">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN40">
         <v>6.8</v>
       </c>
       <c r="BO40">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP40">
         <v>27</v>
       </c>
       <c r="BQ40">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR40">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS40">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT40">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU40">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV40">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW40">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX40">
         <v>32</v>
       </c>
       <c r="BY40">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10717,121 +10717,121 @@
         <v>4.6</v>
       </c>
       <c r="H41">
+        <v>2.06</v>
+      </c>
+      <c r="I41">
+        <v>2.16</v>
+      </c>
+      <c r="J41">
+        <v>3.2</v>
+      </c>
+      <c r="K41">
+        <v>3.5</v>
+      </c>
+      <c r="L41">
+        <v>1.53</v>
+      </c>
+      <c r="M41">
+        <v>1.11</v>
+      </c>
+      <c r="N41">
+        <v>2.98</v>
+      </c>
+      <c r="O41">
+        <v>1.46</v>
+      </c>
+      <c r="P41">
+        <v>1.65</v>
+      </c>
+      <c r="Q41">
+        <v>2.38</v>
+      </c>
+      <c r="R41">
+        <v>1.24</v>
+      </c>
+      <c r="S41">
+        <v>4.7</v>
+      </c>
+      <c r="T41">
         <v>2.04</v>
       </c>
-      <c r="I41">
-        <v>2.14</v>
-      </c>
-      <c r="J41">
-        <v>3.3</v>
-      </c>
-      <c r="K41">
-        <v>3.55</v>
-      </c>
-      <c r="L41">
-        <v>1.49</v>
-      </c>
-      <c r="M41">
-        <v>1.1</v>
-      </c>
-      <c r="N41">
-        <v>3.1</v>
-      </c>
-      <c r="O41">
-        <v>1.43</v>
-      </c>
-      <c r="P41">
-        <v>1.69</v>
-      </c>
-      <c r="Q41">
-        <v>2.3</v>
-      </c>
-      <c r="R41">
-        <v>1.25</v>
-      </c>
-      <c r="S41">
-        <v>4.4</v>
-      </c>
-      <c r="T41">
-        <v>1.98</v>
-      </c>
       <c r="U41">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V41">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W41">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X41">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y41">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA41">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB41">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC41">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD41">
         <v>11</v>
       </c>
       <c r="AE41">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF41">
         <v>32</v>
       </c>
       <c r="AG41">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI41">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AJ41">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK41">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="AL41">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AM41">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN41">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AO41">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP41">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ41">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR41">
         <v>10.5</v>
       </c>
       <c r="AS41">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AT41">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU41">
         <v>6.8</v>
@@ -10840,10 +10840,10 @@
         <v>9.6</v>
       </c>
       <c r="AW41">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AX41">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AY41">
         <v>15.5</v>
@@ -10852,85 +10852,85 @@
         <v>18.5</v>
       </c>
       <c r="BA41">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB41">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC41">
+        <v>23</v>
+      </c>
+      <c r="BD41">
+        <v>26</v>
+      </c>
+      <c r="BE41">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD41">
-        <v>10</v>
-      </c>
-      <c r="BE41">
-        <v>10.5</v>
-      </c>
       <c r="BF41">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG41">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH41">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BI41">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ41">
         <v>11</v>
       </c>
       <c r="BK41">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BN41">
         <v>7.6</v>
       </c>
       <c r="BO41">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP41">
         <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT41">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU41">
         <v>3.6</v>
       </c>
       <c r="BV41">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW41">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX41">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY41">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ41">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA41">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB41" t="s">
         <v>221</v>
@@ -10953,7 +10953,7 @@
         <v>216</v>
       </c>
       <c r="F42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -10962,10 +10962,10 @@
         <v>2.2</v>
       </c>
       <c r="I42">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J42">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K42">
         <v>3.65</v>
@@ -10977,13 +10977,13 @@
         <v>1.09</v>
       </c>
       <c r="N42">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O42">
         <v>1.4</v>
       </c>
       <c r="P42">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q42">
         <v>2.18</v>
@@ -10992,13 +10992,13 @@
         <v>1.25</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T42">
         <v>1.89</v>
       </c>
       <c r="U42">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V42">
         <v>1.64</v>
@@ -11007,13 +11007,13 @@
         <v>1.33</v>
       </c>
       <c r="X42">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y42">
         <v>9</v>
       </c>
       <c r="Z42">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA42">
         <v>36</v>
@@ -11025,7 +11025,7 @@
         <v>8</v>
       </c>
       <c r="AD42">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE42">
         <v>32</v>
@@ -11040,79 +11040,79 @@
         <v>21</v>
       </c>
       <c r="AI42">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ42">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AK42">
         <v>55</v>
       </c>
       <c r="AL42">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM42">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN42">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AO42">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP42">
         <v>4.7</v>
       </c>
       <c r="AQ42">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR42">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS42">
+        <v>6.2</v>
+      </c>
+      <c r="AT42">
+        <v>4.7</v>
+      </c>
+      <c r="AU42">
+        <v>3.85</v>
+      </c>
+      <c r="AV42">
+        <v>4.7</v>
+      </c>
+      <c r="AW42">
+        <v>6</v>
+      </c>
+      <c r="AX42">
+        <v>5.9</v>
+      </c>
+      <c r="AY42">
+        <v>5.1</v>
+      </c>
+      <c r="AZ42">
+        <v>5.5</v>
+      </c>
+      <c r="BA42">
         <v>6.6</v>
       </c>
-      <c r="AT42">
-        <v>4.9</v>
-      </c>
-      <c r="AU42">
-        <v>4</v>
-      </c>
-      <c r="AV42">
-        <v>4.8</v>
-      </c>
-      <c r="AW42">
-        <v>6.4</v>
-      </c>
-      <c r="AX42">
-        <v>6.2</v>
-      </c>
-      <c r="AY42">
-        <v>5.4</v>
-      </c>
-      <c r="AZ42">
+      <c r="BB42">
+        <v>6.8</v>
+      </c>
+      <c r="BC42">
+        <v>6.6</v>
+      </c>
+      <c r="BD42">
+        <v>6.8</v>
+      </c>
+      <c r="BE42">
+        <v>7.2</v>
+      </c>
+      <c r="BF42">
+        <v>6.6</v>
+      </c>
+      <c r="BG42">
         <v>5.9</v>
-      </c>
-      <c r="BA42">
-        <v>7</v>
-      </c>
-      <c r="BB42">
-        <v>7.4</v>
-      </c>
-      <c r="BC42">
-        <v>7</v>
-      </c>
-      <c r="BD42">
-        <v>7.2</v>
-      </c>
-      <c r="BE42">
-        <v>7.6</v>
-      </c>
-      <c r="BF42">
-        <v>7.2</v>
-      </c>
-      <c r="BG42">
-        <v>6.4</v>
       </c>
       <c r="BH42">
         <v>3.15</v>
@@ -11201,46 +11201,46 @@
         <v>2.82</v>
       </c>
       <c r="H43">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J43">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K43">
         <v>2.96</v>
       </c>
       <c r="L43">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M43">
         <v>1.17</v>
       </c>
       <c r="N43">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O43">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P43">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S43">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T43">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V43">
         <v>1.42</v>
@@ -11252,79 +11252,79 @@
         <v>6.8</v>
       </c>
       <c r="Y43">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z43">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA43">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AB43">
         <v>7.2</v>
       </c>
       <c r="AC43">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD43">
         <v>16.5</v>
       </c>
       <c r="AE43">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF43">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG43">
         <v>14.5</v>
       </c>
       <c r="AH43">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI43">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AJ43">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="AK43">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL43">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AM43">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AN43">
         <v>65</v>
       </c>
       <c r="AO43">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="AP43">
         <v>6.2</v>
       </c>
       <c r="AQ43">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS43">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT43">
         <v>6.6</v>
       </c>
       <c r="AU43">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV43">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW43">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX43">
         <v>14</v>
@@ -11333,46 +11333,46 @@
         <v>13</v>
       </c>
       <c r="AZ43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA43">
+        <v>40</v>
+      </c>
+      <c r="BB43">
+        <v>40</v>
+      </c>
+      <c r="BC43">
+        <v>40</v>
+      </c>
+      <c r="BD43">
+        <v>75</v>
+      </c>
+      <c r="BE43">
         <v>50</v>
       </c>
-      <c r="BB43">
-        <v>26</v>
-      </c>
-      <c r="BC43">
-        <v>38</v>
-      </c>
-      <c r="BD43">
-        <v>42</v>
-      </c>
-      <c r="BE43">
-        <v>110</v>
-      </c>
       <c r="BF43">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BG43">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH43">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BI43">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ43">
         <v>12.5</v>
       </c>
       <c r="BK43">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN43">
         <v>5.6</v>
@@ -11384,13 +11384,13 @@
         <v>28</v>
       </c>
       <c r="BQ43">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR43">
         <v>60</v>
       </c>
       <c r="BS43">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT43">
         <v>6.4</v>
@@ -11402,19 +11402,19 @@
         <v>36</v>
       </c>
       <c r="BW43">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY43">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ43">
         <v>70</v>
       </c>
       <c r="CA43">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB43" t="s">
         <v>221</v>
@@ -11437,13 +11437,13 @@
         <v>218</v>
       </c>
       <c r="F44">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G44">
         <v>2.8</v>
       </c>
       <c r="H44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I44">
         <v>3.3</v>
@@ -11458,19 +11458,19 @@
         <v>1.59</v>
       </c>
       <c r="M44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N44">
         <v>2.74</v>
       </c>
       <c r="O44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q44">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R44">
         <v>1.2</v>
@@ -11482,82 +11482,82 @@
         <v>2.12</v>
       </c>
       <c r="U44">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V44">
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X44">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y44">
         <v>9.4</v>
       </c>
       <c r="Z44">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA44">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AB44">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC44">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD44">
         <v>15.5</v>
       </c>
       <c r="AE44">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AF44">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH44">
         <v>23</v>
       </c>
       <c r="AI44">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ44">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK44">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AL44">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AM44">
         <v>1000</v>
       </c>
       <c r="AN44">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AO44">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AP44">
+        <v>7.8</v>
+      </c>
+      <c r="AQ44">
+        <v>8.6</v>
+      </c>
+      <c r="AR44">
+        <v>17.5</v>
+      </c>
+      <c r="AS44">
+        <v>50</v>
+      </c>
+      <c r="AT44">
         <v>7.6</v>
-      </c>
-      <c r="AQ44">
-        <v>8.4</v>
-      </c>
-      <c r="AR44">
-        <v>17</v>
-      </c>
-      <c r="AS44">
-        <v>32</v>
-      </c>
-      <c r="AT44">
-        <v>7.4</v>
       </c>
       <c r="AU44">
         <v>6.4</v>
@@ -11566,37 +11566,37 @@
         <v>13.5</v>
       </c>
       <c r="AW44">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AX44">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ44">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA44">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB44">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BC44">
+        <v>34</v>
+      </c>
+      <c r="BD44">
         <v>32</v>
       </c>
-      <c r="BD44">
-        <v>38</v>
-      </c>
       <c r="BE44">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF44">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG44">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH44">
         <v>2.78</v>
@@ -11679,7 +11679,7 @@
         <v>219</v>
       </c>
       <c r="F45">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G45">
         <v>1.76</v>
@@ -11727,7 +11727,7 @@
         <v>1.65</v>
       </c>
       <c r="V45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W45">
         <v>2.3</v>
@@ -11742,7 +11742,7 @@
         <v>60</v>
       </c>
       <c r="AA45">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="AB45">
         <v>6</v>
@@ -11754,7 +11754,7 @@
         <v>32</v>
       </c>
       <c r="AE45">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="AF45">
         <v>9</v>
@@ -11766,7 +11766,7 @@
         <v>32</v>
       </c>
       <c r="AI45">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AJ45">
         <v>19</v>
@@ -11775,10 +11775,10 @@
         <v>26</v>
       </c>
       <c r="AL45">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM45">
-        <v>700</v>
+        <v>270</v>
       </c>
       <c r="AN45">
         <v>18.5</v>
@@ -11787,10 +11787,10 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ45">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR45">
         <v>40</v>
@@ -11817,7 +11817,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ45">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BA45">
         <v>44</v>
@@ -11832,7 +11832,7 @@
         <v>46</v>
       </c>
       <c r="BE45">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="BF45">
         <v>15</v>
@@ -11868,25 +11868,25 @@
         <v>14</v>
       </c>
       <c r="BQ45">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR45">
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT45">
         <v>10.5</v>
       </c>
       <c r="BU45">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX45">
         <v>1000</v>
@@ -11927,7 +11927,7 @@
         <v>2.08</v>
       </c>
       <c r="H46">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I46">
         <v>5</v>
@@ -11948,22 +11948,22 @@
         <v>3.3</v>
       </c>
       <c r="O46">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P46">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q46">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R46">
         <v>1.28</v>
       </c>
       <c r="S46">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T46">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U46">
         <v>1.9</v>
@@ -11981,10 +11981,10 @@
         <v>15</v>
       </c>
       <c r="Z46">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AA46">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB46">
         <v>8.4</v>
@@ -11996,7 +11996,7 @@
         <v>19.5</v>
       </c>
       <c r="AE46">
-        <v>370</v>
+        <v>70</v>
       </c>
       <c r="AF46">
         <v>12.5</v>
@@ -12008,7 +12008,7 @@
         <v>22</v>
       </c>
       <c r="AI46">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ46">
         <v>26</v>
@@ -12017,70 +12017,70 @@
         <v>25</v>
       </c>
       <c r="AL46">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="AM46">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN46">
         <v>18.5</v>
       </c>
       <c r="AO46">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AP46">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AQ46">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR46">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AS46">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT46">
         <v>6.8</v>
       </c>
       <c r="AU46">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV46">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="AW46">
+        <v>7.4</v>
+      </c>
+      <c r="AX46">
+        <v>5</v>
+      </c>
+      <c r="AY46">
+        <v>4.8</v>
+      </c>
+      <c r="AZ46">
+        <v>6</v>
+      </c>
+      <c r="BA46">
         <v>7.6</v>
       </c>
-      <c r="AX46">
-        <v>10</v>
-      </c>
-      <c r="AY46">
-        <v>9</v>
-      </c>
-      <c r="AZ46">
-        <v>17</v>
-      </c>
-      <c r="BA46">
-        <v>7.8</v>
-      </c>
       <c r="BB46">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BC46">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD46">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE46">
         <v>8</v>
       </c>
       <c r="BF46">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG46">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BH46">
         <v>3.25</v>
@@ -12098,13 +12098,13 @@
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN46">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO46">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP46">
         <v>15.5</v>
@@ -12116,13 +12116,13 @@
         <v>1000</v>
       </c>
       <c r="BS46">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT46">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU46">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV46">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-03.xlsx
@@ -679,7 +679,7 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>2026-08-03 07:32:48</t>
+    <t>2026-08-03 09:40:53</t>
   </si>
 </sst>
 </file>
@@ -1273,226 +1273,226 @@
         <v>176</v>
       </c>
       <c r="F2">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="G2">
+        <v>4.8</v>
+      </c>
+      <c r="H2">
+        <v>2.06</v>
+      </c>
+      <c r="I2">
+        <v>2.1</v>
+      </c>
+      <c r="J2">
+        <v>3.15</v>
+      </c>
+      <c r="K2">
+        <v>3.4</v>
+      </c>
+      <c r="L2">
+        <v>1.67</v>
+      </c>
+      <c r="M2">
+        <v>1.13</v>
+      </c>
+      <c r="N2">
+        <v>2.56</v>
+      </c>
+      <c r="O2">
+        <v>1.58</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.66</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
         <v>5.7</v>
       </c>
-      <c r="H2">
-        <v>1.79</v>
-      </c>
-      <c r="I2">
-        <v>1.81</v>
-      </c>
-      <c r="J2">
-        <v>3.75</v>
-      </c>
-      <c r="K2">
-        <v>3.9</v>
-      </c>
-      <c r="L2">
-        <v>1.52</v>
-      </c>
-      <c r="M2">
-        <v>1.1</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-      <c r="O2">
-        <v>1.46</v>
-      </c>
-      <c r="P2">
-        <v>1.66</v>
-      </c>
-      <c r="Q2">
+      <c r="T2">
+        <v>2.12</v>
+      </c>
+      <c r="U2">
+        <v>1.69</v>
+      </c>
+      <c r="V2">
+        <v>1.9</v>
+      </c>
+      <c r="W2">
+        <v>1.26</v>
+      </c>
+      <c r="X2">
+        <v>9</v>
+      </c>
+      <c r="Y2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>14</v>
+      </c>
+      <c r="AA2">
+        <v>34</v>
+      </c>
+      <c r="AB2">
+        <v>12</v>
+      </c>
+      <c r="AC2">
+        <v>7.6</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>38</v>
+      </c>
+      <c r="AF2">
+        <v>40</v>
+      </c>
+      <c r="AG2">
+        <v>20</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>80</v>
+      </c>
+      <c r="AJ2">
+        <v>150</v>
+      </c>
+      <c r="AK2">
+        <v>110</v>
+      </c>
+      <c r="AL2">
+        <v>130</v>
+      </c>
+      <c r="AM2">
+        <v>270</v>
+      </c>
+      <c r="AN2">
+        <v>170</v>
+      </c>
+      <c r="AO2">
+        <v>38</v>
+      </c>
+      <c r="AP2">
+        <v>7.4</v>
+      </c>
+      <c r="AQ2">
+        <v>5.6</v>
+      </c>
+      <c r="AR2">
+        <v>10</v>
+      </c>
+      <c r="AS2">
+        <v>7</v>
+      </c>
+      <c r="AT2">
+        <v>5.1</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>10</v>
+      </c>
+      <c r="AW2">
+        <v>6.8</v>
+      </c>
+      <c r="AX2">
+        <v>3.5</v>
+      </c>
+      <c r="AY2">
+        <v>4.8</v>
+      </c>
+      <c r="AZ2">
+        <v>20</v>
+      </c>
+      <c r="BA2">
+        <v>5.9</v>
+      </c>
+      <c r="BB2">
+        <v>3.5</v>
+      </c>
+      <c r="BC2">
+        <v>3.5</v>
+      </c>
+      <c r="BD2">
+        <v>3.5</v>
+      </c>
+      <c r="BE2">
+        <v>3.5</v>
+      </c>
+      <c r="BF2">
+        <v>20</v>
+      </c>
+      <c r="BG2">
+        <v>5.6</v>
+      </c>
+      <c r="BH2">
+        <v>2.62</v>
+      </c>
+      <c r="BI2">
         <v>2.38</v>
       </c>
-      <c r="R2">
-        <v>1.24</v>
-      </c>
-      <c r="S2">
+      <c r="BJ2">
+        <v>12.5</v>
+      </c>
+      <c r="BK2">
+        <v>6.4</v>
+      </c>
+      <c r="BL2">
+        <v>270</v>
+      </c>
+      <c r="BM2">
+        <v>19.5</v>
+      </c>
+      <c r="BN2">
+        <v>7.6</v>
+      </c>
+      <c r="BO2">
+        <v>6.6</v>
+      </c>
+      <c r="BP2">
+        <v>50</v>
+      </c>
+      <c r="BQ2">
+        <v>24</v>
+      </c>
+      <c r="BR2">
+        <v>85</v>
+      </c>
+      <c r="BS2">
+        <v>19.5</v>
+      </c>
+      <c r="BT2">
         <v>4.7</v>
       </c>
-      <c r="T2">
-        <v>2.14</v>
-      </c>
-      <c r="U2">
-        <v>1.76</v>
-      </c>
-      <c r="V2">
-        <v>2.22</v>
-      </c>
-      <c r="W2">
-        <v>1.21</v>
-      </c>
-      <c r="X2">
-        <v>11</v>
-      </c>
-      <c r="Y2">
-        <v>6.8</v>
-      </c>
-      <c r="Z2">
-        <v>10.5</v>
-      </c>
-      <c r="AA2">
-        <v>20</v>
-      </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>8.6</v>
-      </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
-      <c r="AE2">
+      <c r="BU2">
+        <v>4.1</v>
+      </c>
+      <c r="BV2">
         <v>23</v>
       </c>
-      <c r="AF2">
-        <v>42</v>
-      </c>
-      <c r="AG2">
-        <v>23</v>
-      </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>55</v>
-      </c>
-      <c r="AJ2">
-        <v>160</v>
-      </c>
-      <c r="AK2">
-        <v>100</v>
-      </c>
-      <c r="AL2">
-        <v>120</v>
-      </c>
-      <c r="AM2">
-        <v>210</v>
-      </c>
-      <c r="AN2">
-        <v>150</v>
-      </c>
-      <c r="AO2">
-        <v>18</v>
-      </c>
-      <c r="AP2">
-        <v>9.4</v>
-      </c>
-      <c r="AQ2">
-        <v>6.2</v>
-      </c>
-      <c r="AR2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS2">
-        <v>17</v>
-      </c>
-      <c r="AT2">
+      <c r="BW2">
         <v>13.5</v>
       </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>9.4</v>
-      </c>
-      <c r="AW2">
-        <v>20</v>
-      </c>
-      <c r="AX2">
-        <v>34</v>
-      </c>
-      <c r="AY2">
-        <v>20</v>
-      </c>
-      <c r="AZ2">
-        <v>22</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>90</v>
-      </c>
-      <c r="BC2">
-        <v>55</v>
-      </c>
-      <c r="BD2">
-        <v>60</v>
-      </c>
-      <c r="BE2">
-        <v>120</v>
-      </c>
-      <c r="BF2">
-        <v>100</v>
-      </c>
-      <c r="BG2">
-        <v>15.5</v>
-      </c>
-      <c r="BH2">
-        <v>2.96</v>
-      </c>
-      <c r="BI2">
-        <v>2.68</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>9.4</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>13.5</v>
-      </c>
-      <c r="BN2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO2">
-        <v>7.4</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>11.5</v>
-      </c>
-      <c r="BR2">
-        <v>100</v>
-      </c>
-      <c r="BS2">
-        <v>12</v>
-      </c>
-      <c r="BT2">
-        <v>4.3</v>
-      </c>
-      <c r="BU2">
-        <v>3.8</v>
-      </c>
-      <c r="BV2">
-        <v>14.5</v>
-      </c>
-      <c r="BW2">
-        <v>7.4</v>
-      </c>
       <c r="BX2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BY2">
         <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="CA2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CB2" t="s">
         <v>221</v>
@@ -1515,7 +1515,7 @@
         <v>177</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
         <v>2.52</v>
@@ -1524,13 +1524,13 @@
         <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
         <v>1.19</v>
@@ -1539,7 +1539,7 @@
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O3">
         <v>1.1</v>
@@ -1581,7 +1581,7 @@
         <v>48</v>
       </c>
       <c r="AB3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AC3">
         <v>14</v>
@@ -1605,7 +1605,7 @@
         <v>23</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AK3">
         <v>21</v>
@@ -1620,7 +1620,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP3">
         <v>30</v>
@@ -1635,7 +1635,7 @@
         <v>34</v>
       </c>
       <c r="AT3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU3">
         <v>12</v>
@@ -1659,7 +1659,7 @@
         <v>19.5</v>
       </c>
       <c r="BB3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BC3">
         <v>18</v>
@@ -1668,13 +1668,13 @@
         <v>19.5</v>
       </c>
       <c r="BE3">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3">
         <v>6.2</v>
@@ -1686,7 +1686,7 @@
         <v>8</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1734,7 +1734,7 @@
         <v>9.4</v>
       </c>
       <c r="CA3">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
         <v>221</v>
@@ -1757,7 +1757,7 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G4">
         <v>1.34</v>
@@ -1772,7 +1772,7 @@
         <v>5.8</v>
       </c>
       <c r="K4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L4">
         <v>1.24</v>
@@ -1793,7 +1793,7 @@
         <v>1.44</v>
       </c>
       <c r="R4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S4">
         <v>2.08</v>
@@ -1999,22 +1999,22 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="G5">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
         <v>5.5</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.34</v>
@@ -2032,7 +2032,7 @@
         <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
         <v>1.46</v>
@@ -2053,7 +2053,7 @@
         <v>2.2</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y5">
         <v>21</v>
@@ -2107,16 +2107,16 @@
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -2128,7 +2128,7 @@
         <v>16</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>10</v>
@@ -2140,7 +2140,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
         <v>15.5</v>
@@ -2152,13 +2152,13 @@
         <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -2241,22 +2241,22 @@
         <v>180</v>
       </c>
       <c r="F6">
+        <v>1.14</v>
+      </c>
+      <c r="G6">
         <v>1.15</v>
       </c>
-      <c r="G6">
-        <v>1.17</v>
-      </c>
       <c r="H6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L6">
         <v>1.24</v>
@@ -2265,85 +2265,85 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q6">
         <v>1.46</v>
       </c>
       <c r="R6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S6">
         <v>2.16</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Y6">
         <v>75</v>
       </c>
       <c r="Z6">
-        <v>380</v>
+        <v>570</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AD6">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AE6">
         <v>1000</v>
       </c>
       <c r="AF6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI6">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AK6">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL6">
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AN6">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="AO6">
         <v>1000</v>
@@ -2352,55 +2352,55 @@
         <v>30</v>
       </c>
       <c r="AQ6">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AS6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>10</v>
       </c>
       <c r="AU6">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AW6">
+        <v>11</v>
+      </c>
+      <c r="AX6">
         <v>6.8</v>
       </c>
-      <c r="AX6">
-        <v>7.2</v>
-      </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BB6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BF6">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
@@ -2412,22 +2412,22 @@
         <v>16</v>
       </c>
       <c r="BK6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BN6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BQ6">
         <v>5.1</v>
@@ -2436,31 +2436,31 @@
         <v>24</v>
       </c>
       <c r="BS6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BU6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BZ6">
         <v>7</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB6" t="s">
         <v>221</v>
@@ -2489,10 +2489,10 @@
         <v>3.5</v>
       </c>
       <c r="H7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J7">
         <v>3.9</v>
@@ -2507,31 +2507,31 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q7">
         <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U7">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
         <v>1.4</v>
@@ -2540,7 +2540,7 @@
         <v>29</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
         <v>21</v>
@@ -2549,46 +2549,46 @@
         <v>32</v>
       </c>
       <c r="AB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7">
         <v>36</v>
       </c>
       <c r="AG7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
         <v>100</v>
       </c>
       <c r="AK7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN7">
         <v>27</v>
       </c>
       <c r="AO7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP7">
         <v>18.5</v>
@@ -2597,13 +2597,13 @@
         <v>13</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS7">
         <v>24</v>
       </c>
       <c r="AT7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2615,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="AX7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY7">
         <v>12.5</v>
@@ -2624,25 +2624,25 @@
         <v>12.5</v>
       </c>
       <c r="BA7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC7">
         <v>25</v>
       </c>
       <c r="BD7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
@@ -2660,7 +2660,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
         <v>7</v>
@@ -2672,13 +2672,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
         <v>5.5</v>
@@ -2693,16 +2693,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="s">
         <v>221</v>
@@ -2725,196 +2725,196 @@
         <v>182</v>
       </c>
       <c r="F8">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G8">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H8">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="X8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA8">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE8">
         <v>65</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
         <v>24</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO8">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP8">
+        <v>13</v>
+      </c>
+      <c r="AQ8">
+        <v>15</v>
+      </c>
+      <c r="AR8">
+        <v>27</v>
+      </c>
+      <c r="AS8">
+        <v>75</v>
+      </c>
+      <c r="AT8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>7.6</v>
+      </c>
+      <c r="AV8">
+        <v>15</v>
+      </c>
+      <c r="AW8">
+        <v>44</v>
+      </c>
+      <c r="AX8">
         <v>11</v>
       </c>
-      <c r="AQ8">
-        <v>14</v>
-      </c>
-      <c r="AR8">
-        <v>29</v>
-      </c>
-      <c r="AS8">
-        <v>95</v>
-      </c>
-      <c r="AT8">
+      <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>17</v>
+      </c>
+      <c r="BA8">
+        <v>48</v>
+      </c>
+      <c r="BB8">
+        <v>20</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
+        <v>30</v>
+      </c>
+      <c r="BE8">
+        <v>75</v>
+      </c>
+      <c r="BF8">
+        <v>12</v>
+      </c>
+      <c r="BG8">
+        <v>44</v>
+      </c>
+      <c r="BH8">
+        <v>3.55</v>
+      </c>
+      <c r="BI8">
+        <v>3.2</v>
+      </c>
+      <c r="BJ8">
+        <v>9.6</v>
+      </c>
+      <c r="BK8">
+        <v>6</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>14.5</v>
+      </c>
+      <c r="BN8">
+        <v>4.7</v>
+      </c>
+      <c r="BO8">
+        <v>4.1</v>
+      </c>
+      <c r="BP8">
+        <v>14.5</v>
+      </c>
+      <c r="BQ8">
         <v>7.6</v>
-      </c>
-      <c r="AU8">
-        <v>7.4</v>
-      </c>
-      <c r="AV8">
-        <v>16.5</v>
-      </c>
-      <c r="AW8">
-        <v>55</v>
-      </c>
-      <c r="AX8">
-        <v>10</v>
-      </c>
-      <c r="AY8">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8">
-        <v>18.5</v>
-      </c>
-      <c r="BA8">
-        <v>60</v>
-      </c>
-      <c r="BB8">
-        <v>16.5</v>
-      </c>
-      <c r="BC8">
-        <v>19</v>
-      </c>
-      <c r="BD8">
-        <v>36</v>
-      </c>
-      <c r="BE8">
-        <v>90</v>
-      </c>
-      <c r="BF8">
-        <v>13.5</v>
-      </c>
-      <c r="BG8">
-        <v>60</v>
-      </c>
-      <c r="BH8">
-        <v>3.25</v>
-      </c>
-      <c r="BI8">
-        <v>2.72</v>
-      </c>
-      <c r="BJ8">
-        <v>10.5</v>
-      </c>
-      <c r="BK8">
-        <v>6.4</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>15</v>
-      </c>
-      <c r="BN8">
-        <v>4.5</v>
-      </c>
-      <c r="BO8">
-        <v>4</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
@@ -2923,28 +2923,28 @@
         <v>10.5</v>
       </c>
       <c r="BT8">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
+        <v>11</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
         <v>12</v>
       </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>13</v>
-      </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>221</v>
@@ -2979,13 +2979,13 @@
         <v>1.93</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2994,22 +2994,22 @@
         <v>3.65</v>
       </c>
       <c r="O9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U9">
         <v>2.02</v>
@@ -3021,7 +3021,7 @@
         <v>1.26</v>
       </c>
       <c r="X9">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -3075,7 +3075,7 @@
         <v>14</v>
       </c>
       <c r="AP9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
         <v>7.6</v>
@@ -3090,7 +3090,7 @@
         <v>12.5</v>
       </c>
       <c r="AU9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
         <v>9</v>
@@ -3099,31 +3099,31 @@
         <v>17.5</v>
       </c>
       <c r="AX9">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9">
         <v>17.5</v>
       </c>
       <c r="BA9">
+        <v>6.6</v>
+      </c>
+      <c r="BB9">
+        <v>7.6</v>
+      </c>
+      <c r="BC9">
+        <v>7.2</v>
+      </c>
+      <c r="BD9">
+        <v>7.2</v>
+      </c>
+      <c r="BE9">
+        <v>7.6</v>
+      </c>
+      <c r="BF9">
         <v>7.4</v>
-      </c>
-      <c r="BB9">
-        <v>8.4</v>
-      </c>
-      <c r="BC9">
-        <v>8</v>
-      </c>
-      <c r="BD9">
-        <v>8</v>
-      </c>
-      <c r="BE9">
-        <v>8.4</v>
-      </c>
-      <c r="BF9">
-        <v>8</v>
       </c>
       <c r="BG9">
         <v>11</v>
@@ -3132,7 +3132,7 @@
         <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
@@ -3209,22 +3209,22 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="G10">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H10">
         <v>5.5</v>
       </c>
       <c r="I10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.35</v>
@@ -3248,25 +3248,25 @@
         <v>1.46</v>
       </c>
       <c r="S10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z10">
         <v>55</v>
@@ -3278,13 +3278,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3296,37 +3296,37 @@
         <v>24</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK10">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL10">
         <v>38</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP10">
         <v>16</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR10">
         <v>34</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
@@ -3335,7 +3335,7 @@
         <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW10">
         <v>46</v>
@@ -3347,82 +3347,82 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA10">
         <v>44</v>
       </c>
       <c r="BB10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE10">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH10">
         <v>3.9</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
         <v>3.95</v>
       </c>
       <c r="BP10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT10">
         <v>9</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>185</v>
       </c>
       <c r="F11">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="G11">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H11">
         <v>5.6</v>
@@ -3463,7 +3463,7 @@
         <v>5.9</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4.2</v>
@@ -3475,25 +3475,25 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O11">
         <v>1.33</v>
       </c>
       <c r="P11">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q11">
         <v>1.95</v>
       </c>
       <c r="R11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U11">
         <v>2.02</v>
@@ -3502,7 +3502,7 @@
         <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X11">
         <v>16</v>
@@ -3511,19 +3511,19 @@
         <v>23</v>
       </c>
       <c r="Z11">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA11">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AB11">
         <v>8.6</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE11">
         <v>80</v>
@@ -3535,22 +3535,22 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>85</v>
       </c>
       <c r="AJ11">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AK11">
         <v>23</v>
       </c>
       <c r="AL11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN11">
         <v>11</v>
@@ -3568,7 +3568,7 @@
         <v>38</v>
       </c>
       <c r="AS11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT11">
         <v>7.8</v>
@@ -3583,40 +3583,40 @@
         <v>65</v>
       </c>
       <c r="AX11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY11">
         <v>9</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
         <v>60</v>
       </c>
       <c r="BB11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
         <v>32</v>
       </c>
       <c r="BE11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG11">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BH11">
         <v>3.5</v>
       </c>
       <c r="BI11">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3628,13 +3628,13 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP11">
         <v>11.5</v>
@@ -3658,10 +3658,10 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
         <v>13.5</v>
@@ -3693,22 +3693,22 @@
         <v>186</v>
       </c>
       <c r="F12">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I12">
         <v>9</v>
       </c>
       <c r="J12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1.32</v>
@@ -3717,28 +3717,28 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R12">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U12">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
         <v>1.12</v>
@@ -3747,28 +3747,28 @@
         <v>3.05</v>
       </c>
       <c r="X12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z12">
         <v>85</v>
       </c>
       <c r="AA12">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE12">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF12">
         <v>9.6</v>
@@ -3777,28 +3777,28 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ12">
         <v>13</v>
       </c>
       <c r="AK12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN12">
         <v>6.2</v>
       </c>
       <c r="AO12">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3813,7 +3813,7 @@
         <v>11.5</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU12">
         <v>9.4</v>
@@ -3825,16 +3825,16 @@
         <v>70</v>
       </c>
       <c r="AX12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY12">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB12">
         <v>10.5</v>
@@ -3846,22 +3846,22 @@
         <v>24</v>
       </c>
       <c r="BE12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF12">
         <v>5.4</v>
       </c>
       <c r="BG12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH12">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK12">
         <v>8.4</v>
@@ -3870,43 +3870,43 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN12">
         <v>4.1</v>
       </c>
       <c r="BO12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ12">
         <v>6.8</v>
       </c>
       <c r="BR12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU12">
         <v>9.199999999999999</v>
       </c>
       <c r="BV12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX12">
         <v>75</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3941,19 +3941,19 @@
         <v>3.65</v>
       </c>
       <c r="H13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I13">
         <v>2.08</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
         <v>1.04</v>
@@ -3968,19 +3968,19 @@
         <v>2.66</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R13">
         <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
         <v>1.55</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V13">
         <v>1.92</v>
@@ -3992,10 +3992,10 @@
         <v>26</v>
       </c>
       <c r="Y13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z13">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA13">
         <v>26</v>
@@ -4004,19 +4004,19 @@
         <v>21</v>
       </c>
       <c r="AC13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH13">
         <v>15</v>
@@ -4025,25 +4025,25 @@
         <v>26</v>
       </c>
       <c r="AJ13">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>55</v>
       </c>
       <c r="AN13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
         <v>13</v>
@@ -4055,16 +4055,16 @@
         <v>23</v>
       </c>
       <c r="AT13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU13">
         <v>9</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX13">
         <v>28</v>
@@ -4091,10 +4091,10 @@
         <v>42</v>
       </c>
       <c r="BF13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -4106,19 +4106,19 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL13"